--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C883DEB-3E82-42D9-A9ED-D71BF949B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD258453-968A-46A8-B218-CE31F8692284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,9 @@
     <t>42761010,42663010</t>
   </si>
   <si>
+    <t>42652007</t>
+  </si>
+  <si>
     <t>drop_exp_num</t>
   </si>
   <si>
@@ -126,10 +129,28 @@
     <t>46700001:5</t>
   </si>
   <si>
+    <t>42761001</t>
+  </si>
+  <si>
+    <t>42663002</t>
+  </si>
+  <si>
+    <t>42761003</t>
+  </si>
+  <si>
     <t>46700001:6</t>
   </si>
   <si>
+    <t>42663004</t>
+  </si>
+  <si>
     <t>46700001:7</t>
+  </si>
+  <si>
+    <t>42655004</t>
+  </si>
+  <si>
+    <t>42761005</t>
   </si>
   <si>
     <t>46700001:12</t>
@@ -141,13 +162,25 @@
     <t>46200001:60</t>
   </si>
   <si>
+    <t>42663006</t>
+  </si>
+  <si>
     <t>46700001:13</t>
+  </si>
+  <si>
+    <t>42657006</t>
   </si>
   <si>
     <t>46700001:10</t>
   </si>
   <si>
     <t>46200001:80</t>
+  </si>
+  <si>
+    <t>42664006</t>
+  </si>
+  <si>
+    <t>42761007</t>
   </si>
   <si>
     <t>46700001:17</t>
@@ -160,6 +193,9 @@
   </si>
   <si>
     <t>46200001:120</t>
+  </si>
+  <si>
+    <t>42668007</t>
   </si>
   <si>
     <t>46700001:18</t>
@@ -528,19 +564,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -557,10 +593,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -577,10 +613,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -590,14 +626,14 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -611,10 +647,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -624,14 +660,14 @@
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2">
-        <v>0</v>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -645,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -658,14 +694,14 @@
       <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="2">
-        <v>0</v>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -679,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -692,14 +728,14 @@
       <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -713,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -726,14 +762,14 @@
       <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -743,14 +779,14 @@
       <c r="B14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
+      <c r="D14" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -764,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -781,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -798,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
@@ -811,14 +847,14 @@
       <c r="B18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
+      <c r="D18" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -832,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -845,14 +881,14 @@
       <c r="B20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -866,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -883,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -896,14 +932,14 @@
       <c r="B23" s="1">
         <v>6</v>
       </c>
-      <c r="D23" s="2">
-        <v>0</v>
+      <c r="D23" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -917,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -930,14 +966,14 @@
       <c r="B25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="2">
-        <v>0</v>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -951,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -968,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -981,14 +1017,14 @@
       <c r="B28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="2">
-        <v>0</v>
+      <c r="D28" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
@@ -1002,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1019,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1032,14 +1068,14 @@
       <c r="B31" s="1">
         <v>7</v>
       </c>
-      <c r="D31" s="2">
-        <v>0</v>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1053,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1070,10 +1106,10 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1087,10 +1123,10 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1104,10 +1140,10 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1121,10 +1157,10 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1138,10 +1174,10 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1155,10 +1191,10 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1172,10 +1208,10 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1189,10 +1225,10 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
@@ -1206,10 +1242,10 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1223,10 +1259,10 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1240,10 +1276,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1257,10 +1293,10 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1274,10 +1310,10 @@
         <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1291,10 +1327,10 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1308,10 +1344,10 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1325,10 +1361,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1342,10 +1378,10 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -1359,10 +1395,10 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -1376,10 +1412,10 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
@@ -1393,10 +1429,10 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -1410,10 +1446,10 @@
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -1427,10 +1463,10 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -1444,10 +1480,10 @@
         <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -1461,10 +1497,10 @@
         <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -1478,10 +1514,10 @@
         <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -1495,10 +1531,10 @@
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -1512,10 +1548,10 @@
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -1529,10 +1565,10 @@
         <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -1546,10 +1582,10 @@
         <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
@@ -1563,10 +1599,10 @@
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
@@ -1580,10 +1616,10 @@
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -1597,10 +1633,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -1614,10 +1650,10 @@
         <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -1631,10 +1667,10 @@
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -1648,10 +1684,10 @@
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -1665,10 +1701,10 @@
         <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -1682,10 +1718,10 @@
         <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -1699,10 +1735,10 @@
         <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -1716,10 +1752,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -1733,10 +1769,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -1750,10 +1786,10 @@
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -1767,10 +1803,10 @@
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -1784,10 +1820,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -1801,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -1818,10 +1854,10 @@
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -1835,10 +1871,10 @@
         <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -1852,10 +1888,10 @@
         <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -1869,10 +1905,10 @@
         <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -1886,10 +1922,10 @@
         <v>11</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -1903,10 +1939,10 @@
         <v>11</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -1920,10 +1956,10 @@
         <v>11</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
@@ -1937,10 +1973,10 @@
         <v>11</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -1954,10 +1990,10 @@
         <v>11</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -1971,10 +2007,10 @@
         <v>11</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -1988,10 +2024,10 @@
         <v>11</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2005,10 +2041,10 @@
         <v>11</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2022,10 +2058,10 @@
         <v>11</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2039,10 +2075,10 @@
         <v>11</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2056,10 +2092,10 @@
         <v>11</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2073,10 +2109,10 @@
         <v>11</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2090,10 +2126,10 @@
         <v>11</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2107,10 +2143,10 @@
         <v>11</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2124,10 +2160,10 @@
         <v>11</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2141,10 +2177,10 @@
         <v>11</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
@@ -2158,10 +2194,10 @@
         <v>11</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2175,10 +2211,10 @@
         <v>11</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
@@ -2192,10 +2228,10 @@
         <v>11</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
@@ -2209,10 +2245,10 @@
         <v>11</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
@@ -2226,10 +2262,10 @@
         <v>11</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
@@ -2243,10 +2279,10 @@
         <v>11</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
@@ -2260,10 +2296,10 @@
         <v>11</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
@@ -2277,10 +2313,10 @@
         <v>11</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
@@ -2294,10 +2330,10 @@
         <v>11</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
@@ -2311,10 +2347,10 @@
         <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
@@ -2328,10 +2364,10 @@
         <v>11</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
@@ -2345,10 +2381,10 @@
         <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
@@ -2362,10 +2398,10 @@
         <v>11</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
@@ -2379,10 +2415,10 @@
         <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
@@ -2396,10 +2432,10 @@
         <v>11</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
@@ -2413,10 +2449,10 @@
         <v>11</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
@@ -2430,10 +2466,10 @@
         <v>11</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
@@ -2447,10 +2483,10 @@
         <v>11</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
@@ -2464,10 +2500,10 @@
         <v>11</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
@@ -2481,10 +2517,10 @@
         <v>11</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
@@ -2498,10 +2534,10 @@
         <v>11</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
@@ -2515,10 +2551,10 @@
         <v>11</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
@@ -2532,10 +2568,10 @@
         <v>11</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -2549,10 +2585,10 @@
         <v>11</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
@@ -2566,10 +2602,10 @@
         <v>11</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.15">
@@ -2583,10 +2619,10 @@
         <v>11</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.15">
@@ -2600,10 +2636,10 @@
         <v>11</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.15">
@@ -2617,10 +2653,10 @@
         <v>11</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.15">
@@ -2634,10 +2670,10 @@
         <v>11</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.15">
@@ -2651,10 +2687,10 @@
         <v>11</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.15">
@@ -2668,10 +2704,10 @@
         <v>11</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.15">
@@ -2685,10 +2721,10 @@
         <v>11</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.15">
@@ -2702,10 +2738,10 @@
         <v>11</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.15">
@@ -2719,10 +2755,10 @@
         <v>11</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -2736,10 +2772,10 @@
         <v>11</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -2753,10 +2789,10 @@
         <v>11</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
@@ -2770,10 +2806,10 @@
         <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
@@ -2787,10 +2823,10 @@
         <v>11</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
@@ -2804,10 +2840,10 @@
         <v>11</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
@@ -2821,10 +2857,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
@@ -2838,10 +2874,10 @@
         <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -2855,10 +2891,10 @@
         <v>11</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
@@ -2872,10 +2908,10 @@
         <v>11</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">
@@ -2889,10 +2925,10 @@
         <v>11</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
@@ -2906,10 +2942,10 @@
         <v>11</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -2923,10 +2959,10 @@
         <v>11</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -2940,10 +2976,10 @@
         <v>11</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -2957,10 +2993,10 @@
         <v>11</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
@@ -2974,10 +3010,10 @@
         <v>11</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
@@ -2991,10 +3027,10 @@
         <v>11</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
@@ -3008,10 +3044,10 @@
         <v>11</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
@@ -3025,10 +3061,10 @@
         <v>11</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
@@ -3042,10 +3078,10 @@
         <v>11</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
@@ -3059,10 +3095,10 @@
         <v>11</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
@@ -3076,10 +3112,10 @@
         <v>11</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.15">
@@ -3093,10 +3129,10 @@
         <v>11</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
@@ -3110,10 +3146,10 @@
         <v>11</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
@@ -3127,10 +3163,10 @@
         <v>11</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
@@ -3144,10 +3180,10 @@
         <v>11</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
@@ -3161,10 +3197,10 @@
         <v>11</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
@@ -3178,10 +3214,10 @@
         <v>11</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
@@ -3195,10 +3231,10 @@
         <v>11</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
@@ -3212,10 +3248,10 @@
         <v>11</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
@@ -3229,10 +3265,10 @@
         <v>11</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
@@ -3246,10 +3282,10 @@
         <v>11</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
@@ -3263,10 +3299,10 @@
         <v>11</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
@@ -3280,10 +3316,10 @@
         <v>11</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
@@ -3297,10 +3333,10 @@
         <v>11</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
@@ -3314,10 +3350,10 @@
         <v>11</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
@@ -3331,10 +3367,10 @@
         <v>11</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -3348,10 +3384,10 @@
         <v>11</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -3365,10 +3401,10 @@
         <v>11</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
@@ -3382,10 +3418,10 @@
         <v>11</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
@@ -3399,10 +3435,10 @@
         <v>11</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
@@ -3416,10 +3452,10 @@
         <v>11</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
@@ -3433,10 +3469,10 @@
         <v>11</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
@@ -3450,10 +3486,10 @@
         <v>11</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
@@ -3467,10 +3503,10 @@
         <v>11</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
@@ -3484,10 +3520,10 @@
         <v>11</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
@@ -3501,10 +3537,10 @@
         <v>11</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
@@ -3518,10 +3554,10 @@
         <v>11</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
@@ -3535,10 +3571,10 @@
         <v>11</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
@@ -3552,10 +3588,10 @@
         <v>11</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
@@ -3569,10 +3605,10 @@
         <v>11</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
@@ -3586,10 +3622,10 @@
         <v>11</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
@@ -3603,10 +3639,10 @@
         <v>11</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
@@ -3620,10 +3656,10 @@
         <v>11</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
@@ -3637,10 +3673,10 @@
         <v>11</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
@@ -3654,10 +3690,10 @@
         <v>11</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
@@ -3671,10 +3707,10 @@
         <v>11</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
@@ -3688,10 +3724,10 @@
         <v>11</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
@@ -3705,10 +3741,10 @@
         <v>11</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
@@ -3722,10 +3758,10 @@
         <v>11</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
@@ -3739,10 +3775,10 @@
         <v>11</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
@@ -3756,10 +3792,10 @@
         <v>11</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
@@ -3773,10 +3809,10 @@
         <v>11</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
@@ -3790,10 +3826,10 @@
         <v>11</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
@@ -3807,10 +3843,10 @@
         <v>11</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
@@ -3824,10 +3860,10 @@
         <v>11</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
@@ -3841,10 +3877,10 @@
         <v>11</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
@@ -3858,10 +3894,10 @@
         <v>11</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
@@ -3875,10 +3911,10 @@
         <v>11</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
@@ -3892,10 +3928,10 @@
         <v>11</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
@@ -3909,10 +3945,10 @@
         <v>11</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
@@ -3926,10 +3962,10 @@
         <v>11</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
@@ -3943,10 +3979,10 @@
         <v>11</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
@@ -3960,10 +3996,10 @@
         <v>11</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
@@ -3977,10 +4013,10 @@
         <v>11</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
@@ -3994,10 +4030,10 @@
         <v>11</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
@@ -4011,10 +4047,10 @@
         <v>11</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
@@ -4028,10 +4064,10 @@
         <v>11</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
@@ -4045,10 +4081,10 @@
         <v>11</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
@@ -4062,10 +4098,10 @@
         <v>11</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -4079,10 +4115,10 @@
         <v>11</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
@@ -4096,10 +4132,10 @@
         <v>11</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
@@ -4113,10 +4149,10 @@
         <v>11</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
@@ -4130,10 +4166,10 @@
         <v>11</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
@@ -4147,10 +4183,10 @@
         <v>11</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
@@ -4164,10 +4200,10 @@
         <v>11</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
@@ -4181,10 +4217,10 @@
         <v>11</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
@@ -4198,10 +4234,10 @@
         <v>11</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
@@ -4215,10 +4251,10 @@
         <v>11</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
@@ -4232,10 +4268,10 @@
         <v>11</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
@@ -4249,10 +4285,10 @@
         <v>11</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
@@ -4266,10 +4302,10 @@
         <v>11</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
@@ -4283,10 +4319,10 @@
         <v>11</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
@@ -4300,10 +4336,10 @@
         <v>11</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
@@ -4317,10 +4353,10 @@
         <v>11</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
@@ -4334,10 +4370,10 @@
         <v>11</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
@@ -4351,10 +4387,10 @@
         <v>11</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
@@ -4368,10 +4404,10 @@
         <v>11</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
@@ -4385,10 +4421,10 @@
         <v>11</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
@@ -4402,10 +4438,10 @@
         <v>11</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
@@ -4419,10 +4455,10 @@
         <v>11</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
@@ -4436,10 +4472,10 @@
         <v>11</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
@@ -4453,10 +4489,10 @@
         <v>11</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
@@ -4470,10 +4506,10 @@
         <v>11</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
@@ -4487,10 +4523,10 @@
         <v>11</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
@@ -4504,10 +4540,10 @@
         <v>11</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
@@ -4521,10 +4557,10 @@
         <v>11</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
@@ -4538,10 +4574,10 @@
         <v>11</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
@@ -4555,10 +4591,10 @@
         <v>11</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
@@ -4572,10 +4608,10 @@
         <v>11</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
@@ -4589,10 +4625,10 @@
         <v>11</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
@@ -4606,10 +4642,10 @@
         <v>11</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
@@ -4623,10 +4659,10 @@
         <v>11</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
@@ -4640,10 +4676,10 @@
         <v>11</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
@@ -4657,10 +4693,10 @@
         <v>11</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
@@ -4674,10 +4710,10 @@
         <v>11</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
@@ -4691,10 +4727,10 @@
         <v>11</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
@@ -4708,10 +4744,10 @@
         <v>11</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
@@ -4725,10 +4761,10 @@
         <v>11</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
@@ -4742,10 +4778,10 @@
         <v>11</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
@@ -4759,10 +4795,10 @@
         <v>11</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.15">
@@ -4776,10 +4812,10 @@
         <v>11</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.15">
@@ -4793,10 +4829,10 @@
         <v>11</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.15">
@@ -4810,10 +4846,10 @@
         <v>11</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.15">
@@ -4827,10 +4863,10 @@
         <v>11</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.15">
@@ -4844,10 +4880,10 @@
         <v>11</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.15">
@@ -4861,10 +4897,10 @@
         <v>11</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.15">
@@ -4878,10 +4914,10 @@
         <v>11</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.15">
@@ -4895,10 +4931,10 @@
         <v>11</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.15">
@@ -4912,10 +4948,10 @@
         <v>11</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.15">
@@ -4929,10 +4965,10 @@
         <v>11</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.15">
@@ -4946,10 +4982,10 @@
         <v>11</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.15">
@@ -4963,10 +4999,10 @@
         <v>11</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.15">
@@ -4980,10 +5016,10 @@
         <v>11</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.15">
@@ -4997,10 +5033,10 @@
         <v>11</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.15">
@@ -5014,10 +5050,10 @@
         <v>11</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.15">
@@ -5031,10 +5067,10 @@
         <v>11</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.15">
@@ -5048,10 +5084,10 @@
         <v>11</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.15">
@@ -5065,10 +5101,10 @@
         <v>11</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.15">
@@ -5082,10 +5118,10 @@
         <v>11</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.15">
@@ -5099,10 +5135,10 @@
         <v>11</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.15">
@@ -5116,10 +5152,10 @@
         <v>11</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.15">
@@ -5133,10 +5169,10 @@
         <v>11</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.15">
@@ -5150,10 +5186,10 @@
         <v>11</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.15">
@@ -5167,10 +5203,10 @@
         <v>11</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.15">
@@ -5184,10 +5220,10 @@
         <v>11</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.15">
@@ -5201,10 +5237,10 @@
         <v>11</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.15">
@@ -5218,10 +5254,10 @@
         <v>11</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.15">
@@ -5235,10 +5271,10 @@
         <v>11</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.15">
@@ -5252,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.15">
@@ -5269,10 +5305,10 @@
         <v>11</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.15">
@@ -5286,10 +5322,10 @@
         <v>11</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.15">
@@ -5303,10 +5339,10 @@
         <v>11</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.15">
@@ -5320,10 +5356,10 @@
         <v>11</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.15">
@@ -5337,10 +5373,10 @@
         <v>11</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.15">
@@ -5354,10 +5390,10 @@
         <v>11</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.15">
@@ -5371,10 +5407,10 @@
         <v>11</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.15">
@@ -5388,10 +5424,10 @@
         <v>11</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.15">
@@ -5405,10 +5441,10 @@
         <v>11</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.15">
@@ -5422,10 +5458,10 @@
         <v>11</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.15">
@@ -5439,10 +5475,10 @@
         <v>11</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.15">
@@ -5456,10 +5492,10 @@
         <v>11</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.15">
@@ -5473,10 +5509,10 @@
         <v>11</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.15">
@@ -5490,10 +5526,10 @@
         <v>11</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.15">
@@ -5507,10 +5543,10 @@
         <v>11</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.15">
@@ -5524,10 +5560,10 @@
         <v>11</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.15">
@@ -5541,10 +5577,10 @@
         <v>11</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.15">
@@ -5558,10 +5594,10 @@
         <v>11</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.15">
@@ -5575,10 +5611,10 @@
         <v>11</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.15">
@@ -5592,10 +5628,10 @@
         <v>11</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.15">
@@ -5609,10 +5645,10 @@
         <v>11</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.15">
@@ -5626,10 +5662,10 @@
         <v>11</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.15">
@@ -5643,10 +5679,10 @@
         <v>11</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.15">
@@ -5660,10 +5696,10 @@
         <v>11</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.15">
@@ -5677,10 +5713,10 @@
         <v>11</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.15">
@@ -5694,10 +5730,10 @@
         <v>11</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.15">
@@ -5711,10 +5747,10 @@
         <v>11</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.15">
@@ -5728,10 +5764,10 @@
         <v>11</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.15">
@@ -5745,10 +5781,10 @@
         <v>11</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.15">
@@ -5762,10 +5798,10 @@
         <v>11</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.15">
@@ -5779,10 +5815,10 @@
         <v>11</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.15">
@@ -5796,10 +5832,10 @@
         <v>11</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.15">
@@ -5813,10 +5849,10 @@
         <v>11</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.15">
@@ -5830,10 +5866,10 @@
         <v>11</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.15">
@@ -5847,10 +5883,10 @@
         <v>11</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.15">
@@ -5864,10 +5900,10 @@
         <v>11</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.15">
@@ -5881,10 +5917,10 @@
         <v>11</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.15">
@@ -5898,10 +5934,10 @@
         <v>11</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.15">
@@ -5915,10 +5951,10 @@
         <v>11</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.15">
@@ -5932,10 +5968,10 @@
         <v>11</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.15">
@@ -5949,10 +5985,10 @@
         <v>11</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.15">
@@ -5966,10 +6002,10 @@
         <v>11</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.15">
@@ -5983,10 +6019,10 @@
         <v>11</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.15">
@@ -6000,10 +6036,10 @@
         <v>11</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.15">
@@ -6017,10 +6053,10 @@
         <v>11</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.15">
@@ -6034,10 +6070,10 @@
         <v>11</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.15">
@@ -6051,10 +6087,10 @@
         <v>11</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.15">
@@ -6068,10 +6104,10 @@
         <v>11</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.15">
@@ -6085,10 +6121,10 @@
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.15">
@@ -6102,10 +6138,10 @@
         <v>11</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.15">
@@ -6119,10 +6155,10 @@
         <v>11</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.15">
@@ -6136,10 +6172,10 @@
         <v>11</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.15">
@@ -6153,10 +6189,10 @@
         <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.15">
@@ -6170,10 +6206,10 @@
         <v>11</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.15">
@@ -6187,10 +6223,10 @@
         <v>11</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.15">
@@ -6204,10 +6240,10 @@
         <v>11</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.15">
@@ -6221,10 +6257,10 @@
         <v>11</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.15">
@@ -6238,10 +6274,10 @@
         <v>11</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.15">
@@ -6255,10 +6291,10 @@
         <v>11</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F338" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.15">
@@ -6272,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.15">
@@ -6289,10 +6325,10 @@
         <v>0</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.15">
@@ -6306,10 +6342,10 @@
         <v>0</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.15">
@@ -6323,10 +6359,10 @@
         <v>0</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.15">
@@ -6340,10 +6376,10 @@
         <v>0</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.15">
@@ -6357,10 +6393,10 @@
         <v>0</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.15">
@@ -6374,10 +6410,10 @@
         <v>0</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.15">
@@ -6391,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.15">
@@ -6408,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.15">
@@ -6425,10 +6461,10 @@
         <v>0</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.15">
@@ -6442,10 +6478,10 @@
         <v>0</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.15">
@@ -6459,10 +6495,10 @@
         <v>0</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.15">
@@ -6476,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.15">
@@ -6493,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.15">
@@ -6510,10 +6546,10 @@
         <v>0</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.15">
@@ -6527,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.15">
@@ -6544,10 +6580,10 @@
         <v>0</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.15">
@@ -6561,10 +6597,10 @@
         <v>0</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.15">
@@ -6578,10 +6614,10 @@
         <v>0</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.15">
@@ -6595,10 +6631,10 @@
         <v>0</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.15">
@@ -6612,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.15">
@@ -6629,10 +6665,10 @@
         <v>0</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.15">
@@ -6646,10 +6682,10 @@
         <v>0</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.15">
@@ -6663,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.15">
@@ -6680,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.15">
@@ -6697,10 +6733,10 @@
         <v>0</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.15">
@@ -6714,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.15">
@@ -6731,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.15">
@@ -6748,10 +6784,10 @@
         <v>0</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.15">
@@ -6765,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.15">
@@ -6782,10 +6818,10 @@
         <v>0</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.15">
@@ -6799,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.15">
@@ -6816,10 +6852,10 @@
         <v>0</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.15">
@@ -6833,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.15">
@@ -6850,10 +6886,10 @@
         <v>0</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.15">
@@ -6867,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.15">
@@ -6884,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.15">
@@ -6901,10 +6937,10 @@
         <v>0</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.15">
@@ -6918,10 +6954,10 @@
         <v>0</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.15">
@@ -6935,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.15">
@@ -6952,10 +6988,10 @@
         <v>0</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.15">
@@ -6969,10 +7005,10 @@
         <v>0</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.15">
@@ -6986,10 +7022,10 @@
         <v>0</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.15">
@@ -7003,10 +7039,10 @@
         <v>0</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.15">
@@ -7020,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.15">
@@ -7037,10 +7073,10 @@
         <v>0</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.15">
@@ -7054,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.15">
@@ -7071,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.15">
@@ -7088,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.15">
@@ -7105,10 +7141,10 @@
         <v>0</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.15">
@@ -7122,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.15">
@@ -7139,10 +7175,10 @@
         <v>0</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.15">
@@ -7156,10 +7192,10 @@
         <v>0</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.15">
@@ -7173,10 +7209,10 @@
         <v>0</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.15">
@@ -7190,10 +7226,10 @@
         <v>0</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.15">
@@ -7207,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.15">
@@ -7224,10 +7260,10 @@
         <v>0</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.15">
@@ -7241,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.15">
@@ -7258,10 +7294,10 @@
         <v>0</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.15">
@@ -7275,10 +7311,10 @@
         <v>0</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.15">
@@ -7292,10 +7328,10 @@
         <v>0</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.15">
@@ -7309,10 +7345,10 @@
         <v>0</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.15">
@@ -7326,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.15">
@@ -7343,10 +7379,10 @@
         <v>0</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.15">
@@ -7360,10 +7396,10 @@
         <v>0</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.15">
@@ -7377,10 +7413,10 @@
         <v>0</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.15">
@@ -7394,10 +7430,10 @@
         <v>0</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.15">
@@ -7411,10 +7447,10 @@
         <v>0</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.15">
@@ -7428,10 +7464,10 @@
         <v>0</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.15">
@@ -7445,10 +7481,10 @@
         <v>0</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.15">
@@ -7462,10 +7498,10 @@
         <v>0</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.15">
@@ -7479,10 +7515,10 @@
         <v>0</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.15">
@@ -7496,10 +7532,10 @@
         <v>0</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.15">
@@ -7513,10 +7549,10 @@
         <v>0</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.15">
@@ -7530,10 +7566,10 @@
         <v>0</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.15">
@@ -7547,10 +7583,10 @@
         <v>0</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.15">
@@ -7564,10 +7600,10 @@
         <v>0</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.15">
@@ -7581,10 +7617,10 @@
         <v>0</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.15">
@@ -7598,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.15">
@@ -7615,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.15">
@@ -7632,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.15">
@@ -7649,10 +7685,10 @@
         <v>0</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.15">
@@ -7666,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.15">
@@ -7683,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.15">
@@ -7700,10 +7736,10 @@
         <v>0</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.15">
@@ -7717,10 +7753,10 @@
         <v>0</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.15">
@@ -7734,10 +7770,10 @@
         <v>0</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.15">
@@ -7751,10 +7787,10 @@
         <v>0</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.15">
@@ -7768,10 +7804,10 @@
         <v>0</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.15">
@@ -7785,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.15">
@@ -7802,10 +7838,10 @@
         <v>0</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.15">
@@ -7819,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.15">
@@ -7836,10 +7872,10 @@
         <v>0</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.15">
@@ -7853,10 +7889,10 @@
         <v>0</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.15">
@@ -7870,10 +7906,10 @@
         <v>0</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.15">
@@ -7887,10 +7923,10 @@
         <v>0</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.15">
@@ -7904,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.15">
@@ -7921,10 +7957,10 @@
         <v>0</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.15">
@@ -7938,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.15">
@@ -7955,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.15">
@@ -7972,10 +8008,10 @@
         <v>0</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.15">
@@ -7989,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.15">
@@ -8006,10 +8042,10 @@
         <v>0</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.15">
@@ -8023,10 +8059,10 @@
         <v>0</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.15">
@@ -8040,10 +8076,10 @@
         <v>0</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.15">
@@ -8057,10 +8093,10 @@
         <v>0</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.15">
@@ -8074,10 +8110,10 @@
         <v>0</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.15">
@@ -8091,10 +8127,10 @@
         <v>0</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.15">
@@ -8108,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.15">
@@ -8125,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.15">
@@ -8142,10 +8178,10 @@
         <v>0</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.15">
@@ -8159,10 +8195,10 @@
         <v>0</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.15">
@@ -8176,10 +8212,10 @@
         <v>0</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.15">
@@ -8193,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.15">
@@ -8210,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.15">
@@ -8227,10 +8263,10 @@
         <v>0</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.15">
@@ -8244,10 +8280,10 @@
         <v>0</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.15">
@@ -8261,10 +8297,10 @@
         <v>0</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.15">
@@ -8278,10 +8314,10 @@
         <v>0</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.15">
@@ -8295,10 +8331,10 @@
         <v>0</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.15">
@@ -8312,10 +8348,10 @@
         <v>0</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.15">
@@ -8329,10 +8365,10 @@
         <v>0</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.15">
@@ -8346,10 +8382,10 @@
         <v>0</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.15">
@@ -8363,10 +8399,10 @@
         <v>0</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.15">
@@ -8380,10 +8416,10 @@
         <v>0</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.15">
@@ -8397,10 +8433,10 @@
         <v>0</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.15">
@@ -8414,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.15">
@@ -8431,10 +8467,10 @@
         <v>0</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.15">
@@ -8448,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.15">
@@ -8465,10 +8501,10 @@
         <v>0</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.15">
@@ -8482,10 +8518,10 @@
         <v>0</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.15">
@@ -8499,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.15">
@@ -8516,10 +8552,10 @@
         <v>0</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.15">
@@ -8533,10 +8569,10 @@
         <v>0</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.15">
@@ -8550,10 +8586,10 @@
         <v>0</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.15">
@@ -8567,10 +8603,10 @@
         <v>0</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.15">
@@ -8584,10 +8620,10 @@
         <v>0</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.15">
@@ -8601,10 +8637,10 @@
         <v>0</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.15">
@@ -8618,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.15">
@@ -8635,10 +8671,10 @@
         <v>0</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.15">
@@ -8652,10 +8688,10 @@
         <v>0</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.15">
@@ -8669,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.15">
@@ -8686,10 +8722,10 @@
         <v>0</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.15">
@@ -8703,10 +8739,10 @@
         <v>0</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.15">
@@ -8720,10 +8756,10 @@
         <v>0</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.15">
@@ -8737,10 +8773,10 @@
         <v>0</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.15">
@@ -8754,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.15">
@@ -8771,10 +8807,10 @@
         <v>0</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.15">
@@ -8788,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.15">
@@ -8805,10 +8841,10 @@
         <v>0</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.15">
@@ -8822,10 +8858,10 @@
         <v>0</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.15">
@@ -8839,10 +8875,10 @@
         <v>0</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.15">
@@ -8856,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.15">
@@ -8873,10 +8909,10 @@
         <v>0</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.15">
@@ -8890,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.15">
@@ -8907,10 +8943,10 @@
         <v>0</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.15">
@@ -8924,10 +8960,10 @@
         <v>0</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.15">
@@ -8941,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.15">
@@ -8958,10 +8994,10 @@
         <v>0</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.15">
@@ -8975,10 +9011,10 @@
         <v>0</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD258453-968A-46A8-B218-CE31F8692284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C883DEB-3E82-42D9-A9ED-D71BF949B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="38">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,9 +83,6 @@
     <t>42761010,42663010</t>
   </si>
   <si>
-    <t>42652007</t>
-  </si>
-  <si>
     <t>drop_exp_num</t>
   </si>
   <si>
@@ -129,28 +126,10 @@
     <t>46700001:5</t>
   </si>
   <si>
-    <t>42761001</t>
-  </si>
-  <si>
-    <t>42663002</t>
-  </si>
-  <si>
-    <t>42761003</t>
-  </si>
-  <si>
     <t>46700001:6</t>
   </si>
   <si>
-    <t>42663004</t>
-  </si>
-  <si>
     <t>46700001:7</t>
-  </si>
-  <si>
-    <t>42655004</t>
-  </si>
-  <si>
-    <t>42761005</t>
   </si>
   <si>
     <t>46700001:12</t>
@@ -162,25 +141,13 @@
     <t>46200001:60</t>
   </si>
   <si>
-    <t>42663006</t>
-  </si>
-  <si>
     <t>46700001:13</t>
-  </si>
-  <si>
-    <t>42657006</t>
   </si>
   <si>
     <t>46700001:10</t>
   </si>
   <si>
     <t>46200001:80</t>
-  </si>
-  <si>
-    <t>42664006</t>
-  </si>
-  <si>
-    <t>42761007</t>
   </si>
   <si>
     <t>46700001:17</t>
@@ -193,9 +160,6 @@
   </si>
   <si>
     <t>46200001:120</t>
-  </si>
-  <si>
-    <t>42668007</t>
   </si>
   <si>
     <t>46700001:18</t>
@@ -564,19 +528,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -593,10 +557,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -613,10 +577,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -626,14 +590,14 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
+      <c r="D5" s="2">
+        <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -647,10 +611,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -660,14 +624,14 @@
       <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
+      <c r="D7" s="2">
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -681,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -694,14 +658,14 @@
       <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
+      <c r="D9" s="2">
+        <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -715,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -728,14 +692,14 @@
       <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
+      <c r="D11" s="2">
+        <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -749,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -762,14 +726,14 @@
       <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -779,14 +743,14 @@
       <c r="B14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
+      <c r="D14" s="2">
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -800,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -817,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -834,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
@@ -847,14 +811,14 @@
       <c r="B18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>37</v>
+      <c r="D18" s="2">
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -868,10 +832,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -881,14 +845,14 @@
       <c r="B20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>39</v>
+      <c r="D20" s="2">
+        <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -902,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -919,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -932,14 +896,14 @@
       <c r="B23" s="1">
         <v>6</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>42</v>
+      <c r="D23" s="2">
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -953,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -966,14 +930,14 @@
       <c r="B25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>43</v>
+      <c r="D25" s="2">
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -987,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -1004,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -1017,14 +981,14 @@
       <c r="B28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>12</v>
+      <c r="D28" s="2">
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
@@ -1038,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1055,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1068,14 +1032,14 @@
       <c r="B31" s="1">
         <v>7</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
+      <c r="D31" s="2">
+        <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1089,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1106,10 +1070,10 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1123,10 +1087,10 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1140,10 +1104,10 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1157,10 +1121,10 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1174,10 +1138,10 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1191,10 +1155,10 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1208,10 +1172,10 @@
         <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1225,10 +1189,10 @@
         <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
@@ -1242,10 +1206,10 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1259,10 +1223,10 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1276,10 +1240,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1293,10 +1257,10 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1310,10 +1274,10 @@
         <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1327,10 +1291,10 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1344,10 +1308,10 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1361,10 +1325,10 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1378,10 +1342,10 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -1395,10 +1359,10 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -1412,10 +1376,10 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
@@ -1429,10 +1393,10 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -1446,10 +1410,10 @@
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -1463,10 +1427,10 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -1480,10 +1444,10 @@
         <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -1497,10 +1461,10 @@
         <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -1514,10 +1478,10 @@
         <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -1531,10 +1495,10 @@
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -1548,10 +1512,10 @@
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -1565,10 +1529,10 @@
         <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -1582,10 +1546,10 @@
         <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
@@ -1599,10 +1563,10 @@
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
@@ -1616,10 +1580,10 @@
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -1633,10 +1597,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -1650,10 +1614,10 @@
         <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -1667,10 +1631,10 @@
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -1684,10 +1648,10 @@
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -1701,10 +1665,10 @@
         <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -1718,10 +1682,10 @@
         <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -1735,10 +1699,10 @@
         <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -1752,10 +1716,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -1769,10 +1733,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -1786,10 +1750,10 @@
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -1803,10 +1767,10 @@
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -1820,10 +1784,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -1837,10 +1801,10 @@
         <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -1854,10 +1818,10 @@
         <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -1871,10 +1835,10 @@
         <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -1888,10 +1852,10 @@
         <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -1905,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -1922,10 +1886,10 @@
         <v>11</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -1939,10 +1903,10 @@
         <v>11</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -1956,10 +1920,10 @@
         <v>11</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
@@ -1973,10 +1937,10 @@
         <v>11</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -1990,10 +1954,10 @@
         <v>11</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -2007,10 +1971,10 @@
         <v>11</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -2024,10 +1988,10 @@
         <v>11</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2041,10 +2005,10 @@
         <v>11</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2058,10 +2022,10 @@
         <v>11</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2075,10 +2039,10 @@
         <v>11</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2092,10 +2056,10 @@
         <v>11</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2109,10 +2073,10 @@
         <v>11</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2126,10 +2090,10 @@
         <v>11</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2143,10 +2107,10 @@
         <v>11</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2160,10 +2124,10 @@
         <v>11</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2177,10 +2141,10 @@
         <v>11</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
@@ -2194,10 +2158,10 @@
         <v>11</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2211,10 +2175,10 @@
         <v>11</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
@@ -2228,10 +2192,10 @@
         <v>11</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
@@ -2245,10 +2209,10 @@
         <v>11</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
@@ -2262,10 +2226,10 @@
         <v>11</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
@@ -2279,10 +2243,10 @@
         <v>11</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
@@ -2296,10 +2260,10 @@
         <v>11</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
@@ -2313,10 +2277,10 @@
         <v>11</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
@@ -2330,10 +2294,10 @@
         <v>11</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
@@ -2347,10 +2311,10 @@
         <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
@@ -2364,10 +2328,10 @@
         <v>11</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
@@ -2381,10 +2345,10 @@
         <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
@@ -2398,10 +2362,10 @@
         <v>11</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
@@ -2415,10 +2379,10 @@
         <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
@@ -2432,10 +2396,10 @@
         <v>11</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
@@ -2449,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
@@ -2466,10 +2430,10 @@
         <v>11</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
@@ -2483,10 +2447,10 @@
         <v>11</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
@@ -2500,10 +2464,10 @@
         <v>11</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
@@ -2517,10 +2481,10 @@
         <v>11</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
@@ -2534,10 +2498,10 @@
         <v>11</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
@@ -2551,10 +2515,10 @@
         <v>11</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
@@ -2568,10 +2532,10 @@
         <v>11</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -2585,10 +2549,10 @@
         <v>11</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
@@ -2602,10 +2566,10 @@
         <v>11</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.15">
@@ -2619,10 +2583,10 @@
         <v>11</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.15">
@@ -2636,10 +2600,10 @@
         <v>11</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.15">
@@ -2653,10 +2617,10 @@
         <v>11</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.15">
@@ -2670,10 +2634,10 @@
         <v>11</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.15">
@@ -2687,10 +2651,10 @@
         <v>11</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.15">
@@ -2704,10 +2668,10 @@
         <v>11</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.15">
@@ -2721,10 +2685,10 @@
         <v>11</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.15">
@@ -2738,10 +2702,10 @@
         <v>11</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.15">
@@ -2755,10 +2719,10 @@
         <v>11</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -2772,10 +2736,10 @@
         <v>11</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -2789,10 +2753,10 @@
         <v>11</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
@@ -2806,10 +2770,10 @@
         <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
@@ -2823,10 +2787,10 @@
         <v>11</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
@@ -2840,10 +2804,10 @@
         <v>11</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
@@ -2857,10 +2821,10 @@
         <v>11</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
@@ -2874,10 +2838,10 @@
         <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -2891,10 +2855,10 @@
         <v>11</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
@@ -2908,10 +2872,10 @@
         <v>11</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">
@@ -2925,10 +2889,10 @@
         <v>11</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
@@ -2942,10 +2906,10 @@
         <v>11</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -2959,10 +2923,10 @@
         <v>11</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -2976,10 +2940,10 @@
         <v>11</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -2993,10 +2957,10 @@
         <v>11</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
@@ -3010,10 +2974,10 @@
         <v>11</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
@@ -3027,10 +2991,10 @@
         <v>11</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
@@ -3044,10 +3008,10 @@
         <v>11</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
@@ -3061,10 +3025,10 @@
         <v>11</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
@@ -3078,10 +3042,10 @@
         <v>11</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
@@ -3095,10 +3059,10 @@
         <v>11</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
@@ -3112,10 +3076,10 @@
         <v>11</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.15">
@@ -3129,10 +3093,10 @@
         <v>11</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
@@ -3146,10 +3110,10 @@
         <v>11</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
@@ -3163,10 +3127,10 @@
         <v>11</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
@@ -3180,10 +3144,10 @@
         <v>11</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
@@ -3197,10 +3161,10 @@
         <v>11</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
@@ -3214,10 +3178,10 @@
         <v>11</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
@@ -3231,10 +3195,10 @@
         <v>11</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
@@ -3248,10 +3212,10 @@
         <v>11</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
@@ -3265,10 +3229,10 @@
         <v>11</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
@@ -3282,10 +3246,10 @@
         <v>11</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
@@ -3299,10 +3263,10 @@
         <v>11</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
@@ -3316,10 +3280,10 @@
         <v>11</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
@@ -3333,10 +3297,10 @@
         <v>11</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
@@ -3350,10 +3314,10 @@
         <v>11</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
@@ -3367,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -3384,10 +3348,10 @@
         <v>11</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -3401,10 +3365,10 @@
         <v>11</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
@@ -3418,10 +3382,10 @@
         <v>11</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
@@ -3435,10 +3399,10 @@
         <v>11</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
@@ -3452,10 +3416,10 @@
         <v>11</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
@@ -3469,10 +3433,10 @@
         <v>11</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
@@ -3486,10 +3450,10 @@
         <v>11</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
@@ -3503,10 +3467,10 @@
         <v>11</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
@@ -3520,10 +3484,10 @@
         <v>11</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
@@ -3537,10 +3501,10 @@
         <v>11</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
@@ -3554,10 +3518,10 @@
         <v>11</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
@@ -3571,10 +3535,10 @@
         <v>11</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
@@ -3588,10 +3552,10 @@
         <v>11</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
@@ -3605,10 +3569,10 @@
         <v>11</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
@@ -3622,10 +3586,10 @@
         <v>11</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
@@ -3639,10 +3603,10 @@
         <v>11</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
@@ -3656,10 +3620,10 @@
         <v>11</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
@@ -3673,10 +3637,10 @@
         <v>11</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
@@ -3690,10 +3654,10 @@
         <v>11</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
@@ -3707,10 +3671,10 @@
         <v>11</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
@@ -3724,10 +3688,10 @@
         <v>11</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
@@ -3741,10 +3705,10 @@
         <v>11</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
@@ -3758,10 +3722,10 @@
         <v>11</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
@@ -3775,10 +3739,10 @@
         <v>11</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
@@ -3792,10 +3756,10 @@
         <v>11</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
@@ -3809,10 +3773,10 @@
         <v>11</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
@@ -3826,10 +3790,10 @@
         <v>11</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
@@ -3843,10 +3807,10 @@
         <v>11</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
@@ -3860,10 +3824,10 @@
         <v>11</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
@@ -3877,10 +3841,10 @@
         <v>11</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
@@ -3894,10 +3858,10 @@
         <v>11</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
@@ -3911,10 +3875,10 @@
         <v>11</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
@@ -3928,10 +3892,10 @@
         <v>11</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
@@ -3945,10 +3909,10 @@
         <v>11</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
@@ -3962,10 +3926,10 @@
         <v>11</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
@@ -3979,10 +3943,10 @@
         <v>11</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
@@ -3996,10 +3960,10 @@
         <v>11</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
@@ -4013,10 +3977,10 @@
         <v>11</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
@@ -4030,10 +3994,10 @@
         <v>11</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
@@ -4047,10 +4011,10 @@
         <v>11</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
@@ -4064,10 +4028,10 @@
         <v>11</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
@@ -4081,10 +4045,10 @@
         <v>11</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
@@ -4098,10 +4062,10 @@
         <v>11</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -4115,10 +4079,10 @@
         <v>11</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
@@ -4132,10 +4096,10 @@
         <v>11</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
@@ -4149,10 +4113,10 @@
         <v>11</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
@@ -4166,10 +4130,10 @@
         <v>11</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
@@ -4183,10 +4147,10 @@
         <v>11</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
@@ -4200,10 +4164,10 @@
         <v>11</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
@@ -4217,10 +4181,10 @@
         <v>11</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
@@ -4234,10 +4198,10 @@
         <v>11</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
@@ -4251,10 +4215,10 @@
         <v>11</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
@@ -4268,10 +4232,10 @@
         <v>11</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
@@ -4285,10 +4249,10 @@
         <v>11</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
@@ -4302,10 +4266,10 @@
         <v>11</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
@@ -4319,10 +4283,10 @@
         <v>11</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
@@ -4336,10 +4300,10 @@
         <v>11</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
@@ -4353,10 +4317,10 @@
         <v>11</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
@@ -4370,10 +4334,10 @@
         <v>11</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
@@ -4387,10 +4351,10 @@
         <v>11</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
@@ -4404,10 +4368,10 @@
         <v>11</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
@@ -4421,10 +4385,10 @@
         <v>11</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
@@ -4438,10 +4402,10 @@
         <v>11</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
@@ -4455,10 +4419,10 @@
         <v>11</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
@@ -4472,10 +4436,10 @@
         <v>11</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
@@ -4489,10 +4453,10 @@
         <v>11</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
@@ -4506,10 +4470,10 @@
         <v>11</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
@@ -4523,10 +4487,10 @@
         <v>11</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
@@ -4540,10 +4504,10 @@
         <v>11</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
@@ -4557,10 +4521,10 @@
         <v>11</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
@@ -4574,10 +4538,10 @@
         <v>11</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
@@ -4591,10 +4555,10 @@
         <v>11</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
@@ -4608,10 +4572,10 @@
         <v>11</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
@@ -4625,10 +4589,10 @@
         <v>11</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
@@ -4642,10 +4606,10 @@
         <v>11</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
@@ -4659,10 +4623,10 @@
         <v>11</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
@@ -4676,10 +4640,10 @@
         <v>11</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
@@ -4693,10 +4657,10 @@
         <v>11</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
@@ -4710,10 +4674,10 @@
         <v>11</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
@@ -4727,10 +4691,10 @@
         <v>11</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
@@ -4744,10 +4708,10 @@
         <v>11</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
@@ -4761,10 +4725,10 @@
         <v>11</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
@@ -4778,10 +4742,10 @@
         <v>11</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
@@ -4795,10 +4759,10 @@
         <v>11</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.15">
@@ -4812,10 +4776,10 @@
         <v>11</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.15">
@@ -4829,10 +4793,10 @@
         <v>11</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.15">
@@ -4846,10 +4810,10 @@
         <v>11</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.15">
@@ -4863,10 +4827,10 @@
         <v>11</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.15">
@@ -4880,10 +4844,10 @@
         <v>11</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.15">
@@ -4897,10 +4861,10 @@
         <v>11</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.15">
@@ -4914,10 +4878,10 @@
         <v>11</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.15">
@@ -4931,10 +4895,10 @@
         <v>11</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.15">
@@ -4948,10 +4912,10 @@
         <v>11</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.15">
@@ -4965,10 +4929,10 @@
         <v>11</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.15">
@@ -4982,10 +4946,10 @@
         <v>11</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.15">
@@ -4999,10 +4963,10 @@
         <v>11</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.15">
@@ -5016,10 +4980,10 @@
         <v>11</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.15">
@@ -5033,10 +4997,10 @@
         <v>11</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.15">
@@ -5050,10 +5014,10 @@
         <v>11</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.15">
@@ -5067,10 +5031,10 @@
         <v>11</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.15">
@@ -5084,10 +5048,10 @@
         <v>11</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.15">
@@ -5101,10 +5065,10 @@
         <v>11</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.15">
@@ -5118,10 +5082,10 @@
         <v>11</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.15">
@@ -5135,10 +5099,10 @@
         <v>11</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.15">
@@ -5152,10 +5116,10 @@
         <v>11</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.15">
@@ -5169,10 +5133,10 @@
         <v>11</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.15">
@@ -5186,10 +5150,10 @@
         <v>11</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.15">
@@ -5203,10 +5167,10 @@
         <v>11</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.15">
@@ -5220,10 +5184,10 @@
         <v>11</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.15">
@@ -5237,10 +5201,10 @@
         <v>11</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.15">
@@ -5254,10 +5218,10 @@
         <v>11</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.15">
@@ -5271,10 +5235,10 @@
         <v>11</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.15">
@@ -5288,10 +5252,10 @@
         <v>11</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.15">
@@ -5305,10 +5269,10 @@
         <v>11</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.15">
@@ -5322,10 +5286,10 @@
         <v>11</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.15">
@@ -5339,10 +5303,10 @@
         <v>11</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.15">
@@ -5356,10 +5320,10 @@
         <v>11</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.15">
@@ -5373,10 +5337,10 @@
         <v>11</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.15">
@@ -5390,10 +5354,10 @@
         <v>11</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.15">
@@ -5407,10 +5371,10 @@
         <v>11</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.15">
@@ -5424,10 +5388,10 @@
         <v>11</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.15">
@@ -5441,10 +5405,10 @@
         <v>11</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.15">
@@ -5458,10 +5422,10 @@
         <v>11</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.15">
@@ -5475,10 +5439,10 @@
         <v>11</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.15">
@@ -5492,10 +5456,10 @@
         <v>11</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.15">
@@ -5509,10 +5473,10 @@
         <v>11</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.15">
@@ -5526,10 +5490,10 @@
         <v>11</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.15">
@@ -5543,10 +5507,10 @@
         <v>11</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.15">
@@ -5560,10 +5524,10 @@
         <v>11</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.15">
@@ -5577,10 +5541,10 @@
         <v>11</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.15">
@@ -5594,10 +5558,10 @@
         <v>11</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.15">
@@ -5611,10 +5575,10 @@
         <v>11</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.15">
@@ -5628,10 +5592,10 @@
         <v>11</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.15">
@@ -5645,10 +5609,10 @@
         <v>11</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.15">
@@ -5662,10 +5626,10 @@
         <v>11</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.15">
@@ -5679,10 +5643,10 @@
         <v>11</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.15">
@@ -5696,10 +5660,10 @@
         <v>11</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.15">
@@ -5713,10 +5677,10 @@
         <v>11</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.15">
@@ -5730,10 +5694,10 @@
         <v>11</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.15">
@@ -5747,10 +5711,10 @@
         <v>11</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.15">
@@ -5764,10 +5728,10 @@
         <v>11</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.15">
@@ -5781,10 +5745,10 @@
         <v>11</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.15">
@@ -5798,10 +5762,10 @@
         <v>11</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.15">
@@ -5815,10 +5779,10 @@
         <v>11</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.15">
@@ -5832,10 +5796,10 @@
         <v>11</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.15">
@@ -5849,10 +5813,10 @@
         <v>11</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.15">
@@ -5866,10 +5830,10 @@
         <v>11</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.15">
@@ -5883,10 +5847,10 @@
         <v>11</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.15">
@@ -5900,10 +5864,10 @@
         <v>11</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.15">
@@ -5917,10 +5881,10 @@
         <v>11</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.15">
@@ -5934,10 +5898,10 @@
         <v>11</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.15">
@@ -5951,10 +5915,10 @@
         <v>11</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.15">
@@ -5968,10 +5932,10 @@
         <v>11</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.15">
@@ -5985,10 +5949,10 @@
         <v>11</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.15">
@@ -6002,10 +5966,10 @@
         <v>11</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.15">
@@ -6019,10 +5983,10 @@
         <v>11</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.15">
@@ -6036,10 +6000,10 @@
         <v>11</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.15">
@@ -6053,10 +6017,10 @@
         <v>11</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.15">
@@ -6070,10 +6034,10 @@
         <v>11</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.15">
@@ -6087,10 +6051,10 @@
         <v>11</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.15">
@@ -6104,10 +6068,10 @@
         <v>11</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.15">
@@ -6121,10 +6085,10 @@
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.15">
@@ -6138,10 +6102,10 @@
         <v>11</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.15">
@@ -6155,10 +6119,10 @@
         <v>11</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.15">
@@ -6172,10 +6136,10 @@
         <v>11</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.15">
@@ -6189,10 +6153,10 @@
         <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.15">
@@ -6206,10 +6170,10 @@
         <v>11</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.15">
@@ -6223,10 +6187,10 @@
         <v>11</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.15">
@@ -6240,10 +6204,10 @@
         <v>11</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.15">
@@ -6257,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.15">
@@ -6274,10 +6238,10 @@
         <v>11</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.15">
@@ -6291,10 +6255,10 @@
         <v>11</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F338" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.15">
@@ -6308,10 +6272,10 @@
         <v>0</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.15">
@@ -6325,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.15">
@@ -6342,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.15">
@@ -6359,10 +6323,10 @@
         <v>0</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.15">
@@ -6376,10 +6340,10 @@
         <v>0</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.15">
@@ -6393,10 +6357,10 @@
         <v>0</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.15">
@@ -6410,10 +6374,10 @@
         <v>0</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.15">
@@ -6427,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.15">
@@ -6444,10 +6408,10 @@
         <v>0</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.15">
@@ -6461,10 +6425,10 @@
         <v>0</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.15">
@@ -6478,10 +6442,10 @@
         <v>0</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.15">
@@ -6495,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.15">
@@ -6512,10 +6476,10 @@
         <v>0</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.15">
@@ -6529,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.15">
@@ -6546,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.15">
@@ -6563,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.15">
@@ -6580,10 +6544,10 @@
         <v>0</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.15">
@@ -6597,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.15">
@@ -6614,10 +6578,10 @@
         <v>0</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.15">
@@ -6631,10 +6595,10 @@
         <v>0</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.15">
@@ -6648,10 +6612,10 @@
         <v>0</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.15">
@@ -6665,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.15">
@@ -6682,10 +6646,10 @@
         <v>0</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.15">
@@ -6699,10 +6663,10 @@
         <v>0</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.15">
@@ -6716,10 +6680,10 @@
         <v>0</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.15">
@@ -6733,10 +6697,10 @@
         <v>0</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.15">
@@ -6750,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.15">
@@ -6767,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.15">
@@ -6784,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.15">
@@ -6801,10 +6765,10 @@
         <v>0</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.15">
@@ -6818,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.15">
@@ -6835,10 +6799,10 @@
         <v>0</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.15">
@@ -6852,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.15">
@@ -6869,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.15">
@@ -6886,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.15">
@@ -6903,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.15">
@@ -6920,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.15">
@@ -6937,10 +6901,10 @@
         <v>0</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.15">
@@ -6954,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.15">
@@ -6971,10 +6935,10 @@
         <v>0</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.15">
@@ -6988,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.15">
@@ -7005,10 +6969,10 @@
         <v>0</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.15">
@@ -7022,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.15">
@@ -7039,10 +7003,10 @@
         <v>0</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.15">
@@ -7056,10 +7020,10 @@
         <v>0</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.15">
@@ -7073,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.15">
@@ -7090,10 +7054,10 @@
         <v>0</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.15">
@@ -7107,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.15">
@@ -7124,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.15">
@@ -7141,10 +7105,10 @@
         <v>0</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.15">
@@ -7158,10 +7122,10 @@
         <v>0</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.15">
@@ -7175,10 +7139,10 @@
         <v>0</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.15">
@@ -7192,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.15">
@@ -7209,10 +7173,10 @@
         <v>0</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.15">
@@ -7226,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.15">
@@ -7243,10 +7207,10 @@
         <v>0</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.15">
@@ -7260,10 +7224,10 @@
         <v>0</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.15">
@@ -7277,10 +7241,10 @@
         <v>0</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.15">
@@ -7294,10 +7258,10 @@
         <v>0</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.15">
@@ -7311,10 +7275,10 @@
         <v>0</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.15">
@@ -7328,10 +7292,10 @@
         <v>0</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.15">
@@ -7345,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.15">
@@ -7362,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.15">
@@ -7379,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.15">
@@ -7396,10 +7360,10 @@
         <v>0</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.15">
@@ -7413,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.15">
@@ -7430,10 +7394,10 @@
         <v>0</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.15">
@@ -7447,10 +7411,10 @@
         <v>0</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.15">
@@ -7464,10 +7428,10 @@
         <v>0</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.15">
@@ -7481,10 +7445,10 @@
         <v>0</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.15">
@@ -7498,10 +7462,10 @@
         <v>0</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.15">
@@ -7515,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.15">
@@ -7532,10 +7496,10 @@
         <v>0</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.15">
@@ -7549,10 +7513,10 @@
         <v>0</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.15">
@@ -7566,10 +7530,10 @@
         <v>0</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.15">
@@ -7583,10 +7547,10 @@
         <v>0</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.15">
@@ -7600,10 +7564,10 @@
         <v>0</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.15">
@@ -7617,10 +7581,10 @@
         <v>0</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.15">
@@ -7634,10 +7598,10 @@
         <v>0</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.15">
@@ -7651,10 +7615,10 @@
         <v>0</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.15">
@@ -7668,10 +7632,10 @@
         <v>0</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.15">
@@ -7685,10 +7649,10 @@
         <v>0</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.15">
@@ -7702,10 +7666,10 @@
         <v>0</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.15">
@@ -7719,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.15">
@@ -7736,10 +7700,10 @@
         <v>0</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.15">
@@ -7753,10 +7717,10 @@
         <v>0</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.15">
@@ -7770,10 +7734,10 @@
         <v>0</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.15">
@@ -7787,10 +7751,10 @@
         <v>0</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.15">
@@ -7804,10 +7768,10 @@
         <v>0</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.15">
@@ -7821,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.15">
@@ -7838,10 +7802,10 @@
         <v>0</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.15">
@@ -7855,10 +7819,10 @@
         <v>0</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.15">
@@ -7872,10 +7836,10 @@
         <v>0</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.15">
@@ -7889,10 +7853,10 @@
         <v>0</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.15">
@@ -7906,10 +7870,10 @@
         <v>0</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.15">
@@ -7923,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.15">
@@ -7940,10 +7904,10 @@
         <v>0</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.15">
@@ -7957,10 +7921,10 @@
         <v>0</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.15">
@@ -7974,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.15">
@@ -7991,10 +7955,10 @@
         <v>0</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.15">
@@ -8008,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.15">
@@ -8025,10 +7989,10 @@
         <v>0</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.15">
@@ -8042,10 +8006,10 @@
         <v>0</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.15">
@@ -8059,10 +8023,10 @@
         <v>0</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.15">
@@ -8076,10 +8040,10 @@
         <v>0</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.15">
@@ -8093,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.15">
@@ -8110,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.15">
@@ -8127,10 +8091,10 @@
         <v>0</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.15">
@@ -8144,10 +8108,10 @@
         <v>0</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.15">
@@ -8161,10 +8125,10 @@
         <v>0</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.15">
@@ -8178,10 +8142,10 @@
         <v>0</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.15">
@@ -8195,10 +8159,10 @@
         <v>0</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.15">
@@ -8212,10 +8176,10 @@
         <v>0</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.15">
@@ -8229,10 +8193,10 @@
         <v>0</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.15">
@@ -8246,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.15">
@@ -8263,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.15">
@@ -8280,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.15">
@@ -8297,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.15">
@@ -8314,10 +8278,10 @@
         <v>0</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.15">
@@ -8331,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.15">
@@ -8348,10 +8312,10 @@
         <v>0</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.15">
@@ -8365,10 +8329,10 @@
         <v>0</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.15">
@@ -8382,10 +8346,10 @@
         <v>0</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.15">
@@ -8399,10 +8363,10 @@
         <v>0</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.15">
@@ -8416,10 +8380,10 @@
         <v>0</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.15">
@@ -8433,10 +8397,10 @@
         <v>0</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.15">
@@ -8450,10 +8414,10 @@
         <v>0</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.15">
@@ -8467,10 +8431,10 @@
         <v>0</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.15">
@@ -8484,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.15">
@@ -8501,10 +8465,10 @@
         <v>0</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.15">
@@ -8518,10 +8482,10 @@
         <v>0</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.15">
@@ -8535,10 +8499,10 @@
         <v>0</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.15">
@@ -8552,10 +8516,10 @@
         <v>0</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.15">
@@ -8569,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.15">
@@ -8586,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.15">
@@ -8603,10 +8567,10 @@
         <v>0</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.15">
@@ -8620,10 +8584,10 @@
         <v>0</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.15">
@@ -8637,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.15">
@@ -8654,10 +8618,10 @@
         <v>0</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.15">
@@ -8671,10 +8635,10 @@
         <v>0</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.15">
@@ -8688,10 +8652,10 @@
         <v>0</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.15">
@@ -8705,10 +8669,10 @@
         <v>0</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.15">
@@ -8722,10 +8686,10 @@
         <v>0</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.15">
@@ -8739,10 +8703,10 @@
         <v>0</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.15">
@@ -8756,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.15">
@@ -8773,10 +8737,10 @@
         <v>0</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.15">
@@ -8790,10 +8754,10 @@
         <v>0</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.15">
@@ -8807,10 +8771,10 @@
         <v>0</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.15">
@@ -8824,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.15">
@@ -8841,10 +8805,10 @@
         <v>0</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.15">
@@ -8858,10 +8822,10 @@
         <v>0</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.15">
@@ -8875,10 +8839,10 @@
         <v>0</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.15">
@@ -8892,10 +8856,10 @@
         <v>0</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.15">
@@ -8909,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.15">
@@ -8926,10 +8890,10 @@
         <v>0</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.15">
@@ -8943,10 +8907,10 @@
         <v>0</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.15">
@@ -8960,10 +8924,10 @@
         <v>0</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.15">
@@ -8977,10 +8941,10 @@
         <v>0</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.15">
@@ -8994,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.15">
@@ -9011,10 +8975,10 @@
         <v>0</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C883DEB-3E82-42D9-A9ED-D71BF949B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A5526B-7FCE-4A3D-9D40-2DFC3E3F8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="41">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,18 @@
   </si>
   <si>
     <t>46700001:18</t>
+  </si>
+  <si>
+    <t>add_kongfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加通关值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -506,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F498"/>
+  <dimension ref="A1:G498"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -515,15 +527,16 @@
     <col min="4" max="4" width="39.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -542,8 +555,11 @@
       <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -562,8 +578,11 @@
       <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -582,8 +601,11 @@
       <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>10020</v>
       </c>
@@ -599,8 +621,11 @@
       <c r="F5" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10010</v>
       </c>
@@ -616,8 +641,11 @@
       <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>20020</v>
       </c>
@@ -633,8 +661,11 @@
       <c r="F7" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>20010</v>
       </c>
@@ -650,8 +681,11 @@
       <c r="F8" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>30020</v>
       </c>
@@ -667,8 +701,11 @@
       <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>30010</v>
       </c>
@@ -684,8 +721,11 @@
       <c r="F10" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>40020</v>
       </c>
@@ -701,8 +741,11 @@
       <c r="F11" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>40010</v>
       </c>
@@ -718,8 +761,11 @@
       <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>40002</v>
       </c>
@@ -735,8 +781,11 @@
       <c r="F13" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>50020</v>
       </c>
@@ -752,8 +801,11 @@
       <c r="F14" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>50010</v>
       </c>
@@ -769,8 +821,11 @@
       <c r="F15" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>50002</v>
       </c>
@@ -786,8 +841,11 @@
       <c r="F16" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>50003</v>
       </c>
@@ -803,8 +861,11 @@
       <c r="F17" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>60020</v>
       </c>
@@ -820,8 +881,11 @@
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>60010</v>
       </c>
@@ -837,8 +901,11 @@
       <c r="F19" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>60002</v>
       </c>
@@ -854,8 +921,11 @@
       <c r="F20" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>60003</v>
       </c>
@@ -871,8 +941,11 @@
       <c r="F21" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>60004</v>
       </c>
@@ -888,8 +961,11 @@
       <c r="F22" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>60005</v>
       </c>
@@ -905,8 +981,11 @@
       <c r="F23" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>60006</v>
       </c>
@@ -922,8 +1001,11 @@
       <c r="F24" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>70020</v>
       </c>
@@ -939,8 +1021,11 @@
       <c r="F25" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>70010</v>
       </c>
@@ -956,8 +1041,11 @@
       <c r="F26" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>70002</v>
       </c>
@@ -973,8 +1061,11 @@
       <c r="F27" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>70003</v>
       </c>
@@ -990,8 +1081,11 @@
       <c r="F28" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G28" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>70004</v>
       </c>
@@ -1007,8 +1101,11 @@
       <c r="F29" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G29" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>70005</v>
       </c>
@@ -1024,8 +1121,11 @@
       <c r="F30" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G30" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>70006</v>
       </c>
@@ -1041,8 +1141,11 @@
       <c r="F31" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G31" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>70007</v>
       </c>
@@ -1058,8 +1161,11 @@
       <c r="F32" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G32" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>80020</v>
       </c>
@@ -1075,8 +1181,11 @@
       <c r="F33" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>80010</v>
       </c>
@@ -1092,8 +1201,11 @@
       <c r="F34" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>90020</v>
       </c>
@@ -1109,8 +1221,11 @@
       <c r="F35" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>90010</v>
       </c>
@@ -1126,8 +1241,11 @@
       <c r="F36" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>100020</v>
       </c>
@@ -1143,8 +1261,11 @@
       <c r="F37" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>100010</v>
       </c>
@@ -1160,8 +1281,11 @@
       <c r="F38" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>110020</v>
       </c>
@@ -1177,8 +1301,11 @@
       <c r="F39" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>110010</v>
       </c>
@@ -1194,8 +1321,11 @@
       <c r="F40" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>120020</v>
       </c>
@@ -1211,8 +1341,11 @@
       <c r="F41" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>120010</v>
       </c>
@@ -1228,8 +1361,11 @@
       <c r="F42" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>130020</v>
       </c>
@@ -1245,8 +1381,11 @@
       <c r="F43" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>130010</v>
       </c>
@@ -1262,8 +1401,11 @@
       <c r="F44" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>140020</v>
       </c>
@@ -1279,8 +1421,11 @@
       <c r="F45" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>140010</v>
       </c>
@@ -1296,8 +1441,11 @@
       <c r="F46" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>150020</v>
       </c>
@@ -1313,8 +1461,11 @@
       <c r="F47" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>150010</v>
       </c>
@@ -1330,8 +1481,11 @@
       <c r="F48" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>160020</v>
       </c>
@@ -1347,8 +1501,11 @@
       <c r="F49" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>160010</v>
       </c>
@@ -1364,8 +1521,11 @@
       <c r="F50" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>170020</v>
       </c>
@@ -1381,8 +1541,11 @@
       <c r="F51" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>170010</v>
       </c>
@@ -1398,8 +1561,11 @@
       <c r="F52" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>180020</v>
       </c>
@@ -1415,8 +1581,11 @@
       <c r="F53" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>180010</v>
       </c>
@@ -1432,8 +1601,11 @@
       <c r="F54" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>190020</v>
       </c>
@@ -1449,8 +1621,11 @@
       <c r="F55" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>190010</v>
       </c>
@@ -1466,8 +1641,11 @@
       <c r="F56" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>200020</v>
       </c>
@@ -1483,8 +1661,11 @@
       <c r="F57" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>200010</v>
       </c>
@@ -1500,8 +1681,11 @@
       <c r="F58" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>210020</v>
       </c>
@@ -1517,8 +1701,11 @@
       <c r="F59" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>210010</v>
       </c>
@@ -1534,8 +1721,11 @@
       <c r="F60" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>220020</v>
       </c>
@@ -1551,8 +1741,11 @@
       <c r="F61" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>220010</v>
       </c>
@@ -1568,8 +1761,11 @@
       <c r="F62" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>230020</v>
       </c>
@@ -1585,8 +1781,11 @@
       <c r="F63" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>230010</v>
       </c>
@@ -1602,8 +1801,11 @@
       <c r="F64" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>240020</v>
       </c>
@@ -1619,8 +1821,11 @@
       <c r="F65" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>240010</v>
       </c>
@@ -1636,8 +1841,11 @@
       <c r="F66" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>250020</v>
       </c>
@@ -1653,8 +1861,11 @@
       <c r="F67" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>250010</v>
       </c>
@@ -1670,8 +1881,11 @@
       <c r="F68" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>260020</v>
       </c>
@@ -1687,8 +1901,11 @@
       <c r="F69" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>260010</v>
       </c>
@@ -1704,8 +1921,11 @@
       <c r="F70" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>270020</v>
       </c>
@@ -1721,8 +1941,11 @@
       <c r="F71" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>270010</v>
       </c>
@@ -1738,8 +1961,11 @@
       <c r="F72" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>280020</v>
       </c>
@@ -1755,8 +1981,11 @@
       <c r="F73" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>280010</v>
       </c>
@@ -1772,8 +2001,11 @@
       <c r="F74" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>290020</v>
       </c>
@@ -1789,8 +2021,11 @@
       <c r="F75" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>290010</v>
       </c>
@@ -1806,8 +2041,11 @@
       <c r="F76" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>300020</v>
       </c>
@@ -1823,8 +2061,11 @@
       <c r="F77" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>300010</v>
       </c>
@@ -1840,8 +2081,11 @@
       <c r="F78" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>310020</v>
       </c>
@@ -1857,8 +2101,11 @@
       <c r="F79" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>310010</v>
       </c>
@@ -1874,8 +2121,11 @@
       <c r="F80" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>320020</v>
       </c>
@@ -1891,8 +2141,11 @@
       <c r="F81" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>320010</v>
       </c>
@@ -1908,8 +2161,11 @@
       <c r="F82" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>330020</v>
       </c>
@@ -1925,8 +2181,11 @@
       <c r="F83" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>330010</v>
       </c>
@@ -1942,8 +2201,11 @@
       <c r="F84" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>340020</v>
       </c>
@@ -1959,8 +2221,11 @@
       <c r="F85" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>340010</v>
       </c>
@@ -1976,8 +2241,11 @@
       <c r="F86" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>350020</v>
       </c>
@@ -1993,8 +2261,11 @@
       <c r="F87" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>350010</v>
       </c>
@@ -2010,8 +2281,11 @@
       <c r="F88" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>360020</v>
       </c>
@@ -2027,8 +2301,11 @@
       <c r="F89" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>360010</v>
       </c>
@@ -2044,8 +2321,11 @@
       <c r="F90" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>370020</v>
       </c>
@@ -2061,8 +2341,11 @@
       <c r="F91" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>370010</v>
       </c>
@@ -2078,8 +2361,11 @@
       <c r="F92" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>380020</v>
       </c>
@@ -2095,8 +2381,11 @@
       <c r="F93" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>380010</v>
       </c>
@@ -2112,8 +2401,11 @@
       <c r="F94" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>390020</v>
       </c>
@@ -2129,8 +2421,11 @@
       <c r="F95" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>390010</v>
       </c>
@@ -2146,8 +2441,11 @@
       <c r="F96" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>400020</v>
       </c>
@@ -2163,8 +2461,11 @@
       <c r="F97" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>400010</v>
       </c>
@@ -2180,8 +2481,11 @@
       <c r="F98" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>410020</v>
       </c>
@@ -2197,8 +2501,11 @@
       <c r="F99" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>410010</v>
       </c>
@@ -2214,8 +2521,11 @@
       <c r="F100" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>420020</v>
       </c>
@@ -2231,8 +2541,11 @@
       <c r="F101" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>420010</v>
       </c>
@@ -2248,8 +2561,11 @@
       <c r="F102" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>430020</v>
       </c>
@@ -2265,8 +2581,11 @@
       <c r="F103" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>430010</v>
       </c>
@@ -2282,8 +2601,11 @@
       <c r="F104" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>440020</v>
       </c>
@@ -2299,8 +2621,11 @@
       <c r="F105" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>440010</v>
       </c>
@@ -2316,8 +2641,11 @@
       <c r="F106" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>450020</v>
       </c>
@@ -2333,8 +2661,11 @@
       <c r="F107" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>450010</v>
       </c>
@@ -2350,8 +2681,11 @@
       <c r="F108" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>460020</v>
       </c>
@@ -2367,8 +2701,11 @@
       <c r="F109" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>460010</v>
       </c>
@@ -2384,8 +2721,11 @@
       <c r="F110" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>470020</v>
       </c>
@@ -2401,8 +2741,11 @@
       <c r="F111" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>470010</v>
       </c>
@@ -2418,8 +2761,11 @@
       <c r="F112" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>480020</v>
       </c>
@@ -2435,8 +2781,11 @@
       <c r="F113" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>480010</v>
       </c>
@@ -2452,8 +2801,11 @@
       <c r="F114" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>490020</v>
       </c>
@@ -2469,8 +2821,11 @@
       <c r="F115" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>490010</v>
       </c>
@@ -2486,8 +2841,11 @@
       <c r="F116" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>500020</v>
       </c>
@@ -2503,8 +2861,11 @@
       <c r="F117" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>500010</v>
       </c>
@@ -2520,8 +2881,11 @@
       <c r="F118" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>510020</v>
       </c>
@@ -2537,8 +2901,11 @@
       <c r="F119" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>510010</v>
       </c>
@@ -2554,8 +2921,11 @@
       <c r="F120" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>520020</v>
       </c>
@@ -2571,8 +2941,11 @@
       <c r="F121" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>520010</v>
       </c>
@@ -2588,8 +2961,11 @@
       <c r="F122" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>530020</v>
       </c>
@@ -2605,8 +2981,11 @@
       <c r="F123" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>530010</v>
       </c>
@@ -2622,8 +3001,11 @@
       <c r="F124" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>540020</v>
       </c>
@@ -2639,8 +3021,11 @@
       <c r="F125" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>540010</v>
       </c>
@@ -2656,8 +3041,11 @@
       <c r="F126" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>550020</v>
       </c>
@@ -2673,8 +3061,11 @@
       <c r="F127" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>550010</v>
       </c>
@@ -2690,8 +3081,11 @@
       <c r="F128" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>560020</v>
       </c>
@@ -2707,8 +3101,11 @@
       <c r="F129" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>560010</v>
       </c>
@@ -2724,8 +3121,11 @@
       <c r="F130" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>570020</v>
       </c>
@@ -2741,8 +3141,11 @@
       <c r="F131" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>570010</v>
       </c>
@@ -2758,8 +3161,11 @@
       <c r="F132" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>580020</v>
       </c>
@@ -2775,8 +3181,11 @@
       <c r="F133" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>580010</v>
       </c>
@@ -2792,8 +3201,11 @@
       <c r="F134" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>590020</v>
       </c>
@@ -2809,8 +3221,11 @@
       <c r="F135" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>590010</v>
       </c>
@@ -2826,8 +3241,11 @@
       <c r="F136" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>600020</v>
       </c>
@@ -2843,8 +3261,11 @@
       <c r="F137" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>600010</v>
       </c>
@@ -2860,8 +3281,11 @@
       <c r="F138" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>610020</v>
       </c>
@@ -2877,8 +3301,11 @@
       <c r="F139" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>610010</v>
       </c>
@@ -2894,8 +3321,11 @@
       <c r="F140" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>620020</v>
       </c>
@@ -2911,8 +3341,11 @@
       <c r="F141" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>620010</v>
       </c>
@@ -2928,8 +3361,11 @@
       <c r="F142" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>630020</v>
       </c>
@@ -2945,8 +3381,11 @@
       <c r="F143" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>630010</v>
       </c>
@@ -2962,8 +3401,11 @@
       <c r="F144" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>640020</v>
       </c>
@@ -2979,8 +3421,11 @@
       <c r="F145" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>640010</v>
       </c>
@@ -2996,8 +3441,11 @@
       <c r="F146" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>650020</v>
       </c>
@@ -3013,8 +3461,11 @@
       <c r="F147" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>650010</v>
       </c>
@@ -3030,8 +3481,11 @@
       <c r="F148" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>660020</v>
       </c>
@@ -3047,8 +3501,11 @@
       <c r="F149" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>660010</v>
       </c>
@@ -3064,8 +3521,11 @@
       <c r="F150" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>670020</v>
       </c>
@@ -3081,8 +3541,11 @@
       <c r="F151" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>670010</v>
       </c>
@@ -3098,8 +3561,11 @@
       <c r="F152" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>680020</v>
       </c>
@@ -3115,8 +3581,11 @@
       <c r="F153" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>680010</v>
       </c>
@@ -3132,8 +3601,11 @@
       <c r="F154" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>690020</v>
       </c>
@@ -3149,8 +3621,11 @@
       <c r="F155" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>690010</v>
       </c>
@@ -3166,8 +3641,11 @@
       <c r="F156" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>700020</v>
       </c>
@@ -3183,8 +3661,11 @@
       <c r="F157" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>700010</v>
       </c>
@@ -3200,8 +3681,11 @@
       <c r="F158" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>710020</v>
       </c>
@@ -3217,8 +3701,11 @@
       <c r="F159" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>710010</v>
       </c>
@@ -3234,8 +3721,11 @@
       <c r="F160" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>720020</v>
       </c>
@@ -3251,8 +3741,11 @@
       <c r="F161" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>720010</v>
       </c>
@@ -3268,8 +3761,11 @@
       <c r="F162" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>730020</v>
       </c>
@@ -3285,8 +3781,11 @@
       <c r="F163" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>730010</v>
       </c>
@@ -3302,8 +3801,11 @@
       <c r="F164" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>740020</v>
       </c>
@@ -3319,8 +3821,11 @@
       <c r="F165" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>740010</v>
       </c>
@@ -3336,8 +3841,11 @@
       <c r="F166" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>750020</v>
       </c>
@@ -3353,8 +3861,11 @@
       <c r="F167" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>750010</v>
       </c>
@@ -3370,8 +3881,11 @@
       <c r="F168" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>760020</v>
       </c>
@@ -3387,8 +3901,11 @@
       <c r="F169" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>760010</v>
       </c>
@@ -3404,8 +3921,11 @@
       <c r="F170" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>770020</v>
       </c>
@@ -3421,8 +3941,11 @@
       <c r="F171" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>770010</v>
       </c>
@@ -3438,8 +3961,11 @@
       <c r="F172" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>780020</v>
       </c>
@@ -3455,8 +3981,11 @@
       <c r="F173" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>780010</v>
       </c>
@@ -3472,8 +4001,11 @@
       <c r="F174" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G174" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>790020</v>
       </c>
@@ -3489,8 +4021,11 @@
       <c r="F175" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G175" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>790010</v>
       </c>
@@ -3506,8 +4041,11 @@
       <c r="F176" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>800020</v>
       </c>
@@ -3523,8 +4061,11 @@
       <c r="F177" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>800010</v>
       </c>
@@ -3540,8 +4081,11 @@
       <c r="F178" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>810020</v>
       </c>
@@ -3557,8 +4101,11 @@
       <c r="F179" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>810010</v>
       </c>
@@ -3574,8 +4121,11 @@
       <c r="F180" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>820020</v>
       </c>
@@ -3591,8 +4141,11 @@
       <c r="F181" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>820010</v>
       </c>
@@ -3608,8 +4161,11 @@
       <c r="F182" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>830020</v>
       </c>
@@ -3625,8 +4181,11 @@
       <c r="F183" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>830010</v>
       </c>
@@ -3642,8 +4201,11 @@
       <c r="F184" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>840020</v>
       </c>
@@ -3659,8 +4221,11 @@
       <c r="F185" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>840010</v>
       </c>
@@ -3676,8 +4241,11 @@
       <c r="F186" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>850020</v>
       </c>
@@ -3693,8 +4261,11 @@
       <c r="F187" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>850010</v>
       </c>
@@ -3710,8 +4281,11 @@
       <c r="F188" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G188" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>860020</v>
       </c>
@@ -3727,8 +4301,11 @@
       <c r="F189" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G189" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>860010</v>
       </c>
@@ -3744,8 +4321,11 @@
       <c r="F190" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G190" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>870020</v>
       </c>
@@ -3761,8 +4341,11 @@
       <c r="F191" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G191" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>870010</v>
       </c>
@@ -3778,8 +4361,11 @@
       <c r="F192" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G192" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>880020</v>
       </c>
@@ -3795,8 +4381,11 @@
       <c r="F193" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G193" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>880010</v>
       </c>
@@ -3812,8 +4401,11 @@
       <c r="F194" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G194" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>890020</v>
       </c>
@@ -3829,8 +4421,11 @@
       <c r="F195" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G195" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>890010</v>
       </c>
@@ -3846,8 +4441,11 @@
       <c r="F196" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G196" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>900020</v>
       </c>
@@ -3863,8 +4461,11 @@
       <c r="F197" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G197" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>900010</v>
       </c>
@@ -3880,8 +4481,11 @@
       <c r="F198" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G198" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>910020</v>
       </c>
@@ -3897,8 +4501,11 @@
       <c r="F199" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G199" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>910010</v>
       </c>
@@ -3914,8 +4521,11 @@
       <c r="F200" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G200" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>920020</v>
       </c>
@@ -3931,8 +4541,11 @@
       <c r="F201" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>920010</v>
       </c>
@@ -3948,8 +4561,11 @@
       <c r="F202" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G202" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>930020</v>
       </c>
@@ -3965,8 +4581,11 @@
       <c r="F203" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G203" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>930010</v>
       </c>
@@ -3982,8 +4601,11 @@
       <c r="F204" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G204" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>940020</v>
       </c>
@@ -3999,8 +4621,11 @@
       <c r="F205" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G205" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>940010</v>
       </c>
@@ -4016,8 +4641,11 @@
       <c r="F206" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G206" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>950020</v>
       </c>
@@ -4033,8 +4661,11 @@
       <c r="F207" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G207" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>950010</v>
       </c>
@@ -4050,8 +4681,11 @@
       <c r="F208" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G208" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>960020</v>
       </c>
@@ -4067,8 +4701,11 @@
       <c r="F209" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G209" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>960010</v>
       </c>
@@ -4084,8 +4721,11 @@
       <c r="F210" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G210" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>970020</v>
       </c>
@@ -4101,8 +4741,11 @@
       <c r="F211" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G211" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>970010</v>
       </c>
@@ -4118,8 +4761,11 @@
       <c r="F212" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G212" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>980020</v>
       </c>
@@ -4135,8 +4781,11 @@
       <c r="F213" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G213" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>980010</v>
       </c>
@@ -4152,8 +4801,11 @@
       <c r="F214" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G214" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>990020</v>
       </c>
@@ -4169,8 +4821,11 @@
       <c r="F215" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G215" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>990010</v>
       </c>
@@ -4186,8 +4841,11 @@
       <c r="F216" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G216" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>1000020</v>
       </c>
@@ -4203,8 +4861,11 @@
       <c r="F217" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G217" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>1000010</v>
       </c>
@@ -4220,8 +4881,11 @@
       <c r="F218" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G218" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>1010020</v>
       </c>
@@ -4237,8 +4901,11 @@
       <c r="F219" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G219" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>1010010</v>
       </c>
@@ -4254,8 +4921,11 @@
       <c r="F220" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G220" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>1020020</v>
       </c>
@@ -4271,8 +4941,11 @@
       <c r="F221" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G221" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>1020010</v>
       </c>
@@ -4288,8 +4961,11 @@
       <c r="F222" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G222" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>1030020</v>
       </c>
@@ -4305,8 +4981,11 @@
       <c r="F223" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G223" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>1030010</v>
       </c>
@@ -4322,8 +5001,11 @@
       <c r="F224" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G224" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>1040020</v>
       </c>
@@ -4339,8 +5021,11 @@
       <c r="F225" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G225" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>1040010</v>
       </c>
@@ -4356,8 +5041,11 @@
       <c r="F226" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G226" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>1050020</v>
       </c>
@@ -4373,8 +5061,11 @@
       <c r="F227" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G227" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>1050010</v>
       </c>
@@ -4390,8 +5081,11 @@
       <c r="F228" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G228" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>1060020</v>
       </c>
@@ -4407,8 +5101,11 @@
       <c r="F229" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G229" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>1060010</v>
       </c>
@@ -4424,8 +5121,11 @@
       <c r="F230" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G230" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>1070020</v>
       </c>
@@ -4441,8 +5141,11 @@
       <c r="F231" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G231" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>1070010</v>
       </c>
@@ -4458,8 +5161,11 @@
       <c r="F232" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G232" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>1080020</v>
       </c>
@@ -4475,8 +5181,11 @@
       <c r="F233" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G233" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>1080010</v>
       </c>
@@ -4492,8 +5201,11 @@
       <c r="F234" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G234" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>1090020</v>
       </c>
@@ -4509,8 +5221,11 @@
       <c r="F235" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G235" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>1090010</v>
       </c>
@@ -4526,8 +5241,11 @@
       <c r="F236" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G236" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>1100020</v>
       </c>
@@ -4543,8 +5261,11 @@
       <c r="F237" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G237" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>1100010</v>
       </c>
@@ -4560,8 +5281,11 @@
       <c r="F238" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G238" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>1110020</v>
       </c>
@@ -4577,8 +5301,11 @@
       <c r="F239" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G239" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>1110010</v>
       </c>
@@ -4594,8 +5321,11 @@
       <c r="F240" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G240" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>1120020</v>
       </c>
@@ -4611,8 +5341,11 @@
       <c r="F241" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G241" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>1120010</v>
       </c>
@@ -4628,8 +5361,11 @@
       <c r="F242" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G242" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>1130020</v>
       </c>
@@ -4645,8 +5381,11 @@
       <c r="F243" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G243" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>1130010</v>
       </c>
@@ -4662,8 +5401,11 @@
       <c r="F244" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G244" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>1140020</v>
       </c>
@@ -4679,8 +5421,11 @@
       <c r="F245" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G245" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>1140010</v>
       </c>
@@ -4696,8 +5441,11 @@
       <c r="F246" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G246" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>1150020</v>
       </c>
@@ -4713,8 +5461,11 @@
       <c r="F247" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G247" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>1150010</v>
       </c>
@@ -4730,8 +5481,11 @@
       <c r="F248" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G248" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>1160020</v>
       </c>
@@ -4747,8 +5501,11 @@
       <c r="F249" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G249" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>1160010</v>
       </c>
@@ -4764,8 +5521,11 @@
       <c r="F250" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G250" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>1170020</v>
       </c>
@@ -4781,8 +5541,11 @@
       <c r="F251" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G251" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>1170010</v>
       </c>
@@ -4798,8 +5561,11 @@
       <c r="F252" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G252" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>1180020</v>
       </c>
@@ -4815,8 +5581,11 @@
       <c r="F253" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G253" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
         <v>1180010</v>
       </c>
@@ -4832,8 +5601,11 @@
       <c r="F254" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G254" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>1190020</v>
       </c>
@@ -4849,8 +5621,11 @@
       <c r="F255" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G255" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
         <v>1190010</v>
       </c>
@@ -4866,8 +5641,11 @@
       <c r="F256" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G256" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>1200020</v>
       </c>
@@ -4883,8 +5661,11 @@
       <c r="F257" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G257" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>1200010</v>
       </c>
@@ -4900,8 +5681,11 @@
       <c r="F258" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G258" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>1210020</v>
       </c>
@@ -4917,8 +5701,11 @@
       <c r="F259" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G259" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>1210010</v>
       </c>
@@ -4934,8 +5721,11 @@
       <c r="F260" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G260" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
         <v>1220020</v>
       </c>
@@ -4951,8 +5741,11 @@
       <c r="F261" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G261" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>1220010</v>
       </c>
@@ -4968,8 +5761,11 @@
       <c r="F262" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G262" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>1230020</v>
       </c>
@@ -4985,8 +5781,11 @@
       <c r="F263" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G263" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>1230010</v>
       </c>
@@ -5002,8 +5801,11 @@
       <c r="F264" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G264" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>1240020</v>
       </c>
@@ -5019,8 +5821,11 @@
       <c r="F265" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G265" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>1240010</v>
       </c>
@@ -5036,8 +5841,11 @@
       <c r="F266" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G266" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>1250020</v>
       </c>
@@ -5053,8 +5861,11 @@
       <c r="F267" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G267" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>1250010</v>
       </c>
@@ -5070,8 +5881,11 @@
       <c r="F268" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G268" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>1260020</v>
       </c>
@@ -5087,8 +5901,11 @@
       <c r="F269" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G269" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>1260010</v>
       </c>
@@ -5104,8 +5921,11 @@
       <c r="F270" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G270" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>1270020</v>
       </c>
@@ -5121,8 +5941,11 @@
       <c r="F271" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G271" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>1270010</v>
       </c>
@@ -5138,8 +5961,11 @@
       <c r="F272" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G272" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>1280020</v>
       </c>
@@ -5155,8 +5981,11 @@
       <c r="F273" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G273" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>1280010</v>
       </c>
@@ -5172,8 +6001,11 @@
       <c r="F274" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G274" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>1290020</v>
       </c>
@@ -5189,8 +6021,11 @@
       <c r="F275" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G275" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>1290010</v>
       </c>
@@ -5206,8 +6041,11 @@
       <c r="F276" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G276" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>1300020</v>
       </c>
@@ -5223,8 +6061,11 @@
       <c r="F277" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G277" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>1300010</v>
       </c>
@@ -5240,8 +6081,11 @@
       <c r="F278" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G278" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>1310020</v>
       </c>
@@ -5257,8 +6101,11 @@
       <c r="F279" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G279" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>1310010</v>
       </c>
@@ -5274,8 +6121,11 @@
       <c r="F280" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G280" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
         <v>1320020</v>
       </c>
@@ -5291,8 +6141,11 @@
       <c r="F281" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G281" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>1320010</v>
       </c>
@@ -5308,8 +6161,11 @@
       <c r="F282" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G282" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>1330020</v>
       </c>
@@ -5325,8 +6181,11 @@
       <c r="F283" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G283" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>1330010</v>
       </c>
@@ -5342,8 +6201,11 @@
       <c r="F284" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G284" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>1340020</v>
       </c>
@@ -5359,8 +6221,11 @@
       <c r="F285" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G285" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>1340010</v>
       </c>
@@ -5376,8 +6241,11 @@
       <c r="F286" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G286" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>1350020</v>
       </c>
@@ -5393,8 +6261,11 @@
       <c r="F287" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G287" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>1350010</v>
       </c>
@@ -5410,8 +6281,11 @@
       <c r="F288" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G288" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>1360020</v>
       </c>
@@ -5427,8 +6301,11 @@
       <c r="F289" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G289" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>1360010</v>
       </c>
@@ -5444,8 +6321,11 @@
       <c r="F290" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G290" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>1370020</v>
       </c>
@@ -5461,8 +6341,11 @@
       <c r="F291" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G291" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>1370010</v>
       </c>
@@ -5478,8 +6361,11 @@
       <c r="F292" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G292" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>1380020</v>
       </c>
@@ -5495,8 +6381,11 @@
       <c r="F293" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G293" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>1380010</v>
       </c>
@@ -5512,8 +6401,11 @@
       <c r="F294" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G294" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>1390020</v>
       </c>
@@ -5529,8 +6421,11 @@
       <c r="F295" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G295" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>1390010</v>
       </c>
@@ -5546,8 +6441,11 @@
       <c r="F296" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G296" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>1400020</v>
       </c>
@@ -5563,8 +6461,11 @@
       <c r="F297" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G297" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>1400010</v>
       </c>
@@ -5580,8 +6481,11 @@
       <c r="F298" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G298" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>1410020</v>
       </c>
@@ -5597,8 +6501,11 @@
       <c r="F299" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G299" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>1410010</v>
       </c>
@@ -5614,8 +6521,11 @@
       <c r="F300" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G300" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>1420020</v>
       </c>
@@ -5631,8 +6541,11 @@
       <c r="F301" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G301" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
         <v>1420010</v>
       </c>
@@ -5648,8 +6561,11 @@
       <c r="F302" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G302" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
         <v>1430020</v>
       </c>
@@ -5665,8 +6581,11 @@
       <c r="F303" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G303" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
         <v>1430010</v>
       </c>
@@ -5682,8 +6601,11 @@
       <c r="F304" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G304" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
         <v>1440020</v>
       </c>
@@ -5699,8 +6621,11 @@
       <c r="F305" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G305" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
         <v>1440010</v>
       </c>
@@ -5716,8 +6641,11 @@
       <c r="F306" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G306" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
         <v>1450020</v>
       </c>
@@ -5733,8 +6661,11 @@
       <c r="F307" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G307" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
         <v>1450010</v>
       </c>
@@ -5750,8 +6681,11 @@
       <c r="F308" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G308" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
         <v>1460020</v>
       </c>
@@ -5767,8 +6701,11 @@
       <c r="F309" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G309" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
         <v>1460010</v>
       </c>
@@ -5784,8 +6721,11 @@
       <c r="F310" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G310" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
         <v>1470020</v>
       </c>
@@ -5801,8 +6741,11 @@
       <c r="F311" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G311" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
         <v>1470010</v>
       </c>
@@ -5818,8 +6761,11 @@
       <c r="F312" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G312" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
         <v>1480020</v>
       </c>
@@ -5835,8 +6781,11 @@
       <c r="F313" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G313" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
         <v>1480010</v>
       </c>
@@ -5852,8 +6801,11 @@
       <c r="F314" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G314" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
         <v>1490020</v>
       </c>
@@ -5869,8 +6821,11 @@
       <c r="F315" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G315" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
         <v>1490010</v>
       </c>
@@ -5886,8 +6841,11 @@
       <c r="F316" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G316" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
         <v>1500020</v>
       </c>
@@ -5903,8 +6861,11 @@
       <c r="F317" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G317" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
         <v>1500010</v>
       </c>
@@ -5920,8 +6881,11 @@
       <c r="F318" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G318" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
         <v>1510020</v>
       </c>
@@ -5937,8 +6901,11 @@
       <c r="F319" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G319" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
         <v>1510010</v>
       </c>
@@ -5954,8 +6921,11 @@
       <c r="F320" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G320" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
         <v>1520020</v>
       </c>
@@ -5971,8 +6941,11 @@
       <c r="F321" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G321" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
         <v>1520010</v>
       </c>
@@ -5988,8 +6961,11 @@
       <c r="F322" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G322" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
         <v>1530020</v>
       </c>
@@ -6005,8 +6981,11 @@
       <c r="F323" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G323" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
         <v>1530010</v>
       </c>
@@ -6022,8 +7001,11 @@
       <c r="F324" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G324" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
         <v>1540020</v>
       </c>
@@ -6039,8 +7021,11 @@
       <c r="F325" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G325" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
         <v>1540010</v>
       </c>
@@ -6056,8 +7041,11 @@
       <c r="F326" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G326" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
         <v>1550020</v>
       </c>
@@ -6073,8 +7061,11 @@
       <c r="F327" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G327" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
         <v>1550010</v>
       </c>
@@ -6090,8 +7081,11 @@
       <c r="F328" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G328" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
         <v>1560020</v>
       </c>
@@ -6107,8 +7101,11 @@
       <c r="F329" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G329" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
         <v>1560010</v>
       </c>
@@ -6124,8 +7121,11 @@
       <c r="F330" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G330" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
         <v>1570020</v>
       </c>
@@ -6141,8 +7141,11 @@
       <c r="F331" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G331" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
         <v>1570010</v>
       </c>
@@ -6158,8 +7161,11 @@
       <c r="F332" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G332" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
         <v>1580020</v>
       </c>
@@ -6175,8 +7181,11 @@
       <c r="F333" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G333" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
         <v>1580010</v>
       </c>
@@ -6192,8 +7201,11 @@
       <c r="F334" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G334" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
         <v>1590020</v>
       </c>
@@ -6209,8 +7221,11 @@
       <c r="F335" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G335" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
         <v>1590010</v>
       </c>
@@ -6226,8 +7241,11 @@
       <c r="F336" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G336" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
         <v>1600020</v>
       </c>
@@ -6243,8 +7261,11 @@
       <c r="F337" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G337" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
         <v>1600010</v>
       </c>
@@ -6260,8 +7281,11 @@
       <c r="F338" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G338" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
         <v>10001</v>
       </c>
@@ -6277,8 +7301,11 @@
       <c r="F339" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G339" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
         <v>20001</v>
       </c>
@@ -6294,8 +7321,11 @@
       <c r="F340" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G340" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
         <v>30001</v>
       </c>
@@ -6311,8 +7341,11 @@
       <c r="F341" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G341" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
         <v>40001</v>
       </c>
@@ -6328,8 +7361,11 @@
       <c r="F342" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G342" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
         <v>50001</v>
       </c>
@@ -6345,8 +7381,11 @@
       <c r="F343" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G343" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
         <v>60001</v>
       </c>
@@ -6362,8 +7401,11 @@
       <c r="F344" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G344" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
         <v>70001</v>
       </c>
@@ -6379,8 +7421,11 @@
       <c r="F345" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G345" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
         <v>80001</v>
       </c>
@@ -6396,8 +7441,11 @@
       <c r="F346" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G346" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
         <v>90001</v>
       </c>
@@ -6413,8 +7461,11 @@
       <c r="F347" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G347" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
         <v>100001</v>
       </c>
@@ -6430,8 +7481,11 @@
       <c r="F348" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G348" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
         <v>110001</v>
       </c>
@@ -6447,8 +7501,11 @@
       <c r="F349" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G349" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
         <v>120001</v>
       </c>
@@ -6464,8 +7521,11 @@
       <c r="F350" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G350" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
         <v>130001</v>
       </c>
@@ -6481,8 +7541,11 @@
       <c r="F351" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G351" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
         <v>140001</v>
       </c>
@@ -6498,8 +7561,11 @@
       <c r="F352" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G352" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
         <v>150001</v>
       </c>
@@ -6515,8 +7581,11 @@
       <c r="F353" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G353" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
         <v>160001</v>
       </c>
@@ -6532,8 +7601,11 @@
       <c r="F354" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G354" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
         <v>170001</v>
       </c>
@@ -6549,8 +7621,11 @@
       <c r="F355" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G355" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
         <v>180001</v>
       </c>
@@ -6566,8 +7641,11 @@
       <c r="F356" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G356" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
         <v>190001</v>
       </c>
@@ -6583,8 +7661,11 @@
       <c r="F357" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G357" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
         <v>200001</v>
       </c>
@@ -6600,8 +7681,11 @@
       <c r="F358" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G358" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
         <v>210001</v>
       </c>
@@ -6617,8 +7701,11 @@
       <c r="F359" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G359" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
         <v>220001</v>
       </c>
@@ -6634,8 +7721,11 @@
       <c r="F360" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G360" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
         <v>230001</v>
       </c>
@@ -6651,8 +7741,11 @@
       <c r="F361" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G361" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
         <v>240001</v>
       </c>
@@ -6668,8 +7761,11 @@
       <c r="F362" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G362" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
         <v>250001</v>
       </c>
@@ -6685,8 +7781,11 @@
       <c r="F363" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G363" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
         <v>260001</v>
       </c>
@@ -6702,8 +7801,11 @@
       <c r="F364" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G364" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
         <v>270001</v>
       </c>
@@ -6719,8 +7821,11 @@
       <c r="F365" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G365" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
         <v>280001</v>
       </c>
@@ -6736,8 +7841,11 @@
       <c r="F366" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G366" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
         <v>290001</v>
       </c>
@@ -6753,8 +7861,11 @@
       <c r="F367" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G367" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
         <v>300001</v>
       </c>
@@ -6770,8 +7881,11 @@
       <c r="F368" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G368" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
         <v>310001</v>
       </c>
@@ -6787,8 +7901,11 @@
       <c r="F369" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G369" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
         <v>320001</v>
       </c>
@@ -6804,8 +7921,11 @@
       <c r="F370" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G370" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
         <v>330001</v>
       </c>
@@ -6821,8 +7941,11 @@
       <c r="F371" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G371" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
         <v>340001</v>
       </c>
@@ -6838,8 +7961,11 @@
       <c r="F372" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G372" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
         <v>350001</v>
       </c>
@@ -6855,8 +7981,11 @@
       <c r="F373" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G373" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
         <v>360001</v>
       </c>
@@ -6872,8 +8001,11 @@
       <c r="F374" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G374" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
         <v>370001</v>
       </c>
@@ -6889,8 +8021,11 @@
       <c r="F375" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G375" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
         <v>380001</v>
       </c>
@@ -6906,8 +8041,11 @@
       <c r="F376" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G376" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
         <v>390001</v>
       </c>
@@ -6923,8 +8061,11 @@
       <c r="F377" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G377" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
         <v>400001</v>
       </c>
@@ -6940,8 +8081,11 @@
       <c r="F378" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G378" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
         <v>410001</v>
       </c>
@@ -6957,8 +8101,11 @@
       <c r="F379" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G379" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
         <v>420001</v>
       </c>
@@ -6974,8 +8121,11 @@
       <c r="F380" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G380" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
         <v>430001</v>
       </c>
@@ -6991,8 +8141,11 @@
       <c r="F381" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G381" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
         <v>440001</v>
       </c>
@@ -7008,8 +8161,11 @@
       <c r="F382" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
         <v>450001</v>
       </c>
@@ -7025,8 +8181,11 @@
       <c r="F383" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G383" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
         <v>460001</v>
       </c>
@@ -7042,8 +8201,11 @@
       <c r="F384" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G384" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
         <v>470001</v>
       </c>
@@ -7059,8 +8221,11 @@
       <c r="F385" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G385" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
         <v>480001</v>
       </c>
@@ -7076,8 +8241,11 @@
       <c r="F386" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G386" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
         <v>490001</v>
       </c>
@@ -7093,8 +8261,11 @@
       <c r="F387" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G387" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
         <v>500001</v>
       </c>
@@ -7110,8 +8281,11 @@
       <c r="F388" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G388" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
         <v>510001</v>
       </c>
@@ -7127,8 +8301,11 @@
       <c r="F389" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G389" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
         <v>520001</v>
       </c>
@@ -7144,8 +8321,11 @@
       <c r="F390" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G390" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
         <v>530001</v>
       </c>
@@ -7161,8 +8341,11 @@
       <c r="F391" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G391" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
         <v>540001</v>
       </c>
@@ -7178,8 +8361,11 @@
       <c r="F392" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G392" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
         <v>550001</v>
       </c>
@@ -7195,8 +8381,11 @@
       <c r="F393" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G393" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
         <v>560001</v>
       </c>
@@ -7212,8 +8401,11 @@
       <c r="F394" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G394" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
         <v>570001</v>
       </c>
@@ -7229,8 +8421,11 @@
       <c r="F395" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G395" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
         <v>580001</v>
       </c>
@@ -7246,8 +8441,11 @@
       <c r="F396" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G396" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
         <v>590001</v>
       </c>
@@ -7263,8 +8461,11 @@
       <c r="F397" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G397" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
         <v>600001</v>
       </c>
@@ -7280,8 +8481,11 @@
       <c r="F398" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G398" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
         <v>610001</v>
       </c>
@@ -7297,8 +8501,11 @@
       <c r="F399" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G399" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
         <v>620001</v>
       </c>
@@ -7314,8 +8521,11 @@
       <c r="F400" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G400" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
         <v>630001</v>
       </c>
@@ -7331,8 +8541,11 @@
       <c r="F401" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G401" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
         <v>640001</v>
       </c>
@@ -7348,8 +8561,11 @@
       <c r="F402" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G402" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
         <v>650001</v>
       </c>
@@ -7365,8 +8581,11 @@
       <c r="F403" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G403" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
         <v>660001</v>
       </c>
@@ -7382,8 +8601,11 @@
       <c r="F404" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G404" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
         <v>670001</v>
       </c>
@@ -7399,8 +8621,11 @@
       <c r="F405" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G405" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
         <v>680001</v>
       </c>
@@ -7416,8 +8641,11 @@
       <c r="F406" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G406" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
         <v>690001</v>
       </c>
@@ -7433,8 +8661,11 @@
       <c r="F407" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G407" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
         <v>700001</v>
       </c>
@@ -7450,8 +8681,11 @@
       <c r="F408" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G408" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
         <v>710001</v>
       </c>
@@ -7467,8 +8701,11 @@
       <c r="F409" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G409" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
         <v>720001</v>
       </c>
@@ -7484,8 +8721,11 @@
       <c r="F410" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G410" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
         <v>730001</v>
       </c>
@@ -7501,8 +8741,11 @@
       <c r="F411" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G411" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
         <v>740001</v>
       </c>
@@ -7518,8 +8761,11 @@
       <c r="F412" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G412" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
         <v>750001</v>
       </c>
@@ -7535,8 +8781,11 @@
       <c r="F413" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G413" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
         <v>760001</v>
       </c>
@@ -7552,8 +8801,11 @@
       <c r="F414" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G414" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
         <v>770001</v>
       </c>
@@ -7569,8 +8821,11 @@
       <c r="F415" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G415" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
         <v>780001</v>
       </c>
@@ -7586,8 +8841,11 @@
       <c r="F416" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G416" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
         <v>790001</v>
       </c>
@@ -7603,8 +8861,11 @@
       <c r="F417" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G417" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
         <v>800001</v>
       </c>
@@ -7620,8 +8881,11 @@
       <c r="F418" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G418" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
         <v>810001</v>
       </c>
@@ -7637,8 +8901,11 @@
       <c r="F419" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G419" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
         <v>820001</v>
       </c>
@@ -7654,8 +8921,11 @@
       <c r="F420" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G420" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
         <v>830001</v>
       </c>
@@ -7671,8 +8941,11 @@
       <c r="F421" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G421" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
         <v>840001</v>
       </c>
@@ -7688,8 +8961,11 @@
       <c r="F422" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G422" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
         <v>850001</v>
       </c>
@@ -7705,8 +8981,11 @@
       <c r="F423" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G423" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
         <v>860001</v>
       </c>
@@ -7722,8 +9001,11 @@
       <c r="F424" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G424" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
         <v>870001</v>
       </c>
@@ -7739,8 +9021,11 @@
       <c r="F425" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G425" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
         <v>880001</v>
       </c>
@@ -7756,8 +9041,11 @@
       <c r="F426" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G426" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
         <v>890001</v>
       </c>
@@ -7773,8 +9061,11 @@
       <c r="F427" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G427" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
         <v>900001</v>
       </c>
@@ -7790,8 +9081,11 @@
       <c r="F428" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G428" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
         <v>910001</v>
       </c>
@@ -7807,8 +9101,11 @@
       <c r="F429" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G429" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
         <v>920001</v>
       </c>
@@ -7824,8 +9121,11 @@
       <c r="F430" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G430" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
         <v>930001</v>
       </c>
@@ -7841,8 +9141,11 @@
       <c r="F431" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G431" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
         <v>940001</v>
       </c>
@@ -7858,8 +9161,11 @@
       <c r="F432" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
         <v>950001</v>
       </c>
@@ -7875,8 +9181,11 @@
       <c r="F433" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G433" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
         <v>960001</v>
       </c>
@@ -7892,8 +9201,11 @@
       <c r="F434" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G434" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
         <v>970001</v>
       </c>
@@ -7909,8 +9221,11 @@
       <c r="F435" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G435" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
         <v>980001</v>
       </c>
@@ -7926,8 +9241,11 @@
       <c r="F436" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G436" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
         <v>990001</v>
       </c>
@@ -7943,8 +9261,11 @@
       <c r="F437" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G437" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
         <v>1000001</v>
       </c>
@@ -7960,8 +9281,11 @@
       <c r="F438" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G438" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
         <v>1010001</v>
       </c>
@@ -7977,8 +9301,11 @@
       <c r="F439" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G439" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
         <v>1020001</v>
       </c>
@@ -7994,8 +9321,11 @@
       <c r="F440" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G440" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
         <v>1030001</v>
       </c>
@@ -8011,8 +9341,11 @@
       <c r="F441" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G441" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
         <v>1040001</v>
       </c>
@@ -8028,8 +9361,11 @@
       <c r="F442" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G442" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
         <v>1050001</v>
       </c>
@@ -8045,8 +9381,11 @@
       <c r="F443" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G443" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
         <v>1060001</v>
       </c>
@@ -8062,8 +9401,11 @@
       <c r="F444" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G444" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
         <v>1070001</v>
       </c>
@@ -8079,8 +9421,11 @@
       <c r="F445" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G445" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
         <v>1080001</v>
       </c>
@@ -8096,8 +9441,11 @@
       <c r="F446" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G446" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
         <v>1090001</v>
       </c>
@@ -8113,8 +9461,11 @@
       <c r="F447" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G447" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
         <v>1100001</v>
       </c>
@@ -8130,8 +9481,11 @@
       <c r="F448" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G448" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
         <v>1110001</v>
       </c>
@@ -8147,8 +9501,11 @@
       <c r="F449" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G449" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
         <v>1120001</v>
       </c>
@@ -8164,8 +9521,11 @@
       <c r="F450" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G450" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
         <v>1130001</v>
       </c>
@@ -8181,8 +9541,11 @@
       <c r="F451" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G451" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
         <v>1140001</v>
       </c>
@@ -8198,8 +9561,11 @@
       <c r="F452" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G452" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
         <v>1150001</v>
       </c>
@@ -8215,8 +9581,11 @@
       <c r="F453" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G453" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
         <v>1160001</v>
       </c>
@@ -8232,8 +9601,11 @@
       <c r="F454" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G454" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
         <v>1170001</v>
       </c>
@@ -8249,8 +9621,11 @@
       <c r="F455" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G455" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
         <v>1180001</v>
       </c>
@@ -8266,8 +9641,11 @@
       <c r="F456" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G456" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
         <v>1190001</v>
       </c>
@@ -8283,8 +9661,11 @@
       <c r="F457" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G457" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
         <v>1200001</v>
       </c>
@@ -8300,8 +9681,11 @@
       <c r="F458" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G458" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
         <v>1210001</v>
       </c>
@@ -8317,8 +9701,11 @@
       <c r="F459" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G459" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
         <v>1220001</v>
       </c>
@@ -8334,8 +9721,11 @@
       <c r="F460" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G460" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
         <v>1230001</v>
       </c>
@@ -8351,8 +9741,11 @@
       <c r="F461" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G461" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
         <v>1240001</v>
       </c>
@@ -8368,8 +9761,11 @@
       <c r="F462" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G462" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
         <v>1250001</v>
       </c>
@@ -8385,8 +9781,11 @@
       <c r="F463" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G463" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
         <v>1260001</v>
       </c>
@@ -8402,8 +9801,11 @@
       <c r="F464" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G464" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
         <v>1270001</v>
       </c>
@@ -8419,8 +9821,11 @@
       <c r="F465" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G465" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
         <v>1280001</v>
       </c>
@@ -8436,8 +9841,11 @@
       <c r="F466" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G466" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
         <v>1290001</v>
       </c>
@@ -8453,8 +9861,11 @@
       <c r="F467" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G467" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
         <v>1300001</v>
       </c>
@@ -8470,8 +9881,11 @@
       <c r="F468" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G468" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
         <v>1310001</v>
       </c>
@@ -8487,8 +9901,11 @@
       <c r="F469" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G469" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
         <v>1320001</v>
       </c>
@@ -8504,8 +9921,11 @@
       <c r="F470" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G470" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
         <v>1330001</v>
       </c>
@@ -8521,8 +9941,11 @@
       <c r="F471" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G471" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
         <v>1340001</v>
       </c>
@@ -8538,8 +9961,11 @@
       <c r="F472" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G472" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
         <v>1350001</v>
       </c>
@@ -8555,8 +9981,11 @@
       <c r="F473" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G473" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
         <v>1360001</v>
       </c>
@@ -8572,8 +10001,11 @@
       <c r="F474" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G474" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
         <v>1370001</v>
       </c>
@@ -8589,8 +10021,11 @@
       <c r="F475" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G475" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
         <v>1380001</v>
       </c>
@@ -8606,8 +10041,11 @@
       <c r="F476" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G476" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
         <v>1390001</v>
       </c>
@@ -8623,8 +10061,11 @@
       <c r="F477" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G477" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
         <v>1400001</v>
       </c>
@@ -8640,8 +10081,11 @@
       <c r="F478" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G478" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
         <v>1410001</v>
       </c>
@@ -8657,8 +10101,11 @@
       <c r="F479" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G479" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
         <v>1420001</v>
       </c>
@@ -8674,8 +10121,11 @@
       <c r="F480" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G480" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
         <v>1430001</v>
       </c>
@@ -8691,8 +10141,11 @@
       <c r="F481" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G481" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
         <v>1440001</v>
       </c>
@@ -8708,8 +10161,11 @@
       <c r="F482" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G482" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
         <v>1450001</v>
       </c>
@@ -8725,8 +10181,11 @@
       <c r="F483" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G483" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
         <v>1460001</v>
       </c>
@@ -8742,8 +10201,11 @@
       <c r="F484" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G484" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
         <v>1470001</v>
       </c>
@@ -8759,8 +10221,11 @@
       <c r="F485" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G485" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
         <v>1480001</v>
       </c>
@@ -8776,8 +10241,11 @@
       <c r="F486" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G486" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
         <v>1490001</v>
       </c>
@@ -8793,8 +10261,11 @@
       <c r="F487" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G487" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A488" s="1">
         <v>1500001</v>
       </c>
@@ -8810,8 +10281,11 @@
       <c r="F488" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G488" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A489" s="1">
         <v>1510001</v>
       </c>
@@ -8827,8 +10301,11 @@
       <c r="F489" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G489" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A490" s="1">
         <v>1520001</v>
       </c>
@@ -8844,8 +10321,11 @@
       <c r="F490" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G490" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A491" s="1">
         <v>1530001</v>
       </c>
@@ -8861,8 +10341,11 @@
       <c r="F491" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G491" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A492" s="1">
         <v>1540001</v>
       </c>
@@ -8878,8 +10361,11 @@
       <c r="F492" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G492" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A493" s="1">
         <v>1550001</v>
       </c>
@@ -8895,8 +10381,11 @@
       <c r="F493" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G493" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A494" s="1">
         <v>1560001</v>
       </c>
@@ -8912,8 +10401,11 @@
       <c r="F494" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G494" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A495" s="1">
         <v>1570001</v>
       </c>
@@ -8929,8 +10421,11 @@
       <c r="F495" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G495" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A496" s="1">
         <v>1580001</v>
       </c>
@@ -8946,8 +10441,11 @@
       <c r="F496" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G496" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A497" s="1">
         <v>1590001</v>
       </c>
@@ -8963,8 +10461,11 @@
       <c r="F497" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G497" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A498" s="1">
         <v>1600001</v>
       </c>
@@ -8979,6 +10480,9 @@
       </c>
       <c r="F498" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="G498" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A5526B-7FCE-4A3D-9D40-2DFC3E3F8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E50B5D7-20E8-4750-AF83-A65CC1840123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="43">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -150,21 +150,6 @@
     <t>46200001:80</t>
   </si>
   <si>
-    <t>46700001:17</t>
-  </si>
-  <si>
-    <t>46200001:100</t>
-  </si>
-  <si>
-    <t>46700001:15</t>
-  </si>
-  <si>
-    <t>46200001:120</t>
-  </si>
-  <si>
-    <t>46700001:18</t>
-  </si>
-  <si>
     <t>add_kongfu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,6 +159,34 @@
   </si>
   <si>
     <t>增加通关值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300006:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300003:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300004:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300002:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300005:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +569,7 @@
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
@@ -579,7 +592,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
@@ -602,7 +615,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
@@ -1039,7 +1052,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -1059,10 +1072,10 @@
         <v>20</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G27" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
@@ -1079,10 +1092,10 @@
         <v>20</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G28" s="1">
-        <v>200</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
@@ -1099,10 +1112,10 @@
         <v>20</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G29" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
@@ -1119,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G30" s="1">
         <v>400</v>
@@ -1139,10 +1152,10 @@
         <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G31" s="1">
-        <v>500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
@@ -1159,10 +1172,10 @@
         <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G32" s="1">
-        <v>600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E50B5D7-20E8-4750-AF83-A65CC1840123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBC5CCB-638D-4559-9537-F4B8CEBFF378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1075,7 +1075,7 @@
         <v>39</v>
       </c>
       <c r="G27" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
@@ -1095,7 +1095,7 @@
         <v>40</v>
       </c>
       <c r="G28" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
@@ -1135,7 +1135,7 @@
         <v>42</v>
       </c>
       <c r="G30" s="1">
-        <v>400</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBC5CCB-638D-4559-9537-F4B8CEBFF378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F285A4E-957D-46BA-85C9-7F01D0F59747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="43">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G498"/>
+  <dimension ref="A1:G499"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1152,7 +1152,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" s="1">
         <v>4000</v>
@@ -1180,27 +1180,27 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
-        <v>80020</v>
+        <v>70008</v>
       </c>
       <c r="B33" s="1">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
-        <v>80010</v>
+        <v>80020</v>
       </c>
       <c r="B34" s="1">
         <v>8</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
-        <v>90020</v>
+        <v>80010</v>
       </c>
       <c r="B35" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
-        <v>90010</v>
+        <v>90020</v>
       </c>
       <c r="B36" s="1">
         <v>9</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>100020</v>
+        <v>90010</v>
       </c>
       <c r="B37" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>11</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>100010</v>
+        <v>100020</v>
       </c>
       <c r="B38" s="1">
         <v>10</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>110020</v>
+        <v>100010</v>
       </c>
       <c r="B39" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>11</v>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>110010</v>
+        <v>110020</v>
       </c>
       <c r="B40" s="1">
         <v>11</v>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>120020</v>
+        <v>110010</v>
       </c>
       <c r="B41" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>11</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>120010</v>
+        <v>120020</v>
       </c>
       <c r="B42" s="1">
         <v>12</v>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>130020</v>
+        <v>120010</v>
       </c>
       <c r="B43" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>130010</v>
+        <v>130020</v>
       </c>
       <c r="B44" s="1">
         <v>13</v>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>140020</v>
+        <v>130010</v>
       </c>
       <c r="B45" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>140010</v>
+        <v>140020</v>
       </c>
       <c r="B46" s="1">
         <v>14</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>150020</v>
+        <v>140010</v>
       </c>
       <c r="B47" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>11</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>150010</v>
+        <v>150020</v>
       </c>
       <c r="B48" s="1">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>160020</v>
+        <v>150010</v>
       </c>
       <c r="B49" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>160010</v>
+        <v>160020</v>
       </c>
       <c r="B50" s="1">
         <v>16</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>170020</v>
+        <v>160010</v>
       </c>
       <c r="B51" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>170010</v>
+        <v>170020</v>
       </c>
       <c r="B52" s="1">
         <v>17</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>180020</v>
+        <v>170010</v>
       </c>
       <c r="B53" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>11</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>180010</v>
+        <v>180020</v>
       </c>
       <c r="B54" s="1">
         <v>18</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>190020</v>
+        <v>180010</v>
       </c>
       <c r="B55" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>11</v>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>190010</v>
+        <v>190020</v>
       </c>
       <c r="B56" s="1">
         <v>19</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>200020</v>
+        <v>190010</v>
       </c>
       <c r="B57" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>11</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>200010</v>
+        <v>200020</v>
       </c>
       <c r="B58" s="1">
         <v>20</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>210020</v>
+        <v>200010</v>
       </c>
       <c r="B59" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>11</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>210010</v>
+        <v>210020</v>
       </c>
       <c r="B60" s="1">
         <v>21</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>220020</v>
+        <v>210010</v>
       </c>
       <c r="B61" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>11</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>220010</v>
+        <v>220020</v>
       </c>
       <c r="B62" s="1">
         <v>22</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>230020</v>
+        <v>220010</v>
       </c>
       <c r="B63" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>11</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>230010</v>
+        <v>230020</v>
       </c>
       <c r="B64" s="1">
         <v>23</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
-        <v>240020</v>
+        <v>230010</v>
       </c>
       <c r="B65" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>11</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>240010</v>
+        <v>240020</v>
       </c>
       <c r="B66" s="1">
         <v>24</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>250020</v>
+        <v>240010</v>
       </c>
       <c r="B67" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>11</v>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>250010</v>
+        <v>250020</v>
       </c>
       <c r="B68" s="1">
         <v>25</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>260020</v>
+        <v>250010</v>
       </c>
       <c r="B69" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>11</v>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>260010</v>
+        <v>260020</v>
       </c>
       <c r="B70" s="1">
         <v>26</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>270020</v>
+        <v>260010</v>
       </c>
       <c r="B71" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>11</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>270010</v>
+        <v>270020</v>
       </c>
       <c r="B72" s="1">
         <v>27</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>280020</v>
+        <v>270010</v>
       </c>
       <c r="B73" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>11</v>
@@ -2000,7 +2000,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>280010</v>
+        <v>280020</v>
       </c>
       <c r="B74" s="1">
         <v>28</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>290020</v>
+        <v>280010</v>
       </c>
       <c r="B75" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>11</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>290010</v>
+        <v>290020</v>
       </c>
       <c r="B76" s="1">
         <v>29</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>300020</v>
+        <v>290010</v>
       </c>
       <c r="B77" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>11</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>300010</v>
+        <v>300020</v>
       </c>
       <c r="B78" s="1">
         <v>30</v>
@@ -2100,10 +2100,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>310020</v>
+        <v>300010</v>
       </c>
       <c r="B79" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>11</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>310010</v>
+        <v>310020</v>
       </c>
       <c r="B80" s="1">
         <v>31</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>320020</v>
+        <v>310010</v>
       </c>
       <c r="B81" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>11</v>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>320010</v>
+        <v>320020</v>
       </c>
       <c r="B82" s="1">
         <v>32</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>330020</v>
+        <v>320010</v>
       </c>
       <c r="B83" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>11</v>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>330010</v>
+        <v>330020</v>
       </c>
       <c r="B84" s="1">
         <v>33</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>340020</v>
+        <v>330010</v>
       </c>
       <c r="B85" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>11</v>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>340010</v>
+        <v>340020</v>
       </c>
       <c r="B86" s="1">
         <v>34</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>350020</v>
+        <v>340010</v>
       </c>
       <c r="B87" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>11</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>350010</v>
+        <v>350020</v>
       </c>
       <c r="B88" s="1">
         <v>35</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>360020</v>
+        <v>350010</v>
       </c>
       <c r="B89" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>11</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>360010</v>
+        <v>360020</v>
       </c>
       <c r="B90" s="1">
         <v>36</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>370020</v>
+        <v>360010</v>
       </c>
       <c r="B91" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>11</v>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>370010</v>
+        <v>370020</v>
       </c>
       <c r="B92" s="1">
         <v>37</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>380020</v>
+        <v>370010</v>
       </c>
       <c r="B93" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>11</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>380010</v>
+        <v>380020</v>
       </c>
       <c r="B94" s="1">
         <v>38</v>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>390020</v>
+        <v>380010</v>
       </c>
       <c r="B95" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>11</v>
@@ -2440,7 +2440,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>390010</v>
+        <v>390020</v>
       </c>
       <c r="B96" s="1">
         <v>39</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>400020</v>
+        <v>390010</v>
       </c>
       <c r="B97" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>11</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>400010</v>
+        <v>400020</v>
       </c>
       <c r="B98" s="1">
         <v>40</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>410020</v>
+        <v>400010</v>
       </c>
       <c r="B99" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>11</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>410010</v>
+        <v>410020</v>
       </c>
       <c r="B100" s="1">
         <v>41</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>420020</v>
+        <v>410010</v>
       </c>
       <c r="B101" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>11</v>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>420010</v>
+        <v>420020</v>
       </c>
       <c r="B102" s="1">
         <v>42</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>430020</v>
+        <v>420010</v>
       </c>
       <c r="B103" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>11</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>430010</v>
+        <v>430020</v>
       </c>
       <c r="B104" s="1">
         <v>43</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>440020</v>
+        <v>430010</v>
       </c>
       <c r="B105" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>11</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>440010</v>
+        <v>440020</v>
       </c>
       <c r="B106" s="1">
         <v>44</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>450020</v>
+        <v>440010</v>
       </c>
       <c r="B107" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>11</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>450010</v>
+        <v>450020</v>
       </c>
       <c r="B108" s="1">
         <v>45</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>460020</v>
+        <v>450010</v>
       </c>
       <c r="B109" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>11</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>460010</v>
+        <v>460020</v>
       </c>
       <c r="B110" s="1">
         <v>46</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>470020</v>
+        <v>460010</v>
       </c>
       <c r="B111" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>11</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>470010</v>
+        <v>470020</v>
       </c>
       <c r="B112" s="1">
         <v>47</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>480020</v>
+        <v>470010</v>
       </c>
       <c r="B113" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>11</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>480010</v>
+        <v>480020</v>
       </c>
       <c r="B114" s="1">
         <v>48</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>490020</v>
+        <v>480010</v>
       </c>
       <c r="B115" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>11</v>
@@ -2840,7 +2840,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>490010</v>
+        <v>490020</v>
       </c>
       <c r="B116" s="1">
         <v>49</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>500020</v>
+        <v>490010</v>
       </c>
       <c r="B117" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>11</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>500010</v>
+        <v>500020</v>
       </c>
       <c r="B118" s="1">
         <v>50</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>510020</v>
+        <v>500010</v>
       </c>
       <c r="B119" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>510010</v>
+        <v>510020</v>
       </c>
       <c r="B120" s="1">
         <v>51</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>520020</v>
+        <v>510010</v>
       </c>
       <c r="B121" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>11</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>520010</v>
+        <v>520020</v>
       </c>
       <c r="B122" s="1">
         <v>52</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>530020</v>
+        <v>520010</v>
       </c>
       <c r="B123" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>530010</v>
+        <v>530020</v>
       </c>
       <c r="B124" s="1">
         <v>53</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>540020</v>
+        <v>530010</v>
       </c>
       <c r="B125" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>11</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>540010</v>
+        <v>540020</v>
       </c>
       <c r="B126" s="1">
         <v>54</v>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>550020</v>
+        <v>540010</v>
       </c>
       <c r="B127" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>11</v>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>550010</v>
+        <v>550020</v>
       </c>
       <c r="B128" s="1">
         <v>55</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>560020</v>
+        <v>550010</v>
       </c>
       <c r="B129" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>11</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>560010</v>
+        <v>560020</v>
       </c>
       <c r="B130" s="1">
         <v>56</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>570020</v>
+        <v>560010</v>
       </c>
       <c r="B131" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>11</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>570010</v>
+        <v>570020</v>
       </c>
       <c r="B132" s="1">
         <v>57</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>580020</v>
+        <v>570010</v>
       </c>
       <c r="B133" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>11</v>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>580010</v>
+        <v>580020</v>
       </c>
       <c r="B134" s="1">
         <v>58</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>590020</v>
+        <v>580010</v>
       </c>
       <c r="B135" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>11</v>
@@ -3240,7 +3240,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>590010</v>
+        <v>590020</v>
       </c>
       <c r="B136" s="1">
         <v>59</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>600020</v>
+        <v>590010</v>
       </c>
       <c r="B137" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>11</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>600010</v>
+        <v>600020</v>
       </c>
       <c r="B138" s="1">
         <v>60</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>610020</v>
+        <v>600010</v>
       </c>
       <c r="B139" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>11</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>610010</v>
+        <v>610020</v>
       </c>
       <c r="B140" s="1">
         <v>61</v>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>620020</v>
+        <v>610010</v>
       </c>
       <c r="B141" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>11</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>620010</v>
+        <v>620020</v>
       </c>
       <c r="B142" s="1">
         <v>62</v>
@@ -3380,10 +3380,10 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>630020</v>
+        <v>620010</v>
       </c>
       <c r="B143" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>11</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>630010</v>
+        <v>630020</v>
       </c>
       <c r="B144" s="1">
         <v>63</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>640020</v>
+        <v>630010</v>
       </c>
       <c r="B145" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>11</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>640010</v>
+        <v>640020</v>
       </c>
       <c r="B146" s="1">
         <v>64</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>650020</v>
+        <v>640010</v>
       </c>
       <c r="B147" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>11</v>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>650010</v>
+        <v>650020</v>
       </c>
       <c r="B148" s="1">
         <v>65</v>
@@ -3500,10 +3500,10 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>660020</v>
+        <v>650010</v>
       </c>
       <c r="B149" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>11</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>660010</v>
+        <v>660020</v>
       </c>
       <c r="B150" s="1">
         <v>66</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>670020</v>
+        <v>660010</v>
       </c>
       <c r="B151" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>11</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>670010</v>
+        <v>670020</v>
       </c>
       <c r="B152" s="1">
         <v>67</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>680020</v>
+        <v>670010</v>
       </c>
       <c r="B153" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>11</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>680010</v>
+        <v>680020</v>
       </c>
       <c r="B154" s="1">
         <v>68</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>690020</v>
+        <v>680010</v>
       </c>
       <c r="B155" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>690010</v>
+        <v>690020</v>
       </c>
       <c r="B156" s="1">
         <v>69</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>700020</v>
+        <v>690010</v>
       </c>
       <c r="B157" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>11</v>
@@ -3680,7 +3680,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>700010</v>
+        <v>700020</v>
       </c>
       <c r="B158" s="1">
         <v>70</v>
@@ -3700,10 +3700,10 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>710020</v>
+        <v>700010</v>
       </c>
       <c r="B159" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>11</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>710010</v>
+        <v>710020</v>
       </c>
       <c r="B160" s="1">
         <v>71</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>720020</v>
+        <v>710010</v>
       </c>
       <c r="B161" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>11</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>720010</v>
+        <v>720020</v>
       </c>
       <c r="B162" s="1">
         <v>72</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>730020</v>
+        <v>720010</v>
       </c>
       <c r="B163" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>11</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>730010</v>
+        <v>730020</v>
       </c>
       <c r="B164" s="1">
         <v>73</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>740020</v>
+        <v>730010</v>
       </c>
       <c r="B165" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>11</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>740010</v>
+        <v>740020</v>
       </c>
       <c r="B166" s="1">
         <v>74</v>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>750020</v>
+        <v>740010</v>
       </c>
       <c r="B167" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>11</v>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>750010</v>
+        <v>750020</v>
       </c>
       <c r="B168" s="1">
         <v>75</v>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>760020</v>
+        <v>750010</v>
       </c>
       <c r="B169" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>11</v>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>760010</v>
+        <v>760020</v>
       </c>
       <c r="B170" s="1">
         <v>76</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>770020</v>
+        <v>760010</v>
       </c>
       <c r="B171" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>11</v>
@@ -3960,7 +3960,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>770010</v>
+        <v>770020</v>
       </c>
       <c r="B172" s="1">
         <v>77</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>780020</v>
+        <v>770010</v>
       </c>
       <c r="B173" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>11</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>780010</v>
+        <v>780020</v>
       </c>
       <c r="B174" s="1">
         <v>78</v>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>790020</v>
+        <v>780010</v>
       </c>
       <c r="B175" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>11</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>790010</v>
+        <v>790020</v>
       </c>
       <c r="B176" s="1">
         <v>79</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>800020</v>
+        <v>790010</v>
       </c>
       <c r="B177" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>11</v>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>800010</v>
+        <v>800020</v>
       </c>
       <c r="B178" s="1">
         <v>80</v>
@@ -4100,10 +4100,10 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>810020</v>
+        <v>800010</v>
       </c>
       <c r="B179" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>11</v>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>810010</v>
+        <v>810020</v>
       </c>
       <c r="B180" s="1">
         <v>81</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>820020</v>
+        <v>810010</v>
       </c>
       <c r="B181" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>11</v>
@@ -4160,7 +4160,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>820010</v>
+        <v>820020</v>
       </c>
       <c r="B182" s="1">
         <v>82</v>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>830020</v>
+        <v>820010</v>
       </c>
       <c r="B183" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>11</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>830010</v>
+        <v>830020</v>
       </c>
       <c r="B184" s="1">
         <v>83</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>840020</v>
+        <v>830010</v>
       </c>
       <c r="B185" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>11</v>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>840010</v>
+        <v>840020</v>
       </c>
       <c r="B186" s="1">
         <v>84</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>850020</v>
+        <v>840010</v>
       </c>
       <c r="B187" s="1">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>11</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>850010</v>
+        <v>850020</v>
       </c>
       <c r="B188" s="1">
         <v>85</v>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>860020</v>
+        <v>850010</v>
       </c>
       <c r="B189" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>11</v>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>860010</v>
+        <v>860020</v>
       </c>
       <c r="B190" s="1">
         <v>86</v>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>870020</v>
+        <v>860010</v>
       </c>
       <c r="B191" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>11</v>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>870010</v>
+        <v>870020</v>
       </c>
       <c r="B192" s="1">
         <v>87</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>880020</v>
+        <v>870010</v>
       </c>
       <c r="B193" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>11</v>
@@ -4400,7 +4400,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>880010</v>
+        <v>880020</v>
       </c>
       <c r="B194" s="1">
         <v>88</v>
@@ -4420,10 +4420,10 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>890020</v>
+        <v>880010</v>
       </c>
       <c r="B195" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>11</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>890010</v>
+        <v>890020</v>
       </c>
       <c r="B196" s="1">
         <v>89</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>900020</v>
+        <v>890010</v>
       </c>
       <c r="B197" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>11</v>
@@ -4480,7 +4480,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>900010</v>
+        <v>900020</v>
       </c>
       <c r="B198" s="1">
         <v>90</v>
@@ -4500,10 +4500,10 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>910020</v>
+        <v>900010</v>
       </c>
       <c r="B199" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>11</v>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>910010</v>
+        <v>910020</v>
       </c>
       <c r="B200" s="1">
         <v>91</v>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>920020</v>
+        <v>910010</v>
       </c>
       <c r="B201" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>11</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>920010</v>
+        <v>920020</v>
       </c>
       <c r="B202" s="1">
         <v>92</v>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>930020</v>
+        <v>920010</v>
       </c>
       <c r="B203" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>11</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>930010</v>
+        <v>930020</v>
       </c>
       <c r="B204" s="1">
         <v>93</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>940020</v>
+        <v>930010</v>
       </c>
       <c r="B205" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>11</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>940010</v>
+        <v>940020</v>
       </c>
       <c r="B206" s="1">
         <v>94</v>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>950020</v>
+        <v>940010</v>
       </c>
       <c r="B207" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>11</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>950010</v>
+        <v>950020</v>
       </c>
       <c r="B208" s="1">
         <v>95</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>960020</v>
+        <v>950010</v>
       </c>
       <c r="B209" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>11</v>
@@ -4720,7 +4720,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>960010</v>
+        <v>960020</v>
       </c>
       <c r="B210" s="1">
         <v>96</v>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>970020</v>
+        <v>960010</v>
       </c>
       <c r="B211" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>11</v>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>970010</v>
+        <v>970020</v>
       </c>
       <c r="B212" s="1">
         <v>97</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>980020</v>
+        <v>970010</v>
       </c>
       <c r="B213" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>11</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>980010</v>
+        <v>980020</v>
       </c>
       <c r="B214" s="1">
         <v>98</v>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>990020</v>
+        <v>980010</v>
       </c>
       <c r="B215" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>11</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>990010</v>
+        <v>990020</v>
       </c>
       <c r="B216" s="1">
         <v>99</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1000020</v>
+        <v>990010</v>
       </c>
       <c r="B217" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>11</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1000010</v>
+        <v>1000020</v>
       </c>
       <c r="B218" s="1">
         <v>100</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1010020</v>
+        <v>1000010</v>
       </c>
       <c r="B219" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>11</v>
@@ -4920,7 +4920,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1010010</v>
+        <v>1010020</v>
       </c>
       <c r="B220" s="1">
         <v>101</v>
@@ -4940,10 +4940,10 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1020020</v>
+        <v>1010010</v>
       </c>
       <c r="B221" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>11</v>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1020010</v>
+        <v>1020020</v>
       </c>
       <c r="B222" s="1">
         <v>102</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1030020</v>
+        <v>1020010</v>
       </c>
       <c r="B223" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>11</v>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1030010</v>
+        <v>1030020</v>
       </c>
       <c r="B224" s="1">
         <v>103</v>
@@ -5020,10 +5020,10 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1040020</v>
+        <v>1030010</v>
       </c>
       <c r="B225" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>11</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1040010</v>
+        <v>1040020</v>
       </c>
       <c r="B226" s="1">
         <v>104</v>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1050020</v>
+        <v>1040010</v>
       </c>
       <c r="B227" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>11</v>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1050010</v>
+        <v>1050020</v>
       </c>
       <c r="B228" s="1">
         <v>105</v>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1060020</v>
+        <v>1050010</v>
       </c>
       <c r="B229" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>11</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1060010</v>
+        <v>1060020</v>
       </c>
       <c r="B230" s="1">
         <v>106</v>
@@ -5140,10 +5140,10 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1070020</v>
+        <v>1060010</v>
       </c>
       <c r="B231" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>11</v>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1070010</v>
+        <v>1070020</v>
       </c>
       <c r="B232" s="1">
         <v>107</v>
@@ -5180,10 +5180,10 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1080020</v>
+        <v>1070010</v>
       </c>
       <c r="B233" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>11</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1080010</v>
+        <v>1080020</v>
       </c>
       <c r="B234" s="1">
         <v>108</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1090020</v>
+        <v>1080010</v>
       </c>
       <c r="B235" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>11</v>
@@ -5240,7 +5240,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1090010</v>
+        <v>1090020</v>
       </c>
       <c r="B236" s="1">
         <v>109</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1100020</v>
+        <v>1090010</v>
       </c>
       <c r="B237" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>11</v>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1100010</v>
+        <v>1100020</v>
       </c>
       <c r="B238" s="1">
         <v>110</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1110020</v>
+        <v>1100010</v>
       </c>
       <c r="B239" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>11</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1110010</v>
+        <v>1110020</v>
       </c>
       <c r="B240" s="1">
         <v>111</v>
@@ -5340,10 +5340,10 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>1120020</v>
+        <v>1110010</v>
       </c>
       <c r="B241" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>11</v>
@@ -5360,7 +5360,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>1120010</v>
+        <v>1120020</v>
       </c>
       <c r="B242" s="1">
         <v>112</v>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>1130020</v>
+        <v>1120010</v>
       </c>
       <c r="B243" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>11</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>1130010</v>
+        <v>1130020</v>
       </c>
       <c r="B244" s="1">
         <v>113</v>
@@ -5420,10 +5420,10 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>1140020</v>
+        <v>1130010</v>
       </c>
       <c r="B245" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>11</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>1140010</v>
+        <v>1140020</v>
       </c>
       <c r="B246" s="1">
         <v>114</v>
@@ -5460,10 +5460,10 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>1150020</v>
+        <v>1140010</v>
       </c>
       <c r="B247" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>11</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>1150010</v>
+        <v>1150020</v>
       </c>
       <c r="B248" s="1">
         <v>115</v>
@@ -5500,10 +5500,10 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>1160020</v>
+        <v>1150010</v>
       </c>
       <c r="B249" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>11</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>1160010</v>
+        <v>1160020</v>
       </c>
       <c r="B250" s="1">
         <v>116</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>1170020</v>
+        <v>1160010</v>
       </c>
       <c r="B251" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>11</v>
@@ -5560,7 +5560,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>1170010</v>
+        <v>1170020</v>
       </c>
       <c r="B252" s="1">
         <v>117</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>1180020</v>
+        <v>1170010</v>
       </c>
       <c r="B253" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>11</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>1180010</v>
+        <v>1180020</v>
       </c>
       <c r="B254" s="1">
         <v>118</v>
@@ -5620,10 +5620,10 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>1190020</v>
+        <v>1180010</v>
       </c>
       <c r="B255" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>11</v>
@@ -5640,7 +5640,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>1190010</v>
+        <v>1190020</v>
       </c>
       <c r="B256" s="1">
         <v>119</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>1200020</v>
+        <v>1190010</v>
       </c>
       <c r="B257" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>11</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1200010</v>
+        <v>1200020</v>
       </c>
       <c r="B258" s="1">
         <v>120</v>
@@ -5700,10 +5700,10 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1210020</v>
+        <v>1200010</v>
       </c>
       <c r="B259" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>11</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1210010</v>
+        <v>1210020</v>
       </c>
       <c r="B260" s="1">
         <v>121</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1220020</v>
+        <v>1210010</v>
       </c>
       <c r="B261" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>11</v>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1220010</v>
+        <v>1220020</v>
       </c>
       <c r="B262" s="1">
         <v>122</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1230020</v>
+        <v>1220010</v>
       </c>
       <c r="B263" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>11</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>1230010</v>
+        <v>1230020</v>
       </c>
       <c r="B264" s="1">
         <v>123</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>1240020</v>
+        <v>1230010</v>
       </c>
       <c r="B265" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>11</v>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>1240010</v>
+        <v>1240020</v>
       </c>
       <c r="B266" s="1">
         <v>124</v>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>1250020</v>
+        <v>1240010</v>
       </c>
       <c r="B267" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>11</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>1250010</v>
+        <v>1250020</v>
       </c>
       <c r="B268" s="1">
         <v>125</v>
@@ -5900,10 +5900,10 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>1260020</v>
+        <v>1250010</v>
       </c>
       <c r="B269" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>11</v>
@@ -5920,7 +5920,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1260010</v>
+        <v>1260020</v>
       </c>
       <c r="B270" s="1">
         <v>126</v>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1270020</v>
+        <v>1260010</v>
       </c>
       <c r="B271" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>11</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1270010</v>
+        <v>1270020</v>
       </c>
       <c r="B272" s="1">
         <v>127</v>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1280020</v>
+        <v>1270010</v>
       </c>
       <c r="B273" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>11</v>
@@ -6000,7 +6000,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1280010</v>
+        <v>1280020</v>
       </c>
       <c r="B274" s="1">
         <v>128</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1290020</v>
+        <v>1280010</v>
       </c>
       <c r="B275" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>11</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1290010</v>
+        <v>1290020</v>
       </c>
       <c r="B276" s="1">
         <v>129</v>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1300020</v>
+        <v>1290010</v>
       </c>
       <c r="B277" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>11</v>
@@ -6080,7 +6080,7 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1300010</v>
+        <v>1300020</v>
       </c>
       <c r="B278" s="1">
         <v>130</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1310020</v>
+        <v>1300010</v>
       </c>
       <c r="B279" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>11</v>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1310010</v>
+        <v>1310020</v>
       </c>
       <c r="B280" s="1">
         <v>131</v>
@@ -6140,10 +6140,10 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1320020</v>
+        <v>1310010</v>
       </c>
       <c r="B281" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>11</v>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1320010</v>
+        <v>1320020</v>
       </c>
       <c r="B282" s="1">
         <v>132</v>
@@ -6180,10 +6180,10 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1330020</v>
+        <v>1320010</v>
       </c>
       <c r="B283" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>11</v>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1330010</v>
+        <v>1330020</v>
       </c>
       <c r="B284" s="1">
         <v>133</v>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1340020</v>
+        <v>1330010</v>
       </c>
       <c r="B285" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>11</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1340010</v>
+        <v>1340020</v>
       </c>
       <c r="B286" s="1">
         <v>134</v>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1350020</v>
+        <v>1340010</v>
       </c>
       <c r="B287" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>11</v>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1350010</v>
+        <v>1350020</v>
       </c>
       <c r="B288" s="1">
         <v>135</v>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1360020</v>
+        <v>1350010</v>
       </c>
       <c r="B289" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>11</v>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1360010</v>
+        <v>1360020</v>
       </c>
       <c r="B290" s="1">
         <v>136</v>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1370020</v>
+        <v>1360010</v>
       </c>
       <c r="B291" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>11</v>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1370010</v>
+        <v>1370020</v>
       </c>
       <c r="B292" s="1">
         <v>137</v>
@@ -6380,10 +6380,10 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1380020</v>
+        <v>1370010</v>
       </c>
       <c r="B293" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>11</v>
@@ -6400,7 +6400,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1380010</v>
+        <v>1380020</v>
       </c>
       <c r="B294" s="1">
         <v>138</v>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1390020</v>
+        <v>1380010</v>
       </c>
       <c r="B295" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>11</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1390010</v>
+        <v>1390020</v>
       </c>
       <c r="B296" s="1">
         <v>139</v>
@@ -6460,10 +6460,10 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1400020</v>
+        <v>1390010</v>
       </c>
       <c r="B297" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>11</v>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1400010</v>
+        <v>1400020</v>
       </c>
       <c r="B298" s="1">
         <v>140</v>
@@ -6500,10 +6500,10 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1410020</v>
+        <v>1400010</v>
       </c>
       <c r="B299" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>11</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1410010</v>
+        <v>1410020</v>
       </c>
       <c r="B300" s="1">
         <v>141</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1420020</v>
+        <v>1410010</v>
       </c>
       <c r="B301" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>11</v>
@@ -6560,7 +6560,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1420010</v>
+        <v>1420020</v>
       </c>
       <c r="B302" s="1">
         <v>142</v>
@@ -6580,10 +6580,10 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1430020</v>
+        <v>1420010</v>
       </c>
       <c r="B303" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>11</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1430010</v>
+        <v>1430020</v>
       </c>
       <c r="B304" s="1">
         <v>143</v>
@@ -6620,10 +6620,10 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1440020</v>
+        <v>1430010</v>
       </c>
       <c r="B305" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>11</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1440010</v>
+        <v>1440020</v>
       </c>
       <c r="B306" s="1">
         <v>144</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1450020</v>
+        <v>1440010</v>
       </c>
       <c r="B307" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>11</v>
@@ -6680,7 +6680,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1450010</v>
+        <v>1450020</v>
       </c>
       <c r="B308" s="1">
         <v>145</v>
@@ -6700,10 +6700,10 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1460020</v>
+        <v>1450010</v>
       </c>
       <c r="B309" s="1">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>11</v>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1460010</v>
+        <v>1460020</v>
       </c>
       <c r="B310" s="1">
         <v>146</v>
@@ -6740,10 +6740,10 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1470020</v>
+        <v>1460010</v>
       </c>
       <c r="B311" s="1">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>11</v>
@@ -6760,7 +6760,7 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1470010</v>
+        <v>1470020</v>
       </c>
       <c r="B312" s="1">
         <v>147</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1480020</v>
+        <v>1470010</v>
       </c>
       <c r="B313" s="1">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>11</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1480010</v>
+        <v>1480020</v>
       </c>
       <c r="B314" s="1">
         <v>148</v>
@@ -6820,10 +6820,10 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1490020</v>
+        <v>1480010</v>
       </c>
       <c r="B315" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>11</v>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1490010</v>
+        <v>1490020</v>
       </c>
       <c r="B316" s="1">
         <v>149</v>
@@ -6860,10 +6860,10 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1500020</v>
+        <v>1490010</v>
       </c>
       <c r="B317" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>11</v>
@@ -6880,7 +6880,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1500010</v>
+        <v>1500020</v>
       </c>
       <c r="B318" s="1">
         <v>150</v>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1510020</v>
+        <v>1500010</v>
       </c>
       <c r="B319" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>11</v>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1510010</v>
+        <v>1510020</v>
       </c>
       <c r="B320" s="1">
         <v>151</v>
@@ -6940,10 +6940,10 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1520020</v>
+        <v>1510010</v>
       </c>
       <c r="B321" s="1">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>11</v>
@@ -6960,7 +6960,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1520010</v>
+        <v>1520020</v>
       </c>
       <c r="B322" s="1">
         <v>152</v>
@@ -6980,10 +6980,10 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1530020</v>
+        <v>1520010</v>
       </c>
       <c r="B323" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>11</v>
@@ -7000,7 +7000,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1530010</v>
+        <v>1530020</v>
       </c>
       <c r="B324" s="1">
         <v>153</v>
@@ -7020,10 +7020,10 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1540020</v>
+        <v>1530010</v>
       </c>
       <c r="B325" s="1">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>11</v>
@@ -7040,7 +7040,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1540010</v>
+        <v>1540020</v>
       </c>
       <c r="B326" s="1">
         <v>154</v>
@@ -7060,10 +7060,10 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1550020</v>
+        <v>1540010</v>
       </c>
       <c r="B327" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>11</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1550010</v>
+        <v>1550020</v>
       </c>
       <c r="B328" s="1">
         <v>155</v>
@@ -7100,10 +7100,10 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1560020</v>
+        <v>1550010</v>
       </c>
       <c r="B329" s="1">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>11</v>
@@ -7120,7 +7120,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1560010</v>
+        <v>1560020</v>
       </c>
       <c r="B330" s="1">
         <v>156</v>
@@ -7140,10 +7140,10 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1570020</v>
+        <v>1560010</v>
       </c>
       <c r="B331" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>11</v>
@@ -7160,7 +7160,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1570010</v>
+        <v>1570020</v>
       </c>
       <c r="B332" s="1">
         <v>157</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1580020</v>
+        <v>1570010</v>
       </c>
       <c r="B333" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>11</v>
@@ -7200,7 +7200,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1580010</v>
+        <v>1580020</v>
       </c>
       <c r="B334" s="1">
         <v>158</v>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1590020</v>
+        <v>1580010</v>
       </c>
       <c r="B335" s="1">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>11</v>
@@ -7240,7 +7240,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1590010</v>
+        <v>1590020</v>
       </c>
       <c r="B336" s="1">
         <v>159</v>
@@ -7260,10 +7260,10 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1600020</v>
+        <v>1590010</v>
       </c>
       <c r="B337" s="1">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>11</v>
@@ -7280,7 +7280,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1600010</v>
+        <v>1600020</v>
       </c>
       <c r="B338" s="1">
         <v>160</v>
@@ -7300,19 +7300,19 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>10001</v>
+        <v>1600010</v>
       </c>
       <c r="B339" s="1">
-        <v>1</v>
-      </c>
-      <c r="D339" s="1">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F339" s="1" t="s">
-        <v>22</v>
+      <c r="F339" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="G339" s="1">
         <v>0</v>
@@ -7320,10 +7320,10 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>20001</v>
+        <v>10001</v>
       </c>
       <c r="B340" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D340" s="1">
         <v>0</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B341" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D341" s="1">
         <v>0</v>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>40001</v>
+        <v>30001</v>
       </c>
       <c r="B342" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D342" s="1">
         <v>0</v>
@@ -7380,10 +7380,10 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>50001</v>
+        <v>40001</v>
       </c>
       <c r="B343" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D343" s="1">
         <v>0</v>
@@ -7400,10 +7400,10 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>60001</v>
+        <v>50001</v>
       </c>
       <c r="B344" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D344" s="1">
         <v>0</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>70001</v>
+        <v>60001</v>
       </c>
       <c r="B345" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D345" s="1">
         <v>0</v>
@@ -7440,10 +7440,10 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="B346" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D346" s="1">
         <v>0</v>
@@ -7460,10 +7460,10 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>90001</v>
+        <v>80001</v>
       </c>
       <c r="B347" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D347" s="1">
         <v>0</v>
@@ -7480,10 +7480,10 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>100001</v>
+        <v>90001</v>
       </c>
       <c r="B348" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D348" s="1">
         <v>0</v>
@@ -7500,10 +7500,10 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>110001</v>
+        <v>100001</v>
       </c>
       <c r="B349" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D349" s="1">
         <v>0</v>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="B350" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D350" s="1">
         <v>0</v>
@@ -7540,10 +7540,10 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>130001</v>
+        <v>120001</v>
       </c>
       <c r="B351" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D351" s="1">
         <v>0</v>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>140001</v>
+        <v>130001</v>
       </c>
       <c r="B352" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D352" s="1">
         <v>0</v>
@@ -7580,10 +7580,10 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>150001</v>
+        <v>140001</v>
       </c>
       <c r="B353" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D353" s="1">
         <v>0</v>
@@ -7600,10 +7600,10 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>160001</v>
+        <v>150001</v>
       </c>
       <c r="B354" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D354" s="1">
         <v>0</v>
@@ -7620,10 +7620,10 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>170001</v>
+        <v>160001</v>
       </c>
       <c r="B355" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D355" s="1">
         <v>0</v>
@@ -7640,10 +7640,10 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>180001</v>
+        <v>170001</v>
       </c>
       <c r="B356" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D356" s="1">
         <v>0</v>
@@ -7660,10 +7660,10 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>190001</v>
+        <v>180001</v>
       </c>
       <c r="B357" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D357" s="1">
         <v>0</v>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>200001</v>
+        <v>190001</v>
       </c>
       <c r="B358" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D358" s="1">
         <v>0</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>210001</v>
+        <v>200001</v>
       </c>
       <c r="B359" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D359" s="1">
         <v>0</v>
@@ -7720,10 +7720,10 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>220001</v>
+        <v>210001</v>
       </c>
       <c r="B360" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D360" s="1">
         <v>0</v>
@@ -7740,10 +7740,10 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>230001</v>
+        <v>220001</v>
       </c>
       <c r="B361" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D361" s="1">
         <v>0</v>
@@ -7760,10 +7760,10 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>240001</v>
+        <v>230001</v>
       </c>
       <c r="B362" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D362" s="1">
         <v>0</v>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>250001</v>
+        <v>240001</v>
       </c>
       <c r="B363" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D363" s="1">
         <v>0</v>
@@ -7800,10 +7800,10 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>260001</v>
+        <v>250001</v>
       </c>
       <c r="B364" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D364" s="1">
         <v>0</v>
@@ -7820,10 +7820,10 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>270001</v>
+        <v>260001</v>
       </c>
       <c r="B365" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D365" s="1">
         <v>0</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>280001</v>
+        <v>270001</v>
       </c>
       <c r="B366" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D366" s="1">
         <v>0</v>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>290001</v>
+        <v>280001</v>
       </c>
       <c r="B367" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D367" s="1">
         <v>0</v>
@@ -7880,10 +7880,10 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>300001</v>
+        <v>290001</v>
       </c>
       <c r="B368" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D368" s="1">
         <v>0</v>
@@ -7900,10 +7900,10 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>310001</v>
+        <v>300001</v>
       </c>
       <c r="B369" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D369" s="1">
         <v>0</v>
@@ -7920,10 +7920,10 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>320001</v>
+        <v>310001</v>
       </c>
       <c r="B370" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D370" s="1">
         <v>0</v>
@@ -7940,10 +7940,10 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>330001</v>
+        <v>320001</v>
       </c>
       <c r="B371" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D371" s="1">
         <v>0</v>
@@ -7960,10 +7960,10 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>340001</v>
+        <v>330001</v>
       </c>
       <c r="B372" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D372" s="1">
         <v>0</v>
@@ -7980,10 +7980,10 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>350001</v>
+        <v>340001</v>
       </c>
       <c r="B373" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D373" s="1">
         <v>0</v>
@@ -8000,10 +8000,10 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>360001</v>
+        <v>350001</v>
       </c>
       <c r="B374" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D374" s="1">
         <v>0</v>
@@ -8020,10 +8020,10 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>370001</v>
+        <v>360001</v>
       </c>
       <c r="B375" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D375" s="1">
         <v>0</v>
@@ -8040,10 +8040,10 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>380001</v>
+        <v>370001</v>
       </c>
       <c r="B376" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D376" s="1">
         <v>0</v>
@@ -8060,10 +8060,10 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>390001</v>
+        <v>380001</v>
       </c>
       <c r="B377" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D377" s="1">
         <v>0</v>
@@ -8080,10 +8080,10 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>400001</v>
+        <v>390001</v>
       </c>
       <c r="B378" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D378" s="1">
         <v>0</v>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>410001</v>
+        <v>400001</v>
       </c>
       <c r="B379" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D379" s="1">
         <v>0</v>
@@ -8120,10 +8120,10 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>420001</v>
+        <v>410001</v>
       </c>
       <c r="B380" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D380" s="1">
         <v>0</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>430001</v>
+        <v>420001</v>
       </c>
       <c r="B381" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D381" s="1">
         <v>0</v>
@@ -8160,10 +8160,10 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>440001</v>
+        <v>430001</v>
       </c>
       <c r="B382" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D382" s="1">
         <v>0</v>
@@ -8180,10 +8180,10 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>450001</v>
+        <v>440001</v>
       </c>
       <c r="B383" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D383" s="1">
         <v>0</v>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>460001</v>
+        <v>450001</v>
       </c>
       <c r="B384" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D384" s="1">
         <v>0</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>470001</v>
+        <v>460001</v>
       </c>
       <c r="B385" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D385" s="1">
         <v>0</v>
@@ -8240,10 +8240,10 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>480001</v>
+        <v>470001</v>
       </c>
       <c r="B386" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D386" s="1">
         <v>0</v>
@@ -8260,10 +8260,10 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>490001</v>
+        <v>480001</v>
       </c>
       <c r="B387" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D387" s="1">
         <v>0</v>
@@ -8280,10 +8280,10 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>500001</v>
+        <v>490001</v>
       </c>
       <c r="B388" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D388" s="1">
         <v>0</v>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>510001</v>
+        <v>500001</v>
       </c>
       <c r="B389" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D389" s="1">
         <v>0</v>
@@ -8320,10 +8320,10 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>520001</v>
+        <v>510001</v>
       </c>
       <c r="B390" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D390" s="1">
         <v>0</v>
@@ -8340,10 +8340,10 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>530001</v>
+        <v>520001</v>
       </c>
       <c r="B391" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D391" s="1">
         <v>0</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>540001</v>
+        <v>530001</v>
       </c>
       <c r="B392" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D392" s="1">
         <v>0</v>
@@ -8380,10 +8380,10 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>550001</v>
+        <v>540001</v>
       </c>
       <c r="B393" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D393" s="1">
         <v>0</v>
@@ -8400,10 +8400,10 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>560001</v>
+        <v>550001</v>
       </c>
       <c r="B394" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D394" s="1">
         <v>0</v>
@@ -8420,10 +8420,10 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>570001</v>
+        <v>560001</v>
       </c>
       <c r="B395" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D395" s="1">
         <v>0</v>
@@ -8440,10 +8440,10 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>580001</v>
+        <v>570001</v>
       </c>
       <c r="B396" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D396" s="1">
         <v>0</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>590001</v>
+        <v>580001</v>
       </c>
       <c r="B397" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D397" s="1">
         <v>0</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>600001</v>
+        <v>590001</v>
       </c>
       <c r="B398" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D398" s="1">
         <v>0</v>
@@ -8500,10 +8500,10 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>610001</v>
+        <v>600001</v>
       </c>
       <c r="B399" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D399" s="1">
         <v>0</v>
@@ -8520,10 +8520,10 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>620001</v>
+        <v>610001</v>
       </c>
       <c r="B400" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D400" s="1">
         <v>0</v>
@@ -8540,10 +8540,10 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>630001</v>
+        <v>620001</v>
       </c>
       <c r="B401" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D401" s="1">
         <v>0</v>
@@ -8560,10 +8560,10 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>640001</v>
+        <v>630001</v>
       </c>
       <c r="B402" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D402" s="1">
         <v>0</v>
@@ -8580,10 +8580,10 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>650001</v>
+        <v>640001</v>
       </c>
       <c r="B403" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D403" s="1">
         <v>0</v>
@@ -8600,10 +8600,10 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>660001</v>
+        <v>650001</v>
       </c>
       <c r="B404" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D404" s="1">
         <v>0</v>
@@ -8620,10 +8620,10 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>670001</v>
+        <v>660001</v>
       </c>
       <c r="B405" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D405" s="1">
         <v>0</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>680001</v>
+        <v>670001</v>
       </c>
       <c r="B406" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D406" s="1">
         <v>0</v>
@@ -8660,10 +8660,10 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>690001</v>
+        <v>680001</v>
       </c>
       <c r="B407" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D407" s="1">
         <v>0</v>
@@ -8680,10 +8680,10 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>700001</v>
+        <v>690001</v>
       </c>
       <c r="B408" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D408" s="1">
         <v>0</v>
@@ -8700,10 +8700,10 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>710001</v>
+        <v>700001</v>
       </c>
       <c r="B409" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D409" s="1">
         <v>0</v>
@@ -8720,10 +8720,10 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>720001</v>
+        <v>710001</v>
       </c>
       <c r="B410" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D410" s="1">
         <v>0</v>
@@ -8740,10 +8740,10 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>730001</v>
+        <v>720001</v>
       </c>
       <c r="B411" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D411" s="1">
         <v>0</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>740001</v>
+        <v>730001</v>
       </c>
       <c r="B412" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D412" s="1">
         <v>0</v>
@@ -8780,10 +8780,10 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>750001</v>
+        <v>740001</v>
       </c>
       <c r="B413" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D413" s="1">
         <v>0</v>
@@ -8800,10 +8800,10 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
-        <v>760001</v>
+        <v>750001</v>
       </c>
       <c r="B414" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D414" s="1">
         <v>0</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>770001</v>
+        <v>760001</v>
       </c>
       <c r="B415" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D415" s="1">
         <v>0</v>
@@ -8840,10 +8840,10 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>780001</v>
+        <v>770001</v>
       </c>
       <c r="B416" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D416" s="1">
         <v>0</v>
@@ -8860,10 +8860,10 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>790001</v>
+        <v>780001</v>
       </c>
       <c r="B417" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D417" s="1">
         <v>0</v>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>800001</v>
+        <v>790001</v>
       </c>
       <c r="B418" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D418" s="1">
         <v>0</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>810001</v>
+        <v>800001</v>
       </c>
       <c r="B419" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D419" s="1">
         <v>0</v>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>820001</v>
+        <v>810001</v>
       </c>
       <c r="B420" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D420" s="1">
         <v>0</v>
@@ -8940,10 +8940,10 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>830001</v>
+        <v>820001</v>
       </c>
       <c r="B421" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D421" s="1">
         <v>0</v>
@@ -8960,10 +8960,10 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>840001</v>
+        <v>830001</v>
       </c>
       <c r="B422" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D422" s="1">
         <v>0</v>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>850001</v>
+        <v>840001</v>
       </c>
       <c r="B423" s="1">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D423" s="1">
         <v>0</v>
@@ -9000,10 +9000,10 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>860001</v>
+        <v>850001</v>
       </c>
       <c r="B424" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D424" s="1">
         <v>0</v>
@@ -9020,10 +9020,10 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>870001</v>
+        <v>860001</v>
       </c>
       <c r="B425" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D425" s="1">
         <v>0</v>
@@ -9040,10 +9040,10 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>880001</v>
+        <v>870001</v>
       </c>
       <c r="B426" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D426" s="1">
         <v>0</v>
@@ -9060,10 +9060,10 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>890001</v>
+        <v>880001</v>
       </c>
       <c r="B427" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D427" s="1">
         <v>0</v>
@@ -9080,10 +9080,10 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>900001</v>
+        <v>890001</v>
       </c>
       <c r="B428" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D428" s="1">
         <v>0</v>
@@ -9100,10 +9100,10 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>910001</v>
+        <v>900001</v>
       </c>
       <c r="B429" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D429" s="1">
         <v>0</v>
@@ -9120,10 +9120,10 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
-        <v>920001</v>
+        <v>910001</v>
       </c>
       <c r="B430" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D430" s="1">
         <v>0</v>
@@ -9140,10 +9140,10 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>930001</v>
+        <v>920001</v>
       </c>
       <c r="B431" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D431" s="1">
         <v>0</v>
@@ -9160,10 +9160,10 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>940001</v>
+        <v>930001</v>
       </c>
       <c r="B432" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D432" s="1">
         <v>0</v>
@@ -9180,10 +9180,10 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>950001</v>
+        <v>940001</v>
       </c>
       <c r="B433" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D433" s="1">
         <v>0</v>
@@ -9200,10 +9200,10 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>960001</v>
+        <v>950001</v>
       </c>
       <c r="B434" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D434" s="1">
         <v>0</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>970001</v>
+        <v>960001</v>
       </c>
       <c r="B435" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D435" s="1">
         <v>0</v>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>980001</v>
+        <v>970001</v>
       </c>
       <c r="B436" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D436" s="1">
         <v>0</v>
@@ -9260,10 +9260,10 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>990001</v>
+        <v>980001</v>
       </c>
       <c r="B437" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D437" s="1">
         <v>0</v>
@@ -9280,10 +9280,10 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>1000001</v>
+        <v>990001</v>
       </c>
       <c r="B438" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D438" s="1">
         <v>0</v>
@@ -9300,10 +9300,10 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>1010001</v>
+        <v>1000001</v>
       </c>
       <c r="B439" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D439" s="1">
         <v>0</v>
@@ -9320,10 +9320,10 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>1020001</v>
+        <v>1010001</v>
       </c>
       <c r="B440" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D440" s="1">
         <v>0</v>
@@ -9340,10 +9340,10 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>1030001</v>
+        <v>1020001</v>
       </c>
       <c r="B441" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D441" s="1">
         <v>0</v>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>1040001</v>
+        <v>1030001</v>
       </c>
       <c r="B442" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D442" s="1">
         <v>0</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>1050001</v>
+        <v>1040001</v>
       </c>
       <c r="B443" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D443" s="1">
         <v>0</v>
@@ -9400,10 +9400,10 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>1060001</v>
+        <v>1050001</v>
       </c>
       <c r="B444" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D444" s="1">
         <v>0</v>
@@ -9420,10 +9420,10 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>1070001</v>
+        <v>1060001</v>
       </c>
       <c r="B445" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D445" s="1">
         <v>0</v>
@@ -9440,10 +9440,10 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>1080001</v>
+        <v>1070001</v>
       </c>
       <c r="B446" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D446" s="1">
         <v>0</v>
@@ -9460,10 +9460,10 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>1090001</v>
+        <v>1080001</v>
       </c>
       <c r="B447" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D447" s="1">
         <v>0</v>
@@ -9480,10 +9480,10 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>1100001</v>
+        <v>1090001</v>
       </c>
       <c r="B448" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D448" s="1">
         <v>0</v>
@@ -9500,10 +9500,10 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>1110001</v>
+        <v>1100001</v>
       </c>
       <c r="B449" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D449" s="1">
         <v>0</v>
@@ -9520,10 +9520,10 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>1120001</v>
+        <v>1110001</v>
       </c>
       <c r="B450" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D450" s="1">
         <v>0</v>
@@ -9540,10 +9540,10 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>1130001</v>
+        <v>1120001</v>
       </c>
       <c r="B451" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D451" s="1">
         <v>0</v>
@@ -9560,10 +9560,10 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>1140001</v>
+        <v>1130001</v>
       </c>
       <c r="B452" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D452" s="1">
         <v>0</v>
@@ -9580,10 +9580,10 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>1150001</v>
+        <v>1140001</v>
       </c>
       <c r="B453" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D453" s="1">
         <v>0</v>
@@ -9600,10 +9600,10 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>1160001</v>
+        <v>1150001</v>
       </c>
       <c r="B454" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D454" s="1">
         <v>0</v>
@@ -9620,10 +9620,10 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>1170001</v>
+        <v>1160001</v>
       </c>
       <c r="B455" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D455" s="1">
         <v>0</v>
@@ -9640,10 +9640,10 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
-        <v>1180001</v>
+        <v>1170001</v>
       </c>
       <c r="B456" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D456" s="1">
         <v>0</v>
@@ -9660,10 +9660,10 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>1190001</v>
+        <v>1180001</v>
       </c>
       <c r="B457" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D457" s="1">
         <v>0</v>
@@ -9680,10 +9680,10 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>1200001</v>
+        <v>1190001</v>
       </c>
       <c r="B458" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D458" s="1">
         <v>0</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>1210001</v>
+        <v>1200001</v>
       </c>
       <c r="B459" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D459" s="1">
         <v>0</v>
@@ -9720,10 +9720,10 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>1220001</v>
+        <v>1210001</v>
       </c>
       <c r="B460" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D460" s="1">
         <v>0</v>
@@ -9740,10 +9740,10 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>1230001</v>
+        <v>1220001</v>
       </c>
       <c r="B461" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D461" s="1">
         <v>0</v>
@@ -9760,10 +9760,10 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>1240001</v>
+        <v>1230001</v>
       </c>
       <c r="B462" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D462" s="1">
         <v>0</v>
@@ -9780,10 +9780,10 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>1250001</v>
+        <v>1240001</v>
       </c>
       <c r="B463" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D463" s="1">
         <v>0</v>
@@ -9800,10 +9800,10 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>1260001</v>
+        <v>1250001</v>
       </c>
       <c r="B464" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D464" s="1">
         <v>0</v>
@@ -9820,10 +9820,10 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
-        <v>1270001</v>
+        <v>1260001</v>
       </c>
       <c r="B465" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D465" s="1">
         <v>0</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
-        <v>1280001</v>
+        <v>1270001</v>
       </c>
       <c r="B466" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D466" s="1">
         <v>0</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
-        <v>1290001</v>
+        <v>1280001</v>
       </c>
       <c r="B467" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D467" s="1">
         <v>0</v>
@@ -9880,10 +9880,10 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
-        <v>1300001</v>
+        <v>1290001</v>
       </c>
       <c r="B468" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D468" s="1">
         <v>0</v>
@@ -9900,10 +9900,10 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
-        <v>1310001</v>
+        <v>1300001</v>
       </c>
       <c r="B469" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D469" s="1">
         <v>0</v>
@@ -9920,10 +9920,10 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
-        <v>1320001</v>
+        <v>1310001</v>
       </c>
       <c r="B470" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D470" s="1">
         <v>0</v>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
-        <v>1330001</v>
+        <v>1320001</v>
       </c>
       <c r="B471" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D471" s="1">
         <v>0</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
-        <v>1340001</v>
+        <v>1330001</v>
       </c>
       <c r="B472" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D472" s="1">
         <v>0</v>
@@ -9980,10 +9980,10 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
-        <v>1350001</v>
+        <v>1340001</v>
       </c>
       <c r="B473" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D473" s="1">
         <v>0</v>
@@ -10000,10 +10000,10 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
-        <v>1360001</v>
+        <v>1350001</v>
       </c>
       <c r="B474" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D474" s="1">
         <v>0</v>
@@ -10020,10 +10020,10 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
-        <v>1370001</v>
+        <v>1360001</v>
       </c>
       <c r="B475" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D475" s="1">
         <v>0</v>
@@ -10040,10 +10040,10 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
-        <v>1380001</v>
+        <v>1370001</v>
       </c>
       <c r="B476" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D476" s="1">
         <v>0</v>
@@ -10060,10 +10060,10 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
-        <v>1390001</v>
+        <v>1380001</v>
       </c>
       <c r="B477" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D477" s="1">
         <v>0</v>
@@ -10080,10 +10080,10 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
-        <v>1400001</v>
+        <v>1390001</v>
       </c>
       <c r="B478" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D478" s="1">
         <v>0</v>
@@ -10100,10 +10100,10 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
-        <v>1410001</v>
+        <v>1400001</v>
       </c>
       <c r="B479" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D479" s="1">
         <v>0</v>
@@ -10120,10 +10120,10 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
-        <v>1420001</v>
+        <v>1410001</v>
       </c>
       <c r="B480" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D480" s="1">
         <v>0</v>
@@ -10140,10 +10140,10 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
-        <v>1430001</v>
+        <v>1420001</v>
       </c>
       <c r="B481" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D481" s="1">
         <v>0</v>
@@ -10160,10 +10160,10 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
-        <v>1440001</v>
+        <v>1430001</v>
       </c>
       <c r="B482" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D482" s="1">
         <v>0</v>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
-        <v>1450001</v>
+        <v>1440001</v>
       </c>
       <c r="B483" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D483" s="1">
         <v>0</v>
@@ -10200,10 +10200,10 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
-        <v>1460001</v>
+        <v>1450001</v>
       </c>
       <c r="B484" s="1">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D484" s="1">
         <v>0</v>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
-        <v>1470001</v>
+        <v>1460001</v>
       </c>
       <c r="B485" s="1">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D485" s="1">
         <v>0</v>
@@ -10240,10 +10240,10 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
-        <v>1480001</v>
+        <v>1470001</v>
       </c>
       <c r="B486" s="1">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D486" s="1">
         <v>0</v>
@@ -10260,10 +10260,10 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
-        <v>1490001</v>
+        <v>1480001</v>
       </c>
       <c r="B487" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D487" s="1">
         <v>0</v>
@@ -10280,10 +10280,10 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A488" s="1">
-        <v>1500001</v>
+        <v>1490001</v>
       </c>
       <c r="B488" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D488" s="1">
         <v>0</v>
@@ -10300,10 +10300,10 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A489" s="1">
-        <v>1510001</v>
+        <v>1500001</v>
       </c>
       <c r="B489" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D489" s="1">
         <v>0</v>
@@ -10320,10 +10320,10 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A490" s="1">
-        <v>1520001</v>
+        <v>1510001</v>
       </c>
       <c r="B490" s="1">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D490" s="1">
         <v>0</v>
@@ -10340,10 +10340,10 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A491" s="1">
-        <v>1530001</v>
+        <v>1520001</v>
       </c>
       <c r="B491" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D491" s="1">
         <v>0</v>
@@ -10360,10 +10360,10 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A492" s="1">
-        <v>1540001</v>
+        <v>1530001</v>
       </c>
       <c r="B492" s="1">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D492" s="1">
         <v>0</v>
@@ -10380,10 +10380,10 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A493" s="1">
-        <v>1550001</v>
+        <v>1540001</v>
       </c>
       <c r="B493" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D493" s="1">
         <v>0</v>
@@ -10400,10 +10400,10 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A494" s="1">
-        <v>1560001</v>
+        <v>1550001</v>
       </c>
       <c r="B494" s="1">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D494" s="1">
         <v>0</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A495" s="1">
-        <v>1570001</v>
+        <v>1560001</v>
       </c>
       <c r="B495" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D495" s="1">
         <v>0</v>
@@ -10440,10 +10440,10 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A496" s="1">
-        <v>1580001</v>
+        <v>1570001</v>
       </c>
       <c r="B496" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D496" s="1">
         <v>0</v>
@@ -10460,10 +10460,10 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A497" s="1">
-        <v>1590001</v>
+        <v>1580001</v>
       </c>
       <c r="B497" s="1">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D497" s="1">
         <v>0</v>
@@ -10480,21 +10480,41 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A498" s="1">
+        <v>1590001</v>
+      </c>
+      <c r="B498" s="1">
+        <v>159</v>
+      </c>
+      <c r="D498" s="1">
+        <v>0</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F498" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G498" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A499" s="1">
         <v>1600001</v>
       </c>
-      <c r="B498" s="1">
+      <c r="B499" s="1">
         <v>160</v>
       </c>
-      <c r="D498" s="1">
-        <v>0</v>
-      </c>
-      <c r="E498" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F498" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G498" s="1">
+      <c r="D499" s="1">
+        <v>0</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F499" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G499" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F285A4E-957D-46BA-85C9-7F01D0F59747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30819770-575A-412E-AE90-4BF0291948EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1175,7 +1175,7 @@
         <v>41</v>
       </c>
       <c r="G32" s="1">
-        <v>2500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30819770-575A-412E-AE90-4BF0291948EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DA555E-AD61-4B20-8852-6F6D2F6600A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1175,7 +1175,7 @@
         <v>41</v>
       </c>
       <c r="G32" s="1">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DA555E-AD61-4B20-8852-6F6D2F6600A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F6ED36-66BA-4F7F-A95C-756D0A5FF604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1155,7 +1155,7 @@
         <v>37</v>
       </c>
       <c r="G31" s="1">
-        <v>4000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
@@ -1175,7 +1175,7 @@
         <v>41</v>
       </c>
       <c r="G32" s="1">
-        <v>5000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F6ED36-66BA-4F7F-A95C-756D0A5FF604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E67A13-EC40-4B23-A04D-829701D55F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="42">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,10 +179,6 @@
   </si>
   <si>
     <t>48300004:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300002:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1132,7 +1128,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" s="1">
         <v>360</v>
@@ -1172,7 +1168,7 @@
         <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G32" s="1">
         <v>16000</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E67A13-EC40-4B23-A04D-829701D55F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA16E337-2D37-44AC-9105-2100AF283000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="43">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -183,6 +183,10 @@
   </si>
   <si>
     <t>48300005:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300002:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1148,10 +1152,10 @@
         <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
@@ -1168,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G32" s="1">
         <v>16000</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA16E337-2D37-44AC-9105-2100AF283000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A64FCC-0F40-4B00-9F50-EDA074A1462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,10 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>48300006:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>48300003:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,11 +178,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>48300005:1</t>
+    <t>48300002:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>48300002:1</t>
+    <t>48300005:1_46700001:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300006:1_46700001:5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -251,6 +251,7 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1065,14 +1066,14 @@
       <c r="B27" s="1">
         <v>7</v>
       </c>
-      <c r="D27" s="2">
-        <v>0</v>
+      <c r="D27" s="5">
+        <v>42614001</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" s="1">
         <v>50</v>
@@ -1092,7 +1093,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28" s="1">
         <v>100</v>
@@ -1146,7 +1147,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="2">
-        <v>0</v>
+        <v>42635001</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>20</v>
@@ -1172,7 +1173,7 @@
         <v>20</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G32" s="1">
         <v>16000</v>
@@ -1192,7 +1193,7 @@
         <v>20</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G33" s="1">
         <v>300</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAB974A-7787-40CE-9A61-16E6E8D90535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9DF0DC-9B63-455B-9C0A-C52ED26CDA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="52">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J499"/>
+  <dimension ref="A1:J520"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1592,8 +1592,8 @@
       <c r="B36" s="1">
         <v>9</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
+      <c r="D36" s="2">
+        <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>16</v>
@@ -1616,13 +1616,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>90010</v>
+        <v>90001</v>
       </c>
       <c r="B37" s="1">
         <v>9</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
+      <c r="D37" s="2">
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>16</v>
@@ -1631,7 +1631,7 @@
         <v>17</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -1645,13 +1645,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>100020</v>
+        <v>90002</v>
       </c>
       <c r="B38" s="1">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>16</v>
@@ -1660,7 +1660,7 @@
         <v>17</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -1674,13 +1674,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>100010</v>
+        <v>90003</v>
       </c>
       <c r="B39" s="1">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>16</v>
@@ -1689,7 +1689,7 @@
         <v>17</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -1703,13 +1703,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>110020</v>
+        <v>90004</v>
       </c>
       <c r="B40" s="1">
-        <v>11</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>16</v>
@@ -1718,7 +1718,7 @@
         <v>17</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -1732,13 +1732,13 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>110010</v>
+        <v>90005</v>
       </c>
       <c r="B41" s="1">
-        <v>11</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>16</v>
@@ -1747,7 +1747,7 @@
         <v>17</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -1761,13 +1761,13 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>120020</v>
+        <v>90006</v>
       </c>
       <c r="B42" s="1">
-        <v>12</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>16</v>
@@ -1776,7 +1776,7 @@
         <v>17</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>120010</v>
+        <v>90007</v>
       </c>
       <c r="B43" s="1">
-        <v>12</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>16</v>
@@ -1805,7 +1805,7 @@
         <v>17</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -1819,13 +1819,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>130020</v>
+        <v>90008</v>
       </c>
       <c r="B44" s="1">
-        <v>13</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>16</v>
@@ -1834,7 +1834,7 @@
         <v>17</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -1848,13 +1848,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>130010</v>
+        <v>90009</v>
       </c>
       <c r="B45" s="1">
-        <v>13</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>16</v>
@@ -1863,7 +1863,7 @@
         <v>17</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>140020</v>
+        <v>90011</v>
       </c>
       <c r="B46" s="1">
-        <v>14</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>16</v>
@@ -1892,7 +1892,7 @@
         <v>17</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>140010</v>
+        <v>90012</v>
       </c>
       <c r="B47" s="1">
-        <v>14</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>16</v>
@@ -1921,7 +1921,7 @@
         <v>17</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -1935,13 +1935,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>150020</v>
+        <v>90013</v>
       </c>
       <c r="B48" s="1">
-        <v>15</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>16</v>
@@ -1950,7 +1950,7 @@
         <v>17</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -1964,13 +1964,13 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>150010</v>
+        <v>90014</v>
       </c>
       <c r="B49" s="1">
-        <v>15</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>16</v>
@@ -1979,7 +1979,7 @@
         <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -1993,13 +1993,13 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>160020</v>
+        <v>90015</v>
       </c>
       <c r="B50" s="1">
-        <v>16</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>16</v>
@@ -2008,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2022,13 +2022,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>160010</v>
+        <v>90016</v>
       </c>
       <c r="B51" s="1">
-        <v>16</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>16</v>
@@ -2037,7 +2037,7 @@
         <v>17</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2051,13 +2051,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>170020</v>
+        <v>90017</v>
       </c>
       <c r="B52" s="1">
-        <v>17</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D52" s="2">
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>16</v>
@@ -2066,7 +2066,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2080,13 +2080,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>170010</v>
+        <v>90018</v>
       </c>
       <c r="B53" s="1">
-        <v>17</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>16</v>
@@ -2095,7 +2095,7 @@
         <v>17</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2109,13 +2109,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>180020</v>
+        <v>90021</v>
       </c>
       <c r="B54" s="1">
-        <v>18</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>16</v>
@@ -2124,7 +2124,7 @@
         <v>17</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>180010</v>
+        <v>90019</v>
       </c>
       <c r="B55" s="1">
-        <v>18</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>16</v>
@@ -2153,7 +2153,7 @@
         <v>17</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2167,13 +2167,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>190020</v>
+        <v>90023</v>
       </c>
       <c r="B56" s="1">
-        <v>19</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>16</v>
@@ -2182,7 +2182,7 @@
         <v>17</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2196,13 +2196,13 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>190010</v>
+        <v>90022</v>
       </c>
       <c r="B57" s="1">
-        <v>19</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>16</v>
@@ -2211,7 +2211,7 @@
         <v>17</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2225,13 +2225,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>200020</v>
+        <v>90024</v>
       </c>
       <c r="B58" s="1">
-        <v>20</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>16</v>
@@ -2240,7 +2240,7 @@
         <v>17</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>200010</v>
+        <v>100020</v>
       </c>
       <c r="B59" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>210020</v>
+        <v>100010</v>
       </c>
       <c r="B60" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>210010</v>
+        <v>110020</v>
       </c>
       <c r="B61" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>220020</v>
+        <v>110010</v>
       </c>
       <c r="B62" s="1">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>220010</v>
+        <v>120020</v>
       </c>
       <c r="B63" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>230020</v>
+        <v>120010</v>
       </c>
       <c r="B64" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
-        <v>230010</v>
+        <v>130020</v>
       </c>
       <c r="B65" s="1">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>240020</v>
+        <v>130010</v>
       </c>
       <c r="B66" s="1">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>240010</v>
+        <v>140020</v>
       </c>
       <c r="B67" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>250020</v>
+        <v>140010</v>
       </c>
       <c r="B68" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>250010</v>
+        <v>150020</v>
       </c>
       <c r="B69" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
@@ -2573,10 +2573,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>260020</v>
+        <v>150010</v>
       </c>
       <c r="B70" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>260010</v>
+        <v>160020</v>
       </c>
       <c r="B71" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>270020</v>
+        <v>160010</v>
       </c>
       <c r="B72" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>270010</v>
+        <v>170020</v>
       </c>
       <c r="B73" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>280020</v>
+        <v>170010</v>
       </c>
       <c r="B74" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>280010</v>
+        <v>180020</v>
       </c>
       <c r="B75" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>290020</v>
+        <v>180010</v>
       </c>
       <c r="B76" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>10</v>
@@ -2776,10 +2776,10 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>290010</v>
+        <v>190020</v>
       </c>
       <c r="B77" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>300020</v>
+        <v>190010</v>
       </c>
       <c r="B78" s="1">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>300010</v>
+        <v>200020</v>
       </c>
       <c r="B79" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>10</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>310020</v>
+        <v>200010</v>
       </c>
       <c r="B80" s="1">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>310010</v>
+        <v>210020</v>
       </c>
       <c r="B81" s="1">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>320020</v>
+        <v>210010</v>
       </c>
       <c r="B82" s="1">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>10</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>320010</v>
+        <v>220020</v>
       </c>
       <c r="B83" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>330020</v>
+        <v>220010</v>
       </c>
       <c r="B84" s="1">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>10</v>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>330010</v>
+        <v>230020</v>
       </c>
       <c r="B85" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>10</v>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>340020</v>
+        <v>230010</v>
       </c>
       <c r="B86" s="1">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -3066,10 +3066,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>340010</v>
+        <v>240020</v>
       </c>
       <c r="B87" s="1">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -3095,10 +3095,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>350020</v>
+        <v>240010</v>
       </c>
       <c r="B88" s="1">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>350010</v>
+        <v>250020</v>
       </c>
       <c r="B89" s="1">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>360020</v>
+        <v>250010</v>
       </c>
       <c r="B90" s="1">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>360010</v>
+        <v>260020</v>
       </c>
       <c r="B91" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>370020</v>
+        <v>260010</v>
       </c>
       <c r="B92" s="1">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>370010</v>
+        <v>270020</v>
       </c>
       <c r="B93" s="1">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>10</v>
@@ -3269,10 +3269,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>380020</v>
+        <v>270010</v>
       </c>
       <c r="B94" s="1">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>10</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>380010</v>
+        <v>280020</v>
       </c>
       <c r="B95" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>390020</v>
+        <v>280010</v>
       </c>
       <c r="B96" s="1">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>10</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>390010</v>
+        <v>290020</v>
       </c>
       <c r="B97" s="1">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>10</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>400020</v>
+        <v>290010</v>
       </c>
       <c r="B98" s="1">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>10</v>
@@ -3414,10 +3414,10 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>400010</v>
+        <v>300020</v>
       </c>
       <c r="B99" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>10</v>
@@ -3443,10 +3443,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>410020</v>
+        <v>300010</v>
       </c>
       <c r="B100" s="1">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>10</v>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>410010</v>
+        <v>310020</v>
       </c>
       <c r="B101" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>10</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>420020</v>
+        <v>310010</v>
       </c>
       <c r="B102" s="1">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>10</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>420010</v>
+        <v>320020</v>
       </c>
       <c r="B103" s="1">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>10</v>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>430020</v>
+        <v>320010</v>
       </c>
       <c r="B104" s="1">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>10</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>430010</v>
+        <v>330020</v>
       </c>
       <c r="B105" s="1">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>10</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>440020</v>
+        <v>330010</v>
       </c>
       <c r="B106" s="1">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>10</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>440010</v>
+        <v>340020</v>
       </c>
       <c r="B107" s="1">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>450020</v>
+        <v>340010</v>
       </c>
       <c r="B108" s="1">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>10</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>450010</v>
+        <v>350020</v>
       </c>
       <c r="B109" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>460020</v>
+        <v>350010</v>
       </c>
       <c r="B110" s="1">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>460010</v>
+        <v>360020</v>
       </c>
       <c r="B111" s="1">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>470020</v>
+        <v>360010</v>
       </c>
       <c r="B112" s="1">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>10</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>470010</v>
+        <v>370020</v>
       </c>
       <c r="B113" s="1">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>10</v>
@@ -3849,10 +3849,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>480020</v>
+        <v>370010</v>
       </c>
       <c r="B114" s="1">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>480010</v>
+        <v>380020</v>
       </c>
       <c r="B115" s="1">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>490020</v>
+        <v>380010</v>
       </c>
       <c r="B116" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>10</v>
@@ -3936,10 +3936,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>490010</v>
+        <v>390020</v>
       </c>
       <c r="B117" s="1">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>500020</v>
+        <v>390010</v>
       </c>
       <c r="B118" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>10</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>500010</v>
+        <v>400020</v>
       </c>
       <c r="B119" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>10</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>510020</v>
+        <v>400010</v>
       </c>
       <c r="B120" s="1">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>510010</v>
+        <v>410020</v>
       </c>
       <c r="B121" s="1">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>10</v>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>520020</v>
+        <v>410010</v>
       </c>
       <c r="B122" s="1">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>10</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>520010</v>
+        <v>420020</v>
       </c>
       <c r="B123" s="1">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>530020</v>
+        <v>420010</v>
       </c>
       <c r="B124" s="1">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>530010</v>
+        <v>430020</v>
       </c>
       <c r="B125" s="1">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>10</v>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>540020</v>
+        <v>430010</v>
       </c>
       <c r="B126" s="1">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>10</v>
@@ -4226,10 +4226,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>540010</v>
+        <v>440020</v>
       </c>
       <c r="B127" s="1">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>10</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>550020</v>
+        <v>440010</v>
       </c>
       <c r="B128" s="1">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>550010</v>
+        <v>450020</v>
       </c>
       <c r="B129" s="1">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>10</v>
@@ -4313,10 +4313,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>560020</v>
+        <v>450010</v>
       </c>
       <c r="B130" s="1">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>10</v>
@@ -4342,10 +4342,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>560010</v>
+        <v>460020</v>
       </c>
       <c r="B131" s="1">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>570020</v>
+        <v>460010</v>
       </c>
       <c r="B132" s="1">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>10</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>570010</v>
+        <v>470020</v>
       </c>
       <c r="B133" s="1">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>10</v>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>580020</v>
+        <v>470010</v>
       </c>
       <c r="B134" s="1">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>580010</v>
+        <v>480020</v>
       </c>
       <c r="B135" s="1">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>10</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>590020</v>
+        <v>480010</v>
       </c>
       <c r="B136" s="1">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>590010</v>
+        <v>490020</v>
       </c>
       <c r="B137" s="1">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>10</v>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>600020</v>
+        <v>490010</v>
       </c>
       <c r="B138" s="1">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>10</v>
@@ -4574,10 +4574,10 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>600010</v>
+        <v>500020</v>
       </c>
       <c r="B139" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>10</v>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>610020</v>
+        <v>500010</v>
       </c>
       <c r="B140" s="1">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>10</v>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>610010</v>
+        <v>510020</v>
       </c>
       <c r="B141" s="1">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>10</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>620020</v>
+        <v>510010</v>
       </c>
       <c r="B142" s="1">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>10</v>
@@ -4690,10 +4690,10 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>620010</v>
+        <v>520020</v>
       </c>
       <c r="B143" s="1">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>630020</v>
+        <v>520010</v>
       </c>
       <c r="B144" s="1">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>630010</v>
+        <v>530020</v>
       </c>
       <c r="B145" s="1">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>10</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>640020</v>
+        <v>530010</v>
       </c>
       <c r="B146" s="1">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>10</v>
@@ -4806,10 +4806,10 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>640010</v>
+        <v>540020</v>
       </c>
       <c r="B147" s="1">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>10</v>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>650020</v>
+        <v>540010</v>
       </c>
       <c r="B148" s="1">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>10</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>650010</v>
+        <v>550020</v>
       </c>
       <c r="B149" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>10</v>
@@ -4893,10 +4893,10 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>660020</v>
+        <v>550010</v>
       </c>
       <c r="B150" s="1">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>10</v>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>660010</v>
+        <v>560020</v>
       </c>
       <c r="B151" s="1">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>670020</v>
+        <v>560010</v>
       </c>
       <c r="B152" s="1">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>10</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>670010</v>
+        <v>570020</v>
       </c>
       <c r="B153" s="1">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>680020</v>
+        <v>570010</v>
       </c>
       <c r="B154" s="1">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>10</v>
@@ -5038,10 +5038,10 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>680010</v>
+        <v>580020</v>
       </c>
       <c r="B155" s="1">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>10</v>
@@ -5067,10 +5067,10 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>690020</v>
+        <v>580010</v>
       </c>
       <c r="B156" s="1">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>690010</v>
+        <v>590020</v>
       </c>
       <c r="B157" s="1">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>10</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>700020</v>
+        <v>590010</v>
       </c>
       <c r="B158" s="1">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>700010</v>
+        <v>600020</v>
       </c>
       <c r="B159" s="1">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>10</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>710020</v>
+        <v>600010</v>
       </c>
       <c r="B160" s="1">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>10</v>
@@ -5212,10 +5212,10 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>710010</v>
+        <v>610020</v>
       </c>
       <c r="B161" s="1">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>10</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>720020</v>
+        <v>610010</v>
       </c>
       <c r="B162" s="1">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>10</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>720010</v>
+        <v>620020</v>
       </c>
       <c r="B163" s="1">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>10</v>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>730020</v>
+        <v>620010</v>
       </c>
       <c r="B164" s="1">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>10</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>730010</v>
+        <v>630020</v>
       </c>
       <c r="B165" s="1">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>10</v>
@@ -5357,10 +5357,10 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>740020</v>
+        <v>630010</v>
       </c>
       <c r="B166" s="1">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>740010</v>
+        <v>640020</v>
       </c>
       <c r="B167" s="1">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>10</v>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>750020</v>
+        <v>640010</v>
       </c>
       <c r="B168" s="1">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>10</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>750010</v>
+        <v>650020</v>
       </c>
       <c r="B169" s="1">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>760020</v>
+        <v>650010</v>
       </c>
       <c r="B170" s="1">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>10</v>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>760010</v>
+        <v>660020</v>
       </c>
       <c r="B171" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>10</v>
@@ -5531,10 +5531,10 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>770020</v>
+        <v>660010</v>
       </c>
       <c r="B172" s="1">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>10</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>770010</v>
+        <v>670020</v>
       </c>
       <c r="B173" s="1">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>10</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>780020</v>
+        <v>670010</v>
       </c>
       <c r="B174" s="1">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>10</v>
@@ -5618,10 +5618,10 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>780010</v>
+        <v>680020</v>
       </c>
       <c r="B175" s="1">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>790020</v>
+        <v>680010</v>
       </c>
       <c r="B176" s="1">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>10</v>
@@ -5676,10 +5676,10 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>790010</v>
+        <v>690020</v>
       </c>
       <c r="B177" s="1">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>10</v>
@@ -5705,10 +5705,10 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>800020</v>
+        <v>690010</v>
       </c>
       <c r="B178" s="1">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>800010</v>
+        <v>700020</v>
       </c>
       <c r="B179" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>10</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>810020</v>
+        <v>700010</v>
       </c>
       <c r="B180" s="1">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>10</v>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>810010</v>
+        <v>710020</v>
       </c>
       <c r="B181" s="1">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>10</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>820020</v>
+        <v>710010</v>
       </c>
       <c r="B182" s="1">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>10</v>
@@ -5850,10 +5850,10 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>820010</v>
+        <v>720020</v>
       </c>
       <c r="B183" s="1">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>10</v>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>830020</v>
+        <v>720010</v>
       </c>
       <c r="B184" s="1">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>10</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>830010</v>
+        <v>730020</v>
       </c>
       <c r="B185" s="1">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>10</v>
@@ -5937,10 +5937,10 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>840020</v>
+        <v>730010</v>
       </c>
       <c r="B186" s="1">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>10</v>
@@ -5966,10 +5966,10 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>840010</v>
+        <v>740020</v>
       </c>
       <c r="B187" s="1">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>10</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>850020</v>
+        <v>740010</v>
       </c>
       <c r="B188" s="1">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>10</v>
@@ -6024,10 +6024,10 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>850010</v>
+        <v>750020</v>
       </c>
       <c r="B189" s="1">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>10</v>
@@ -6053,10 +6053,10 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>860020</v>
+        <v>750010</v>
       </c>
       <c r="B190" s="1">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>10</v>
@@ -6082,10 +6082,10 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>860010</v>
+        <v>760020</v>
       </c>
       <c r="B191" s="1">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>870020</v>
+        <v>760010</v>
       </c>
       <c r="B192" s="1">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>10</v>
@@ -6140,10 +6140,10 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>870010</v>
+        <v>770020</v>
       </c>
       <c r="B193" s="1">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>10</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>880020</v>
+        <v>770010</v>
       </c>
       <c r="B194" s="1">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>10</v>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>880010</v>
+        <v>780020</v>
       </c>
       <c r="B195" s="1">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>10</v>
@@ -6227,10 +6227,10 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>890020</v>
+        <v>780010</v>
       </c>
       <c r="B196" s="1">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>10</v>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>890010</v>
+        <v>790020</v>
       </c>
       <c r="B197" s="1">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>10</v>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>900020</v>
+        <v>790010</v>
       </c>
       <c r="B198" s="1">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>10</v>
@@ -6314,10 +6314,10 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>900010</v>
+        <v>800020</v>
       </c>
       <c r="B199" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>10</v>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>910020</v>
+        <v>800010</v>
       </c>
       <c r="B200" s="1">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>910010</v>
+        <v>810020</v>
       </c>
       <c r="B201" s="1">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>10</v>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>920020</v>
+        <v>810010</v>
       </c>
       <c r="B202" s="1">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>10</v>
@@ -6430,10 +6430,10 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>920010</v>
+        <v>820020</v>
       </c>
       <c r="B203" s="1">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>10</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>930020</v>
+        <v>820010</v>
       </c>
       <c r="B204" s="1">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>10</v>
@@ -6488,10 +6488,10 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>930010</v>
+        <v>830020</v>
       </c>
       <c r="B205" s="1">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>10</v>
@@ -6517,10 +6517,10 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>940020</v>
+        <v>830010</v>
       </c>
       <c r="B206" s="1">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>10</v>
@@ -6546,10 +6546,10 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>940010</v>
+        <v>840020</v>
       </c>
       <c r="B207" s="1">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>950020</v>
+        <v>840010</v>
       </c>
       <c r="B208" s="1">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>10</v>
@@ -6604,10 +6604,10 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>950010</v>
+        <v>850020</v>
       </c>
       <c r="B209" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>10</v>
@@ -6633,10 +6633,10 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>960020</v>
+        <v>850010</v>
       </c>
       <c r="B210" s="1">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>960010</v>
+        <v>860020</v>
       </c>
       <c r="B211" s="1">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>10</v>
@@ -6691,10 +6691,10 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>970020</v>
+        <v>860010</v>
       </c>
       <c r="B212" s="1">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>10</v>
@@ -6720,10 +6720,10 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>970010</v>
+        <v>870020</v>
       </c>
       <c r="B213" s="1">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>980020</v>
+        <v>870010</v>
       </c>
       <c r="B214" s="1">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>10</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>980010</v>
+        <v>880020</v>
       </c>
       <c r="B215" s="1">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>10</v>
@@ -6807,10 +6807,10 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>990020</v>
+        <v>880010</v>
       </c>
       <c r="B216" s="1">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>10</v>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>990010</v>
+        <v>890020</v>
       </c>
       <c r="B217" s="1">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>10</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1000020</v>
+        <v>890010</v>
       </c>
       <c r="B218" s="1">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>10</v>
@@ -6894,10 +6894,10 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1000010</v>
+        <v>900020</v>
       </c>
       <c r="B219" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>10</v>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1010020</v>
+        <v>900010</v>
       </c>
       <c r="B220" s="1">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>10</v>
@@ -6952,10 +6952,10 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1010010</v>
+        <v>910020</v>
       </c>
       <c r="B221" s="1">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>10</v>
@@ -6981,10 +6981,10 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1020020</v>
+        <v>910010</v>
       </c>
       <c r="B222" s="1">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>10</v>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1020010</v>
+        <v>920020</v>
       </c>
       <c r="B223" s="1">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>10</v>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1030020</v>
+        <v>920010</v>
       </c>
       <c r="B224" s="1">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>10</v>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1030010</v>
+        <v>930020</v>
       </c>
       <c r="B225" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>10</v>
@@ -7097,10 +7097,10 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1040020</v>
+        <v>930010</v>
       </c>
       <c r="B226" s="1">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>10</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1040010</v>
+        <v>940020</v>
       </c>
       <c r="B227" s="1">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>10</v>
@@ -7155,10 +7155,10 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1050020</v>
+        <v>940010</v>
       </c>
       <c r="B228" s="1">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>10</v>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1050010</v>
+        <v>950020</v>
       </c>
       <c r="B229" s="1">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>10</v>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1060020</v>
+        <v>950010</v>
       </c>
       <c r="B230" s="1">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>10</v>
@@ -7242,10 +7242,10 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1060010</v>
+        <v>960020</v>
       </c>
       <c r="B231" s="1">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1070020</v>
+        <v>960010</v>
       </c>
       <c r="B232" s="1">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>10</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1070010</v>
+        <v>970020</v>
       </c>
       <c r="B233" s="1">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>10</v>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1080020</v>
+        <v>970010</v>
       </c>
       <c r="B234" s="1">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>10</v>
@@ -7358,10 +7358,10 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1080010</v>
+        <v>980020</v>
       </c>
       <c r="B235" s="1">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>10</v>
@@ -7387,10 +7387,10 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1090020</v>
+        <v>980010</v>
       </c>
       <c r="B236" s="1">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>10</v>
@@ -7416,10 +7416,10 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1090010</v>
+        <v>990020</v>
       </c>
       <c r="B237" s="1">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>10</v>
@@ -7445,10 +7445,10 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1100020</v>
+        <v>990010</v>
       </c>
       <c r="B238" s="1">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>10</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1100010</v>
+        <v>1000020</v>
       </c>
       <c r="B239" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>10</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1110020</v>
+        <v>1000010</v>
       </c>
       <c r="B240" s="1">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>10</v>
@@ -7532,10 +7532,10 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>1110010</v>
+        <v>1010020</v>
       </c>
       <c r="B241" s="1">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>10</v>
@@ -7561,10 +7561,10 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>1120020</v>
+        <v>1010010</v>
       </c>
       <c r="B242" s="1">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>10</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>1120010</v>
+        <v>1020020</v>
       </c>
       <c r="B243" s="1">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>10</v>
@@ -7619,10 +7619,10 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>1130020</v>
+        <v>1020010</v>
       </c>
       <c r="B244" s="1">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>10</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>1130010</v>
+        <v>1030020</v>
       </c>
       <c r="B245" s="1">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>10</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>1140020</v>
+        <v>1030010</v>
       </c>
       <c r="B246" s="1">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>10</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>1140010</v>
+        <v>1040020</v>
       </c>
       <c r="B247" s="1">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>10</v>
@@ -7735,10 +7735,10 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>1150020</v>
+        <v>1040010</v>
       </c>
       <c r="B248" s="1">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>10</v>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>1150010</v>
+        <v>1050020</v>
       </c>
       <c r="B249" s="1">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>10</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>1160020</v>
+        <v>1050010</v>
       </c>
       <c r="B250" s="1">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>1160010</v>
+        <v>1060020</v>
       </c>
       <c r="B251" s="1">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>10</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>1170020</v>
+        <v>1060010</v>
       </c>
       <c r="B252" s="1">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>10</v>
@@ -7880,10 +7880,10 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>1170010</v>
+        <v>1070020</v>
       </c>
       <c r="B253" s="1">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>1180020</v>
+        <v>1070010</v>
       </c>
       <c r="B254" s="1">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>10</v>
@@ -7938,10 +7938,10 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>1180010</v>
+        <v>1080020</v>
       </c>
       <c r="B255" s="1">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>10</v>
@@ -7967,10 +7967,10 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>1190020</v>
+        <v>1080010</v>
       </c>
       <c r="B256" s="1">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>10</v>
@@ -7996,10 +7996,10 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>1190010</v>
+        <v>1090020</v>
       </c>
       <c r="B257" s="1">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>10</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1200020</v>
+        <v>1090010</v>
       </c>
       <c r="B258" s="1">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>10</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1200010</v>
+        <v>1100020</v>
       </c>
       <c r="B259" s="1">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>10</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1210020</v>
+        <v>1100010</v>
       </c>
       <c r="B260" s="1">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>10</v>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1210010</v>
+        <v>1110020</v>
       </c>
       <c r="B261" s="1">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1220020</v>
+        <v>1110010</v>
       </c>
       <c r="B262" s="1">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>10</v>
@@ -8170,10 +8170,10 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1220010</v>
+        <v>1120020</v>
       </c>
       <c r="B263" s="1">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>10</v>
@@ -8199,10 +8199,10 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>1230020</v>
+        <v>1120010</v>
       </c>
       <c r="B264" s="1">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>10</v>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>1230010</v>
+        <v>1130020</v>
       </c>
       <c r="B265" s="1">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>10</v>
@@ -8257,10 +8257,10 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>1240020</v>
+        <v>1130010</v>
       </c>
       <c r="B266" s="1">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>10</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>1240010</v>
+        <v>1140020</v>
       </c>
       <c r="B267" s="1">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>10</v>
@@ -8315,10 +8315,10 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>1250020</v>
+        <v>1140010</v>
       </c>
       <c r="B268" s="1">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>10</v>
@@ -8344,10 +8344,10 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>1250010</v>
+        <v>1150020</v>
       </c>
       <c r="B269" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>10</v>
@@ -8373,10 +8373,10 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1260020</v>
+        <v>1150010</v>
       </c>
       <c r="B270" s="1">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>10</v>
@@ -8402,10 +8402,10 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1260010</v>
+        <v>1160020</v>
       </c>
       <c r="B271" s="1">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>10</v>
@@ -8431,10 +8431,10 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1270020</v>
+        <v>1160010</v>
       </c>
       <c r="B272" s="1">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>10</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1270010</v>
+        <v>1170020</v>
       </c>
       <c r="B273" s="1">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>10</v>
@@ -8489,10 +8489,10 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1280020</v>
+        <v>1170010</v>
       </c>
       <c r="B274" s="1">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>10</v>
@@ -8518,10 +8518,10 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1280010</v>
+        <v>1180020</v>
       </c>
       <c r="B275" s="1">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>10</v>
@@ -8547,10 +8547,10 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1290020</v>
+        <v>1180010</v>
       </c>
       <c r="B276" s="1">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>10</v>
@@ -8576,10 +8576,10 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1290010</v>
+        <v>1190020</v>
       </c>
       <c r="B277" s="1">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>10</v>
@@ -8605,10 +8605,10 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1300020</v>
+        <v>1190010</v>
       </c>
       <c r="B278" s="1">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>10</v>
@@ -8634,10 +8634,10 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1300010</v>
+        <v>1200020</v>
       </c>
       <c r="B279" s="1">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>10</v>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1310020</v>
+        <v>1200010</v>
       </c>
       <c r="B280" s="1">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>10</v>
@@ -8692,10 +8692,10 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1310010</v>
+        <v>1210020</v>
       </c>
       <c r="B281" s="1">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>10</v>
@@ -8721,10 +8721,10 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1320020</v>
+        <v>1210010</v>
       </c>
       <c r="B282" s="1">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>10</v>
@@ -8750,10 +8750,10 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1320010</v>
+        <v>1220020</v>
       </c>
       <c r="B283" s="1">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>10</v>
@@ -8779,10 +8779,10 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1330020</v>
+        <v>1220010</v>
       </c>
       <c r="B284" s="1">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>10</v>
@@ -8808,10 +8808,10 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1330010</v>
+        <v>1230020</v>
       </c>
       <c r="B285" s="1">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>10</v>
@@ -8837,10 +8837,10 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1340020</v>
+        <v>1230010</v>
       </c>
       <c r="B286" s="1">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>10</v>
@@ -8866,10 +8866,10 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1340010</v>
+        <v>1240020</v>
       </c>
       <c r="B287" s="1">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>10</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1350020</v>
+        <v>1240010</v>
       </c>
       <c r="B288" s="1">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>10</v>
@@ -8924,10 +8924,10 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1350010</v>
+        <v>1250020</v>
       </c>
       <c r="B289" s="1">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>10</v>
@@ -8953,10 +8953,10 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1360020</v>
+        <v>1250010</v>
       </c>
       <c r="B290" s="1">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>10</v>
@@ -8982,10 +8982,10 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1360010</v>
+        <v>1260020</v>
       </c>
       <c r="B291" s="1">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1370020</v>
+        <v>1260010</v>
       </c>
       <c r="B292" s="1">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>10</v>
@@ -9040,10 +9040,10 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1370010</v>
+        <v>1270020</v>
       </c>
       <c r="B293" s="1">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>10</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1380020</v>
+        <v>1270010</v>
       </c>
       <c r="B294" s="1">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>10</v>
@@ -9098,10 +9098,10 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1380010</v>
+        <v>1280020</v>
       </c>
       <c r="B295" s="1">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>10</v>
@@ -9127,10 +9127,10 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1390020</v>
+        <v>1280010</v>
       </c>
       <c r="B296" s="1">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>10</v>
@@ -9156,10 +9156,10 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1390010</v>
+        <v>1290020</v>
       </c>
       <c r="B297" s="1">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>10</v>
@@ -9185,10 +9185,10 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1400020</v>
+        <v>1290010</v>
       </c>
       <c r="B298" s="1">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>10</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1400010</v>
+        <v>1300020</v>
       </c>
       <c r="B299" s="1">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>10</v>
@@ -9243,10 +9243,10 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1410020</v>
+        <v>1300010</v>
       </c>
       <c r="B300" s="1">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>10</v>
@@ -9272,10 +9272,10 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1410010</v>
+        <v>1310020</v>
       </c>
       <c r="B301" s="1">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>10</v>
@@ -9301,10 +9301,10 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1420020</v>
+        <v>1310010</v>
       </c>
       <c r="B302" s="1">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1420010</v>
+        <v>1320020</v>
       </c>
       <c r="B303" s="1">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>10</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1430020</v>
+        <v>1320010</v>
       </c>
       <c r="B304" s="1">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>10</v>
@@ -9388,10 +9388,10 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1430010</v>
+        <v>1330020</v>
       </c>
       <c r="B305" s="1">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>10</v>
@@ -9417,10 +9417,10 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1440020</v>
+        <v>1330010</v>
       </c>
       <c r="B306" s="1">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>10</v>
@@ -9446,10 +9446,10 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1440010</v>
+        <v>1340020</v>
       </c>
       <c r="B307" s="1">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>10</v>
@@ -9475,10 +9475,10 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1450020</v>
+        <v>1340010</v>
       </c>
       <c r="B308" s="1">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>10</v>
@@ -9504,10 +9504,10 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1450010</v>
+        <v>1350020</v>
       </c>
       <c r="B309" s="1">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>10</v>
@@ -9533,10 +9533,10 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1460020</v>
+        <v>1350010</v>
       </c>
       <c r="B310" s="1">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>10</v>
@@ -9562,10 +9562,10 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1460010</v>
+        <v>1360020</v>
       </c>
       <c r="B311" s="1">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>10</v>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1470020</v>
+        <v>1360010</v>
       </c>
       <c r="B312" s="1">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>10</v>
@@ -9620,10 +9620,10 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1470010</v>
+        <v>1370020</v>
       </c>
       <c r="B313" s="1">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>10</v>
@@ -9649,10 +9649,10 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1480020</v>
+        <v>1370010</v>
       </c>
       <c r="B314" s="1">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>10</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1480010</v>
+        <v>1380020</v>
       </c>
       <c r="B315" s="1">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>10</v>
@@ -9707,10 +9707,10 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1490020</v>
+        <v>1380010</v>
       </c>
       <c r="B316" s="1">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>10</v>
@@ -9736,10 +9736,10 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1490010</v>
+        <v>1390020</v>
       </c>
       <c r="B317" s="1">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>10</v>
@@ -9765,10 +9765,10 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1500020</v>
+        <v>1390010</v>
       </c>
       <c r="B318" s="1">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>10</v>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1500010</v>
+        <v>1400020</v>
       </c>
       <c r="B319" s="1">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>10</v>
@@ -9823,10 +9823,10 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1510020</v>
+        <v>1400010</v>
       </c>
       <c r="B320" s="1">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>10</v>
@@ -9852,10 +9852,10 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1510010</v>
+        <v>1410020</v>
       </c>
       <c r="B321" s="1">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>10</v>
@@ -9881,10 +9881,10 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1520020</v>
+        <v>1410010</v>
       </c>
       <c r="B322" s="1">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1520010</v>
+        <v>1420020</v>
       </c>
       <c r="B323" s="1">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>10</v>
@@ -9939,10 +9939,10 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1530020</v>
+        <v>1420010</v>
       </c>
       <c r="B324" s="1">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>10</v>
@@ -9968,10 +9968,10 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1530010</v>
+        <v>1430020</v>
       </c>
       <c r="B325" s="1">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>10</v>
@@ -9997,10 +9997,10 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1540020</v>
+        <v>1430010</v>
       </c>
       <c r="B326" s="1">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>10</v>
@@ -10026,10 +10026,10 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1540010</v>
+        <v>1440020</v>
       </c>
       <c r="B327" s="1">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>10</v>
@@ -10055,10 +10055,10 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1550020</v>
+        <v>1440010</v>
       </c>
       <c r="B328" s="1">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>10</v>
@@ -10084,10 +10084,10 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1550010</v>
+        <v>1450020</v>
       </c>
       <c r="B329" s="1">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1560020</v>
+        <v>1450010</v>
       </c>
       <c r="B330" s="1">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>10</v>
@@ -10142,10 +10142,10 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1560010</v>
+        <v>1460020</v>
       </c>
       <c r="B331" s="1">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>10</v>
@@ -10171,10 +10171,10 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1570020</v>
+        <v>1460010</v>
       </c>
       <c r="B332" s="1">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>10</v>
@@ -10200,10 +10200,10 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1570010</v>
+        <v>1470020</v>
       </c>
       <c r="B333" s="1">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1580020</v>
+        <v>1470010</v>
       </c>
       <c r="B334" s="1">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>10</v>
@@ -10258,10 +10258,10 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1580010</v>
+        <v>1480020</v>
       </c>
       <c r="B335" s="1">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>10</v>
@@ -10287,10 +10287,10 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1590020</v>
+        <v>1480010</v>
       </c>
       <c r="B336" s="1">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>10</v>
@@ -10316,10 +10316,10 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1590010</v>
+        <v>1490020</v>
       </c>
       <c r="B337" s="1">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>10</v>
@@ -10345,10 +10345,10 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1600020</v>
+        <v>1490010</v>
       </c>
       <c r="B338" s="1">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>10</v>
@@ -10374,10 +10374,10 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1600010</v>
+        <v>1500020</v>
       </c>
       <c r="B339" s="1">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>10</v>
@@ -10403,19 +10403,19 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>10001</v>
+        <v>1500010</v>
       </c>
       <c r="B340" s="1">
-        <v>1</v>
-      </c>
-      <c r="D340" s="1">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F340" s="1" t="s">
-        <v>18</v>
+      <c r="F340" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G340" s="1">
         <v>0</v>
@@ -10432,19 +10432,19 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>20001</v>
+        <v>1510020</v>
       </c>
       <c r="B341" s="1">
-        <v>2</v>
-      </c>
-      <c r="D341" s="1">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F341" s="1" t="s">
-        <v>18</v>
+      <c r="F341" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G341" s="1">
         <v>0</v>
@@ -10461,19 +10461,19 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>30001</v>
+        <v>1510010</v>
       </c>
       <c r="B342" s="1">
-        <v>3</v>
-      </c>
-      <c r="D342" s="1">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F342" s="1" t="s">
-        <v>18</v>
+      <c r="F342" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G342" s="1">
         <v>0</v>
@@ -10490,19 +10490,19 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>40001</v>
+        <v>1520020</v>
       </c>
       <c r="B343" s="1">
-        <v>4</v>
-      </c>
-      <c r="D343" s="1">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F343" s="1" t="s">
-        <v>18</v>
+      <c r="F343" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G343" s="1">
         <v>0</v>
@@ -10519,19 +10519,19 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>50001</v>
+        <v>1520010</v>
       </c>
       <c r="B344" s="1">
-        <v>5</v>
-      </c>
-      <c r="D344" s="1">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F344" s="1" t="s">
-        <v>18</v>
+      <c r="F344" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G344" s="1">
         <v>0</v>
@@ -10548,19 +10548,19 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>60001</v>
+        <v>1530020</v>
       </c>
       <c r="B345" s="1">
-        <v>6</v>
-      </c>
-      <c r="D345" s="1">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F345" s="1" t="s">
-        <v>18</v>
+      <c r="F345" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G345" s="1">
         <v>0</v>
@@ -10577,19 +10577,19 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>70001</v>
+        <v>1530010</v>
       </c>
       <c r="B346" s="1">
-        <v>7</v>
-      </c>
-      <c r="D346" s="1">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F346" s="1" t="s">
-        <v>18</v>
+      <c r="F346" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G346" s="1">
         <v>0</v>
@@ -10606,19 +10606,19 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>80001</v>
+        <v>1540020</v>
       </c>
       <c r="B347" s="1">
-        <v>8</v>
-      </c>
-      <c r="D347" s="1">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F347" s="1" t="s">
-        <v>18</v>
+      <c r="F347" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G347" s="1">
         <v>0</v>
@@ -10635,19 +10635,19 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>90001</v>
+        <v>1540010</v>
       </c>
       <c r="B348" s="1">
-        <v>9</v>
-      </c>
-      <c r="D348" s="1">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F348" s="1" t="s">
-        <v>18</v>
+      <c r="F348" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G348" s="1">
         <v>0</v>
@@ -10664,19 +10664,19 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>100001</v>
+        <v>1550020</v>
       </c>
       <c r="B349" s="1">
-        <v>10</v>
-      </c>
-      <c r="D349" s="1">
-        <v>0</v>
+        <v>155</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F349" s="1" t="s">
-        <v>18</v>
+      <c r="F349" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G349" s="1">
         <v>0</v>
@@ -10693,19 +10693,19 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>110001</v>
+        <v>1550010</v>
       </c>
       <c r="B350" s="1">
-        <v>11</v>
-      </c>
-      <c r="D350" s="1">
-        <v>0</v>
+        <v>155</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F350" s="1" t="s">
-        <v>18</v>
+      <c r="F350" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G350" s="1">
         <v>0</v>
@@ -10722,19 +10722,19 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>120001</v>
+        <v>1560020</v>
       </c>
       <c r="B351" s="1">
-        <v>12</v>
-      </c>
-      <c r="D351" s="1">
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F351" s="1" t="s">
-        <v>18</v>
+      <c r="F351" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G351" s="1">
         <v>0</v>
@@ -10751,19 +10751,19 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>130001</v>
+        <v>1560010</v>
       </c>
       <c r="B352" s="1">
-        <v>13</v>
-      </c>
-      <c r="D352" s="1">
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F352" s="1" t="s">
-        <v>18</v>
+      <c r="F352" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G352" s="1">
         <v>0</v>
@@ -10780,19 +10780,19 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>140001</v>
+        <v>1570020</v>
       </c>
       <c r="B353" s="1">
-        <v>14</v>
-      </c>
-      <c r="D353" s="1">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F353" s="1" t="s">
-        <v>18</v>
+      <c r="F353" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G353" s="1">
         <v>0</v>
@@ -10809,19 +10809,19 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>150001</v>
+        <v>1570010</v>
       </c>
       <c r="B354" s="1">
-        <v>15</v>
-      </c>
-      <c r="D354" s="1">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F354" s="1" t="s">
-        <v>18</v>
+      <c r="F354" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G354" s="1">
         <v>0</v>
@@ -10838,19 +10838,19 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>160001</v>
+        <v>1580020</v>
       </c>
       <c r="B355" s="1">
-        <v>16</v>
-      </c>
-      <c r="D355" s="1">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F355" s="1" t="s">
-        <v>18</v>
+      <c r="F355" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G355" s="1">
         <v>0</v>
@@ -10867,19 +10867,19 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>170001</v>
+        <v>1580010</v>
       </c>
       <c r="B356" s="1">
-        <v>17</v>
-      </c>
-      <c r="D356" s="1">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F356" s="1" t="s">
-        <v>18</v>
+      <c r="F356" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G356" s="1">
         <v>0</v>
@@ -10896,19 +10896,19 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>180001</v>
+        <v>1590020</v>
       </c>
       <c r="B357" s="1">
-        <v>18</v>
-      </c>
-      <c r="D357" s="1">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F357" s="1" t="s">
-        <v>18</v>
+      <c r="F357" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G357" s="1">
         <v>0</v>
@@ -10925,19 +10925,19 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>190001</v>
+        <v>1590010</v>
       </c>
       <c r="B358" s="1">
-        <v>19</v>
-      </c>
-      <c r="D358" s="1">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F358" s="1" t="s">
-        <v>18</v>
+      <c r="F358" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G358" s="1">
         <v>0</v>
@@ -10954,19 +10954,19 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>200001</v>
+        <v>1600020</v>
       </c>
       <c r="B359" s="1">
-        <v>20</v>
-      </c>
-      <c r="D359" s="1">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F359" s="1" t="s">
-        <v>18</v>
+      <c r="F359" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G359" s="1">
         <v>0</v>
@@ -10983,19 +10983,19 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>210001</v>
+        <v>1600010</v>
       </c>
       <c r="B360" s="1">
-        <v>21</v>
-      </c>
-      <c r="D360" s="1">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F360" s="1" t="s">
-        <v>18</v>
+      <c r="F360" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G360" s="1">
         <v>0</v>
@@ -11012,10 +11012,10 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>220001</v>
+        <v>10001</v>
       </c>
       <c r="B361" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D361" s="1">
         <v>0</v>
@@ -11041,10 +11041,10 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>230001</v>
+        <v>20001</v>
       </c>
       <c r="B362" s="1">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D362" s="1">
         <v>0</v>
@@ -11070,10 +11070,10 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>240001</v>
+        <v>30001</v>
       </c>
       <c r="B363" s="1">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D363" s="1">
         <v>0</v>
@@ -11099,10 +11099,10 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>250001</v>
+        <v>40001</v>
       </c>
       <c r="B364" s="1">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D364" s="1">
         <v>0</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>260001</v>
+        <v>50001</v>
       </c>
       <c r="B365" s="1">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D365" s="1">
         <v>0</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>270001</v>
+        <v>60001</v>
       </c>
       <c r="B366" s="1">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D366" s="1">
         <v>0</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>280001</v>
+        <v>70001</v>
       </c>
       <c r="B367" s="1">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D367" s="1">
         <v>0</v>
@@ -11215,10 +11215,10 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>290001</v>
+        <v>80001</v>
       </c>
       <c r="B368" s="1">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D368" s="1">
         <v>0</v>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>300001</v>
+        <v>90001</v>
       </c>
       <c r="B369" s="1">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D369" s="1">
         <v>0</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>310001</v>
+        <v>100001</v>
       </c>
       <c r="B370" s="1">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D370" s="1">
         <v>0</v>
@@ -11302,10 +11302,10 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>320001</v>
+        <v>110001</v>
       </c>
       <c r="B371" s="1">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D371" s="1">
         <v>0</v>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>330001</v>
+        <v>120001</v>
       </c>
       <c r="B372" s="1">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D372" s="1">
         <v>0</v>
@@ -11360,10 +11360,10 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>340001</v>
+        <v>130001</v>
       </c>
       <c r="B373" s="1">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D373" s="1">
         <v>0</v>
@@ -11389,10 +11389,10 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>350001</v>
+        <v>140001</v>
       </c>
       <c r="B374" s="1">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D374" s="1">
         <v>0</v>
@@ -11418,10 +11418,10 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>360001</v>
+        <v>150001</v>
       </c>
       <c r="B375" s="1">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D375" s="1">
         <v>0</v>
@@ -11447,10 +11447,10 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>370001</v>
+        <v>160001</v>
       </c>
       <c r="B376" s="1">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D376" s="1">
         <v>0</v>
@@ -11476,10 +11476,10 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>380001</v>
+        <v>170001</v>
       </c>
       <c r="B377" s="1">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D377" s="1">
         <v>0</v>
@@ -11505,10 +11505,10 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>390001</v>
+        <v>180001</v>
       </c>
       <c r="B378" s="1">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D378" s="1">
         <v>0</v>
@@ -11534,10 +11534,10 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>400001</v>
+        <v>190001</v>
       </c>
       <c r="B379" s="1">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D379" s="1">
         <v>0</v>
@@ -11563,10 +11563,10 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>410001</v>
+        <v>200001</v>
       </c>
       <c r="B380" s="1">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D380" s="1">
         <v>0</v>
@@ -11592,10 +11592,10 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>420001</v>
+        <v>210001</v>
       </c>
       <c r="B381" s="1">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D381" s="1">
         <v>0</v>
@@ -11621,10 +11621,10 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>430001</v>
+        <v>220001</v>
       </c>
       <c r="B382" s="1">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D382" s="1">
         <v>0</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>440001</v>
+        <v>230001</v>
       </c>
       <c r="B383" s="1">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D383" s="1">
         <v>0</v>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>450001</v>
+        <v>240001</v>
       </c>
       <c r="B384" s="1">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D384" s="1">
         <v>0</v>
@@ -11708,10 +11708,10 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>460001</v>
+        <v>250001</v>
       </c>
       <c r="B385" s="1">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D385" s="1">
         <v>0</v>
@@ -11737,10 +11737,10 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>470001</v>
+        <v>260001</v>
       </c>
       <c r="B386" s="1">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D386" s="1">
         <v>0</v>
@@ -11766,10 +11766,10 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>480001</v>
+        <v>270001</v>
       </c>
       <c r="B387" s="1">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D387" s="1">
         <v>0</v>
@@ -11795,10 +11795,10 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>490001</v>
+        <v>280001</v>
       </c>
       <c r="B388" s="1">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D388" s="1">
         <v>0</v>
@@ -11824,10 +11824,10 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>500001</v>
+        <v>290001</v>
       </c>
       <c r="B389" s="1">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D389" s="1">
         <v>0</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>510001</v>
+        <v>300001</v>
       </c>
       <c r="B390" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D390" s="1">
         <v>0</v>
@@ -11882,10 +11882,10 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>520001</v>
+        <v>310001</v>
       </c>
       <c r="B391" s="1">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D391" s="1">
         <v>0</v>
@@ -11911,10 +11911,10 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>530001</v>
+        <v>320001</v>
       </c>
       <c r="B392" s="1">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D392" s="1">
         <v>0</v>
@@ -11940,10 +11940,10 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>540001</v>
+        <v>330001</v>
       </c>
       <c r="B393" s="1">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D393" s="1">
         <v>0</v>
@@ -11969,10 +11969,10 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>550001</v>
+        <v>340001</v>
       </c>
       <c r="B394" s="1">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D394" s="1">
         <v>0</v>
@@ -11998,10 +11998,10 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>560001</v>
+        <v>350001</v>
       </c>
       <c r="B395" s="1">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D395" s="1">
         <v>0</v>
@@ -12027,10 +12027,10 @@
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>570001</v>
+        <v>360001</v>
       </c>
       <c r="B396" s="1">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D396" s="1">
         <v>0</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>580001</v>
+        <v>370001</v>
       </c>
       <c r="B397" s="1">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D397" s="1">
         <v>0</v>
@@ -12085,10 +12085,10 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>590001</v>
+        <v>380001</v>
       </c>
       <c r="B398" s="1">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D398" s="1">
         <v>0</v>
@@ -12114,10 +12114,10 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>600001</v>
+        <v>390001</v>
       </c>
       <c r="B399" s="1">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D399" s="1">
         <v>0</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>610001</v>
+        <v>400001</v>
       </c>
       <c r="B400" s="1">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D400" s="1">
         <v>0</v>
@@ -12172,10 +12172,10 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>620001</v>
+        <v>410001</v>
       </c>
       <c r="B401" s="1">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D401" s="1">
         <v>0</v>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>630001</v>
+        <v>420001</v>
       </c>
       <c r="B402" s="1">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D402" s="1">
         <v>0</v>
@@ -12230,10 +12230,10 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>640001</v>
+        <v>430001</v>
       </c>
       <c r="B403" s="1">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D403" s="1">
         <v>0</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>650001</v>
+        <v>440001</v>
       </c>
       <c r="B404" s="1">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D404" s="1">
         <v>0</v>
@@ -12288,10 +12288,10 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>660001</v>
+        <v>450001</v>
       </c>
       <c r="B405" s="1">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D405" s="1">
         <v>0</v>
@@ -12317,10 +12317,10 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>670001</v>
+        <v>460001</v>
       </c>
       <c r="B406" s="1">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D406" s="1">
         <v>0</v>
@@ -12346,10 +12346,10 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>680001</v>
+        <v>470001</v>
       </c>
       <c r="B407" s="1">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D407" s="1">
         <v>0</v>
@@ -12375,10 +12375,10 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>690001</v>
+        <v>480001</v>
       </c>
       <c r="B408" s="1">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D408" s="1">
         <v>0</v>
@@ -12404,10 +12404,10 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>700001</v>
+        <v>490001</v>
       </c>
       <c r="B409" s="1">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D409" s="1">
         <v>0</v>
@@ -12433,10 +12433,10 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>710001</v>
+        <v>500001</v>
       </c>
       <c r="B410" s="1">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D410" s="1">
         <v>0</v>
@@ -12462,10 +12462,10 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>720001</v>
+        <v>510001</v>
       </c>
       <c r="B411" s="1">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D411" s="1">
         <v>0</v>
@@ -12491,10 +12491,10 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>730001</v>
+        <v>520001</v>
       </c>
       <c r="B412" s="1">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D412" s="1">
         <v>0</v>
@@ -12520,10 +12520,10 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>740001</v>
+        <v>530001</v>
       </c>
       <c r="B413" s="1">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="D413" s="1">
         <v>0</v>
@@ -12549,10 +12549,10 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
-        <v>750001</v>
+        <v>540001</v>
       </c>
       <c r="B414" s="1">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D414" s="1">
         <v>0</v>
@@ -12578,10 +12578,10 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>760001</v>
+        <v>550001</v>
       </c>
       <c r="B415" s="1">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D415" s="1">
         <v>0</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>770001</v>
+        <v>560001</v>
       </c>
       <c r="B416" s="1">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D416" s="1">
         <v>0</v>
@@ -12636,10 +12636,10 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>780001</v>
+        <v>570001</v>
       </c>
       <c r="B417" s="1">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D417" s="1">
         <v>0</v>
@@ -12665,10 +12665,10 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>790001</v>
+        <v>580001</v>
       </c>
       <c r="B418" s="1">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D418" s="1">
         <v>0</v>
@@ -12694,10 +12694,10 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>800001</v>
+        <v>590001</v>
       </c>
       <c r="B419" s="1">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D419" s="1">
         <v>0</v>
@@ -12723,10 +12723,10 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>810001</v>
+        <v>600001</v>
       </c>
       <c r="B420" s="1">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D420" s="1">
         <v>0</v>
@@ -12752,10 +12752,10 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>820001</v>
+        <v>610001</v>
       </c>
       <c r="B421" s="1">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D421" s="1">
         <v>0</v>
@@ -12781,10 +12781,10 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>830001</v>
+        <v>620001</v>
       </c>
       <c r="B422" s="1">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D422" s="1">
         <v>0</v>
@@ -12810,10 +12810,10 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>840001</v>
+        <v>630001</v>
       </c>
       <c r="B423" s="1">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D423" s="1">
         <v>0</v>
@@ -12839,10 +12839,10 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>850001</v>
+        <v>640001</v>
       </c>
       <c r="B424" s="1">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D424" s="1">
         <v>0</v>
@@ -12868,10 +12868,10 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>860001</v>
+        <v>650001</v>
       </c>
       <c r="B425" s="1">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D425" s="1">
         <v>0</v>
@@ -12897,10 +12897,10 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>870001</v>
+        <v>660001</v>
       </c>
       <c r="B426" s="1">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D426" s="1">
         <v>0</v>
@@ -12926,10 +12926,10 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>880001</v>
+        <v>670001</v>
       </c>
       <c r="B427" s="1">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D427" s="1">
         <v>0</v>
@@ -12955,10 +12955,10 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>890001</v>
+        <v>680001</v>
       </c>
       <c r="B428" s="1">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D428" s="1">
         <v>0</v>
@@ -12984,10 +12984,10 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>900001</v>
+        <v>690001</v>
       </c>
       <c r="B429" s="1">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="D429" s="1">
         <v>0</v>
@@ -13013,10 +13013,10 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
-        <v>910001</v>
+        <v>700001</v>
       </c>
       <c r="B430" s="1">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D430" s="1">
         <v>0</v>
@@ -13042,10 +13042,10 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>920001</v>
+        <v>710001</v>
       </c>
       <c r="B431" s="1">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D431" s="1">
         <v>0</v>
@@ -13071,10 +13071,10 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>930001</v>
+        <v>720001</v>
       </c>
       <c r="B432" s="1">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D432" s="1">
         <v>0</v>
@@ -13100,10 +13100,10 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>940001</v>
+        <v>730001</v>
       </c>
       <c r="B433" s="1">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D433" s="1">
         <v>0</v>
@@ -13129,10 +13129,10 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>950001</v>
+        <v>740001</v>
       </c>
       <c r="B434" s="1">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D434" s="1">
         <v>0</v>
@@ -13158,10 +13158,10 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>960001</v>
+        <v>750001</v>
       </c>
       <c r="B435" s="1">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D435" s="1">
         <v>0</v>
@@ -13187,10 +13187,10 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>970001</v>
+        <v>760001</v>
       </c>
       <c r="B436" s="1">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D436" s="1">
         <v>0</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>980001</v>
+        <v>770001</v>
       </c>
       <c r="B437" s="1">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D437" s="1">
         <v>0</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>990001</v>
+        <v>780001</v>
       </c>
       <c r="B438" s="1">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D438" s="1">
         <v>0</v>
@@ -13274,10 +13274,10 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>1000001</v>
+        <v>790001</v>
       </c>
       <c r="B439" s="1">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D439" s="1">
         <v>0</v>
@@ -13303,10 +13303,10 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>1010001</v>
+        <v>800001</v>
       </c>
       <c r="B440" s="1">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D440" s="1">
         <v>0</v>
@@ -13332,10 +13332,10 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>1020001</v>
+        <v>810001</v>
       </c>
       <c r="B441" s="1">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D441" s="1">
         <v>0</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>1030001</v>
+        <v>820001</v>
       </c>
       <c r="B442" s="1">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D442" s="1">
         <v>0</v>
@@ -13390,10 +13390,10 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>1040001</v>
+        <v>830001</v>
       </c>
       <c r="B443" s="1">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D443" s="1">
         <v>0</v>
@@ -13419,10 +13419,10 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>1050001</v>
+        <v>840001</v>
       </c>
       <c r="B444" s="1">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D444" s="1">
         <v>0</v>
@@ -13448,10 +13448,10 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>1060001</v>
+        <v>850001</v>
       </c>
       <c r="B445" s="1">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D445" s="1">
         <v>0</v>
@@ -13477,10 +13477,10 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>1070001</v>
+        <v>860001</v>
       </c>
       <c r="B446" s="1">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D446" s="1">
         <v>0</v>
@@ -13506,10 +13506,10 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>1080001</v>
+        <v>870001</v>
       </c>
       <c r="B447" s="1">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D447" s="1">
         <v>0</v>
@@ -13535,10 +13535,10 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>1090001</v>
+        <v>880001</v>
       </c>
       <c r="B448" s="1">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D448" s="1">
         <v>0</v>
@@ -13564,10 +13564,10 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>1100001</v>
+        <v>890001</v>
       </c>
       <c r="B449" s="1">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D449" s="1">
         <v>0</v>
@@ -13593,10 +13593,10 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>1110001</v>
+        <v>900001</v>
       </c>
       <c r="B450" s="1">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D450" s="1">
         <v>0</v>
@@ -13622,10 +13622,10 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>1120001</v>
+        <v>910001</v>
       </c>
       <c r="B451" s="1">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D451" s="1">
         <v>0</v>
@@ -13651,10 +13651,10 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>1130001</v>
+        <v>920001</v>
       </c>
       <c r="B452" s="1">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D452" s="1">
         <v>0</v>
@@ -13680,10 +13680,10 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>1140001</v>
+        <v>930001</v>
       </c>
       <c r="B453" s="1">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D453" s="1">
         <v>0</v>
@@ -13709,10 +13709,10 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>1150001</v>
+        <v>940001</v>
       </c>
       <c r="B454" s="1">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D454" s="1">
         <v>0</v>
@@ -13738,10 +13738,10 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>1160001</v>
+        <v>950001</v>
       </c>
       <c r="B455" s="1">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D455" s="1">
         <v>0</v>
@@ -13767,10 +13767,10 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
-        <v>1170001</v>
+        <v>960001</v>
       </c>
       <c r="B456" s="1">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D456" s="1">
         <v>0</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>1180001</v>
+        <v>970001</v>
       </c>
       <c r="B457" s="1">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D457" s="1">
         <v>0</v>
@@ -13825,10 +13825,10 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>1190001</v>
+        <v>980001</v>
       </c>
       <c r="B458" s="1">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D458" s="1">
         <v>0</v>
@@ -13854,10 +13854,10 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>1200001</v>
+        <v>990001</v>
       </c>
       <c r="B459" s="1">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D459" s="1">
         <v>0</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>1210001</v>
+        <v>1000001</v>
       </c>
       <c r="B460" s="1">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D460" s="1">
         <v>0</v>
@@ -13912,10 +13912,10 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>1220001</v>
+        <v>1010001</v>
       </c>
       <c r="B461" s="1">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D461" s="1">
         <v>0</v>
@@ -13941,10 +13941,10 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>1230001</v>
+        <v>1020001</v>
       </c>
       <c r="B462" s="1">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D462" s="1">
         <v>0</v>
@@ -13970,10 +13970,10 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>1240001</v>
+        <v>1030001</v>
       </c>
       <c r="B463" s="1">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="D463" s="1">
         <v>0</v>
@@ -13999,10 +13999,10 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>1250001</v>
+        <v>1040001</v>
       </c>
       <c r="B464" s="1">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="D464" s="1">
         <v>0</v>
@@ -14028,10 +14028,10 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
-        <v>1260001</v>
+        <v>1050001</v>
       </c>
       <c r="B465" s="1">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="D465" s="1">
         <v>0</v>
@@ -14057,10 +14057,10 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
-        <v>1270001</v>
+        <v>1060001</v>
       </c>
       <c r="B466" s="1">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D466" s="1">
         <v>0</v>
@@ -14086,10 +14086,10 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
-        <v>1280001</v>
+        <v>1070001</v>
       </c>
       <c r="B467" s="1">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D467" s="1">
         <v>0</v>
@@ -14115,10 +14115,10 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
-        <v>1290001</v>
+        <v>1080001</v>
       </c>
       <c r="B468" s="1">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="D468" s="1">
         <v>0</v>
@@ -14144,10 +14144,10 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
-        <v>1300001</v>
+        <v>1090001</v>
       </c>
       <c r="B469" s="1">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D469" s="1">
         <v>0</v>
@@ -14173,10 +14173,10 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
-        <v>1310001</v>
+        <v>1100001</v>
       </c>
       <c r="B470" s="1">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="D470" s="1">
         <v>0</v>
@@ -14202,10 +14202,10 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
-        <v>1320001</v>
+        <v>1110001</v>
       </c>
       <c r="B471" s="1">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="D471" s="1">
         <v>0</v>
@@ -14231,10 +14231,10 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
-        <v>1330001</v>
+        <v>1120001</v>
       </c>
       <c r="B472" s="1">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D472" s="1">
         <v>0</v>
@@ -14260,10 +14260,10 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
-        <v>1340001</v>
+        <v>1130001</v>
       </c>
       <c r="B473" s="1">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D473" s="1">
         <v>0</v>
@@ -14289,10 +14289,10 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
-        <v>1350001</v>
+        <v>1140001</v>
       </c>
       <c r="B474" s="1">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D474" s="1">
         <v>0</v>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
-        <v>1360001</v>
+        <v>1150001</v>
       </c>
       <c r="B475" s="1">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D475" s="1">
         <v>0</v>
@@ -14347,10 +14347,10 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
-        <v>1370001</v>
+        <v>1160001</v>
       </c>
       <c r="B476" s="1">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="D476" s="1">
         <v>0</v>
@@ -14376,10 +14376,10 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
-        <v>1380001</v>
+        <v>1170001</v>
       </c>
       <c r="B477" s="1">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="D477" s="1">
         <v>0</v>
@@ -14405,10 +14405,10 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
-        <v>1390001</v>
+        <v>1180001</v>
       </c>
       <c r="B478" s="1">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D478" s="1">
         <v>0</v>
@@ -14434,10 +14434,10 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
-        <v>1400001</v>
+        <v>1190001</v>
       </c>
       <c r="B479" s="1">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D479" s="1">
         <v>0</v>
@@ -14463,10 +14463,10 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
-        <v>1410001</v>
+        <v>1200001</v>
       </c>
       <c r="B480" s="1">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D480" s="1">
         <v>0</v>
@@ -14492,10 +14492,10 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
-        <v>1420001</v>
+        <v>1210001</v>
       </c>
       <c r="B481" s="1">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D481" s="1">
         <v>0</v>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
-        <v>1430001</v>
+        <v>1220001</v>
       </c>
       <c r="B482" s="1">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D482" s="1">
         <v>0</v>
@@ -14550,10 +14550,10 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
-        <v>1440001</v>
+        <v>1230001</v>
       </c>
       <c r="B483" s="1">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="D483" s="1">
         <v>0</v>
@@ -14579,10 +14579,10 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
-        <v>1450001</v>
+        <v>1240001</v>
       </c>
       <c r="B484" s="1">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D484" s="1">
         <v>0</v>
@@ -14608,10 +14608,10 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
-        <v>1460001</v>
+        <v>1250001</v>
       </c>
       <c r="B485" s="1">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D485" s="1">
         <v>0</v>
@@ -14637,10 +14637,10 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
-        <v>1470001</v>
+        <v>1260001</v>
       </c>
       <c r="B486" s="1">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D486" s="1">
         <v>0</v>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
-        <v>1480001</v>
+        <v>1270001</v>
       </c>
       <c r="B487" s="1">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="D487" s="1">
         <v>0</v>
@@ -14695,10 +14695,10 @@
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A488" s="1">
-        <v>1490001</v>
+        <v>1280001</v>
       </c>
       <c r="B488" s="1">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="D488" s="1">
         <v>0</v>
@@ -14724,10 +14724,10 @@
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A489" s="1">
-        <v>1500001</v>
+        <v>1290001</v>
       </c>
       <c r="B489" s="1">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D489" s="1">
         <v>0</v>
@@ -14753,10 +14753,10 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A490" s="1">
-        <v>1510001</v>
+        <v>1300001</v>
       </c>
       <c r="B490" s="1">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D490" s="1">
         <v>0</v>
@@ -14782,10 +14782,10 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A491" s="1">
-        <v>1520001</v>
+        <v>1310001</v>
       </c>
       <c r="B491" s="1">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D491" s="1">
         <v>0</v>
@@ -14811,10 +14811,10 @@
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A492" s="1">
-        <v>1530001</v>
+        <v>1320001</v>
       </c>
       <c r="B492" s="1">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D492" s="1">
         <v>0</v>
@@ -14840,10 +14840,10 @@
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A493" s="1">
-        <v>1540001</v>
+        <v>1330001</v>
       </c>
       <c r="B493" s="1">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D493" s="1">
         <v>0</v>
@@ -14869,10 +14869,10 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A494" s="1">
-        <v>1550001</v>
+        <v>1340001</v>
       </c>
       <c r="B494" s="1">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D494" s="1">
         <v>0</v>
@@ -14898,10 +14898,10 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A495" s="1">
-        <v>1560001</v>
+        <v>1350001</v>
       </c>
       <c r="B495" s="1">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D495" s="1">
         <v>0</v>
@@ -14927,10 +14927,10 @@
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A496" s="1">
-        <v>1570001</v>
+        <v>1360001</v>
       </c>
       <c r="B496" s="1">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D496" s="1">
         <v>0</v>
@@ -14956,10 +14956,10 @@
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A497" s="1">
-        <v>1580001</v>
+        <v>1370001</v>
       </c>
       <c r="B497" s="1">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D497" s="1">
         <v>0</v>
@@ -14985,10 +14985,10 @@
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A498" s="1">
-        <v>1590001</v>
+        <v>1380001</v>
       </c>
       <c r="B498" s="1">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D498" s="1">
         <v>0</v>
@@ -15014,30 +15014,639 @@
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A499" s="1">
+        <v>1390001</v>
+      </c>
+      <c r="B499" s="1">
+        <v>139</v>
+      </c>
+      <c r="D499" s="1">
+        <v>0</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F499" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G499" s="1">
+        <v>0</v>
+      </c>
+      <c r="H499" s="2">
+        <v>0</v>
+      </c>
+      <c r="I499" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J499" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A500" s="1">
+        <v>1400001</v>
+      </c>
+      <c r="B500" s="1">
+        <v>140</v>
+      </c>
+      <c r="D500" s="1">
+        <v>0</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F500" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G500" s="1">
+        <v>0</v>
+      </c>
+      <c r="H500" s="2">
+        <v>0</v>
+      </c>
+      <c r="I500" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J500" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A501" s="1">
+        <v>1410001</v>
+      </c>
+      <c r="B501" s="1">
+        <v>141</v>
+      </c>
+      <c r="D501" s="1">
+        <v>0</v>
+      </c>
+      <c r="E501" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F501" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G501" s="1">
+        <v>0</v>
+      </c>
+      <c r="H501" s="2">
+        <v>0</v>
+      </c>
+      <c r="I501" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J501" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A502" s="1">
+        <v>1420001</v>
+      </c>
+      <c r="B502" s="1">
+        <v>142</v>
+      </c>
+      <c r="D502" s="1">
+        <v>0</v>
+      </c>
+      <c r="E502" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F502" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G502" s="1">
+        <v>0</v>
+      </c>
+      <c r="H502" s="2">
+        <v>0</v>
+      </c>
+      <c r="I502" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J502" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A503" s="1">
+        <v>1430001</v>
+      </c>
+      <c r="B503" s="1">
+        <v>143</v>
+      </c>
+      <c r="D503" s="1">
+        <v>0</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F503" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G503" s="1">
+        <v>0</v>
+      </c>
+      <c r="H503" s="2">
+        <v>0</v>
+      </c>
+      <c r="I503" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J503" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A504" s="1">
+        <v>1440001</v>
+      </c>
+      <c r="B504" s="1">
+        <v>144</v>
+      </c>
+      <c r="D504" s="1">
+        <v>0</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F504" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G504" s="1">
+        <v>0</v>
+      </c>
+      <c r="H504" s="2">
+        <v>0</v>
+      </c>
+      <c r="I504" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J504" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A505" s="1">
+        <v>1450001</v>
+      </c>
+      <c r="B505" s="1">
+        <v>145</v>
+      </c>
+      <c r="D505" s="1">
+        <v>0</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F505" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G505" s="1">
+        <v>0</v>
+      </c>
+      <c r="H505" s="2">
+        <v>0</v>
+      </c>
+      <c r="I505" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J505" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A506" s="1">
+        <v>1460001</v>
+      </c>
+      <c r="B506" s="1">
+        <v>146</v>
+      </c>
+      <c r="D506" s="1">
+        <v>0</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F506" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G506" s="1">
+        <v>0</v>
+      </c>
+      <c r="H506" s="2">
+        <v>0</v>
+      </c>
+      <c r="I506" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J506" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A507" s="1">
+        <v>1470001</v>
+      </c>
+      <c r="B507" s="1">
+        <v>147</v>
+      </c>
+      <c r="D507" s="1">
+        <v>0</v>
+      </c>
+      <c r="E507" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F507" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G507" s="1">
+        <v>0</v>
+      </c>
+      <c r="H507" s="2">
+        <v>0</v>
+      </c>
+      <c r="I507" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J507" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A508" s="1">
+        <v>1480001</v>
+      </c>
+      <c r="B508" s="1">
+        <v>148</v>
+      </c>
+      <c r="D508" s="1">
+        <v>0</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F508" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G508" s="1">
+        <v>0</v>
+      </c>
+      <c r="H508" s="2">
+        <v>0</v>
+      </c>
+      <c r="I508" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J508" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A509" s="1">
+        <v>1490001</v>
+      </c>
+      <c r="B509" s="1">
+        <v>149</v>
+      </c>
+      <c r="D509" s="1">
+        <v>0</v>
+      </c>
+      <c r="E509" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F509" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G509" s="1">
+        <v>0</v>
+      </c>
+      <c r="H509" s="2">
+        <v>0</v>
+      </c>
+      <c r="I509" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J509" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A510" s="1">
+        <v>1500001</v>
+      </c>
+      <c r="B510" s="1">
+        <v>150</v>
+      </c>
+      <c r="D510" s="1">
+        <v>0</v>
+      </c>
+      <c r="E510" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F510" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G510" s="1">
+        <v>0</v>
+      </c>
+      <c r="H510" s="2">
+        <v>0</v>
+      </c>
+      <c r="I510" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J510" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A511" s="1">
+        <v>1510001</v>
+      </c>
+      <c r="B511" s="1">
+        <v>151</v>
+      </c>
+      <c r="D511" s="1">
+        <v>0</v>
+      </c>
+      <c r="E511" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F511" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G511" s="1">
+        <v>0</v>
+      </c>
+      <c r="H511" s="2">
+        <v>0</v>
+      </c>
+      <c r="I511" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J511" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A512" s="1">
+        <v>1520001</v>
+      </c>
+      <c r="B512" s="1">
+        <v>152</v>
+      </c>
+      <c r="D512" s="1">
+        <v>0</v>
+      </c>
+      <c r="E512" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F512" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G512" s="1">
+        <v>0</v>
+      </c>
+      <c r="H512" s="2">
+        <v>0</v>
+      </c>
+      <c r="I512" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J512" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A513" s="1">
+        <v>1530001</v>
+      </c>
+      <c r="B513" s="1">
+        <v>153</v>
+      </c>
+      <c r="D513" s="1">
+        <v>0</v>
+      </c>
+      <c r="E513" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F513" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G513" s="1">
+        <v>0</v>
+      </c>
+      <c r="H513" s="2">
+        <v>0</v>
+      </c>
+      <c r="I513" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J513" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A514" s="1">
+        <v>1540001</v>
+      </c>
+      <c r="B514" s="1">
+        <v>154</v>
+      </c>
+      <c r="D514" s="1">
+        <v>0</v>
+      </c>
+      <c r="E514" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F514" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G514" s="1">
+        <v>0</v>
+      </c>
+      <c r="H514" s="2">
+        <v>0</v>
+      </c>
+      <c r="I514" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J514" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A515" s="1">
+        <v>1550001</v>
+      </c>
+      <c r="B515" s="1">
+        <v>155</v>
+      </c>
+      <c r="D515" s="1">
+        <v>0</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G515" s="1">
+        <v>0</v>
+      </c>
+      <c r="H515" s="2">
+        <v>0</v>
+      </c>
+      <c r="I515" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J515" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A516" s="1">
+        <v>1560001</v>
+      </c>
+      <c r="B516" s="1">
+        <v>156</v>
+      </c>
+      <c r="D516" s="1">
+        <v>0</v>
+      </c>
+      <c r="E516" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F516" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G516" s="1">
+        <v>0</v>
+      </c>
+      <c r="H516" s="2">
+        <v>0</v>
+      </c>
+      <c r="I516" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J516" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A517" s="1">
+        <v>1570001</v>
+      </c>
+      <c r="B517" s="1">
+        <v>157</v>
+      </c>
+      <c r="D517" s="1">
+        <v>0</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F517" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G517" s="1">
+        <v>0</v>
+      </c>
+      <c r="H517" s="2">
+        <v>0</v>
+      </c>
+      <c r="I517" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J517" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A518" s="1">
+        <v>1580001</v>
+      </c>
+      <c r="B518" s="1">
+        <v>158</v>
+      </c>
+      <c r="D518" s="1">
+        <v>0</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G518" s="1">
+        <v>0</v>
+      </c>
+      <c r="H518" s="2">
+        <v>0</v>
+      </c>
+      <c r="I518" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J518" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A519" s="1">
+        <v>1590001</v>
+      </c>
+      <c r="B519" s="1">
+        <v>159</v>
+      </c>
+      <c r="D519" s="1">
+        <v>0</v>
+      </c>
+      <c r="E519" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F519" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G519" s="1">
+        <v>0</v>
+      </c>
+      <c r="H519" s="2">
+        <v>0</v>
+      </c>
+      <c r="I519" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J519" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A520" s="1">
         <v>1600001</v>
       </c>
-      <c r="B499" s="1">
+      <c r="B520" s="1">
         <v>160</v>
       </c>
-      <c r="D499" s="1">
-        <v>0</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G499" s="1">
-        <v>0</v>
-      </c>
-      <c r="H499" s="2">
-        <v>0</v>
-      </c>
-      <c r="I499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J499" s="4" t="s">
+      <c r="D520" s="1">
+        <v>0</v>
+      </c>
+      <c r="E520" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F520" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G520" s="1">
+        <v>0</v>
+      </c>
+      <c r="H520" s="2">
+        <v>0</v>
+      </c>
+      <c r="I520" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J520" s="4" t="s">
         <v>18</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9DF0DC-9B63-455B-9C0A-C52ED26CDA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6374D1B6-39AA-43CE-9FC1-B8E6D15BE88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1616,13 +1616,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>90001</v>
+        <v>100020</v>
       </c>
       <c r="B37" s="1">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>16</v>
@@ -1631,7 +1631,7 @@
         <v>17</v>
       </c>
       <c r="G37" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -1645,13 +1645,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>90002</v>
+        <v>100010</v>
       </c>
       <c r="B38" s="1">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>16</v>
@@ -1660,7 +1660,7 @@
         <v>17</v>
       </c>
       <c r="G38" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>90003</v>
+        <v>90001</v>
       </c>
       <c r="B39" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>17</v>
       </c>
       <c r="G39" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>90004</v>
+        <v>90002</v>
       </c>
       <c r="B40" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>17</v>
       </c>
       <c r="G40" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>90005</v>
+        <v>90003</v>
       </c>
       <c r="B41" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>17</v>
       </c>
       <c r="G41" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>90006</v>
+        <v>90004</v>
       </c>
       <c r="B42" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>17</v>
       </c>
       <c r="G42" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>90007</v>
+        <v>90005</v>
       </c>
       <c r="B43" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>17</v>
       </c>
       <c r="G43" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>90008</v>
+        <v>90006</v>
       </c>
       <c r="B44" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>17</v>
       </c>
       <c r="G44" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>90009</v>
+        <v>90007</v>
       </c>
       <c r="B45" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>17</v>
       </c>
       <c r="G45" s="1">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>90011</v>
+        <v>90008</v>
       </c>
       <c r="B46" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>17</v>
       </c>
       <c r="G46" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>90012</v>
+        <v>90009</v>
       </c>
       <c r="B47" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>17</v>
       </c>
       <c r="G47" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>90013</v>
+        <v>90011</v>
       </c>
       <c r="B48" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>17</v>
       </c>
       <c r="G48" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>90014</v>
+        <v>90012</v>
       </c>
       <c r="B49" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>90015</v>
+        <v>90013</v>
       </c>
       <c r="B50" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="G50" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>90016</v>
+        <v>90014</v>
       </c>
       <c r="B51" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>17</v>
       </c>
       <c r="G51" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>90017</v>
+        <v>90015</v>
       </c>
       <c r="B52" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="1">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>90018</v>
+        <v>90016</v>
       </c>
       <c r="B53" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>17</v>
       </c>
       <c r="G53" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>90021</v>
+        <v>90017</v>
       </c>
       <c r="B54" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>17</v>
       </c>
       <c r="G54" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>90019</v>
+        <v>90018</v>
       </c>
       <c r="B55" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>17</v>
       </c>
       <c r="G55" s="1">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>90023</v>
+        <v>90021</v>
       </c>
       <c r="B56" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>17</v>
       </c>
       <c r="G56" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>90022</v>
+        <v>90019</v>
       </c>
       <c r="B57" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -2211,7 +2211,7 @@
         <v>17</v>
       </c>
       <c r="G57" s="1">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>90024</v>
+        <v>90023</v>
       </c>
       <c r="B58" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>17</v>
       </c>
       <c r="G58" s="1">
-        <v>5600</v>
+        <v>3000</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2254,13 +2254,13 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>100020</v>
+        <v>90022</v>
       </c>
       <c r="B59" s="1">
         <v>10</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>10</v>
+      <c r="D59" s="2">
+        <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>16</v>
@@ -2269,7 +2269,7 @@
         <v>17</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>100010</v>
+        <v>90024</v>
       </c>
       <c r="B60" s="1">
         <v>10</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>10</v>
+      <c r="D60" s="2">
+        <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>16</v>
@@ -2298,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6374D1B6-39AA-43CE-9FC1-B8E6D15BE88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0086767D-B473-4E5E-84B1-4795786BFE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1674,13 +1674,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>90001</v>
+        <v>110020</v>
       </c>
       <c r="B39" s="1">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>16</v>
@@ -1689,7 +1689,7 @@
         <v>17</v>
       </c>
       <c r="G39" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -1703,13 +1703,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>90002</v>
+        <v>110010</v>
       </c>
       <c r="B40" s="1">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>16</v>
@@ -1718,7 +1718,7 @@
         <v>17</v>
       </c>
       <c r="G40" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>90003</v>
+        <v>110001</v>
       </c>
       <c r="B41" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         <v>17</v>
       </c>
       <c r="G41" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>90004</v>
+        <v>110002</v>
       </c>
       <c r="B42" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>17</v>
       </c>
       <c r="G42" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>90005</v>
+        <v>110003</v>
       </c>
       <c r="B43" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>17</v>
       </c>
       <c r="G43" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>90006</v>
+        <v>110004</v>
       </c>
       <c r="B44" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>17</v>
       </c>
       <c r="G44" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>90007</v>
+        <v>110005</v>
       </c>
       <c r="B45" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>17</v>
       </c>
       <c r="G45" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>90008</v>
+        <v>110006</v>
       </c>
       <c r="B46" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>17</v>
       </c>
       <c r="G46" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>90009</v>
+        <v>110007</v>
       </c>
       <c r="B47" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>17</v>
       </c>
       <c r="G47" s="1">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>90011</v>
+        <v>110008</v>
       </c>
       <c r="B48" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>17</v>
       </c>
       <c r="G48" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>90012</v>
+        <v>110009</v>
       </c>
       <c r="B49" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>90013</v>
+        <v>110011</v>
       </c>
       <c r="B50" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="G50" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>90014</v>
+        <v>110012</v>
       </c>
       <c r="B51" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>17</v>
       </c>
       <c r="G51" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>90015</v>
+        <v>110013</v>
       </c>
       <c r="B52" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>90016</v>
+        <v>110014</v>
       </c>
       <c r="B53" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>17</v>
       </c>
       <c r="G53" s="1">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>90017</v>
+        <v>110015</v>
       </c>
       <c r="B54" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>17</v>
       </c>
       <c r="G54" s="1">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>90018</v>
+        <v>110016</v>
       </c>
       <c r="B55" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>17</v>
       </c>
       <c r="G55" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>90021</v>
+        <v>110017</v>
       </c>
       <c r="B56" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>17</v>
       </c>
       <c r="G56" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>90019</v>
+        <v>110018</v>
       </c>
       <c r="B57" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -2211,7 +2211,7 @@
         <v>17</v>
       </c>
       <c r="G57" s="1">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>90023</v>
+        <v>110021</v>
       </c>
       <c r="B58" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>17</v>
       </c>
       <c r="G58" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>90022</v>
+        <v>110019</v>
       </c>
       <c r="B59" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>17</v>
       </c>
       <c r="G59" s="1">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>90024</v>
+        <v>110023</v>
       </c>
       <c r="B60" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="G60" s="1">
-        <v>5600</v>
+        <v>3000</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -2312,13 +2312,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110020</v>
+        <v>110022</v>
       </c>
       <c r="B61" s="1">
         <v>11</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>10</v>
+      <c r="D61" s="2">
+        <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>16</v>
@@ -2327,7 +2327,7 @@
         <v>17</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -2341,13 +2341,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>110010</v>
+        <v>110024</v>
       </c>
       <c r="B62" s="1">
         <v>11</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>10</v>
+      <c r="D62" s="2">
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>16</v>
@@ -2356,7 +2356,7 @@
         <v>17</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0086767D-B473-4E5E-84B1-4795786BFE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EC69D2-95A2-4F0B-B00C-1DD279E27D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="71">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -226,6 +226,63 @@
   <si>
     <t>drop_exp_num</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:2</t>
+  </si>
+  <si>
+    <t>42617001</t>
+  </si>
+  <si>
+    <t>48300003:1</t>
+  </si>
+  <si>
+    <t>46700001:1</t>
+  </si>
+  <si>
+    <t>42633001</t>
+  </si>
+  <si>
+    <t>46700001:2</t>
+  </si>
+  <si>
+    <t>48300005:1</t>
+  </si>
+  <si>
+    <t>42614001</t>
+  </si>
+  <si>
+    <t>42731001</t>
+  </si>
+  <si>
+    <t>48200001:1</t>
+  </si>
+  <si>
+    <t>42636001</t>
+  </si>
+  <si>
+    <t>48300004:1</t>
+  </si>
+  <si>
+    <t>46200001:3</t>
+  </si>
+  <si>
+    <t>46700001:3</t>
+  </si>
+  <si>
+    <t>42635001</t>
+  </si>
+  <si>
+    <t>48300002:1</t>
+  </si>
+  <si>
+    <t>42654001</t>
+  </si>
+  <si>
+    <t>48300006:1</t>
+  </si>
+  <si>
+    <t>42656001</t>
   </si>
 </sst>
 </file>
@@ -1534,8 +1591,8 @@
       <c r="B34" s="1">
         <v>8</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
+      <c r="D34" s="2">
+        <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>16</v>
@@ -1563,8 +1620,8 @@
       <c r="B35" s="1">
         <v>8</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
+      <c r="D35" s="2">
+        <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>16</v>
@@ -1621,8 +1678,8 @@
       <c r="B37" s="1">
         <v>10</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
+      <c r="D37" s="2">
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>16</v>
@@ -1650,8 +1707,8 @@
       <c r="B38" s="1">
         <v>10</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>10</v>
+      <c r="D38" s="2">
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>16</v>
@@ -1679,8 +1736,8 @@
       <c r="B39" s="1">
         <v>11</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>10</v>
+      <c r="D39" s="2">
+        <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>16</v>
@@ -1708,8 +1765,8 @@
       <c r="B40" s="1">
         <v>11</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
+      <c r="D40" s="2">
+        <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>16</v>
@@ -1744,13 +1801,13 @@
         <v>16</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G41" s="1">
         <v>30</v>
       </c>
-      <c r="H41" s="2">
-        <v>0</v>
+      <c r="H41" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>16</v>
@@ -1773,7 +1830,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G42" s="1">
         <v>50</v>
@@ -1785,7 +1842,7 @@
         <v>16</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.15">
@@ -1802,13 +1859,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G43" s="1">
         <v>60</v>
       </c>
-      <c r="H43" s="2">
-        <v>0</v>
+      <c r="H43" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>16</v>
@@ -1831,7 +1888,7 @@
         <v>16</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G44" s="1">
         <v>70</v>
@@ -1843,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
@@ -1860,7 +1917,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G45" s="1">
         <v>80</v>
@@ -1872,7 +1929,7 @@
         <v>16</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
@@ -1889,13 +1946,13 @@
         <v>16</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G46" s="1">
         <v>100</v>
       </c>
-      <c r="H46" s="2">
-        <v>0</v>
+      <c r="H46" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>16</v>
@@ -1918,7 +1975,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G47" s="1">
         <v>120</v>
@@ -1930,7 +1987,7 @@
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
@@ -1947,13 +2004,13 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G48" s="1">
         <v>150</v>
       </c>
-      <c r="H48" s="2">
-        <v>0</v>
+      <c r="H48" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>16</v>
@@ -1976,7 +2033,7 @@
         <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G49" s="1">
         <v>200</v>
@@ -1988,7 +2045,7 @@
         <v>16</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
@@ -2005,13 +2062,13 @@
         <v>16</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G50" s="1">
         <v>250</v>
       </c>
-      <c r="H50" s="2">
-        <v>0</v>
+      <c r="H50" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
@@ -2034,7 +2091,7 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G51" s="1">
         <v>300</v>
@@ -2046,7 +2103,7 @@
         <v>16</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
@@ -2063,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G52" s="1">
         <v>500</v>
@@ -2075,7 +2132,7 @@
         <v>16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
@@ -2092,13 +2149,13 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G53" s="1">
         <v>600</v>
       </c>
-      <c r="H53" s="2">
-        <v>0</v>
+      <c r="H53" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>16</v>
@@ -2121,7 +2178,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="G54" s="1">
         <v>900</v>
@@ -2133,7 +2190,7 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
@@ -2150,7 +2207,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G55" s="1">
         <v>1200</v>
@@ -2162,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
@@ -2179,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G56" s="1">
         <v>1500</v>
       </c>
-      <c r="H56" s="2">
-        <v>0</v>
+      <c r="H56" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>16</v>
@@ -2208,7 +2265,7 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G57" s="1">
         <v>1800</v>
@@ -2220,7 +2277,7 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
@@ -2237,7 +2294,7 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="G58" s="1">
         <v>2000</v>
@@ -2249,7 +2306,7 @@
         <v>16</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
@@ -2266,7 +2323,7 @@
         <v>16</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G59" s="1">
         <v>2500</v>
@@ -2278,7 +2335,7 @@
         <v>16</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
@@ -2295,13 +2352,13 @@
         <v>16</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G60" s="1">
         <v>3000</v>
       </c>
-      <c r="H60" s="2">
-        <v>0</v>
+      <c r="H60" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>16</v>
@@ -2324,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="G61" s="1">
         <v>3500</v>
@@ -2336,7 +2393,7 @@
         <v>16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">
@@ -2353,7 +2410,7 @@
         <v>16</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G62" s="1">
         <v>5600</v>
@@ -2365,7 +2422,7 @@
         <v>16</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EC69D2-95A2-4F0B-B00C-1DD279E27D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B505868E-F1C4-4ADE-B0E6-4DAF6CBF1C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$J$360</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="71">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -626,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J520"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -11067,4646 +11070,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A361" s="1">
-        <v>10001</v>
-      </c>
-      <c r="B361" s="1">
-        <v>1</v>
-      </c>
-      <c r="D361" s="1">
-        <v>0</v>
-      </c>
-      <c r="E361" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F361" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G361" s="1">
-        <v>0</v>
-      </c>
-      <c r="H361" s="2">
-        <v>0</v>
-      </c>
-      <c r="I361" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J361" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A362" s="1">
-        <v>20001</v>
-      </c>
-      <c r="B362" s="1">
-        <v>2</v>
-      </c>
-      <c r="D362" s="1">
-        <v>0</v>
-      </c>
-      <c r="E362" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F362" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G362" s="1">
-        <v>0</v>
-      </c>
-      <c r="H362" s="2">
-        <v>0</v>
-      </c>
-      <c r="I362" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J362" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A363" s="1">
-        <v>30001</v>
-      </c>
-      <c r="B363" s="1">
-        <v>3</v>
-      </c>
-      <c r="D363" s="1">
-        <v>0</v>
-      </c>
-      <c r="E363" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F363" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G363" s="1">
-        <v>0</v>
-      </c>
-      <c r="H363" s="2">
-        <v>0</v>
-      </c>
-      <c r="I363" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J363" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A364" s="1">
-        <v>40001</v>
-      </c>
-      <c r="B364" s="1">
-        <v>4</v>
-      </c>
-      <c r="D364" s="1">
-        <v>0</v>
-      </c>
-      <c r="E364" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F364" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G364" s="1">
-        <v>0</v>
-      </c>
-      <c r="H364" s="2">
-        <v>0</v>
-      </c>
-      <c r="I364" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J364" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A365" s="1">
-        <v>50001</v>
-      </c>
-      <c r="B365" s="1">
-        <v>5</v>
-      </c>
-      <c r="D365" s="1">
-        <v>0</v>
-      </c>
-      <c r="E365" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F365" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G365" s="1">
-        <v>0</v>
-      </c>
-      <c r="H365" s="2">
-        <v>0</v>
-      </c>
-      <c r="I365" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J365" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A366" s="1">
-        <v>60001</v>
-      </c>
-      <c r="B366" s="1">
-        <v>6</v>
-      </c>
-      <c r="D366" s="1">
-        <v>0</v>
-      </c>
-      <c r="E366" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F366" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G366" s="1">
-        <v>0</v>
-      </c>
-      <c r="H366" s="2">
-        <v>0</v>
-      </c>
-      <c r="I366" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J366" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A367" s="1">
-        <v>70001</v>
-      </c>
-      <c r="B367" s="1">
-        <v>7</v>
-      </c>
-      <c r="D367" s="1">
-        <v>0</v>
-      </c>
-      <c r="E367" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F367" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G367" s="1">
-        <v>0</v>
-      </c>
-      <c r="H367" s="2">
-        <v>0</v>
-      </c>
-      <c r="I367" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J367" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A368" s="1">
-        <v>80001</v>
-      </c>
-      <c r="B368" s="1">
-        <v>8</v>
-      </c>
-      <c r="D368" s="1">
-        <v>0</v>
-      </c>
-      <c r="E368" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F368" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G368" s="1">
-        <v>0</v>
-      </c>
-      <c r="H368" s="2">
-        <v>0</v>
-      </c>
-      <c r="I368" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J368" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A369" s="1">
-        <v>90001</v>
-      </c>
-      <c r="B369" s="1">
-        <v>9</v>
-      </c>
-      <c r="D369" s="1">
-        <v>0</v>
-      </c>
-      <c r="E369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F369" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G369" s="1">
-        <v>0</v>
-      </c>
-      <c r="H369" s="2">
-        <v>0</v>
-      </c>
-      <c r="I369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J369" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A370" s="1">
-        <v>100001</v>
-      </c>
-      <c r="B370" s="1">
-        <v>10</v>
-      </c>
-      <c r="D370" s="1">
-        <v>0</v>
-      </c>
-      <c r="E370" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F370" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G370" s="1">
-        <v>0</v>
-      </c>
-      <c r="H370" s="2">
-        <v>0</v>
-      </c>
-      <c r="I370" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J370" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A371" s="1">
-        <v>110001</v>
-      </c>
-      <c r="B371" s="1">
-        <v>11</v>
-      </c>
-      <c r="D371" s="1">
-        <v>0</v>
-      </c>
-      <c r="E371" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F371" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G371" s="1">
-        <v>0</v>
-      </c>
-      <c r="H371" s="2">
-        <v>0</v>
-      </c>
-      <c r="I371" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J371" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A372" s="1">
-        <v>120001</v>
-      </c>
-      <c r="B372" s="1">
-        <v>12</v>
-      </c>
-      <c r="D372" s="1">
-        <v>0</v>
-      </c>
-      <c r="E372" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F372" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G372" s="1">
-        <v>0</v>
-      </c>
-      <c r="H372" s="2">
-        <v>0</v>
-      </c>
-      <c r="I372" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J372" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A373" s="1">
-        <v>130001</v>
-      </c>
-      <c r="B373" s="1">
-        <v>13</v>
-      </c>
-      <c r="D373" s="1">
-        <v>0</v>
-      </c>
-      <c r="E373" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F373" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G373" s="1">
-        <v>0</v>
-      </c>
-      <c r="H373" s="2">
-        <v>0</v>
-      </c>
-      <c r="I373" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J373" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A374" s="1">
-        <v>140001</v>
-      </c>
-      <c r="B374" s="1">
-        <v>14</v>
-      </c>
-      <c r="D374" s="1">
-        <v>0</v>
-      </c>
-      <c r="E374" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F374" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G374" s="1">
-        <v>0</v>
-      </c>
-      <c r="H374" s="2">
-        <v>0</v>
-      </c>
-      <c r="I374" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J374" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A375" s="1">
-        <v>150001</v>
-      </c>
-      <c r="B375" s="1">
-        <v>15</v>
-      </c>
-      <c r="D375" s="1">
-        <v>0</v>
-      </c>
-      <c r="E375" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F375" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G375" s="1">
-        <v>0</v>
-      </c>
-      <c r="H375" s="2">
-        <v>0</v>
-      </c>
-      <c r="I375" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J375" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A376" s="1">
-        <v>160001</v>
-      </c>
-      <c r="B376" s="1">
-        <v>16</v>
-      </c>
-      <c r="D376" s="1">
-        <v>0</v>
-      </c>
-      <c r="E376" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F376" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G376" s="1">
-        <v>0</v>
-      </c>
-      <c r="H376" s="2">
-        <v>0</v>
-      </c>
-      <c r="I376" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J376" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A377" s="1">
-        <v>170001</v>
-      </c>
-      <c r="B377" s="1">
-        <v>17</v>
-      </c>
-      <c r="D377" s="1">
-        <v>0</v>
-      </c>
-      <c r="E377" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F377" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G377" s="1">
-        <v>0</v>
-      </c>
-      <c r="H377" s="2">
-        <v>0</v>
-      </c>
-      <c r="I377" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J377" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A378" s="1">
-        <v>180001</v>
-      </c>
-      <c r="B378" s="1">
-        <v>18</v>
-      </c>
-      <c r="D378" s="1">
-        <v>0</v>
-      </c>
-      <c r="E378" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F378" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G378" s="1">
-        <v>0</v>
-      </c>
-      <c r="H378" s="2">
-        <v>0</v>
-      </c>
-      <c r="I378" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J378" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A379" s="1">
-        <v>190001</v>
-      </c>
-      <c r="B379" s="1">
-        <v>19</v>
-      </c>
-      <c r="D379" s="1">
-        <v>0</v>
-      </c>
-      <c r="E379" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F379" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G379" s="1">
-        <v>0</v>
-      </c>
-      <c r="H379" s="2">
-        <v>0</v>
-      </c>
-      <c r="I379" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J379" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A380" s="1">
-        <v>200001</v>
-      </c>
-      <c r="B380" s="1">
-        <v>20</v>
-      </c>
-      <c r="D380" s="1">
-        <v>0</v>
-      </c>
-      <c r="E380" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F380" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G380" s="1">
-        <v>0</v>
-      </c>
-      <c r="H380" s="2">
-        <v>0</v>
-      </c>
-      <c r="I380" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J380" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A381" s="1">
-        <v>210001</v>
-      </c>
-      <c r="B381" s="1">
-        <v>21</v>
-      </c>
-      <c r="D381" s="1">
-        <v>0</v>
-      </c>
-      <c r="E381" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F381" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G381" s="1">
-        <v>0</v>
-      </c>
-      <c r="H381" s="2">
-        <v>0</v>
-      </c>
-      <c r="I381" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J381" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A382" s="1">
-        <v>220001</v>
-      </c>
-      <c r="B382" s="1">
-        <v>22</v>
-      </c>
-      <c r="D382" s="1">
-        <v>0</v>
-      </c>
-      <c r="E382" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F382" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G382" s="1">
-        <v>0</v>
-      </c>
-      <c r="H382" s="2">
-        <v>0</v>
-      </c>
-      <c r="I382" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J382" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A383" s="1">
-        <v>230001</v>
-      </c>
-      <c r="B383" s="1">
-        <v>23</v>
-      </c>
-      <c r="D383" s="1">
-        <v>0</v>
-      </c>
-      <c r="E383" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F383" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G383" s="1">
-        <v>0</v>
-      </c>
-      <c r="H383" s="2">
-        <v>0</v>
-      </c>
-      <c r="I383" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J383" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A384" s="1">
-        <v>240001</v>
-      </c>
-      <c r="B384" s="1">
-        <v>24</v>
-      </c>
-      <c r="D384" s="1">
-        <v>0</v>
-      </c>
-      <c r="E384" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F384" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G384" s="1">
-        <v>0</v>
-      </c>
-      <c r="H384" s="2">
-        <v>0</v>
-      </c>
-      <c r="I384" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J384" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A385" s="1">
-        <v>250001</v>
-      </c>
-      <c r="B385" s="1">
-        <v>25</v>
-      </c>
-      <c r="D385" s="1">
-        <v>0</v>
-      </c>
-      <c r="E385" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F385" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G385" s="1">
-        <v>0</v>
-      </c>
-      <c r="H385" s="2">
-        <v>0</v>
-      </c>
-      <c r="I385" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J385" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A386" s="1">
-        <v>260001</v>
-      </c>
-      <c r="B386" s="1">
-        <v>26</v>
-      </c>
-      <c r="D386" s="1">
-        <v>0</v>
-      </c>
-      <c r="E386" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F386" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G386" s="1">
-        <v>0</v>
-      </c>
-      <c r="H386" s="2">
-        <v>0</v>
-      </c>
-      <c r="I386" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J386" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A387" s="1">
-        <v>270001</v>
-      </c>
-      <c r="B387" s="1">
-        <v>27</v>
-      </c>
-      <c r="D387" s="1">
-        <v>0</v>
-      </c>
-      <c r="E387" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F387" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G387" s="1">
-        <v>0</v>
-      </c>
-      <c r="H387" s="2">
-        <v>0</v>
-      </c>
-      <c r="I387" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J387" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A388" s="1">
-        <v>280001</v>
-      </c>
-      <c r="B388" s="1">
-        <v>28</v>
-      </c>
-      <c r="D388" s="1">
-        <v>0</v>
-      </c>
-      <c r="E388" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F388" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G388" s="1">
-        <v>0</v>
-      </c>
-      <c r="H388" s="2">
-        <v>0</v>
-      </c>
-      <c r="I388" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J388" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A389" s="1">
-        <v>290001</v>
-      </c>
-      <c r="B389" s="1">
-        <v>29</v>
-      </c>
-      <c r="D389" s="1">
-        <v>0</v>
-      </c>
-      <c r="E389" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F389" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G389" s="1">
-        <v>0</v>
-      </c>
-      <c r="H389" s="2">
-        <v>0</v>
-      </c>
-      <c r="I389" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J389" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A390" s="1">
-        <v>300001</v>
-      </c>
-      <c r="B390" s="1">
-        <v>30</v>
-      </c>
-      <c r="D390" s="1">
-        <v>0</v>
-      </c>
-      <c r="E390" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F390" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G390" s="1">
-        <v>0</v>
-      </c>
-      <c r="H390" s="2">
-        <v>0</v>
-      </c>
-      <c r="I390" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J390" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A391" s="1">
-        <v>310001</v>
-      </c>
-      <c r="B391" s="1">
-        <v>31</v>
-      </c>
-      <c r="D391" s="1">
-        <v>0</v>
-      </c>
-      <c r="E391" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F391" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G391" s="1">
-        <v>0</v>
-      </c>
-      <c r="H391" s="2">
-        <v>0</v>
-      </c>
-      <c r="I391" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J391" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A392" s="1">
-        <v>320001</v>
-      </c>
-      <c r="B392" s="1">
-        <v>32</v>
-      </c>
-      <c r="D392" s="1">
-        <v>0</v>
-      </c>
-      <c r="E392" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F392" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G392" s="1">
-        <v>0</v>
-      </c>
-      <c r="H392" s="2">
-        <v>0</v>
-      </c>
-      <c r="I392" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J392" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A393" s="1">
-        <v>330001</v>
-      </c>
-      <c r="B393" s="1">
-        <v>33</v>
-      </c>
-      <c r="D393" s="1">
-        <v>0</v>
-      </c>
-      <c r="E393" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F393" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G393" s="1">
-        <v>0</v>
-      </c>
-      <c r="H393" s="2">
-        <v>0</v>
-      </c>
-      <c r="I393" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J393" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A394" s="1">
-        <v>340001</v>
-      </c>
-      <c r="B394" s="1">
-        <v>34</v>
-      </c>
-      <c r="D394" s="1">
-        <v>0</v>
-      </c>
-      <c r="E394" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F394" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G394" s="1">
-        <v>0</v>
-      </c>
-      <c r="H394" s="2">
-        <v>0</v>
-      </c>
-      <c r="I394" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J394" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A395" s="1">
-        <v>350001</v>
-      </c>
-      <c r="B395" s="1">
-        <v>35</v>
-      </c>
-      <c r="D395" s="1">
-        <v>0</v>
-      </c>
-      <c r="E395" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F395" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G395" s="1">
-        <v>0</v>
-      </c>
-      <c r="H395" s="2">
-        <v>0</v>
-      </c>
-      <c r="I395" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J395" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A396" s="1">
-        <v>360001</v>
-      </c>
-      <c r="B396" s="1">
-        <v>36</v>
-      </c>
-      <c r="D396" s="1">
-        <v>0</v>
-      </c>
-      <c r="E396" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F396" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G396" s="1">
-        <v>0</v>
-      </c>
-      <c r="H396" s="2">
-        <v>0</v>
-      </c>
-      <c r="I396" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J396" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A397" s="1">
-        <v>370001</v>
-      </c>
-      <c r="B397" s="1">
-        <v>37</v>
-      </c>
-      <c r="D397" s="1">
-        <v>0</v>
-      </c>
-      <c r="E397" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F397" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G397" s="1">
-        <v>0</v>
-      </c>
-      <c r="H397" s="2">
-        <v>0</v>
-      </c>
-      <c r="I397" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J397" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A398" s="1">
-        <v>380001</v>
-      </c>
-      <c r="B398" s="1">
-        <v>38</v>
-      </c>
-      <c r="D398" s="1">
-        <v>0</v>
-      </c>
-      <c r="E398" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F398" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G398" s="1">
-        <v>0</v>
-      </c>
-      <c r="H398" s="2">
-        <v>0</v>
-      </c>
-      <c r="I398" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J398" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A399" s="1">
-        <v>390001</v>
-      </c>
-      <c r="B399" s="1">
-        <v>39</v>
-      </c>
-      <c r="D399" s="1">
-        <v>0</v>
-      </c>
-      <c r="E399" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F399" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G399" s="1">
-        <v>0</v>
-      </c>
-      <c r="H399" s="2">
-        <v>0</v>
-      </c>
-      <c r="I399" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J399" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A400" s="1">
-        <v>400001</v>
-      </c>
-      <c r="B400" s="1">
-        <v>40</v>
-      </c>
-      <c r="D400" s="1">
-        <v>0</v>
-      </c>
-      <c r="E400" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F400" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G400" s="1">
-        <v>0</v>
-      </c>
-      <c r="H400" s="2">
-        <v>0</v>
-      </c>
-      <c r="I400" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J400" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A401" s="1">
-        <v>410001</v>
-      </c>
-      <c r="B401" s="1">
-        <v>41</v>
-      </c>
-      <c r="D401" s="1">
-        <v>0</v>
-      </c>
-      <c r="E401" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F401" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G401" s="1">
-        <v>0</v>
-      </c>
-      <c r="H401" s="2">
-        <v>0</v>
-      </c>
-      <c r="I401" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J401" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A402" s="1">
-        <v>420001</v>
-      </c>
-      <c r="B402" s="1">
-        <v>42</v>
-      </c>
-      <c r="D402" s="1">
-        <v>0</v>
-      </c>
-      <c r="E402" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F402" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G402" s="1">
-        <v>0</v>
-      </c>
-      <c r="H402" s="2">
-        <v>0</v>
-      </c>
-      <c r="I402" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J402" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A403" s="1">
-        <v>430001</v>
-      </c>
-      <c r="B403" s="1">
-        <v>43</v>
-      </c>
-      <c r="D403" s="1">
-        <v>0</v>
-      </c>
-      <c r="E403" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F403" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G403" s="1">
-        <v>0</v>
-      </c>
-      <c r="H403" s="2">
-        <v>0</v>
-      </c>
-      <c r="I403" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J403" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A404" s="1">
-        <v>440001</v>
-      </c>
-      <c r="B404" s="1">
-        <v>44</v>
-      </c>
-      <c r="D404" s="1">
-        <v>0</v>
-      </c>
-      <c r="E404" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F404" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G404" s="1">
-        <v>0</v>
-      </c>
-      <c r="H404" s="2">
-        <v>0</v>
-      </c>
-      <c r="I404" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J404" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A405" s="1">
-        <v>450001</v>
-      </c>
-      <c r="B405" s="1">
-        <v>45</v>
-      </c>
-      <c r="D405" s="1">
-        <v>0</v>
-      </c>
-      <c r="E405" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F405" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G405" s="1">
-        <v>0</v>
-      </c>
-      <c r="H405" s="2">
-        <v>0</v>
-      </c>
-      <c r="I405" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J405" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A406" s="1">
-        <v>460001</v>
-      </c>
-      <c r="B406" s="1">
-        <v>46</v>
-      </c>
-      <c r="D406" s="1">
-        <v>0</v>
-      </c>
-      <c r="E406" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F406" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G406" s="1">
-        <v>0</v>
-      </c>
-      <c r="H406" s="2">
-        <v>0</v>
-      </c>
-      <c r="I406" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J406" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A407" s="1">
-        <v>470001</v>
-      </c>
-      <c r="B407" s="1">
-        <v>47</v>
-      </c>
-      <c r="D407" s="1">
-        <v>0</v>
-      </c>
-      <c r="E407" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F407" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G407" s="1">
-        <v>0</v>
-      </c>
-      <c r="H407" s="2">
-        <v>0</v>
-      </c>
-      <c r="I407" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J407" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A408" s="1">
-        <v>480001</v>
-      </c>
-      <c r="B408" s="1">
-        <v>48</v>
-      </c>
-      <c r="D408" s="1">
-        <v>0</v>
-      </c>
-      <c r="E408" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F408" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G408" s="1">
-        <v>0</v>
-      </c>
-      <c r="H408" s="2">
-        <v>0</v>
-      </c>
-      <c r="I408" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J408" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A409" s="1">
-        <v>490001</v>
-      </c>
-      <c r="B409" s="1">
-        <v>49</v>
-      </c>
-      <c r="D409" s="1">
-        <v>0</v>
-      </c>
-      <c r="E409" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F409" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G409" s="1">
-        <v>0</v>
-      </c>
-      <c r="H409" s="2">
-        <v>0</v>
-      </c>
-      <c r="I409" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J409" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A410" s="1">
-        <v>500001</v>
-      </c>
-      <c r="B410" s="1">
-        <v>50</v>
-      </c>
-      <c r="D410" s="1">
-        <v>0</v>
-      </c>
-      <c r="E410" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F410" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G410" s="1">
-        <v>0</v>
-      </c>
-      <c r="H410" s="2">
-        <v>0</v>
-      </c>
-      <c r="I410" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J410" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A411" s="1">
-        <v>510001</v>
-      </c>
-      <c r="B411" s="1">
-        <v>51</v>
-      </c>
-      <c r="D411" s="1">
-        <v>0</v>
-      </c>
-      <c r="E411" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F411" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G411" s="1">
-        <v>0</v>
-      </c>
-      <c r="H411" s="2">
-        <v>0</v>
-      </c>
-      <c r="I411" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J411" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A412" s="1">
-        <v>520001</v>
-      </c>
-      <c r="B412" s="1">
-        <v>52</v>
-      </c>
-      <c r="D412" s="1">
-        <v>0</v>
-      </c>
-      <c r="E412" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F412" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G412" s="1">
-        <v>0</v>
-      </c>
-      <c r="H412" s="2">
-        <v>0</v>
-      </c>
-      <c r="I412" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J412" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A413" s="1">
-        <v>530001</v>
-      </c>
-      <c r="B413" s="1">
-        <v>53</v>
-      </c>
-      <c r="D413" s="1">
-        <v>0</v>
-      </c>
-      <c r="E413" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F413" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G413" s="1">
-        <v>0</v>
-      </c>
-      <c r="H413" s="2">
-        <v>0</v>
-      </c>
-      <c r="I413" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J413" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A414" s="1">
-        <v>540001</v>
-      </c>
-      <c r="B414" s="1">
-        <v>54</v>
-      </c>
-      <c r="D414" s="1">
-        <v>0</v>
-      </c>
-      <c r="E414" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F414" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G414" s="1">
-        <v>0</v>
-      </c>
-      <c r="H414" s="2">
-        <v>0</v>
-      </c>
-      <c r="I414" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J414" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A415" s="1">
-        <v>550001</v>
-      </c>
-      <c r="B415" s="1">
-        <v>55</v>
-      </c>
-      <c r="D415" s="1">
-        <v>0</v>
-      </c>
-      <c r="E415" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F415" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G415" s="1">
-        <v>0</v>
-      </c>
-      <c r="H415" s="2">
-        <v>0</v>
-      </c>
-      <c r="I415" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J415" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A416" s="1">
-        <v>560001</v>
-      </c>
-      <c r="B416" s="1">
-        <v>56</v>
-      </c>
-      <c r="D416" s="1">
-        <v>0</v>
-      </c>
-      <c r="E416" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F416" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G416" s="1">
-        <v>0</v>
-      </c>
-      <c r="H416" s="2">
-        <v>0</v>
-      </c>
-      <c r="I416" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J416" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A417" s="1">
-        <v>570001</v>
-      </c>
-      <c r="B417" s="1">
-        <v>57</v>
-      </c>
-      <c r="D417" s="1">
-        <v>0</v>
-      </c>
-      <c r="E417" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F417" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G417" s="1">
-        <v>0</v>
-      </c>
-      <c r="H417" s="2">
-        <v>0</v>
-      </c>
-      <c r="I417" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J417" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A418" s="1">
-        <v>580001</v>
-      </c>
-      <c r="B418" s="1">
-        <v>58</v>
-      </c>
-      <c r="D418" s="1">
-        <v>0</v>
-      </c>
-      <c r="E418" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F418" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G418" s="1">
-        <v>0</v>
-      </c>
-      <c r="H418" s="2">
-        <v>0</v>
-      </c>
-      <c r="I418" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J418" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A419" s="1">
-        <v>590001</v>
-      </c>
-      <c r="B419" s="1">
-        <v>59</v>
-      </c>
-      <c r="D419" s="1">
-        <v>0</v>
-      </c>
-      <c r="E419" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F419" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G419" s="1">
-        <v>0</v>
-      </c>
-      <c r="H419" s="2">
-        <v>0</v>
-      </c>
-      <c r="I419" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J419" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A420" s="1">
-        <v>600001</v>
-      </c>
-      <c r="B420" s="1">
-        <v>60</v>
-      </c>
-      <c r="D420" s="1">
-        <v>0</v>
-      </c>
-      <c r="E420" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F420" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G420" s="1">
-        <v>0</v>
-      </c>
-      <c r="H420" s="2">
-        <v>0</v>
-      </c>
-      <c r="I420" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J420" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A421" s="1">
-        <v>610001</v>
-      </c>
-      <c r="B421" s="1">
-        <v>61</v>
-      </c>
-      <c r="D421" s="1">
-        <v>0</v>
-      </c>
-      <c r="E421" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F421" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G421" s="1">
-        <v>0</v>
-      </c>
-      <c r="H421" s="2">
-        <v>0</v>
-      </c>
-      <c r="I421" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J421" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A422" s="1">
-        <v>620001</v>
-      </c>
-      <c r="B422" s="1">
-        <v>62</v>
-      </c>
-      <c r="D422" s="1">
-        <v>0</v>
-      </c>
-      <c r="E422" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F422" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G422" s="1">
-        <v>0</v>
-      </c>
-      <c r="H422" s="2">
-        <v>0</v>
-      </c>
-      <c r="I422" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J422" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A423" s="1">
-        <v>630001</v>
-      </c>
-      <c r="B423" s="1">
-        <v>63</v>
-      </c>
-      <c r="D423" s="1">
-        <v>0</v>
-      </c>
-      <c r="E423" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F423" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G423" s="1">
-        <v>0</v>
-      </c>
-      <c r="H423" s="2">
-        <v>0</v>
-      </c>
-      <c r="I423" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J423" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A424" s="1">
-        <v>640001</v>
-      </c>
-      <c r="B424" s="1">
-        <v>64</v>
-      </c>
-      <c r="D424" s="1">
-        <v>0</v>
-      </c>
-      <c r="E424" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F424" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G424" s="1">
-        <v>0</v>
-      </c>
-      <c r="H424" s="2">
-        <v>0</v>
-      </c>
-      <c r="I424" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J424" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A425" s="1">
-        <v>650001</v>
-      </c>
-      <c r="B425" s="1">
-        <v>65</v>
-      </c>
-      <c r="D425" s="1">
-        <v>0</v>
-      </c>
-      <c r="E425" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F425" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G425" s="1">
-        <v>0</v>
-      </c>
-      <c r="H425" s="2">
-        <v>0</v>
-      </c>
-      <c r="I425" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J425" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A426" s="1">
-        <v>660001</v>
-      </c>
-      <c r="B426" s="1">
-        <v>66</v>
-      </c>
-      <c r="D426" s="1">
-        <v>0</v>
-      </c>
-      <c r="E426" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F426" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G426" s="1">
-        <v>0</v>
-      </c>
-      <c r="H426" s="2">
-        <v>0</v>
-      </c>
-      <c r="I426" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J426" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A427" s="1">
-        <v>670001</v>
-      </c>
-      <c r="B427" s="1">
-        <v>67</v>
-      </c>
-      <c r="D427" s="1">
-        <v>0</v>
-      </c>
-      <c r="E427" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F427" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G427" s="1">
-        <v>0</v>
-      </c>
-      <c r="H427" s="2">
-        <v>0</v>
-      </c>
-      <c r="I427" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J427" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A428" s="1">
-        <v>680001</v>
-      </c>
-      <c r="B428" s="1">
-        <v>68</v>
-      </c>
-      <c r="D428" s="1">
-        <v>0</v>
-      </c>
-      <c r="E428" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F428" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G428" s="1">
-        <v>0</v>
-      </c>
-      <c r="H428" s="2">
-        <v>0</v>
-      </c>
-      <c r="I428" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J428" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A429" s="1">
-        <v>690001</v>
-      </c>
-      <c r="B429" s="1">
-        <v>69</v>
-      </c>
-      <c r="D429" s="1">
-        <v>0</v>
-      </c>
-      <c r="E429" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F429" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G429" s="1">
-        <v>0</v>
-      </c>
-      <c r="H429" s="2">
-        <v>0</v>
-      </c>
-      <c r="I429" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J429" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A430" s="1">
-        <v>700001</v>
-      </c>
-      <c r="B430" s="1">
-        <v>70</v>
-      </c>
-      <c r="D430" s="1">
-        <v>0</v>
-      </c>
-      <c r="E430" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F430" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G430" s="1">
-        <v>0</v>
-      </c>
-      <c r="H430" s="2">
-        <v>0</v>
-      </c>
-      <c r="I430" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J430" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A431" s="1">
-        <v>710001</v>
-      </c>
-      <c r="B431" s="1">
-        <v>71</v>
-      </c>
-      <c r="D431" s="1">
-        <v>0</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F431" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G431" s="1">
-        <v>0</v>
-      </c>
-      <c r="H431" s="2">
-        <v>0</v>
-      </c>
-      <c r="I431" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J431" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A432" s="1">
-        <v>720001</v>
-      </c>
-      <c r="B432" s="1">
-        <v>72</v>
-      </c>
-      <c r="D432" s="1">
-        <v>0</v>
-      </c>
-      <c r="E432" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F432" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G432" s="1">
-        <v>0</v>
-      </c>
-      <c r="H432" s="2">
-        <v>0</v>
-      </c>
-      <c r="I432" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J432" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A433" s="1">
-        <v>730001</v>
-      </c>
-      <c r="B433" s="1">
-        <v>73</v>
-      </c>
-      <c r="D433" s="1">
-        <v>0</v>
-      </c>
-      <c r="E433" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F433" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G433" s="1">
-        <v>0</v>
-      </c>
-      <c r="H433" s="2">
-        <v>0</v>
-      </c>
-      <c r="I433" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J433" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A434" s="1">
-        <v>740001</v>
-      </c>
-      <c r="B434" s="1">
-        <v>74</v>
-      </c>
-      <c r="D434" s="1">
-        <v>0</v>
-      </c>
-      <c r="E434" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F434" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G434" s="1">
-        <v>0</v>
-      </c>
-      <c r="H434" s="2">
-        <v>0</v>
-      </c>
-      <c r="I434" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J434" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A435" s="1">
-        <v>750001</v>
-      </c>
-      <c r="B435" s="1">
-        <v>75</v>
-      </c>
-      <c r="D435" s="1">
-        <v>0</v>
-      </c>
-      <c r="E435" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F435" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G435" s="1">
-        <v>0</v>
-      </c>
-      <c r="H435" s="2">
-        <v>0</v>
-      </c>
-      <c r="I435" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J435" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A436" s="1">
-        <v>760001</v>
-      </c>
-      <c r="B436" s="1">
-        <v>76</v>
-      </c>
-      <c r="D436" s="1">
-        <v>0</v>
-      </c>
-      <c r="E436" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F436" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G436" s="1">
-        <v>0</v>
-      </c>
-      <c r="H436" s="2">
-        <v>0</v>
-      </c>
-      <c r="I436" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J436" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A437" s="1">
-        <v>770001</v>
-      </c>
-      <c r="B437" s="1">
-        <v>77</v>
-      </c>
-      <c r="D437" s="1">
-        <v>0</v>
-      </c>
-      <c r="E437" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F437" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G437" s="1">
-        <v>0</v>
-      </c>
-      <c r="H437" s="2">
-        <v>0</v>
-      </c>
-      <c r="I437" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J437" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A438" s="1">
-        <v>780001</v>
-      </c>
-      <c r="B438" s="1">
-        <v>78</v>
-      </c>
-      <c r="D438" s="1">
-        <v>0</v>
-      </c>
-      <c r="E438" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F438" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G438" s="1">
-        <v>0</v>
-      </c>
-      <c r="H438" s="2">
-        <v>0</v>
-      </c>
-      <c r="I438" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J438" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A439" s="1">
-        <v>790001</v>
-      </c>
-      <c r="B439" s="1">
-        <v>79</v>
-      </c>
-      <c r="D439" s="1">
-        <v>0</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F439" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G439" s="1">
-        <v>0</v>
-      </c>
-      <c r="H439" s="2">
-        <v>0</v>
-      </c>
-      <c r="I439" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J439" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A440" s="1">
-        <v>800001</v>
-      </c>
-      <c r="B440" s="1">
-        <v>80</v>
-      </c>
-      <c r="D440" s="1">
-        <v>0</v>
-      </c>
-      <c r="E440" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F440" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G440" s="1">
-        <v>0</v>
-      </c>
-      <c r="H440" s="2">
-        <v>0</v>
-      </c>
-      <c r="I440" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J440" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A441" s="1">
-        <v>810001</v>
-      </c>
-      <c r="B441" s="1">
-        <v>81</v>
-      </c>
-      <c r="D441" s="1">
-        <v>0</v>
-      </c>
-      <c r="E441" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F441" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G441" s="1">
-        <v>0</v>
-      </c>
-      <c r="H441" s="2">
-        <v>0</v>
-      </c>
-      <c r="I441" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J441" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A442" s="1">
-        <v>820001</v>
-      </c>
-      <c r="B442" s="1">
-        <v>82</v>
-      </c>
-      <c r="D442" s="1">
-        <v>0</v>
-      </c>
-      <c r="E442" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F442" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G442" s="1">
-        <v>0</v>
-      </c>
-      <c r="H442" s="2">
-        <v>0</v>
-      </c>
-      <c r="I442" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J442" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A443" s="1">
-        <v>830001</v>
-      </c>
-      <c r="B443" s="1">
-        <v>83</v>
-      </c>
-      <c r="D443" s="1">
-        <v>0</v>
-      </c>
-      <c r="E443" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F443" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G443" s="1">
-        <v>0</v>
-      </c>
-      <c r="H443" s="2">
-        <v>0</v>
-      </c>
-      <c r="I443" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J443" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A444" s="1">
-        <v>840001</v>
-      </c>
-      <c r="B444" s="1">
-        <v>84</v>
-      </c>
-      <c r="D444" s="1">
-        <v>0</v>
-      </c>
-      <c r="E444" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F444" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G444" s="1">
-        <v>0</v>
-      </c>
-      <c r="H444" s="2">
-        <v>0</v>
-      </c>
-      <c r="I444" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J444" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A445" s="1">
-        <v>850001</v>
-      </c>
-      <c r="B445" s="1">
-        <v>85</v>
-      </c>
-      <c r="D445" s="1">
-        <v>0</v>
-      </c>
-      <c r="E445" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F445" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G445" s="1">
-        <v>0</v>
-      </c>
-      <c r="H445" s="2">
-        <v>0</v>
-      </c>
-      <c r="I445" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J445" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A446" s="1">
-        <v>860001</v>
-      </c>
-      <c r="B446" s="1">
-        <v>86</v>
-      </c>
-      <c r="D446" s="1">
-        <v>0</v>
-      </c>
-      <c r="E446" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F446" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G446" s="1">
-        <v>0</v>
-      </c>
-      <c r="H446" s="2">
-        <v>0</v>
-      </c>
-      <c r="I446" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J446" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A447" s="1">
-        <v>870001</v>
-      </c>
-      <c r="B447" s="1">
-        <v>87</v>
-      </c>
-      <c r="D447" s="1">
-        <v>0</v>
-      </c>
-      <c r="E447" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F447" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G447" s="1">
-        <v>0</v>
-      </c>
-      <c r="H447" s="2">
-        <v>0</v>
-      </c>
-      <c r="I447" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J447" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A448" s="1">
-        <v>880001</v>
-      </c>
-      <c r="B448" s="1">
-        <v>88</v>
-      </c>
-      <c r="D448" s="1">
-        <v>0</v>
-      </c>
-      <c r="E448" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F448" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G448" s="1">
-        <v>0</v>
-      </c>
-      <c r="H448" s="2">
-        <v>0</v>
-      </c>
-      <c r="I448" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J448" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A449" s="1">
-        <v>890001</v>
-      </c>
-      <c r="B449" s="1">
-        <v>89</v>
-      </c>
-      <c r="D449" s="1">
-        <v>0</v>
-      </c>
-      <c r="E449" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F449" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G449" s="1">
-        <v>0</v>
-      </c>
-      <c r="H449" s="2">
-        <v>0</v>
-      </c>
-      <c r="I449" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J449" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A450" s="1">
-        <v>900001</v>
-      </c>
-      <c r="B450" s="1">
-        <v>90</v>
-      </c>
-      <c r="D450" s="1">
-        <v>0</v>
-      </c>
-      <c r="E450" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F450" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G450" s="1">
-        <v>0</v>
-      </c>
-      <c r="H450" s="2">
-        <v>0</v>
-      </c>
-      <c r="I450" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J450" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A451" s="1">
-        <v>910001</v>
-      </c>
-      <c r="B451" s="1">
-        <v>91</v>
-      </c>
-      <c r="D451" s="1">
-        <v>0</v>
-      </c>
-      <c r="E451" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F451" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G451" s="1">
-        <v>0</v>
-      </c>
-      <c r="H451" s="2">
-        <v>0</v>
-      </c>
-      <c r="I451" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J451" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A452" s="1">
-        <v>920001</v>
-      </c>
-      <c r="B452" s="1">
-        <v>92</v>
-      </c>
-      <c r="D452" s="1">
-        <v>0</v>
-      </c>
-      <c r="E452" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F452" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G452" s="1">
-        <v>0</v>
-      </c>
-      <c r="H452" s="2">
-        <v>0</v>
-      </c>
-      <c r="I452" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J452" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A453" s="1">
-        <v>930001</v>
-      </c>
-      <c r="B453" s="1">
-        <v>93</v>
-      </c>
-      <c r="D453" s="1">
-        <v>0</v>
-      </c>
-      <c r="E453" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F453" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G453" s="1">
-        <v>0</v>
-      </c>
-      <c r="H453" s="2">
-        <v>0</v>
-      </c>
-      <c r="I453" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J453" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A454" s="1">
-        <v>940001</v>
-      </c>
-      <c r="B454" s="1">
-        <v>94</v>
-      </c>
-      <c r="D454" s="1">
-        <v>0</v>
-      </c>
-      <c r="E454" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F454" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G454" s="1">
-        <v>0</v>
-      </c>
-      <c r="H454" s="2">
-        <v>0</v>
-      </c>
-      <c r="I454" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J454" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A455" s="1">
-        <v>950001</v>
-      </c>
-      <c r="B455" s="1">
-        <v>95</v>
-      </c>
-      <c r="D455" s="1">
-        <v>0</v>
-      </c>
-      <c r="E455" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F455" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G455" s="1">
-        <v>0</v>
-      </c>
-      <c r="H455" s="2">
-        <v>0</v>
-      </c>
-      <c r="I455" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J455" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A456" s="1">
-        <v>960001</v>
-      </c>
-      <c r="B456" s="1">
-        <v>96</v>
-      </c>
-      <c r="D456" s="1">
-        <v>0</v>
-      </c>
-      <c r="E456" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F456" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G456" s="1">
-        <v>0</v>
-      </c>
-      <c r="H456" s="2">
-        <v>0</v>
-      </c>
-      <c r="I456" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J456" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A457" s="1">
-        <v>970001</v>
-      </c>
-      <c r="B457" s="1">
-        <v>97</v>
-      </c>
-      <c r="D457" s="1">
-        <v>0</v>
-      </c>
-      <c r="E457" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F457" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G457" s="1">
-        <v>0</v>
-      </c>
-      <c r="H457" s="2">
-        <v>0</v>
-      </c>
-      <c r="I457" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J457" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A458" s="1">
-        <v>980001</v>
-      </c>
-      <c r="B458" s="1">
-        <v>98</v>
-      </c>
-      <c r="D458" s="1">
-        <v>0</v>
-      </c>
-      <c r="E458" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F458" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G458" s="1">
-        <v>0</v>
-      </c>
-      <c r="H458" s="2">
-        <v>0</v>
-      </c>
-      <c r="I458" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J458" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A459" s="1">
-        <v>990001</v>
-      </c>
-      <c r="B459" s="1">
-        <v>99</v>
-      </c>
-      <c r="D459" s="1">
-        <v>0</v>
-      </c>
-      <c r="E459" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F459" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G459" s="1">
-        <v>0</v>
-      </c>
-      <c r="H459" s="2">
-        <v>0</v>
-      </c>
-      <c r="I459" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J459" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A460" s="1">
-        <v>1000001</v>
-      </c>
-      <c r="B460" s="1">
-        <v>100</v>
-      </c>
-      <c r="D460" s="1">
-        <v>0</v>
-      </c>
-      <c r="E460" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F460" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G460" s="1">
-        <v>0</v>
-      </c>
-      <c r="H460" s="2">
-        <v>0</v>
-      </c>
-      <c r="I460" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J460" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A461" s="1">
-        <v>1010001</v>
-      </c>
-      <c r="B461" s="1">
-        <v>101</v>
-      </c>
-      <c r="D461" s="1">
-        <v>0</v>
-      </c>
-      <c r="E461" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F461" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G461" s="1">
-        <v>0</v>
-      </c>
-      <c r="H461" s="2">
-        <v>0</v>
-      </c>
-      <c r="I461" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J461" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A462" s="1">
-        <v>1020001</v>
-      </c>
-      <c r="B462" s="1">
-        <v>102</v>
-      </c>
-      <c r="D462" s="1">
-        <v>0</v>
-      </c>
-      <c r="E462" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F462" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G462" s="1">
-        <v>0</v>
-      </c>
-      <c r="H462" s="2">
-        <v>0</v>
-      </c>
-      <c r="I462" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J462" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A463" s="1">
-        <v>1030001</v>
-      </c>
-      <c r="B463" s="1">
-        <v>103</v>
-      </c>
-      <c r="D463" s="1">
-        <v>0</v>
-      </c>
-      <c r="E463" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F463" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G463" s="1">
-        <v>0</v>
-      </c>
-      <c r="H463" s="2">
-        <v>0</v>
-      </c>
-      <c r="I463" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J463" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A464" s="1">
-        <v>1040001</v>
-      </c>
-      <c r="B464" s="1">
-        <v>104</v>
-      </c>
-      <c r="D464" s="1">
-        <v>0</v>
-      </c>
-      <c r="E464" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F464" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G464" s="1">
-        <v>0</v>
-      </c>
-      <c r="H464" s="2">
-        <v>0</v>
-      </c>
-      <c r="I464" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J464" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A465" s="1">
-        <v>1050001</v>
-      </c>
-      <c r="B465" s="1">
-        <v>105</v>
-      </c>
-      <c r="D465" s="1">
-        <v>0</v>
-      </c>
-      <c r="E465" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F465" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G465" s="1">
-        <v>0</v>
-      </c>
-      <c r="H465" s="2">
-        <v>0</v>
-      </c>
-      <c r="I465" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J465" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A466" s="1">
-        <v>1060001</v>
-      </c>
-      <c r="B466" s="1">
-        <v>106</v>
-      </c>
-      <c r="D466" s="1">
-        <v>0</v>
-      </c>
-      <c r="E466" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F466" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G466" s="1">
-        <v>0</v>
-      </c>
-      <c r="H466" s="2">
-        <v>0</v>
-      </c>
-      <c r="I466" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J466" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A467" s="1">
-        <v>1070001</v>
-      </c>
-      <c r="B467" s="1">
-        <v>107</v>
-      </c>
-      <c r="D467" s="1">
-        <v>0</v>
-      </c>
-      <c r="E467" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F467" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G467" s="1">
-        <v>0</v>
-      </c>
-      <c r="H467" s="2">
-        <v>0</v>
-      </c>
-      <c r="I467" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J467" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A468" s="1">
-        <v>1080001</v>
-      </c>
-      <c r="B468" s="1">
-        <v>108</v>
-      </c>
-      <c r="D468" s="1">
-        <v>0</v>
-      </c>
-      <c r="E468" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F468" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G468" s="1">
-        <v>0</v>
-      </c>
-      <c r="H468" s="2">
-        <v>0</v>
-      </c>
-      <c r="I468" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J468" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A469" s="1">
-        <v>1090001</v>
-      </c>
-      <c r="B469" s="1">
-        <v>109</v>
-      </c>
-      <c r="D469" s="1">
-        <v>0</v>
-      </c>
-      <c r="E469" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F469" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G469" s="1">
-        <v>0</v>
-      </c>
-      <c r="H469" s="2">
-        <v>0</v>
-      </c>
-      <c r="I469" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J469" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A470" s="1">
-        <v>1100001</v>
-      </c>
-      <c r="B470" s="1">
-        <v>110</v>
-      </c>
-      <c r="D470" s="1">
-        <v>0</v>
-      </c>
-      <c r="E470" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F470" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G470" s="1">
-        <v>0</v>
-      </c>
-      <c r="H470" s="2">
-        <v>0</v>
-      </c>
-      <c r="I470" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J470" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A471" s="1">
-        <v>1110001</v>
-      </c>
-      <c r="B471" s="1">
-        <v>111</v>
-      </c>
-      <c r="D471" s="1">
-        <v>0</v>
-      </c>
-      <c r="E471" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F471" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G471" s="1">
-        <v>0</v>
-      </c>
-      <c r="H471" s="2">
-        <v>0</v>
-      </c>
-      <c r="I471" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J471" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A472" s="1">
-        <v>1120001</v>
-      </c>
-      <c r="B472" s="1">
-        <v>112</v>
-      </c>
-      <c r="D472" s="1">
-        <v>0</v>
-      </c>
-      <c r="E472" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F472" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G472" s="1">
-        <v>0</v>
-      </c>
-      <c r="H472" s="2">
-        <v>0</v>
-      </c>
-      <c r="I472" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J472" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A473" s="1">
-        <v>1130001</v>
-      </c>
-      <c r="B473" s="1">
-        <v>113</v>
-      </c>
-      <c r="D473" s="1">
-        <v>0</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F473" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G473" s="1">
-        <v>0</v>
-      </c>
-      <c r="H473" s="2">
-        <v>0</v>
-      </c>
-      <c r="I473" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J473" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A474" s="1">
-        <v>1140001</v>
-      </c>
-      <c r="B474" s="1">
-        <v>114</v>
-      </c>
-      <c r="D474" s="1">
-        <v>0</v>
-      </c>
-      <c r="E474" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F474" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G474" s="1">
-        <v>0</v>
-      </c>
-      <c r="H474" s="2">
-        <v>0</v>
-      </c>
-      <c r="I474" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J474" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A475" s="1">
-        <v>1150001</v>
-      </c>
-      <c r="B475" s="1">
-        <v>115</v>
-      </c>
-      <c r="D475" s="1">
-        <v>0</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F475" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G475" s="1">
-        <v>0</v>
-      </c>
-      <c r="H475" s="2">
-        <v>0</v>
-      </c>
-      <c r="I475" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J475" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A476" s="1">
-        <v>1160001</v>
-      </c>
-      <c r="B476" s="1">
-        <v>116</v>
-      </c>
-      <c r="D476" s="1">
-        <v>0</v>
-      </c>
-      <c r="E476" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F476" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G476" s="1">
-        <v>0</v>
-      </c>
-      <c r="H476" s="2">
-        <v>0</v>
-      </c>
-      <c r="I476" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J476" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A477" s="1">
-        <v>1170001</v>
-      </c>
-      <c r="B477" s="1">
-        <v>117</v>
-      </c>
-      <c r="D477" s="1">
-        <v>0</v>
-      </c>
-      <c r="E477" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F477" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G477" s="1">
-        <v>0</v>
-      </c>
-      <c r="H477" s="2">
-        <v>0</v>
-      </c>
-      <c r="I477" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J477" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A478" s="1">
-        <v>1180001</v>
-      </c>
-      <c r="B478" s="1">
-        <v>118</v>
-      </c>
-      <c r="D478" s="1">
-        <v>0</v>
-      </c>
-      <c r="E478" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F478" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G478" s="1">
-        <v>0</v>
-      </c>
-      <c r="H478" s="2">
-        <v>0</v>
-      </c>
-      <c r="I478" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J478" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A479" s="1">
-        <v>1190001</v>
-      </c>
-      <c r="B479" s="1">
-        <v>119</v>
-      </c>
-      <c r="D479" s="1">
-        <v>0</v>
-      </c>
-      <c r="E479" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F479" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G479" s="1">
-        <v>0</v>
-      </c>
-      <c r="H479" s="2">
-        <v>0</v>
-      </c>
-      <c r="I479" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J479" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A480" s="1">
-        <v>1200001</v>
-      </c>
-      <c r="B480" s="1">
-        <v>120</v>
-      </c>
-      <c r="D480" s="1">
-        <v>0</v>
-      </c>
-      <c r="E480" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F480" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G480" s="1">
-        <v>0</v>
-      </c>
-      <c r="H480" s="2">
-        <v>0</v>
-      </c>
-      <c r="I480" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J480" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A481" s="1">
-        <v>1210001</v>
-      </c>
-      <c r="B481" s="1">
-        <v>121</v>
-      </c>
-      <c r="D481" s="1">
-        <v>0</v>
-      </c>
-      <c r="E481" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F481" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G481" s="1">
-        <v>0</v>
-      </c>
-      <c r="H481" s="2">
-        <v>0</v>
-      </c>
-      <c r="I481" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J481" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A482" s="1">
-        <v>1220001</v>
-      </c>
-      <c r="B482" s="1">
-        <v>122</v>
-      </c>
-      <c r="D482" s="1">
-        <v>0</v>
-      </c>
-      <c r="E482" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F482" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G482" s="1">
-        <v>0</v>
-      </c>
-      <c r="H482" s="2">
-        <v>0</v>
-      </c>
-      <c r="I482" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J482" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A483" s="1">
-        <v>1230001</v>
-      </c>
-      <c r="B483" s="1">
-        <v>123</v>
-      </c>
-      <c r="D483" s="1">
-        <v>0</v>
-      </c>
-      <c r="E483" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F483" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G483" s="1">
-        <v>0</v>
-      </c>
-      <c r="H483" s="2">
-        <v>0</v>
-      </c>
-      <c r="I483" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J483" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A484" s="1">
-        <v>1240001</v>
-      </c>
-      <c r="B484" s="1">
-        <v>124</v>
-      </c>
-      <c r="D484" s="1">
-        <v>0</v>
-      </c>
-      <c r="E484" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F484" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G484" s="1">
-        <v>0</v>
-      </c>
-      <c r="H484" s="2">
-        <v>0</v>
-      </c>
-      <c r="I484" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J484" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A485" s="1">
-        <v>1250001</v>
-      </c>
-      <c r="B485" s="1">
-        <v>125</v>
-      </c>
-      <c r="D485" s="1">
-        <v>0</v>
-      </c>
-      <c r="E485" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F485" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G485" s="1">
-        <v>0</v>
-      </c>
-      <c r="H485" s="2">
-        <v>0</v>
-      </c>
-      <c r="I485" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J485" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A486" s="1">
-        <v>1260001</v>
-      </c>
-      <c r="B486" s="1">
-        <v>126</v>
-      </c>
-      <c r="D486" s="1">
-        <v>0</v>
-      </c>
-      <c r="E486" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F486" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G486" s="1">
-        <v>0</v>
-      </c>
-      <c r="H486" s="2">
-        <v>0</v>
-      </c>
-      <c r="I486" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J486" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A487" s="1">
-        <v>1270001</v>
-      </c>
-      <c r="B487" s="1">
-        <v>127</v>
-      </c>
-      <c r="D487" s="1">
-        <v>0</v>
-      </c>
-      <c r="E487" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F487" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G487" s="1">
-        <v>0</v>
-      </c>
-      <c r="H487" s="2">
-        <v>0</v>
-      </c>
-      <c r="I487" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J487" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A488" s="1">
-        <v>1280001</v>
-      </c>
-      <c r="B488" s="1">
-        <v>128</v>
-      </c>
-      <c r="D488" s="1">
-        <v>0</v>
-      </c>
-      <c r="E488" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F488" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G488" s="1">
-        <v>0</v>
-      </c>
-      <c r="H488" s="2">
-        <v>0</v>
-      </c>
-      <c r="I488" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J488" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A489" s="1">
-        <v>1290001</v>
-      </c>
-      <c r="B489" s="1">
-        <v>129</v>
-      </c>
-      <c r="D489" s="1">
-        <v>0</v>
-      </c>
-      <c r="E489" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F489" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G489" s="1">
-        <v>0</v>
-      </c>
-      <c r="H489" s="2">
-        <v>0</v>
-      </c>
-      <c r="I489" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J489" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A490" s="1">
-        <v>1300001</v>
-      </c>
-      <c r="B490" s="1">
-        <v>130</v>
-      </c>
-      <c r="D490" s="1">
-        <v>0</v>
-      </c>
-      <c r="E490" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F490" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G490" s="1">
-        <v>0</v>
-      </c>
-      <c r="H490" s="2">
-        <v>0</v>
-      </c>
-      <c r="I490" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J490" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A491" s="1">
-        <v>1310001</v>
-      </c>
-      <c r="B491" s="1">
-        <v>131</v>
-      </c>
-      <c r="D491" s="1">
-        <v>0</v>
-      </c>
-      <c r="E491" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F491" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G491" s="1">
-        <v>0</v>
-      </c>
-      <c r="H491" s="2">
-        <v>0</v>
-      </c>
-      <c r="I491" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J491" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A492" s="1">
-        <v>1320001</v>
-      </c>
-      <c r="B492" s="1">
-        <v>132</v>
-      </c>
-      <c r="D492" s="1">
-        <v>0</v>
-      </c>
-      <c r="E492" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F492" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G492" s="1">
-        <v>0</v>
-      </c>
-      <c r="H492" s="2">
-        <v>0</v>
-      </c>
-      <c r="I492" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J492" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A493" s="1">
-        <v>1330001</v>
-      </c>
-      <c r="B493" s="1">
-        <v>133</v>
-      </c>
-      <c r="D493" s="1">
-        <v>0</v>
-      </c>
-      <c r="E493" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F493" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G493" s="1">
-        <v>0</v>
-      </c>
-      <c r="H493" s="2">
-        <v>0</v>
-      </c>
-      <c r="I493" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J493" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A494" s="1">
-        <v>1340001</v>
-      </c>
-      <c r="B494" s="1">
-        <v>134</v>
-      </c>
-      <c r="D494" s="1">
-        <v>0</v>
-      </c>
-      <c r="E494" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F494" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G494" s="1">
-        <v>0</v>
-      </c>
-      <c r="H494" s="2">
-        <v>0</v>
-      </c>
-      <c r="I494" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J494" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A495" s="1">
-        <v>1350001</v>
-      </c>
-      <c r="B495" s="1">
-        <v>135</v>
-      </c>
-      <c r="D495" s="1">
-        <v>0</v>
-      </c>
-      <c r="E495" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F495" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G495" s="1">
-        <v>0</v>
-      </c>
-      <c r="H495" s="2">
-        <v>0</v>
-      </c>
-      <c r="I495" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J495" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A496" s="1">
-        <v>1360001</v>
-      </c>
-      <c r="B496" s="1">
-        <v>136</v>
-      </c>
-      <c r="D496" s="1">
-        <v>0</v>
-      </c>
-      <c r="E496" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F496" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G496" s="1">
-        <v>0</v>
-      </c>
-      <c r="H496" s="2">
-        <v>0</v>
-      </c>
-      <c r="I496" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J496" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A497" s="1">
-        <v>1370001</v>
-      </c>
-      <c r="B497" s="1">
-        <v>137</v>
-      </c>
-      <c r="D497" s="1">
-        <v>0</v>
-      </c>
-      <c r="E497" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F497" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G497" s="1">
-        <v>0</v>
-      </c>
-      <c r="H497" s="2">
-        <v>0</v>
-      </c>
-      <c r="I497" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J497" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A498" s="1">
-        <v>1380001</v>
-      </c>
-      <c r="B498" s="1">
-        <v>138</v>
-      </c>
-      <c r="D498" s="1">
-        <v>0</v>
-      </c>
-      <c r="E498" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F498" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G498" s="1">
-        <v>0</v>
-      </c>
-      <c r="H498" s="2">
-        <v>0</v>
-      </c>
-      <c r="I498" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J498" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A499" s="1">
-        <v>1390001</v>
-      </c>
-      <c r="B499" s="1">
-        <v>139</v>
-      </c>
-      <c r="D499" s="1">
-        <v>0</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G499" s="1">
-        <v>0</v>
-      </c>
-      <c r="H499" s="2">
-        <v>0</v>
-      </c>
-      <c r="I499" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J499" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A500" s="1">
-        <v>1400001</v>
-      </c>
-      <c r="B500" s="1">
-        <v>140</v>
-      </c>
-      <c r="D500" s="1">
-        <v>0</v>
-      </c>
-      <c r="E500" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F500" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G500" s="1">
-        <v>0</v>
-      </c>
-      <c r="H500" s="2">
-        <v>0</v>
-      </c>
-      <c r="I500" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J500" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A501" s="1">
-        <v>1410001</v>
-      </c>
-      <c r="B501" s="1">
-        <v>141</v>
-      </c>
-      <c r="D501" s="1">
-        <v>0</v>
-      </c>
-      <c r="E501" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F501" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G501" s="1">
-        <v>0</v>
-      </c>
-      <c r="H501" s="2">
-        <v>0</v>
-      </c>
-      <c r="I501" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J501" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A502" s="1">
-        <v>1420001</v>
-      </c>
-      <c r="B502" s="1">
-        <v>142</v>
-      </c>
-      <c r="D502" s="1">
-        <v>0</v>
-      </c>
-      <c r="E502" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F502" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G502" s="1">
-        <v>0</v>
-      </c>
-      <c r="H502" s="2">
-        <v>0</v>
-      </c>
-      <c r="I502" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J502" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A503" s="1">
-        <v>1430001</v>
-      </c>
-      <c r="B503" s="1">
-        <v>143</v>
-      </c>
-      <c r="D503" s="1">
-        <v>0</v>
-      </c>
-      <c r="E503" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F503" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G503" s="1">
-        <v>0</v>
-      </c>
-      <c r="H503" s="2">
-        <v>0</v>
-      </c>
-      <c r="I503" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J503" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A504" s="1">
-        <v>1440001</v>
-      </c>
-      <c r="B504" s="1">
-        <v>144</v>
-      </c>
-      <c r="D504" s="1">
-        <v>0</v>
-      </c>
-      <c r="E504" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F504" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G504" s="1">
-        <v>0</v>
-      </c>
-      <c r="H504" s="2">
-        <v>0</v>
-      </c>
-      <c r="I504" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J504" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A505" s="1">
-        <v>1450001</v>
-      </c>
-      <c r="B505" s="1">
-        <v>145</v>
-      </c>
-      <c r="D505" s="1">
-        <v>0</v>
-      </c>
-      <c r="E505" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F505" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G505" s="1">
-        <v>0</v>
-      </c>
-      <c r="H505" s="2">
-        <v>0</v>
-      </c>
-      <c r="I505" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J505" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A506" s="1">
-        <v>1460001</v>
-      </c>
-      <c r="B506" s="1">
-        <v>146</v>
-      </c>
-      <c r="D506" s="1">
-        <v>0</v>
-      </c>
-      <c r="E506" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F506" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G506" s="1">
-        <v>0</v>
-      </c>
-      <c r="H506" s="2">
-        <v>0</v>
-      </c>
-      <c r="I506" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J506" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A507" s="1">
-        <v>1470001</v>
-      </c>
-      <c r="B507" s="1">
-        <v>147</v>
-      </c>
-      <c r="D507" s="1">
-        <v>0</v>
-      </c>
-      <c r="E507" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F507" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G507" s="1">
-        <v>0</v>
-      </c>
-      <c r="H507" s="2">
-        <v>0</v>
-      </c>
-      <c r="I507" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J507" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A508" s="1">
-        <v>1480001</v>
-      </c>
-      <c r="B508" s="1">
-        <v>148</v>
-      </c>
-      <c r="D508" s="1">
-        <v>0</v>
-      </c>
-      <c r="E508" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F508" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G508" s="1">
-        <v>0</v>
-      </c>
-      <c r="H508" s="2">
-        <v>0</v>
-      </c>
-      <c r="I508" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J508" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A509" s="1">
-        <v>1490001</v>
-      </c>
-      <c r="B509" s="1">
-        <v>149</v>
-      </c>
-      <c r="D509" s="1">
-        <v>0</v>
-      </c>
-      <c r="E509" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F509" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G509" s="1">
-        <v>0</v>
-      </c>
-      <c r="H509" s="2">
-        <v>0</v>
-      </c>
-      <c r="I509" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J509" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A510" s="1">
-        <v>1500001</v>
-      </c>
-      <c r="B510" s="1">
-        <v>150</v>
-      </c>
-      <c r="D510" s="1">
-        <v>0</v>
-      </c>
-      <c r="E510" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F510" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G510" s="1">
-        <v>0</v>
-      </c>
-      <c r="H510" s="2">
-        <v>0</v>
-      </c>
-      <c r="I510" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J510" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A511" s="1">
-        <v>1510001</v>
-      </c>
-      <c r="B511" s="1">
-        <v>151</v>
-      </c>
-      <c r="D511" s="1">
-        <v>0</v>
-      </c>
-      <c r="E511" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F511" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G511" s="1">
-        <v>0</v>
-      </c>
-      <c r="H511" s="2">
-        <v>0</v>
-      </c>
-      <c r="I511" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J511" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A512" s="1">
-        <v>1520001</v>
-      </c>
-      <c r="B512" s="1">
-        <v>152</v>
-      </c>
-      <c r="D512" s="1">
-        <v>0</v>
-      </c>
-      <c r="E512" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F512" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G512" s="1">
-        <v>0</v>
-      </c>
-      <c r="H512" s="2">
-        <v>0</v>
-      </c>
-      <c r="I512" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J512" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A513" s="1">
-        <v>1530001</v>
-      </c>
-      <c r="B513" s="1">
-        <v>153</v>
-      </c>
-      <c r="D513" s="1">
-        <v>0</v>
-      </c>
-      <c r="E513" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F513" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G513" s="1">
-        <v>0</v>
-      </c>
-      <c r="H513" s="2">
-        <v>0</v>
-      </c>
-      <c r="I513" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J513" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A514" s="1">
-        <v>1540001</v>
-      </c>
-      <c r="B514" s="1">
-        <v>154</v>
-      </c>
-      <c r="D514" s="1">
-        <v>0</v>
-      </c>
-      <c r="E514" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F514" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G514" s="1">
-        <v>0</v>
-      </c>
-      <c r="H514" s="2">
-        <v>0</v>
-      </c>
-      <c r="I514" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J514" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A515" s="1">
-        <v>1550001</v>
-      </c>
-      <c r="B515" s="1">
-        <v>155</v>
-      </c>
-      <c r="D515" s="1">
-        <v>0</v>
-      </c>
-      <c r="E515" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F515" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G515" s="1">
-        <v>0</v>
-      </c>
-      <c r="H515" s="2">
-        <v>0</v>
-      </c>
-      <c r="I515" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J515" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A516" s="1">
-        <v>1560001</v>
-      </c>
-      <c r="B516" s="1">
-        <v>156</v>
-      </c>
-      <c r="D516" s="1">
-        <v>0</v>
-      </c>
-      <c r="E516" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F516" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G516" s="1">
-        <v>0</v>
-      </c>
-      <c r="H516" s="2">
-        <v>0</v>
-      </c>
-      <c r="I516" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J516" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A517" s="1">
-        <v>1570001</v>
-      </c>
-      <c r="B517" s="1">
-        <v>157</v>
-      </c>
-      <c r="D517" s="1">
-        <v>0</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G517" s="1">
-        <v>0</v>
-      </c>
-      <c r="H517" s="2">
-        <v>0</v>
-      </c>
-      <c r="I517" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J517" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A518" s="1">
-        <v>1580001</v>
-      </c>
-      <c r="B518" s="1">
-        <v>158</v>
-      </c>
-      <c r="D518" s="1">
-        <v>0</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F518" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G518" s="1">
-        <v>0</v>
-      </c>
-      <c r="H518" s="2">
-        <v>0</v>
-      </c>
-      <c r="I518" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J518" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A519" s="1">
-        <v>1590001</v>
-      </c>
-      <c r="B519" s="1">
-        <v>159</v>
-      </c>
-      <c r="D519" s="1">
-        <v>0</v>
-      </c>
-      <c r="E519" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G519" s="1">
-        <v>0</v>
-      </c>
-      <c r="H519" s="2">
-        <v>0</v>
-      </c>
-      <c r="I519" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J519" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A520" s="1">
-        <v>1600001</v>
-      </c>
-      <c r="B520" s="1">
-        <v>160</v>
-      </c>
-      <c r="D520" s="1">
-        <v>0</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G520" s="1">
-        <v>0</v>
-      </c>
-      <c r="H520" s="2">
-        <v>0</v>
-      </c>
-      <c r="I520" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J520" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B505868E-F1C4-4ADE-B0E6-4DAF6CBF1C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE9D135-E29B-49A5-81FC-2F2B1B6AE6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="70">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -274,9 +274,6 @@
   </si>
   <si>
     <t>42635001</t>
-  </si>
-  <si>
-    <t>48300002:1</t>
   </si>
   <si>
     <t>42654001</t>
@@ -1836,7 +1833,7 @@
         <v>54</v>
       </c>
       <c r="G42" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -1865,7 +1862,7 @@
         <v>55</v>
       </c>
       <c r="G43" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>56</v>
@@ -1891,7 +1888,7 @@
         <v>16</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G44" s="1">
         <v>70</v>
@@ -1903,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
@@ -1920,10 +1917,10 @@
         <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G45" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -1932,7 +1929,7 @@
         <v>16</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
@@ -1952,7 +1949,7 @@
         <v>52</v>
       </c>
       <c r="G46" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>59</v>
@@ -1978,19 +1975,19 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G47" s="1">
-        <v>120</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
@@ -2010,10 +2007,10 @@
         <v>55</v>
       </c>
       <c r="G48" s="1">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>16</v>
@@ -2039,7 +2036,7 @@
         <v>61</v>
       </c>
       <c r="G49" s="1">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -2068,10 +2065,10 @@
         <v>55</v>
       </c>
       <c r="G50" s="1">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
@@ -2094,19 +2091,19 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G51" s="1">
-        <v>300</v>
-      </c>
-      <c r="H51" s="2">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.15">
@@ -2123,10 +2120,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G52" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2135,7 +2132,7 @@
         <v>16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
@@ -2152,19 +2149,19 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G53" s="1">
-        <v>600</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>66</v>
+        <v>1200</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
@@ -2181,10 +2178,10 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G54" s="1">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2193,7 +2190,7 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
@@ -2213,7 +2210,7 @@
         <v>64</v>
       </c>
       <c r="G55" s="1">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2242,10 +2239,10 @@
         <v>57</v>
       </c>
       <c r="G56" s="1">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>16</v>
@@ -2268,10 +2265,10 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G57" s="1">
-        <v>1800</v>
+        <v>3500</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2280,12 +2277,12 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>110021</v>
+        <v>110019</v>
       </c>
       <c r="B58" s="1">
         <v>11</v>
@@ -2297,10 +2294,10 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G58" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2309,12 +2306,12 @@
         <v>16</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>110019</v>
+        <v>110021</v>
       </c>
       <c r="B59" s="1">
         <v>11</v>
@@ -2326,10 +2323,10 @@
         <v>16</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="G59" s="1">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2338,12 +2335,12 @@
         <v>16</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>110023</v>
+        <v>110022</v>
       </c>
       <c r="B60" s="1">
         <v>11</v>
@@ -2355,13 +2352,13 @@
         <v>16</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="G60" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>16</v>
@@ -2372,7 +2369,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110022</v>
+        <v>110023</v>
       </c>
       <c r="B61" s="1">
         <v>11</v>
@@ -2384,10 +2381,10 @@
         <v>16</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G61" s="1">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -2396,7 +2393,7 @@
         <v>16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">
@@ -2413,10 +2410,10 @@
         <v>16</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G62" s="1">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -2425,7 +2422,7 @@
         <v>16</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE9D135-E29B-49A5-81FC-2F2B1B6AE6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C4AD0-A851-4B33-A8AE-59FF13A9E6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="72">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -243,9 +243,6 @@
     <t>46700001:1</t>
   </si>
   <si>
-    <t>42633001</t>
-  </si>
-  <si>
     <t>46700001:2</t>
   </si>
   <si>
@@ -283,6 +280,16 @@
   </si>
   <si>
     <t>42656001</t>
+  </si>
+  <si>
+    <t>46700001:1_48300001:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>42613001</t>
   </si>
 </sst>
 </file>
@@ -1859,13 +1866,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G43" s="1">
         <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>16</v>
@@ -1888,7 +1895,7 @@
         <v>16</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G44" s="1">
         <v>70</v>
@@ -1900,7 +1907,7 @@
         <v>16</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.15">
@@ -1929,7 +1936,7 @@
         <v>16</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.15">
@@ -1952,7 +1959,7 @@
         <v>150</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>16</v>
@@ -1975,19 +1982,19 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G47" s="1">
         <v>210</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
@@ -2010,7 +2017,7 @@
         <v>300</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>16</v>
@@ -2033,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G49" s="1">
         <v>400</v>
@@ -2045,7 +2052,7 @@
         <v>16</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
@@ -2068,7 +2075,7 @@
         <v>600</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
@@ -2091,13 +2098,13 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G51" s="1">
         <v>800</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>16</v>
@@ -2149,7 +2156,7 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G53" s="1">
         <v>1200</v>
@@ -2161,7 +2168,7 @@
         <v>16</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
@@ -2178,7 +2185,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G54" s="1">
         <v>1500</v>
@@ -2190,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
@@ -2207,7 +2214,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G55" s="1">
         <v>2000</v>
@@ -2219,7 +2226,7 @@
         <v>16</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
@@ -2236,13 +2243,13 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G56" s="1">
         <v>2500</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>16</v>
@@ -2265,7 +2272,7 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G57" s="1">
         <v>3500</v>
@@ -2277,7 +2284,7 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C4AD0-A851-4B33-A8AE-59FF13A9E6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5C891E-CE95-4B38-BC8A-846364EB9FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="71">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -258,9 +258,6 @@
     <t>48200001:1</t>
   </si>
   <si>
-    <t>42636001</t>
-  </si>
-  <si>
     <t>48300004:1</t>
   </si>
   <si>
@@ -282,14 +279,15 @@
     <t>42656001</t>
   </si>
   <si>
-    <t>46700001:1_48300001:1</t>
+    <t>42613001</t>
+  </si>
+  <si>
+    <t>46700001:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48300001:1</t>
-  </si>
-  <si>
-    <t>42613001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1872,7 +1870,7 @@
         <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>16</v>
@@ -1994,7 +1992,7 @@
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
@@ -2011,19 +2009,19 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G48" s="1">
-        <v>300</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>61</v>
+        <v>250</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
@@ -2075,7 +2073,7 @@
         <v>600</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
@@ -2104,7 +2102,7 @@
         <v>800</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>16</v>
@@ -2156,7 +2154,7 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G53" s="1">
         <v>1200</v>
@@ -2168,7 +2166,7 @@
         <v>16</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
@@ -2185,7 +2183,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G54" s="1">
         <v>1500</v>
@@ -2197,7 +2195,7 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
@@ -2214,7 +2212,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G55" s="1">
         <v>2000</v>
@@ -2226,7 +2224,7 @@
         <v>16</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
@@ -2249,7 +2247,7 @@
         <v>2500</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>16</v>
@@ -2272,7 +2270,7 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G57" s="1">
         <v>3500</v>
@@ -2284,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5C891E-CE95-4B38-BC8A-846364EB9FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A721C528-AF33-460E-A8B8-F8BBB183F2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -282,11 +282,11 @@
     <t>42613001</t>
   </si>
   <si>
-    <t>46700001:1</t>
+    <t>48300001:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>48300001:1</t>
+    <t>46700001:1_48300001:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1980,7 +1980,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G47" s="1">
         <v>210</v>
@@ -1992,7 +1992,7 @@
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">
@@ -2009,7 +2009,7 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G48" s="1">
         <v>250</v>
@@ -2021,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A721C528-AF33-460E-A8B8-F8BBB183F2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90B744F-4F5C-4453-BC5E-F5EE1E214FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46700001:1_48300001:1</t>
+    <t>46700001:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1992,7 +1992,7 @@
         <v>16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90B744F-4F5C-4453-BC5E-F5EE1E214FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A8338-A449-4842-AE72-FC16A71DED26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="74">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -258,9 +258,6 @@
     <t>48200001:1</t>
   </si>
   <si>
-    <t>48300004:1</t>
-  </si>
-  <si>
     <t>46200001:3</t>
   </si>
   <si>
@@ -273,9 +270,6 @@
     <t>42654001</t>
   </si>
   <si>
-    <t>48300006:1</t>
-  </si>
-  <si>
     <t>42656001</t>
   </si>
   <si>
@@ -283,11 +277,24 @@
   </si>
   <si>
     <t>48300001:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46700001:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>48200004:1</t>
+  </si>
+  <si>
+    <t>46700001:2_48300001:1</t>
+  </si>
+  <si>
+    <t>48200006:1</t>
+  </si>
+  <si>
+    <t>42653001</t>
+  </si>
+  <si>
+    <t>46700001:1_48300001:1</t>
+  </si>
+  <si>
+    <t>46700001:5_48300001:1</t>
   </si>
 </sst>
 </file>
@@ -1870,7 +1877,7 @@
         <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>16</v>
@@ -1980,7 +1987,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G47" s="1">
         <v>210</v>
@@ -2009,7 +2016,7 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G48" s="1">
         <v>250</v>
@@ -2021,7 +2028,7 @@
         <v>16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
@@ -2067,19 +2074,19 @@
         <v>16</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G50" s="1">
-        <v>600</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>64</v>
+        <v>500</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.15">
@@ -2096,13 +2103,13 @@
         <v>16</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G51" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>16</v>
@@ -2125,10 +2132,10 @@
         <v>16</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2137,7 +2144,7 @@
         <v>16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
@@ -2154,19 +2161,19 @@
         <v>16</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G53" s="1">
-        <v>1200</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.15">
@@ -2183,10 +2190,10 @@
         <v>16</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G54" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -2195,7 +2202,7 @@
         <v>16</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.15">
@@ -2212,19 +2219,19 @@
         <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1500</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.15">
@@ -2241,19 +2248,19 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G56" s="1">
-        <v>2500</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>67</v>
+        <v>1800</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
@@ -2270,10 +2277,10 @@
         <v>16</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G57" s="1">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2282,7 +2289,7 @@
         <v>16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
@@ -2299,19 +2306,19 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G58" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H58" s="2">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
@@ -2328,10 +2335,10 @@
         <v>16</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G59" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2340,7 +2347,7 @@
         <v>16</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
@@ -2357,13 +2364,13 @@
         <v>16</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
+        <v>6000</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>16</v>
@@ -2386,10 +2393,10 @@
         <v>16</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -2398,7 +2405,7 @@
         <v>16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A8338-A449-4842-AE72-FC16A71DED26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCDF196-24EE-4F20-8490-B5EB77129D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="71">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -276,13 +276,7 @@
     <t>42613001</t>
   </si>
   <si>
-    <t>48300001:1</t>
-  </si>
-  <si>
     <t>48200004:1</t>
-  </si>
-  <si>
-    <t>46700001:2_48300001:1</t>
   </si>
   <si>
     <t>48200006:1</t>
@@ -291,10 +285,7 @@
     <t>42653001</t>
   </si>
   <si>
-    <t>46700001:1_48300001:1</t>
-  </si>
-  <si>
-    <t>46700001:5_48300001:1</t>
+    <t>48300004:1</t>
   </si>
 </sst>
 </file>
@@ -2016,7 +2007,7 @@
         <v>16</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G48" s="1">
         <v>250</v>
@@ -2028,7 +2019,7 @@
         <v>16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.15">
@@ -2132,7 +2123,7 @@
         <v>16</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G52" s="1">
         <v>800</v>
@@ -2144,7 +2135,7 @@
         <v>16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.15">
@@ -2248,7 +2239,7 @@
         <v>16</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G56" s="1">
         <v>1800</v>
@@ -2260,7 +2251,7 @@
         <v>16</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.15">
@@ -2306,7 +2297,7 @@
         <v>16</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G58" s="1">
         <v>2500</v>
@@ -2318,7 +2309,7 @@
         <v>16</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.15">
@@ -2335,7 +2326,7 @@
         <v>16</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G59" s="1">
         <v>3000</v>
@@ -2347,7 +2338,7 @@
         <v>16</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
@@ -2370,7 +2361,7 @@
         <v>6000</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>16</v>
@@ -2393,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="G61" s="1">
         <v>8000</v>
@@ -2405,7 +2396,7 @@
         <v>16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC1AC40-46F6-4324-AA4C-AB6D06DEE0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DB668C-8E17-4815-A823-3AE7F514E8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,8 +36,36 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>cltx</author>
+  </authors>
+  <commentList>
+    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{CD6BF67F-DF52-462F-BD8C-4D92BF76E221}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1.宝箱
+2.装备
+3.武器
+4.item道具</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="80">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -290,12 +318,43 @@
   <si>
     <t>48300002:1_48300003:1_48300004:1_48300005:1_48300006:1</t>
   </si>
+  <si>
+    <t>res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res_first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源类型（首次）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res_type_first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res_type</t>
+  </si>
+  <si>
+    <t>资源id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源id（首次）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,6 +391,14 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -375,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -386,6 +453,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,8 +736,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J369"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N369"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -680,15 +750,19 @@
     <col min="8" max="8" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="29.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -719,8 +793,20 @@
       <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -751,8 +837,20 @@
       <c r="J3" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -783,8 +881,20 @@
       <c r="J4" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>10020</v>
       </c>
@@ -813,7 +923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10010</v>
       </c>
@@ -842,7 +952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>10001</v>
       </c>
@@ -872,7 +982,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>10002</v>
       </c>
@@ -902,7 +1012,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>10003</v>
       </c>
@@ -932,7 +1042,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>10004</v>
       </c>
@@ -962,7 +1072,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10005</v>
       </c>
@@ -992,7 +1102,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>10006</v>
       </c>
@@ -1022,7 +1132,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>10007</v>
       </c>
@@ -1052,7 +1162,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>10008</v>
       </c>
@@ -1082,7 +1192,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>10009</v>
       </c>
@@ -1112,7 +1222,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>20020</v>
       </c>
@@ -11381,5 +11491,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DB668C-8E17-4815-A823-3AE7F514E8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52428D7-2812-4F24-85AF-4452DEF2990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{CD6BF67F-DF52-462F-BD8C-4D92BF76E221}">
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{6C23EEB7-1E7B-4570-865B-E36F9A3C82A4}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,24 @@
           <t>1.宝箱
 2.装备
 3.武器
-4.item道具</t>
+4.金币
+5.强化石</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{CD6BF67F-DF52-462F-BD8C-4D92BF76E221}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>装备2 武器3:1~5=档位
+金币4 强化石:1~3=小中大</t>
         </r>
       </text>
     </comment>
@@ -319,14 +336,6 @@
     <t>48300002:1_48300003:1_48300004:1_48300005:1_48300006:1</t>
   </si>
   <si>
-    <t>res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>res_first</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>资源类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -342,11 +351,17 @@
     <t>res_type</t>
   </si>
   <si>
-    <t>资源id</t>
+    <t>res_type_id res_type_id_first</t>
+  </si>
+  <si>
+    <t>res_type_id_first</t>
+  </si>
+  <si>
+    <t>资源类型id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资源id（首次）</t>
+    <t>资源类型id（首次）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -457,6 +472,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -750,10 +766,10 @@
     <col min="8" max="8" width="19.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="29.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.375" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -806,7 +822,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -838,16 +854,16 @@
         <v>48</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="M3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.15">
@@ -882,16 +898,16 @@
         <v>46</v>
       </c>
       <c r="K4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
@@ -922,6 +938,18 @@
       <c r="J5" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
@@ -951,6 +979,18 @@
       <c r="J6" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
@@ -981,6 +1021,18 @@
       <c r="J7" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
@@ -1011,6 +1063,18 @@
       <c r="J8" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
@@ -1041,6 +1105,18 @@
       <c r="J9" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
@@ -1071,6 +1147,18 @@
       <c r="J10" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
@@ -1101,6 +1189,18 @@
       <c r="J11" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
@@ -1131,6 +1231,18 @@
       <c r="J12" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
@@ -1161,6 +1273,18 @@
       <c r="J13" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
@@ -1191,6 +1315,18 @@
       <c r="J14" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
@@ -1221,6 +1357,18 @@
       <c r="J15" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="K15" s="7">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
@@ -1250,8 +1398,20 @@
       <c r="J16" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>20010</v>
       </c>
@@ -1279,8 +1439,20 @@
       <c r="J17" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K17" s="7">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>30020</v>
       </c>
@@ -1308,8 +1480,20 @@
       <c r="J18" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>30010</v>
       </c>
@@ -1337,8 +1521,20 @@
       <c r="J19" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K19" s="7">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>40020</v>
       </c>
@@ -1366,8 +1562,20 @@
       <c r="J20" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K20" s="7">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>40010</v>
       </c>
@@ -1395,8 +1603,20 @@
       <c r="J21" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K21" s="7">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>40002</v>
       </c>
@@ -1424,8 +1644,20 @@
       <c r="J22" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K22" s="7">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7">
+        <v>0</v>
+      </c>
+      <c r="M22" s="7">
+        <v>0</v>
+      </c>
+      <c r="N22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>50020</v>
       </c>
@@ -1453,8 +1685,20 @@
       <c r="J23" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K23" s="7">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7">
+        <v>0</v>
+      </c>
+      <c r="N23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>50010</v>
       </c>
@@ -1482,8 +1726,20 @@
       <c r="J24" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K24" s="7">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>50002</v>
       </c>
@@ -1511,8 +1767,20 @@
       <c r="J25" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K25" s="7">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7">
+        <v>0</v>
+      </c>
+      <c r="N25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>50003</v>
       </c>
@@ -1540,8 +1808,20 @@
       <c r="J26" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K26" s="7">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>60020</v>
       </c>
@@ -1569,8 +1849,20 @@
       <c r="J27" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K27" s="7">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7">
+        <v>0</v>
+      </c>
+      <c r="N27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>60010</v>
       </c>
@@ -1598,8 +1890,20 @@
       <c r="J28" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K28" s="7">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7">
+        <v>0</v>
+      </c>
+      <c r="N28" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>60002</v>
       </c>
@@ -1627,8 +1931,20 @@
       <c r="J29" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K29" s="7">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7">
+        <v>0</v>
+      </c>
+      <c r="N29" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>60003</v>
       </c>
@@ -1656,8 +1972,20 @@
       <c r="J30" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K30" s="7">
+        <v>0</v>
+      </c>
+      <c r="L30" s="7">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7">
+        <v>0</v>
+      </c>
+      <c r="N30" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>60004</v>
       </c>
@@ -1685,8 +2013,20 @@
       <c r="J31" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K31" s="7">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <v>0</v>
+      </c>
+      <c r="M31" s="7">
+        <v>0</v>
+      </c>
+      <c r="N31" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>60005</v>
       </c>
@@ -1714,8 +2054,20 @@
       <c r="J32" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K32" s="7">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7">
+        <v>0</v>
+      </c>
+      <c r="N32" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>60006</v>
       </c>
@@ -1743,8 +2095,20 @@
       <c r="J33" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K33" s="7">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <v>0</v>
+      </c>
+      <c r="M33" s="7">
+        <v>0</v>
+      </c>
+      <c r="N33" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>70020</v>
       </c>
@@ -1772,8 +2136,20 @@
       <c r="J34" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7">
+        <v>0</v>
+      </c>
+      <c r="N34" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>70010</v>
       </c>
@@ -1801,8 +2177,20 @@
       <c r="J35" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K35" s="7">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <v>0</v>
+      </c>
+      <c r="M35" s="7">
+        <v>0</v>
+      </c>
+      <c r="N35" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>70002</v>
       </c>
@@ -1830,8 +2218,20 @@
       <c r="J36" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K36" s="7">
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7">
+        <v>0</v>
+      </c>
+      <c r="N36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>70003</v>
       </c>
@@ -1859,8 +2259,20 @@
       <c r="J37" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K37" s="7">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7">
+        <v>0</v>
+      </c>
+      <c r="M37" s="7">
+        <v>0</v>
+      </c>
+      <c r="N37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>70004</v>
       </c>
@@ -1888,8 +2300,20 @@
       <c r="J38" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K38" s="7">
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7">
+        <v>0</v>
+      </c>
+      <c r="N38" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>70005</v>
       </c>
@@ -1917,8 +2341,20 @@
       <c r="J39" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K39" s="7">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7">
+        <v>0</v>
+      </c>
+      <c r="N39" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>70006</v>
       </c>
@@ -1946,8 +2382,20 @@
       <c r="J40" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K40" s="7">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7">
+        <v>0</v>
+      </c>
+      <c r="M40" s="7">
+        <v>0</v>
+      </c>
+      <c r="N40" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>70007</v>
       </c>
@@ -1975,8 +2423,20 @@
       <c r="J41" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K41" s="7">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7">
+        <v>0</v>
+      </c>
+      <c r="N41" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>70008</v>
       </c>
@@ -2004,8 +2464,20 @@
       <c r="J42" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K42" s="7">
+        <v>0</v>
+      </c>
+      <c r="L42" s="7">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7">
+        <v>0</v>
+      </c>
+      <c r="N42" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>80020</v>
       </c>
@@ -2033,8 +2505,20 @@
       <c r="J43" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K43" s="7">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7">
+        <v>0</v>
+      </c>
+      <c r="N43" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>80010</v>
       </c>
@@ -2062,8 +2546,20 @@
       <c r="J44" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K44" s="7">
+        <v>0</v>
+      </c>
+      <c r="L44" s="7">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>90020</v>
       </c>
@@ -2091,8 +2587,20 @@
       <c r="J45" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K45" s="7">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>100020</v>
       </c>
@@ -2120,8 +2628,20 @@
       <c r="J46" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K46" s="7">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>100010</v>
       </c>
@@ -2149,8 +2669,20 @@
       <c r="J47" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K47" s="7">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7">
+        <v>0</v>
+      </c>
+      <c r="M47" s="7">
+        <v>0</v>
+      </c>
+      <c r="N47" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>110020</v>
       </c>
@@ -2178,8 +2710,20 @@
       <c r="J48" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K48" s="7">
+        <v>0</v>
+      </c>
+      <c r="L48" s="7">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7">
+        <v>0</v>
+      </c>
+      <c r="N48" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>110010</v>
       </c>
@@ -2207,8 +2751,20 @@
       <c r="J49" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K49" s="7">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7">
+        <v>0</v>
+      </c>
+      <c r="N49" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>110001</v>
       </c>
@@ -2236,8 +2792,20 @@
       <c r="J50" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K50" s="7">
+        <v>4</v>
+      </c>
+      <c r="L50" s="7">
+        <v>2</v>
+      </c>
+      <c r="M50" s="7">
+        <v>1</v>
+      </c>
+      <c r="N50" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>110002</v>
       </c>
@@ -2265,8 +2833,20 @@
       <c r="J51" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K51" s="7">
+        <v>4</v>
+      </c>
+      <c r="L51" s="7">
+        <v>2</v>
+      </c>
+      <c r="M51" s="7">
+        <v>1</v>
+      </c>
+      <c r="N51" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>110003</v>
       </c>
@@ -2294,8 +2874,20 @@
       <c r="J52" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K52" s="7">
+        <v>4</v>
+      </c>
+      <c r="L52" s="7">
+        <v>2</v>
+      </c>
+      <c r="M52" s="7">
+        <v>2</v>
+      </c>
+      <c r="N52" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>110004</v>
       </c>
@@ -2323,8 +2915,20 @@
       <c r="J53" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K53" s="7">
+        <v>4</v>
+      </c>
+      <c r="L53" s="7">
+        <v>2</v>
+      </c>
+      <c r="M53" s="7">
+        <v>2</v>
+      </c>
+      <c r="N53" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>110005</v>
       </c>
@@ -2352,8 +2956,20 @@
       <c r="J54" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K54" s="7">
+        <v>4</v>
+      </c>
+      <c r="L54" s="7">
+        <v>2</v>
+      </c>
+      <c r="M54" s="7">
+        <v>3</v>
+      </c>
+      <c r="N54" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>110006</v>
       </c>
@@ -2381,8 +2997,20 @@
       <c r="J55" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K55" s="7">
+        <v>5</v>
+      </c>
+      <c r="L55" s="7">
+        <v>3</v>
+      </c>
+      <c r="M55" s="7">
+        <v>1</v>
+      </c>
+      <c r="N55" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>110007</v>
       </c>
@@ -2410,8 +3038,20 @@
       <c r="J56" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K56" s="7">
+        <v>5</v>
+      </c>
+      <c r="L56" s="7">
+        <v>3</v>
+      </c>
+      <c r="M56" s="7">
+        <v>1</v>
+      </c>
+      <c r="N56" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>110008</v>
       </c>
@@ -2439,8 +3079,20 @@
       <c r="J57" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K57" s="7">
+        <v>5</v>
+      </c>
+      <c r="L57" s="7">
+        <v>3</v>
+      </c>
+      <c r="M57" s="7">
+        <v>2</v>
+      </c>
+      <c r="N57" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>110009</v>
       </c>
@@ -2468,8 +3120,20 @@
       <c r="J58" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K58" s="7">
+        <v>5</v>
+      </c>
+      <c r="L58" s="7">
+        <v>3</v>
+      </c>
+      <c r="M58" s="7">
+        <v>2</v>
+      </c>
+      <c r="N58" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>110011</v>
       </c>
@@ -2497,8 +3161,20 @@
       <c r="J59" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K59" s="7">
+        <v>5</v>
+      </c>
+      <c r="L59" s="7">
+        <v>3</v>
+      </c>
+      <c r="M59" s="7">
+        <v>3</v>
+      </c>
+      <c r="N59" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>110012</v>
       </c>
@@ -2526,8 +3202,20 @@
       <c r="J60" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K60" s="7">
+        <v>0</v>
+      </c>
+      <c r="L60" s="7">
+        <v>0</v>
+      </c>
+      <c r="M60" s="7">
+        <v>0</v>
+      </c>
+      <c r="N60" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>110013</v>
       </c>
@@ -2555,8 +3243,20 @@
       <c r="J61" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K61" s="7">
+        <v>0</v>
+      </c>
+      <c r="L61" s="7">
+        <v>0</v>
+      </c>
+      <c r="M61" s="7">
+        <v>0</v>
+      </c>
+      <c r="N61" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>110014</v>
       </c>
@@ -2584,8 +3284,20 @@
       <c r="J62" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K62" s="7">
+        <v>0</v>
+      </c>
+      <c r="L62" s="7">
+        <v>0</v>
+      </c>
+      <c r="M62" s="7">
+        <v>0</v>
+      </c>
+      <c r="N62" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>110015</v>
       </c>
@@ -2613,8 +3325,20 @@
       <c r="J63" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K63" s="7">
+        <v>0</v>
+      </c>
+      <c r="L63" s="7">
+        <v>0</v>
+      </c>
+      <c r="M63" s="7">
+        <v>0</v>
+      </c>
+      <c r="N63" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>110016</v>
       </c>
@@ -2642,8 +3366,20 @@
       <c r="J64" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K64" s="7">
+        <v>0</v>
+      </c>
+      <c r="L64" s="7">
+        <v>0</v>
+      </c>
+      <c r="M64" s="7">
+        <v>0</v>
+      </c>
+      <c r="N64" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>110017</v>
       </c>
@@ -2671,8 +3407,20 @@
       <c r="J65" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K65" s="7">
+        <v>0</v>
+      </c>
+      <c r="L65" s="7">
+        <v>0</v>
+      </c>
+      <c r="M65" s="7">
+        <v>0</v>
+      </c>
+      <c r="N65" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>110018</v>
       </c>
@@ -2700,8 +3448,20 @@
       <c r="J66" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K66" s="7">
+        <v>0</v>
+      </c>
+      <c r="L66" s="7">
+        <v>0</v>
+      </c>
+      <c r="M66" s="7">
+        <v>0</v>
+      </c>
+      <c r="N66" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>110019</v>
       </c>
@@ -2729,8 +3489,20 @@
       <c r="J67" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K67" s="7">
+        <v>0</v>
+      </c>
+      <c r="L67" s="7">
+        <v>0</v>
+      </c>
+      <c r="M67" s="7">
+        <v>0</v>
+      </c>
+      <c r="N67" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>110021</v>
       </c>
@@ -2758,8 +3530,20 @@
       <c r="J68" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K68" s="7">
+        <v>0</v>
+      </c>
+      <c r="L68" s="7">
+        <v>0</v>
+      </c>
+      <c r="M68" s="7">
+        <v>0</v>
+      </c>
+      <c r="N68" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>110022</v>
       </c>
@@ -2787,8 +3571,20 @@
       <c r="J69" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K69" s="7">
+        <v>0</v>
+      </c>
+      <c r="L69" s="7">
+        <v>0</v>
+      </c>
+      <c r="M69" s="7">
+        <v>0</v>
+      </c>
+      <c r="N69" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>110023</v>
       </c>
@@ -2816,8 +3612,20 @@
       <c r="J70" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K70" s="7">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7">
+        <v>0</v>
+      </c>
+      <c r="M70" s="7">
+        <v>0</v>
+      </c>
+      <c r="N70" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>110024</v>
       </c>
@@ -2845,8 +3653,20 @@
       <c r="J71" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K71" s="7">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7">
+        <v>0</v>
+      </c>
+      <c r="M71" s="7">
+        <v>0</v>
+      </c>
+      <c r="N71" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>120020</v>
       </c>
@@ -2874,8 +3694,20 @@
       <c r="J72" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K72" s="7">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7">
+        <v>0</v>
+      </c>
+      <c r="M72" s="7">
+        <v>0</v>
+      </c>
+      <c r="N72" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>120010</v>
       </c>
@@ -2903,8 +3735,20 @@
       <c r="J73" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K73" s="7">
+        <v>0</v>
+      </c>
+      <c r="L73" s="7">
+        <v>0</v>
+      </c>
+      <c r="M73" s="7">
+        <v>0</v>
+      </c>
+      <c r="N73" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>130020</v>
       </c>
@@ -2932,8 +3776,20 @@
       <c r="J74" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K74" s="7">
+        <v>0</v>
+      </c>
+      <c r="L74" s="7">
+        <v>0</v>
+      </c>
+      <c r="M74" s="7">
+        <v>0</v>
+      </c>
+      <c r="N74" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>130010</v>
       </c>
@@ -2961,8 +3817,20 @@
       <c r="J75" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K75" s="7">
+        <v>0</v>
+      </c>
+      <c r="L75" s="7">
+        <v>0</v>
+      </c>
+      <c r="M75" s="7">
+        <v>0</v>
+      </c>
+      <c r="N75" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>140020</v>
       </c>
@@ -2990,8 +3858,20 @@
       <c r="J76" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K76" s="7">
+        <v>0</v>
+      </c>
+      <c r="L76" s="7">
+        <v>0</v>
+      </c>
+      <c r="M76" s="7">
+        <v>0</v>
+      </c>
+      <c r="N76" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>140010</v>
       </c>
@@ -3019,8 +3899,20 @@
       <c r="J77" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K77" s="7">
+        <v>0</v>
+      </c>
+      <c r="L77" s="7">
+        <v>0</v>
+      </c>
+      <c r="M77" s="7">
+        <v>0</v>
+      </c>
+      <c r="N77" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>150020</v>
       </c>
@@ -3048,8 +3940,20 @@
       <c r="J78" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K78" s="7">
+        <v>0</v>
+      </c>
+      <c r="L78" s="7">
+        <v>0</v>
+      </c>
+      <c r="M78" s="7">
+        <v>0</v>
+      </c>
+      <c r="N78" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>150010</v>
       </c>
@@ -3077,8 +3981,20 @@
       <c r="J79" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K79" s="7">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7">
+        <v>0</v>
+      </c>
+      <c r="M79" s="7">
+        <v>0</v>
+      </c>
+      <c r="N79" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>160020</v>
       </c>
@@ -3106,8 +4022,20 @@
       <c r="J80" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K80" s="7">
+        <v>0</v>
+      </c>
+      <c r="L80" s="7">
+        <v>0</v>
+      </c>
+      <c r="M80" s="7">
+        <v>0</v>
+      </c>
+      <c r="N80" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>160010</v>
       </c>
@@ -3135,8 +4063,20 @@
       <c r="J81" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K81" s="7">
+        <v>0</v>
+      </c>
+      <c r="L81" s="7">
+        <v>0</v>
+      </c>
+      <c r="M81" s="7">
+        <v>0</v>
+      </c>
+      <c r="N81" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>170020</v>
       </c>
@@ -3164,8 +4104,20 @@
       <c r="J82" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K82" s="7">
+        <v>0</v>
+      </c>
+      <c r="L82" s="7">
+        <v>0</v>
+      </c>
+      <c r="M82" s="7">
+        <v>0</v>
+      </c>
+      <c r="N82" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>170010</v>
       </c>
@@ -3193,8 +4145,20 @@
       <c r="J83" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K83" s="7">
+        <v>0</v>
+      </c>
+      <c r="L83" s="7">
+        <v>0</v>
+      </c>
+      <c r="M83" s="7">
+        <v>0</v>
+      </c>
+      <c r="N83" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>180020</v>
       </c>
@@ -3222,8 +4186,20 @@
       <c r="J84" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K84" s="7">
+        <v>0</v>
+      </c>
+      <c r="L84" s="7">
+        <v>0</v>
+      </c>
+      <c r="M84" s="7">
+        <v>0</v>
+      </c>
+      <c r="N84" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>180010</v>
       </c>
@@ -3251,8 +4227,20 @@
       <c r="J85" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K85" s="7">
+        <v>0</v>
+      </c>
+      <c r="L85" s="7">
+        <v>0</v>
+      </c>
+      <c r="M85" s="7">
+        <v>0</v>
+      </c>
+      <c r="N85" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>190020</v>
       </c>
@@ -3280,8 +4268,20 @@
       <c r="J86" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K86" s="7">
+        <v>0</v>
+      </c>
+      <c r="L86" s="7">
+        <v>0</v>
+      </c>
+      <c r="M86" s="7">
+        <v>0</v>
+      </c>
+      <c r="N86" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>190010</v>
       </c>
@@ -3309,8 +4309,20 @@
       <c r="J87" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K87" s="7">
+        <v>0</v>
+      </c>
+      <c r="L87" s="7">
+        <v>0</v>
+      </c>
+      <c r="M87" s="7">
+        <v>0</v>
+      </c>
+      <c r="N87" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>200020</v>
       </c>
@@ -3338,8 +4350,20 @@
       <c r="J88" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K88" s="7">
+        <v>0</v>
+      </c>
+      <c r="L88" s="7">
+        <v>0</v>
+      </c>
+      <c r="M88" s="7">
+        <v>0</v>
+      </c>
+      <c r="N88" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>200010</v>
       </c>
@@ -3367,8 +4391,20 @@
       <c r="J89" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K89" s="7">
+        <v>0</v>
+      </c>
+      <c r="L89" s="7">
+        <v>0</v>
+      </c>
+      <c r="M89" s="7">
+        <v>0</v>
+      </c>
+      <c r="N89" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>210020</v>
       </c>
@@ -3396,8 +4432,20 @@
       <c r="J90" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K90" s="7">
+        <v>0</v>
+      </c>
+      <c r="L90" s="7">
+        <v>0</v>
+      </c>
+      <c r="M90" s="7">
+        <v>0</v>
+      </c>
+      <c r="N90" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>210010</v>
       </c>
@@ -3425,8 +4473,20 @@
       <c r="J91" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K91" s="7">
+        <v>0</v>
+      </c>
+      <c r="L91" s="7">
+        <v>0</v>
+      </c>
+      <c r="M91" s="7">
+        <v>0</v>
+      </c>
+      <c r="N91" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>220020</v>
       </c>
@@ -3454,8 +4514,20 @@
       <c r="J92" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K92" s="7">
+        <v>0</v>
+      </c>
+      <c r="L92" s="7">
+        <v>0</v>
+      </c>
+      <c r="M92" s="7">
+        <v>0</v>
+      </c>
+      <c r="N92" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>220010</v>
       </c>
@@ -3483,8 +4555,20 @@
       <c r="J93" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K93" s="7">
+        <v>0</v>
+      </c>
+      <c r="L93" s="7">
+        <v>0</v>
+      </c>
+      <c r="M93" s="7">
+        <v>0</v>
+      </c>
+      <c r="N93" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>230020</v>
       </c>
@@ -3512,8 +4596,20 @@
       <c r="J94" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K94" s="7">
+        <v>0</v>
+      </c>
+      <c r="L94" s="7">
+        <v>0</v>
+      </c>
+      <c r="M94" s="7">
+        <v>0</v>
+      </c>
+      <c r="N94" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>230010</v>
       </c>
@@ -3541,8 +4637,20 @@
       <c r="J95" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K95" s="7">
+        <v>0</v>
+      </c>
+      <c r="L95" s="7">
+        <v>0</v>
+      </c>
+      <c r="M95" s="7">
+        <v>0</v>
+      </c>
+      <c r="N95" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>240020</v>
       </c>
@@ -3570,8 +4678,20 @@
       <c r="J96" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K96" s="7">
+        <v>0</v>
+      </c>
+      <c r="L96" s="7">
+        <v>0</v>
+      </c>
+      <c r="M96" s="7">
+        <v>0</v>
+      </c>
+      <c r="N96" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>240010</v>
       </c>
@@ -3599,8 +4719,20 @@
       <c r="J97" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K97" s="7">
+        <v>0</v>
+      </c>
+      <c r="L97" s="7">
+        <v>0</v>
+      </c>
+      <c r="M97" s="7">
+        <v>0</v>
+      </c>
+      <c r="N97" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>250020</v>
       </c>
@@ -3628,8 +4760,20 @@
       <c r="J98" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K98" s="7">
+        <v>0</v>
+      </c>
+      <c r="L98" s="7">
+        <v>0</v>
+      </c>
+      <c r="M98" s="7">
+        <v>0</v>
+      </c>
+      <c r="N98" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>250010</v>
       </c>
@@ -3657,8 +4801,20 @@
       <c r="J99" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K99" s="7">
+        <v>0</v>
+      </c>
+      <c r="L99" s="7">
+        <v>0</v>
+      </c>
+      <c r="M99" s="7">
+        <v>0</v>
+      </c>
+      <c r="N99" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>260020</v>
       </c>
@@ -3686,8 +4842,20 @@
       <c r="J100" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K100" s="7">
+        <v>0</v>
+      </c>
+      <c r="L100" s="7">
+        <v>0</v>
+      </c>
+      <c r="M100" s="7">
+        <v>0</v>
+      </c>
+      <c r="N100" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>260010</v>
       </c>
@@ -3715,8 +4883,20 @@
       <c r="J101" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K101" s="7">
+        <v>0</v>
+      </c>
+      <c r="L101" s="7">
+        <v>0</v>
+      </c>
+      <c r="M101" s="7">
+        <v>0</v>
+      </c>
+      <c r="N101" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>270020</v>
       </c>
@@ -3744,8 +4924,20 @@
       <c r="J102" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K102" s="7">
+        <v>0</v>
+      </c>
+      <c r="L102" s="7">
+        <v>0</v>
+      </c>
+      <c r="M102" s="7">
+        <v>0</v>
+      </c>
+      <c r="N102" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>270010</v>
       </c>
@@ -3773,8 +4965,20 @@
       <c r="J103" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K103" s="7">
+        <v>0</v>
+      </c>
+      <c r="L103" s="7">
+        <v>0</v>
+      </c>
+      <c r="M103" s="7">
+        <v>0</v>
+      </c>
+      <c r="N103" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>280020</v>
       </c>
@@ -3802,8 +5006,20 @@
       <c r="J104" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K104" s="7">
+        <v>0</v>
+      </c>
+      <c r="L104" s="7">
+        <v>0</v>
+      </c>
+      <c r="M104" s="7">
+        <v>0</v>
+      </c>
+      <c r="N104" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>280010</v>
       </c>
@@ -3831,8 +5047,20 @@
       <c r="J105" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K105" s="7">
+        <v>0</v>
+      </c>
+      <c r="L105" s="7">
+        <v>0</v>
+      </c>
+      <c r="M105" s="7">
+        <v>0</v>
+      </c>
+      <c r="N105" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>290020</v>
       </c>
@@ -3860,8 +5088,20 @@
       <c r="J106" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K106" s="7">
+        <v>0</v>
+      </c>
+      <c r="L106" s="7">
+        <v>0</v>
+      </c>
+      <c r="M106" s="7">
+        <v>0</v>
+      </c>
+      <c r="N106" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>290010</v>
       </c>
@@ -3889,8 +5129,20 @@
       <c r="J107" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K107" s="7">
+        <v>0</v>
+      </c>
+      <c r="L107" s="7">
+        <v>0</v>
+      </c>
+      <c r="M107" s="7">
+        <v>0</v>
+      </c>
+      <c r="N107" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>300020</v>
       </c>
@@ -3918,8 +5170,20 @@
       <c r="J108" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K108" s="7">
+        <v>0</v>
+      </c>
+      <c r="L108" s="7">
+        <v>0</v>
+      </c>
+      <c r="M108" s="7">
+        <v>0</v>
+      </c>
+      <c r="N108" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>300010</v>
       </c>
@@ -3947,8 +5211,20 @@
       <c r="J109" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K109" s="7">
+        <v>0</v>
+      </c>
+      <c r="L109" s="7">
+        <v>0</v>
+      </c>
+      <c r="M109" s="7">
+        <v>0</v>
+      </c>
+      <c r="N109" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>310020</v>
       </c>
@@ -3976,8 +5252,20 @@
       <c r="J110" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K110" s="7">
+        <v>0</v>
+      </c>
+      <c r="L110" s="7">
+        <v>0</v>
+      </c>
+      <c r="M110" s="7">
+        <v>0</v>
+      </c>
+      <c r="N110" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>310010</v>
       </c>
@@ -4005,8 +5293,20 @@
       <c r="J111" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K111" s="7">
+        <v>0</v>
+      </c>
+      <c r="L111" s="7">
+        <v>0</v>
+      </c>
+      <c r="M111" s="7">
+        <v>0</v>
+      </c>
+      <c r="N111" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>320020</v>
       </c>
@@ -4034,8 +5334,20 @@
       <c r="J112" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K112" s="7">
+        <v>0</v>
+      </c>
+      <c r="L112" s="7">
+        <v>0</v>
+      </c>
+      <c r="M112" s="7">
+        <v>0</v>
+      </c>
+      <c r="N112" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>320010</v>
       </c>
@@ -4063,8 +5375,20 @@
       <c r="J113" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K113" s="7">
+        <v>0</v>
+      </c>
+      <c r="L113" s="7">
+        <v>0</v>
+      </c>
+      <c r="M113" s="7">
+        <v>0</v>
+      </c>
+      <c r="N113" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>330020</v>
       </c>
@@ -4092,8 +5416,20 @@
       <c r="J114" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K114" s="7">
+        <v>0</v>
+      </c>
+      <c r="L114" s="7">
+        <v>0</v>
+      </c>
+      <c r="M114" s="7">
+        <v>0</v>
+      </c>
+      <c r="N114" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>330010</v>
       </c>
@@ -4121,8 +5457,20 @@
       <c r="J115" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K115" s="7">
+        <v>0</v>
+      </c>
+      <c r="L115" s="7">
+        <v>0</v>
+      </c>
+      <c r="M115" s="7">
+        <v>0</v>
+      </c>
+      <c r="N115" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>340020</v>
       </c>
@@ -4150,8 +5498,20 @@
       <c r="J116" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K116" s="7">
+        <v>0</v>
+      </c>
+      <c r="L116" s="7">
+        <v>0</v>
+      </c>
+      <c r="M116" s="7">
+        <v>0</v>
+      </c>
+      <c r="N116" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>340010</v>
       </c>
@@ -4179,8 +5539,20 @@
       <c r="J117" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K117" s="7">
+        <v>0</v>
+      </c>
+      <c r="L117" s="7">
+        <v>0</v>
+      </c>
+      <c r="M117" s="7">
+        <v>0</v>
+      </c>
+      <c r="N117" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>350020</v>
       </c>
@@ -4208,8 +5580,20 @@
       <c r="J118" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K118" s="7">
+        <v>0</v>
+      </c>
+      <c r="L118" s="7">
+        <v>0</v>
+      </c>
+      <c r="M118" s="7">
+        <v>0</v>
+      </c>
+      <c r="N118" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>350010</v>
       </c>
@@ -4237,8 +5621,20 @@
       <c r="J119" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K119" s="7">
+        <v>0</v>
+      </c>
+      <c r="L119" s="7">
+        <v>0</v>
+      </c>
+      <c r="M119" s="7">
+        <v>0</v>
+      </c>
+      <c r="N119" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>360020</v>
       </c>
@@ -4266,8 +5662,20 @@
       <c r="J120" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K120" s="7">
+        <v>0</v>
+      </c>
+      <c r="L120" s="7">
+        <v>0</v>
+      </c>
+      <c r="M120" s="7">
+        <v>0</v>
+      </c>
+      <c r="N120" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>360010</v>
       </c>
@@ -4295,8 +5703,20 @@
       <c r="J121" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K121" s="7">
+        <v>0</v>
+      </c>
+      <c r="L121" s="7">
+        <v>0</v>
+      </c>
+      <c r="M121" s="7">
+        <v>0</v>
+      </c>
+      <c r="N121" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>370020</v>
       </c>
@@ -4324,8 +5744,20 @@
       <c r="J122" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K122" s="7">
+        <v>0</v>
+      </c>
+      <c r="L122" s="7">
+        <v>0</v>
+      </c>
+      <c r="M122" s="7">
+        <v>0</v>
+      </c>
+      <c r="N122" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>370010</v>
       </c>
@@ -4353,8 +5785,20 @@
       <c r="J123" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K123" s="7">
+        <v>0</v>
+      </c>
+      <c r="L123" s="7">
+        <v>0</v>
+      </c>
+      <c r="M123" s="7">
+        <v>0</v>
+      </c>
+      <c r="N123" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>380020</v>
       </c>
@@ -4382,8 +5826,20 @@
       <c r="J124" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K124" s="7">
+        <v>0</v>
+      </c>
+      <c r="L124" s="7">
+        <v>0</v>
+      </c>
+      <c r="M124" s="7">
+        <v>0</v>
+      </c>
+      <c r="N124" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>380010</v>
       </c>
@@ -4411,8 +5867,20 @@
       <c r="J125" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K125" s="7">
+        <v>0</v>
+      </c>
+      <c r="L125" s="7">
+        <v>0</v>
+      </c>
+      <c r="M125" s="7">
+        <v>0</v>
+      </c>
+      <c r="N125" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>390020</v>
       </c>
@@ -4440,8 +5908,20 @@
       <c r="J126" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K126" s="7">
+        <v>0</v>
+      </c>
+      <c r="L126" s="7">
+        <v>0</v>
+      </c>
+      <c r="M126" s="7">
+        <v>0</v>
+      </c>
+      <c r="N126" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>390010</v>
       </c>
@@ -4469,8 +5949,20 @@
       <c r="J127" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K127" s="7">
+        <v>0</v>
+      </c>
+      <c r="L127" s="7">
+        <v>0</v>
+      </c>
+      <c r="M127" s="7">
+        <v>0</v>
+      </c>
+      <c r="N127" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>400020</v>
       </c>
@@ -4498,8 +5990,20 @@
       <c r="J128" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K128" s="7">
+        <v>0</v>
+      </c>
+      <c r="L128" s="7">
+        <v>0</v>
+      </c>
+      <c r="M128" s="7">
+        <v>0</v>
+      </c>
+      <c r="N128" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>400010</v>
       </c>
@@ -4527,8 +6031,20 @@
       <c r="J129" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K129" s="7">
+        <v>0</v>
+      </c>
+      <c r="L129" s="7">
+        <v>0</v>
+      </c>
+      <c r="M129" s="7">
+        <v>0</v>
+      </c>
+      <c r="N129" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>410020</v>
       </c>
@@ -4556,8 +6072,20 @@
       <c r="J130" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K130" s="7">
+        <v>0</v>
+      </c>
+      <c r="L130" s="7">
+        <v>0</v>
+      </c>
+      <c r="M130" s="7">
+        <v>0</v>
+      </c>
+      <c r="N130" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>410010</v>
       </c>
@@ -4585,8 +6113,20 @@
       <c r="J131" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K131" s="7">
+        <v>0</v>
+      </c>
+      <c r="L131" s="7">
+        <v>0</v>
+      </c>
+      <c r="M131" s="7">
+        <v>0</v>
+      </c>
+      <c r="N131" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>420020</v>
       </c>
@@ -4614,8 +6154,20 @@
       <c r="J132" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K132" s="7">
+        <v>0</v>
+      </c>
+      <c r="L132" s="7">
+        <v>0</v>
+      </c>
+      <c r="M132" s="7">
+        <v>0</v>
+      </c>
+      <c r="N132" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>420010</v>
       </c>
@@ -4643,8 +6195,20 @@
       <c r="J133" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K133" s="7">
+        <v>0</v>
+      </c>
+      <c r="L133" s="7">
+        <v>0</v>
+      </c>
+      <c r="M133" s="7">
+        <v>0</v>
+      </c>
+      <c r="N133" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>430020</v>
       </c>
@@ -4672,8 +6236,20 @@
       <c r="J134" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K134" s="7">
+        <v>0</v>
+      </c>
+      <c r="L134" s="7">
+        <v>0</v>
+      </c>
+      <c r="M134" s="7">
+        <v>0</v>
+      </c>
+      <c r="N134" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>430010</v>
       </c>
@@ -4701,8 +6277,20 @@
       <c r="J135" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K135" s="7">
+        <v>0</v>
+      </c>
+      <c r="L135" s="7">
+        <v>0</v>
+      </c>
+      <c r="M135" s="7">
+        <v>0</v>
+      </c>
+      <c r="N135" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>440020</v>
       </c>
@@ -4730,8 +6318,20 @@
       <c r="J136" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K136" s="7">
+        <v>0</v>
+      </c>
+      <c r="L136" s="7">
+        <v>0</v>
+      </c>
+      <c r="M136" s="7">
+        <v>0</v>
+      </c>
+      <c r="N136" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>440010</v>
       </c>
@@ -4759,8 +6359,20 @@
       <c r="J137" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K137" s="7">
+        <v>0</v>
+      </c>
+      <c r="L137" s="7">
+        <v>0</v>
+      </c>
+      <c r="M137" s="7">
+        <v>0</v>
+      </c>
+      <c r="N137" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>450020</v>
       </c>
@@ -4788,8 +6400,20 @@
       <c r="J138" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K138" s="7">
+        <v>0</v>
+      </c>
+      <c r="L138" s="7">
+        <v>0</v>
+      </c>
+      <c r="M138" s="7">
+        <v>0</v>
+      </c>
+      <c r="N138" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>450010</v>
       </c>
@@ -4817,8 +6441,20 @@
       <c r="J139" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K139" s="7">
+        <v>0</v>
+      </c>
+      <c r="L139" s="7">
+        <v>0</v>
+      </c>
+      <c r="M139" s="7">
+        <v>0</v>
+      </c>
+      <c r="N139" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>460020</v>
       </c>
@@ -4846,8 +6482,20 @@
       <c r="J140" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K140" s="7">
+        <v>0</v>
+      </c>
+      <c r="L140" s="7">
+        <v>0</v>
+      </c>
+      <c r="M140" s="7">
+        <v>0</v>
+      </c>
+      <c r="N140" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>460010</v>
       </c>
@@ -4875,8 +6523,20 @@
       <c r="J141" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K141" s="7">
+        <v>0</v>
+      </c>
+      <c r="L141" s="7">
+        <v>0</v>
+      </c>
+      <c r="M141" s="7">
+        <v>0</v>
+      </c>
+      <c r="N141" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>470020</v>
       </c>
@@ -4904,8 +6564,20 @@
       <c r="J142" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K142" s="7">
+        <v>0</v>
+      </c>
+      <c r="L142" s="7">
+        <v>0</v>
+      </c>
+      <c r="M142" s="7">
+        <v>0</v>
+      </c>
+      <c r="N142" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>470010</v>
       </c>
@@ -4933,8 +6605,20 @@
       <c r="J143" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K143" s="7">
+        <v>0</v>
+      </c>
+      <c r="L143" s="7">
+        <v>0</v>
+      </c>
+      <c r="M143" s="7">
+        <v>0</v>
+      </c>
+      <c r="N143" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>480020</v>
       </c>
@@ -4962,8 +6646,20 @@
       <c r="J144" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K144" s="7">
+        <v>0</v>
+      </c>
+      <c r="L144" s="7">
+        <v>0</v>
+      </c>
+      <c r="M144" s="7">
+        <v>0</v>
+      </c>
+      <c r="N144" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>480010</v>
       </c>
@@ -4991,8 +6687,20 @@
       <c r="J145" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K145" s="7">
+        <v>0</v>
+      </c>
+      <c r="L145" s="7">
+        <v>0</v>
+      </c>
+      <c r="M145" s="7">
+        <v>0</v>
+      </c>
+      <c r="N145" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>490020</v>
       </c>
@@ -5020,8 +6728,20 @@
       <c r="J146" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K146" s="7">
+        <v>0</v>
+      </c>
+      <c r="L146" s="7">
+        <v>0</v>
+      </c>
+      <c r="M146" s="7">
+        <v>0</v>
+      </c>
+      <c r="N146" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>490010</v>
       </c>
@@ -5049,8 +6769,20 @@
       <c r="J147" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K147" s="7">
+        <v>0</v>
+      </c>
+      <c r="L147" s="7">
+        <v>0</v>
+      </c>
+      <c r="M147" s="7">
+        <v>0</v>
+      </c>
+      <c r="N147" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>500020</v>
       </c>
@@ -5078,8 +6810,20 @@
       <c r="J148" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K148" s="7">
+        <v>0</v>
+      </c>
+      <c r="L148" s="7">
+        <v>0</v>
+      </c>
+      <c r="M148" s="7">
+        <v>0</v>
+      </c>
+      <c r="N148" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>500010</v>
       </c>
@@ -5107,8 +6851,20 @@
       <c r="J149" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K149" s="7">
+        <v>0</v>
+      </c>
+      <c r="L149" s="7">
+        <v>0</v>
+      </c>
+      <c r="M149" s="7">
+        <v>0</v>
+      </c>
+      <c r="N149" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>510020</v>
       </c>
@@ -5136,8 +6892,20 @@
       <c r="J150" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K150" s="7">
+        <v>0</v>
+      </c>
+      <c r="L150" s="7">
+        <v>0</v>
+      </c>
+      <c r="M150" s="7">
+        <v>0</v>
+      </c>
+      <c r="N150" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>510010</v>
       </c>
@@ -5165,8 +6933,20 @@
       <c r="J151" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K151" s="7">
+        <v>0</v>
+      </c>
+      <c r="L151" s="7">
+        <v>0</v>
+      </c>
+      <c r="M151" s="7">
+        <v>0</v>
+      </c>
+      <c r="N151" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>520020</v>
       </c>
@@ -5194,8 +6974,20 @@
       <c r="J152" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K152" s="7">
+        <v>0</v>
+      </c>
+      <c r="L152" s="7">
+        <v>0</v>
+      </c>
+      <c r="M152" s="7">
+        <v>0</v>
+      </c>
+      <c r="N152" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>520010</v>
       </c>
@@ -5223,8 +7015,20 @@
       <c r="J153" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K153" s="7">
+        <v>0</v>
+      </c>
+      <c r="L153" s="7">
+        <v>0</v>
+      </c>
+      <c r="M153" s="7">
+        <v>0</v>
+      </c>
+      <c r="N153" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>530020</v>
       </c>
@@ -5252,8 +7056,20 @@
       <c r="J154" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K154" s="7">
+        <v>0</v>
+      </c>
+      <c r="L154" s="7">
+        <v>0</v>
+      </c>
+      <c r="M154" s="7">
+        <v>0</v>
+      </c>
+      <c r="N154" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>530010</v>
       </c>
@@ -5281,8 +7097,20 @@
       <c r="J155" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K155" s="7">
+        <v>0</v>
+      </c>
+      <c r="L155" s="7">
+        <v>0</v>
+      </c>
+      <c r="M155" s="7">
+        <v>0</v>
+      </c>
+      <c r="N155" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>540020</v>
       </c>
@@ -5310,8 +7138,20 @@
       <c r="J156" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K156" s="7">
+        <v>0</v>
+      </c>
+      <c r="L156" s="7">
+        <v>0</v>
+      </c>
+      <c r="M156" s="7">
+        <v>0</v>
+      </c>
+      <c r="N156" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>540010</v>
       </c>
@@ -5339,8 +7179,20 @@
       <c r="J157" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K157" s="7">
+        <v>0</v>
+      </c>
+      <c r="L157" s="7">
+        <v>0</v>
+      </c>
+      <c r="M157" s="7">
+        <v>0</v>
+      </c>
+      <c r="N157" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>550020</v>
       </c>
@@ -5368,8 +7220,20 @@
       <c r="J158" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K158" s="7">
+        <v>0</v>
+      </c>
+      <c r="L158" s="7">
+        <v>0</v>
+      </c>
+      <c r="M158" s="7">
+        <v>0</v>
+      </c>
+      <c r="N158" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>550010</v>
       </c>
@@ -5397,8 +7261,20 @@
       <c r="J159" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K159" s="7">
+        <v>0</v>
+      </c>
+      <c r="L159" s="7">
+        <v>0</v>
+      </c>
+      <c r="M159" s="7">
+        <v>0</v>
+      </c>
+      <c r="N159" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>560020</v>
       </c>
@@ -5426,8 +7302,20 @@
       <c r="J160" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K160" s="7">
+        <v>0</v>
+      </c>
+      <c r="L160" s="7">
+        <v>0</v>
+      </c>
+      <c r="M160" s="7">
+        <v>0</v>
+      </c>
+      <c r="N160" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>560010</v>
       </c>
@@ -5455,8 +7343,20 @@
       <c r="J161" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K161" s="7">
+        <v>0</v>
+      </c>
+      <c r="L161" s="7">
+        <v>0</v>
+      </c>
+      <c r="M161" s="7">
+        <v>0</v>
+      </c>
+      <c r="N161" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>570020</v>
       </c>
@@ -5484,8 +7384,20 @@
       <c r="J162" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K162" s="7">
+        <v>0</v>
+      </c>
+      <c r="L162" s="7">
+        <v>0</v>
+      </c>
+      <c r="M162" s="7">
+        <v>0</v>
+      </c>
+      <c r="N162" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>570010</v>
       </c>
@@ -5513,8 +7425,20 @@
       <c r="J163" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K163" s="7">
+        <v>0</v>
+      </c>
+      <c r="L163" s="7">
+        <v>0</v>
+      </c>
+      <c r="M163" s="7">
+        <v>0</v>
+      </c>
+      <c r="N163" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>580020</v>
       </c>
@@ -5542,8 +7466,20 @@
       <c r="J164" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K164" s="7">
+        <v>0</v>
+      </c>
+      <c r="L164" s="7">
+        <v>0</v>
+      </c>
+      <c r="M164" s="7">
+        <v>0</v>
+      </c>
+      <c r="N164" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>580010</v>
       </c>
@@ -5571,8 +7507,20 @@
       <c r="J165" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K165" s="7">
+        <v>0</v>
+      </c>
+      <c r="L165" s="7">
+        <v>0</v>
+      </c>
+      <c r="M165" s="7">
+        <v>0</v>
+      </c>
+      <c r="N165" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>590020</v>
       </c>
@@ -5600,8 +7548,20 @@
       <c r="J166" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K166" s="7">
+        <v>0</v>
+      </c>
+      <c r="L166" s="7">
+        <v>0</v>
+      </c>
+      <c r="M166" s="7">
+        <v>0</v>
+      </c>
+      <c r="N166" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>590010</v>
       </c>
@@ -5629,8 +7589,20 @@
       <c r="J167" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K167" s="7">
+        <v>0</v>
+      </c>
+      <c r="L167" s="7">
+        <v>0</v>
+      </c>
+      <c r="M167" s="7">
+        <v>0</v>
+      </c>
+      <c r="N167" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>600020</v>
       </c>
@@ -5658,8 +7630,20 @@
       <c r="J168" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K168" s="7">
+        <v>0</v>
+      </c>
+      <c r="L168" s="7">
+        <v>0</v>
+      </c>
+      <c r="M168" s="7">
+        <v>0</v>
+      </c>
+      <c r="N168" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>600010</v>
       </c>
@@ -5687,8 +7671,20 @@
       <c r="J169" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K169" s="7">
+        <v>0</v>
+      </c>
+      <c r="L169" s="7">
+        <v>0</v>
+      </c>
+      <c r="M169" s="7">
+        <v>0</v>
+      </c>
+      <c r="N169" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>610020</v>
       </c>
@@ -5716,8 +7712,20 @@
       <c r="J170" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K170" s="7">
+        <v>0</v>
+      </c>
+      <c r="L170" s="7">
+        <v>0</v>
+      </c>
+      <c r="M170" s="7">
+        <v>0</v>
+      </c>
+      <c r="N170" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>610010</v>
       </c>
@@ -5745,8 +7753,20 @@
       <c r="J171" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K171" s="7">
+        <v>0</v>
+      </c>
+      <c r="L171" s="7">
+        <v>0</v>
+      </c>
+      <c r="M171" s="7">
+        <v>0</v>
+      </c>
+      <c r="N171" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>620020</v>
       </c>
@@ -5774,8 +7794,20 @@
       <c r="J172" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K172" s="7">
+        <v>0</v>
+      </c>
+      <c r="L172" s="7">
+        <v>0</v>
+      </c>
+      <c r="M172" s="7">
+        <v>0</v>
+      </c>
+      <c r="N172" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>620010</v>
       </c>
@@ -5803,8 +7835,20 @@
       <c r="J173" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K173" s="7">
+        <v>0</v>
+      </c>
+      <c r="L173" s="7">
+        <v>0</v>
+      </c>
+      <c r="M173" s="7">
+        <v>0</v>
+      </c>
+      <c r="N173" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>630020</v>
       </c>
@@ -5832,8 +7876,20 @@
       <c r="J174" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K174" s="7">
+        <v>0</v>
+      </c>
+      <c r="L174" s="7">
+        <v>0</v>
+      </c>
+      <c r="M174" s="7">
+        <v>0</v>
+      </c>
+      <c r="N174" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>630010</v>
       </c>
@@ -5861,8 +7917,20 @@
       <c r="J175" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K175" s="7">
+        <v>0</v>
+      </c>
+      <c r="L175" s="7">
+        <v>0</v>
+      </c>
+      <c r="M175" s="7">
+        <v>0</v>
+      </c>
+      <c r="N175" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>640020</v>
       </c>
@@ -5890,8 +7958,20 @@
       <c r="J176" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K176" s="7">
+        <v>0</v>
+      </c>
+      <c r="L176" s="7">
+        <v>0</v>
+      </c>
+      <c r="M176" s="7">
+        <v>0</v>
+      </c>
+      <c r="N176" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>640010</v>
       </c>
@@ -5919,8 +7999,20 @@
       <c r="J177" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K177" s="7">
+        <v>0</v>
+      </c>
+      <c r="L177" s="7">
+        <v>0</v>
+      </c>
+      <c r="M177" s="7">
+        <v>0</v>
+      </c>
+      <c r="N177" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>650020</v>
       </c>
@@ -5948,8 +8040,20 @@
       <c r="J178" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K178" s="7">
+        <v>0</v>
+      </c>
+      <c r="L178" s="7">
+        <v>0</v>
+      </c>
+      <c r="M178" s="7">
+        <v>0</v>
+      </c>
+      <c r="N178" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>650010</v>
       </c>
@@ -5977,8 +8081,20 @@
       <c r="J179" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K179" s="7">
+        <v>0</v>
+      </c>
+      <c r="L179" s="7">
+        <v>0</v>
+      </c>
+      <c r="M179" s="7">
+        <v>0</v>
+      </c>
+      <c r="N179" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>660020</v>
       </c>
@@ -6006,8 +8122,20 @@
       <c r="J180" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K180" s="7">
+        <v>0</v>
+      </c>
+      <c r="L180" s="7">
+        <v>0</v>
+      </c>
+      <c r="M180" s="7">
+        <v>0</v>
+      </c>
+      <c r="N180" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>660010</v>
       </c>
@@ -6035,8 +8163,20 @@
       <c r="J181" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K181" s="7">
+        <v>0</v>
+      </c>
+      <c r="L181" s="7">
+        <v>0</v>
+      </c>
+      <c r="M181" s="7">
+        <v>0</v>
+      </c>
+      <c r="N181" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>670020</v>
       </c>
@@ -6064,8 +8204,20 @@
       <c r="J182" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K182" s="7">
+        <v>0</v>
+      </c>
+      <c r="L182" s="7">
+        <v>0</v>
+      </c>
+      <c r="M182" s="7">
+        <v>0</v>
+      </c>
+      <c r="N182" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>670010</v>
       </c>
@@ -6093,8 +8245,20 @@
       <c r="J183" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K183" s="7">
+        <v>0</v>
+      </c>
+      <c r="L183" s="7">
+        <v>0</v>
+      </c>
+      <c r="M183" s="7">
+        <v>0</v>
+      </c>
+      <c r="N183" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>680020</v>
       </c>
@@ -6122,8 +8286,20 @@
       <c r="J184" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K184" s="7">
+        <v>0</v>
+      </c>
+      <c r="L184" s="7">
+        <v>0</v>
+      </c>
+      <c r="M184" s="7">
+        <v>0</v>
+      </c>
+      <c r="N184" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>680010</v>
       </c>
@@ -6151,8 +8327,20 @@
       <c r="J185" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K185" s="7">
+        <v>0</v>
+      </c>
+      <c r="L185" s="7">
+        <v>0</v>
+      </c>
+      <c r="M185" s="7">
+        <v>0</v>
+      </c>
+      <c r="N185" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>690020</v>
       </c>
@@ -6180,8 +8368,20 @@
       <c r="J186" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K186" s="7">
+        <v>0</v>
+      </c>
+      <c r="L186" s="7">
+        <v>0</v>
+      </c>
+      <c r="M186" s="7">
+        <v>0</v>
+      </c>
+      <c r="N186" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>690010</v>
       </c>
@@ -6209,8 +8409,20 @@
       <c r="J187" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K187" s="7">
+        <v>0</v>
+      </c>
+      <c r="L187" s="7">
+        <v>0</v>
+      </c>
+      <c r="M187" s="7">
+        <v>0</v>
+      </c>
+      <c r="N187" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>700020</v>
       </c>
@@ -6238,8 +8450,20 @@
       <c r="J188" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K188" s="7">
+        <v>0</v>
+      </c>
+      <c r="L188" s="7">
+        <v>0</v>
+      </c>
+      <c r="M188" s="7">
+        <v>0</v>
+      </c>
+      <c r="N188" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>700010</v>
       </c>
@@ -6267,8 +8491,20 @@
       <c r="J189" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K189" s="7">
+        <v>0</v>
+      </c>
+      <c r="L189" s="7">
+        <v>0</v>
+      </c>
+      <c r="M189" s="7">
+        <v>0</v>
+      </c>
+      <c r="N189" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>710020</v>
       </c>
@@ -6296,8 +8532,20 @@
       <c r="J190" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K190" s="7">
+        <v>0</v>
+      </c>
+      <c r="L190" s="7">
+        <v>0</v>
+      </c>
+      <c r="M190" s="7">
+        <v>0</v>
+      </c>
+      <c r="N190" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>710010</v>
       </c>
@@ -6325,8 +8573,20 @@
       <c r="J191" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K191" s="7">
+        <v>0</v>
+      </c>
+      <c r="L191" s="7">
+        <v>0</v>
+      </c>
+      <c r="M191" s="7">
+        <v>0</v>
+      </c>
+      <c r="N191" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>720020</v>
       </c>
@@ -6354,8 +8614,20 @@
       <c r="J192" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K192" s="7">
+        <v>0</v>
+      </c>
+      <c r="L192" s="7">
+        <v>0</v>
+      </c>
+      <c r="M192" s="7">
+        <v>0</v>
+      </c>
+      <c r="N192" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>720010</v>
       </c>
@@ -6383,8 +8655,20 @@
       <c r="J193" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K193" s="7">
+        <v>0</v>
+      </c>
+      <c r="L193" s="7">
+        <v>0</v>
+      </c>
+      <c r="M193" s="7">
+        <v>0</v>
+      </c>
+      <c r="N193" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>730020</v>
       </c>
@@ -6412,8 +8696,20 @@
       <c r="J194" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K194" s="7">
+        <v>0</v>
+      </c>
+      <c r="L194" s="7">
+        <v>0</v>
+      </c>
+      <c r="M194" s="7">
+        <v>0</v>
+      </c>
+      <c r="N194" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>730010</v>
       </c>
@@ -6441,8 +8737,20 @@
       <c r="J195" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K195" s="7">
+        <v>0</v>
+      </c>
+      <c r="L195" s="7">
+        <v>0</v>
+      </c>
+      <c r="M195" s="7">
+        <v>0</v>
+      </c>
+      <c r="N195" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>740020</v>
       </c>
@@ -6470,8 +8778,20 @@
       <c r="J196" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K196" s="7">
+        <v>0</v>
+      </c>
+      <c r="L196" s="7">
+        <v>0</v>
+      </c>
+      <c r="M196" s="7">
+        <v>0</v>
+      </c>
+      <c r="N196" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>740010</v>
       </c>
@@ -6499,8 +8819,20 @@
       <c r="J197" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K197" s="7">
+        <v>0</v>
+      </c>
+      <c r="L197" s="7">
+        <v>0</v>
+      </c>
+      <c r="M197" s="7">
+        <v>0</v>
+      </c>
+      <c r="N197" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>750020</v>
       </c>
@@ -6528,8 +8860,20 @@
       <c r="J198" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K198" s="7">
+        <v>0</v>
+      </c>
+      <c r="L198" s="7">
+        <v>0</v>
+      </c>
+      <c r="M198" s="7">
+        <v>0</v>
+      </c>
+      <c r="N198" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>750010</v>
       </c>
@@ -6557,8 +8901,20 @@
       <c r="J199" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K199" s="7">
+        <v>0</v>
+      </c>
+      <c r="L199" s="7">
+        <v>0</v>
+      </c>
+      <c r="M199" s="7">
+        <v>0</v>
+      </c>
+      <c r="N199" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>760020</v>
       </c>
@@ -6586,8 +8942,20 @@
       <c r="J200" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K200" s="7">
+        <v>0</v>
+      </c>
+      <c r="L200" s="7">
+        <v>0</v>
+      </c>
+      <c r="M200" s="7">
+        <v>0</v>
+      </c>
+      <c r="N200" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>760010</v>
       </c>
@@ -6615,8 +8983,20 @@
       <c r="J201" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K201" s="7">
+        <v>0</v>
+      </c>
+      <c r="L201" s="7">
+        <v>0</v>
+      </c>
+      <c r="M201" s="7">
+        <v>0</v>
+      </c>
+      <c r="N201" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>770020</v>
       </c>
@@ -6644,8 +9024,20 @@
       <c r="J202" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K202" s="7">
+        <v>0</v>
+      </c>
+      <c r="L202" s="7">
+        <v>0</v>
+      </c>
+      <c r="M202" s="7">
+        <v>0</v>
+      </c>
+      <c r="N202" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>770010</v>
       </c>
@@ -6673,8 +9065,20 @@
       <c r="J203" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K203" s="7">
+        <v>0</v>
+      </c>
+      <c r="L203" s="7">
+        <v>0</v>
+      </c>
+      <c r="M203" s="7">
+        <v>0</v>
+      </c>
+      <c r="N203" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>780020</v>
       </c>
@@ -6702,8 +9106,20 @@
       <c r="J204" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K204" s="7">
+        <v>0</v>
+      </c>
+      <c r="L204" s="7">
+        <v>0</v>
+      </c>
+      <c r="M204" s="7">
+        <v>0</v>
+      </c>
+      <c r="N204" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>780010</v>
       </c>
@@ -6731,8 +9147,20 @@
       <c r="J205" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K205" s="7">
+        <v>0</v>
+      </c>
+      <c r="L205" s="7">
+        <v>0</v>
+      </c>
+      <c r="M205" s="7">
+        <v>0</v>
+      </c>
+      <c r="N205" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>790020</v>
       </c>
@@ -6760,8 +9188,20 @@
       <c r="J206" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K206" s="7">
+        <v>0</v>
+      </c>
+      <c r="L206" s="7">
+        <v>0</v>
+      </c>
+      <c r="M206" s="7">
+        <v>0</v>
+      </c>
+      <c r="N206" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>790010</v>
       </c>
@@ -6789,8 +9229,20 @@
       <c r="J207" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K207" s="7">
+        <v>0</v>
+      </c>
+      <c r="L207" s="7">
+        <v>0</v>
+      </c>
+      <c r="M207" s="7">
+        <v>0</v>
+      </c>
+      <c r="N207" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>800020</v>
       </c>
@@ -6818,8 +9270,20 @@
       <c r="J208" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K208" s="7">
+        <v>0</v>
+      </c>
+      <c r="L208" s="7">
+        <v>0</v>
+      </c>
+      <c r="M208" s="7">
+        <v>0</v>
+      </c>
+      <c r="N208" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>800010</v>
       </c>
@@ -6847,8 +9311,20 @@
       <c r="J209" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K209" s="7">
+        <v>0</v>
+      </c>
+      <c r="L209" s="7">
+        <v>0</v>
+      </c>
+      <c r="M209" s="7">
+        <v>0</v>
+      </c>
+      <c r="N209" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>810020</v>
       </c>
@@ -6876,8 +9352,20 @@
       <c r="J210" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K210" s="7">
+        <v>0</v>
+      </c>
+      <c r="L210" s="7">
+        <v>0</v>
+      </c>
+      <c r="M210" s="7">
+        <v>0</v>
+      </c>
+      <c r="N210" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>810010</v>
       </c>
@@ -6905,8 +9393,20 @@
       <c r="J211" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K211" s="7">
+        <v>0</v>
+      </c>
+      <c r="L211" s="7">
+        <v>0</v>
+      </c>
+      <c r="M211" s="7">
+        <v>0</v>
+      </c>
+      <c r="N211" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>820020</v>
       </c>
@@ -6934,8 +9434,20 @@
       <c r="J212" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K212" s="7">
+        <v>0</v>
+      </c>
+      <c r="L212" s="7">
+        <v>0</v>
+      </c>
+      <c r="M212" s="7">
+        <v>0</v>
+      </c>
+      <c r="N212" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>820010</v>
       </c>
@@ -6963,8 +9475,20 @@
       <c r="J213" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K213" s="7">
+        <v>0</v>
+      </c>
+      <c r="L213" s="7">
+        <v>0</v>
+      </c>
+      <c r="M213" s="7">
+        <v>0</v>
+      </c>
+      <c r="N213" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>830020</v>
       </c>
@@ -6992,8 +9516,20 @@
       <c r="J214" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K214" s="7">
+        <v>0</v>
+      </c>
+      <c r="L214" s="7">
+        <v>0</v>
+      </c>
+      <c r="M214" s="7">
+        <v>0</v>
+      </c>
+      <c r="N214" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>830010</v>
       </c>
@@ -7021,8 +9557,20 @@
       <c r="J215" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K215" s="7">
+        <v>0</v>
+      </c>
+      <c r="L215" s="7">
+        <v>0</v>
+      </c>
+      <c r="M215" s="7">
+        <v>0</v>
+      </c>
+      <c r="N215" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>840020</v>
       </c>
@@ -7050,8 +9598,20 @@
       <c r="J216" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K216" s="7">
+        <v>0</v>
+      </c>
+      <c r="L216" s="7">
+        <v>0</v>
+      </c>
+      <c r="M216" s="7">
+        <v>0</v>
+      </c>
+      <c r="N216" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>840010</v>
       </c>
@@ -7079,8 +9639,20 @@
       <c r="J217" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K217" s="7">
+        <v>0</v>
+      </c>
+      <c r="L217" s="7">
+        <v>0</v>
+      </c>
+      <c r="M217" s="7">
+        <v>0</v>
+      </c>
+      <c r="N217" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>850020</v>
       </c>
@@ -7108,8 +9680,20 @@
       <c r="J218" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K218" s="7">
+        <v>0</v>
+      </c>
+      <c r="L218" s="7">
+        <v>0</v>
+      </c>
+      <c r="M218" s="7">
+        <v>0</v>
+      </c>
+      <c r="N218" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>850010</v>
       </c>
@@ -7137,8 +9721,20 @@
       <c r="J219" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K219" s="7">
+        <v>0</v>
+      </c>
+      <c r="L219" s="7">
+        <v>0</v>
+      </c>
+      <c r="M219" s="7">
+        <v>0</v>
+      </c>
+      <c r="N219" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>860020</v>
       </c>
@@ -7166,8 +9762,20 @@
       <c r="J220" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K220" s="7">
+        <v>0</v>
+      </c>
+      <c r="L220" s="7">
+        <v>0</v>
+      </c>
+      <c r="M220" s="7">
+        <v>0</v>
+      </c>
+      <c r="N220" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>860010</v>
       </c>
@@ -7195,8 +9803,20 @@
       <c r="J221" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K221" s="7">
+        <v>0</v>
+      </c>
+      <c r="L221" s="7">
+        <v>0</v>
+      </c>
+      <c r="M221" s="7">
+        <v>0</v>
+      </c>
+      <c r="N221" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>870020</v>
       </c>
@@ -7224,8 +9844,20 @@
       <c r="J222" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K222" s="7">
+        <v>0</v>
+      </c>
+      <c r="L222" s="7">
+        <v>0</v>
+      </c>
+      <c r="M222" s="7">
+        <v>0</v>
+      </c>
+      <c r="N222" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>870010</v>
       </c>
@@ -7253,8 +9885,20 @@
       <c r="J223" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K223" s="7">
+        <v>0</v>
+      </c>
+      <c r="L223" s="7">
+        <v>0</v>
+      </c>
+      <c r="M223" s="7">
+        <v>0</v>
+      </c>
+      <c r="N223" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>880020</v>
       </c>
@@ -7282,8 +9926,20 @@
       <c r="J224" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K224" s="7">
+        <v>0</v>
+      </c>
+      <c r="L224" s="7">
+        <v>0</v>
+      </c>
+      <c r="M224" s="7">
+        <v>0</v>
+      </c>
+      <c r="N224" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>880010</v>
       </c>
@@ -7311,8 +9967,20 @@
       <c r="J225" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K225" s="7">
+        <v>0</v>
+      </c>
+      <c r="L225" s="7">
+        <v>0</v>
+      </c>
+      <c r="M225" s="7">
+        <v>0</v>
+      </c>
+      <c r="N225" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>890020</v>
       </c>
@@ -7340,8 +10008,20 @@
       <c r="J226" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K226" s="7">
+        <v>0</v>
+      </c>
+      <c r="L226" s="7">
+        <v>0</v>
+      </c>
+      <c r="M226" s="7">
+        <v>0</v>
+      </c>
+      <c r="N226" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>890010</v>
       </c>
@@ -7369,8 +10049,20 @@
       <c r="J227" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K227" s="7">
+        <v>0</v>
+      </c>
+      <c r="L227" s="7">
+        <v>0</v>
+      </c>
+      <c r="M227" s="7">
+        <v>0</v>
+      </c>
+      <c r="N227" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>900020</v>
       </c>
@@ -7398,8 +10090,20 @@
       <c r="J228" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K228" s="7">
+        <v>0</v>
+      </c>
+      <c r="L228" s="7">
+        <v>0</v>
+      </c>
+      <c r="M228" s="7">
+        <v>0</v>
+      </c>
+      <c r="N228" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>900010</v>
       </c>
@@ -7427,8 +10131,20 @@
       <c r="J229" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K229" s="7">
+        <v>0</v>
+      </c>
+      <c r="L229" s="7">
+        <v>0</v>
+      </c>
+      <c r="M229" s="7">
+        <v>0</v>
+      </c>
+      <c r="N229" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>910020</v>
       </c>
@@ -7456,8 +10172,20 @@
       <c r="J230" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K230" s="7">
+        <v>0</v>
+      </c>
+      <c r="L230" s="7">
+        <v>0</v>
+      </c>
+      <c r="M230" s="7">
+        <v>0</v>
+      </c>
+      <c r="N230" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>910010</v>
       </c>
@@ -7485,8 +10213,20 @@
       <c r="J231" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K231" s="7">
+        <v>0</v>
+      </c>
+      <c r="L231" s="7">
+        <v>0</v>
+      </c>
+      <c r="M231" s="7">
+        <v>0</v>
+      </c>
+      <c r="N231" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>920020</v>
       </c>
@@ -7514,8 +10254,20 @@
       <c r="J232" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K232" s="7">
+        <v>0</v>
+      </c>
+      <c r="L232" s="7">
+        <v>0</v>
+      </c>
+      <c r="M232" s="7">
+        <v>0</v>
+      </c>
+      <c r="N232" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>920010</v>
       </c>
@@ -7543,8 +10295,20 @@
       <c r="J233" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K233" s="7">
+        <v>0</v>
+      </c>
+      <c r="L233" s="7">
+        <v>0</v>
+      </c>
+      <c r="M233" s="7">
+        <v>0</v>
+      </c>
+      <c r="N233" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>930020</v>
       </c>
@@ -7572,8 +10336,20 @@
       <c r="J234" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K234" s="7">
+        <v>0</v>
+      </c>
+      <c r="L234" s="7">
+        <v>0</v>
+      </c>
+      <c r="M234" s="7">
+        <v>0</v>
+      </c>
+      <c r="N234" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>930010</v>
       </c>
@@ -7601,8 +10377,20 @@
       <c r="J235" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K235" s="7">
+        <v>0</v>
+      </c>
+      <c r="L235" s="7">
+        <v>0</v>
+      </c>
+      <c r="M235" s="7">
+        <v>0</v>
+      </c>
+      <c r="N235" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>940020</v>
       </c>
@@ -7630,8 +10418,20 @@
       <c r="J236" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K236" s="7">
+        <v>0</v>
+      </c>
+      <c r="L236" s="7">
+        <v>0</v>
+      </c>
+      <c r="M236" s="7">
+        <v>0</v>
+      </c>
+      <c r="N236" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>940010</v>
       </c>
@@ -7659,8 +10459,20 @@
       <c r="J237" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K237" s="7">
+        <v>0</v>
+      </c>
+      <c r="L237" s="7">
+        <v>0</v>
+      </c>
+      <c r="M237" s="7">
+        <v>0</v>
+      </c>
+      <c r="N237" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>950020</v>
       </c>
@@ -7688,8 +10500,20 @@
       <c r="J238" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K238" s="7">
+        <v>0</v>
+      </c>
+      <c r="L238" s="7">
+        <v>0</v>
+      </c>
+      <c r="M238" s="7">
+        <v>0</v>
+      </c>
+      <c r="N238" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>950010</v>
       </c>
@@ -7717,8 +10541,20 @@
       <c r="J239" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K239" s="7">
+        <v>0</v>
+      </c>
+      <c r="L239" s="7">
+        <v>0</v>
+      </c>
+      <c r="M239" s="7">
+        <v>0</v>
+      </c>
+      <c r="N239" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>960020</v>
       </c>
@@ -7746,8 +10582,20 @@
       <c r="J240" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K240" s="7">
+        <v>0</v>
+      </c>
+      <c r="L240" s="7">
+        <v>0</v>
+      </c>
+      <c r="M240" s="7">
+        <v>0</v>
+      </c>
+      <c r="N240" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>960010</v>
       </c>
@@ -7775,8 +10623,20 @@
       <c r="J241" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K241" s="7">
+        <v>0</v>
+      </c>
+      <c r="L241" s="7">
+        <v>0</v>
+      </c>
+      <c r="M241" s="7">
+        <v>0</v>
+      </c>
+      <c r="N241" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>970020</v>
       </c>
@@ -7804,8 +10664,20 @@
       <c r="J242" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K242" s="7">
+        <v>0</v>
+      </c>
+      <c r="L242" s="7">
+        <v>0</v>
+      </c>
+      <c r="M242" s="7">
+        <v>0</v>
+      </c>
+      <c r="N242" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>970010</v>
       </c>
@@ -7833,8 +10705,20 @@
       <c r="J243" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K243" s="7">
+        <v>0</v>
+      </c>
+      <c r="L243" s="7">
+        <v>0</v>
+      </c>
+      <c r="M243" s="7">
+        <v>0</v>
+      </c>
+      <c r="N243" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>980020</v>
       </c>
@@ -7862,8 +10746,20 @@
       <c r="J244" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K244" s="7">
+        <v>0</v>
+      </c>
+      <c r="L244" s="7">
+        <v>0</v>
+      </c>
+      <c r="M244" s="7">
+        <v>0</v>
+      </c>
+      <c r="N244" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>980010</v>
       </c>
@@ -7891,8 +10787,20 @@
       <c r="J245" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K245" s="7">
+        <v>0</v>
+      </c>
+      <c r="L245" s="7">
+        <v>0</v>
+      </c>
+      <c r="M245" s="7">
+        <v>0</v>
+      </c>
+      <c r="N245" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>990020</v>
       </c>
@@ -7920,8 +10828,20 @@
       <c r="J246" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K246" s="7">
+        <v>0</v>
+      </c>
+      <c r="L246" s="7">
+        <v>0</v>
+      </c>
+      <c r="M246" s="7">
+        <v>0</v>
+      </c>
+      <c r="N246" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>990010</v>
       </c>
@@ -7949,8 +10869,20 @@
       <c r="J247" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K247" s="7">
+        <v>0</v>
+      </c>
+      <c r="L247" s="7">
+        <v>0</v>
+      </c>
+      <c r="M247" s="7">
+        <v>0</v>
+      </c>
+      <c r="N247" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>1000020</v>
       </c>
@@ -7978,8 +10910,20 @@
       <c r="J248" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K248" s="7">
+        <v>0</v>
+      </c>
+      <c r="L248" s="7">
+        <v>0</v>
+      </c>
+      <c r="M248" s="7">
+        <v>0</v>
+      </c>
+      <c r="N248" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>1000010</v>
       </c>
@@ -8007,8 +10951,20 @@
       <c r="J249" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K249" s="7">
+        <v>0</v>
+      </c>
+      <c r="L249" s="7">
+        <v>0</v>
+      </c>
+      <c r="M249" s="7">
+        <v>0</v>
+      </c>
+      <c r="N249" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>1010020</v>
       </c>
@@ -8036,8 +10992,20 @@
       <c r="J250" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K250" s="7">
+        <v>0</v>
+      </c>
+      <c r="L250" s="7">
+        <v>0</v>
+      </c>
+      <c r="M250" s="7">
+        <v>0</v>
+      </c>
+      <c r="N250" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>1010010</v>
       </c>
@@ -8065,8 +11033,20 @@
       <c r="J251" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K251" s="7">
+        <v>0</v>
+      </c>
+      <c r="L251" s="7">
+        <v>0</v>
+      </c>
+      <c r="M251" s="7">
+        <v>0</v>
+      </c>
+      <c r="N251" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>1020020</v>
       </c>
@@ -8094,8 +11074,20 @@
       <c r="J252" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K252" s="7">
+        <v>0</v>
+      </c>
+      <c r="L252" s="7">
+        <v>0</v>
+      </c>
+      <c r="M252" s="7">
+        <v>0</v>
+      </c>
+      <c r="N252" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>1020010</v>
       </c>
@@ -8123,8 +11115,20 @@
       <c r="J253" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K253" s="7">
+        <v>0</v>
+      </c>
+      <c r="L253" s="7">
+        <v>0</v>
+      </c>
+      <c r="M253" s="7">
+        <v>0</v>
+      </c>
+      <c r="N253" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
         <v>1030020</v>
       </c>
@@ -8152,8 +11156,20 @@
       <c r="J254" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K254" s="7">
+        <v>0</v>
+      </c>
+      <c r="L254" s="7">
+        <v>0</v>
+      </c>
+      <c r="M254" s="7">
+        <v>0</v>
+      </c>
+      <c r="N254" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>1030010</v>
       </c>
@@ -8181,8 +11197,20 @@
       <c r="J255" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K255" s="7">
+        <v>0</v>
+      </c>
+      <c r="L255" s="7">
+        <v>0</v>
+      </c>
+      <c r="M255" s="7">
+        <v>0</v>
+      </c>
+      <c r="N255" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
         <v>1040020</v>
       </c>
@@ -8210,8 +11238,20 @@
       <c r="J256" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K256" s="7">
+        <v>0</v>
+      </c>
+      <c r="L256" s="7">
+        <v>0</v>
+      </c>
+      <c r="M256" s="7">
+        <v>0</v>
+      </c>
+      <c r="N256" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>1040010</v>
       </c>
@@ -8239,8 +11279,20 @@
       <c r="J257" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K257" s="7">
+        <v>0</v>
+      </c>
+      <c r="L257" s="7">
+        <v>0</v>
+      </c>
+      <c r="M257" s="7">
+        <v>0</v>
+      </c>
+      <c r="N257" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>1050020</v>
       </c>
@@ -8268,8 +11320,20 @@
       <c r="J258" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K258" s="7">
+        <v>0</v>
+      </c>
+      <c r="L258" s="7">
+        <v>0</v>
+      </c>
+      <c r="M258" s="7">
+        <v>0</v>
+      </c>
+      <c r="N258" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>1050010</v>
       </c>
@@ -8297,8 +11361,20 @@
       <c r="J259" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K259" s="7">
+        <v>0</v>
+      </c>
+      <c r="L259" s="7">
+        <v>0</v>
+      </c>
+      <c r="M259" s="7">
+        <v>0</v>
+      </c>
+      <c r="N259" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>1060020</v>
       </c>
@@ -8326,8 +11402,20 @@
       <c r="J260" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K260" s="7">
+        <v>0</v>
+      </c>
+      <c r="L260" s="7">
+        <v>0</v>
+      </c>
+      <c r="M260" s="7">
+        <v>0</v>
+      </c>
+      <c r="N260" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
         <v>1060010</v>
       </c>
@@ -8355,8 +11443,20 @@
       <c r="J261" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K261" s="7">
+        <v>0</v>
+      </c>
+      <c r="L261" s="7">
+        <v>0</v>
+      </c>
+      <c r="M261" s="7">
+        <v>0</v>
+      </c>
+      <c r="N261" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>1070020</v>
       </c>
@@ -8384,8 +11484,20 @@
       <c r="J262" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K262" s="7">
+        <v>0</v>
+      </c>
+      <c r="L262" s="7">
+        <v>0</v>
+      </c>
+      <c r="M262" s="7">
+        <v>0</v>
+      </c>
+      <c r="N262" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>1070010</v>
       </c>
@@ -8413,8 +11525,20 @@
       <c r="J263" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K263" s="7">
+        <v>0</v>
+      </c>
+      <c r="L263" s="7">
+        <v>0</v>
+      </c>
+      <c r="M263" s="7">
+        <v>0</v>
+      </c>
+      <c r="N263" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>1080020</v>
       </c>
@@ -8442,8 +11566,20 @@
       <c r="J264" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K264" s="7">
+        <v>0</v>
+      </c>
+      <c r="L264" s="7">
+        <v>0</v>
+      </c>
+      <c r="M264" s="7">
+        <v>0</v>
+      </c>
+      <c r="N264" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>1080010</v>
       </c>
@@ -8471,8 +11607,20 @@
       <c r="J265" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K265" s="7">
+        <v>0</v>
+      </c>
+      <c r="L265" s="7">
+        <v>0</v>
+      </c>
+      <c r="M265" s="7">
+        <v>0</v>
+      </c>
+      <c r="N265" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>1090020</v>
       </c>
@@ -8500,8 +11648,20 @@
       <c r="J266" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K266" s="7">
+        <v>0</v>
+      </c>
+      <c r="L266" s="7">
+        <v>0</v>
+      </c>
+      <c r="M266" s="7">
+        <v>0</v>
+      </c>
+      <c r="N266" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>1090010</v>
       </c>
@@ -8529,8 +11689,20 @@
       <c r="J267" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K267" s="7">
+        <v>0</v>
+      </c>
+      <c r="L267" s="7">
+        <v>0</v>
+      </c>
+      <c r="M267" s="7">
+        <v>0</v>
+      </c>
+      <c r="N267" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>1100020</v>
       </c>
@@ -8558,8 +11730,20 @@
       <c r="J268" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K268" s="7">
+        <v>0</v>
+      </c>
+      <c r="L268" s="7">
+        <v>0</v>
+      </c>
+      <c r="M268" s="7">
+        <v>0</v>
+      </c>
+      <c r="N268" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>1100010</v>
       </c>
@@ -8587,8 +11771,20 @@
       <c r="J269" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K269" s="7">
+        <v>0</v>
+      </c>
+      <c r="L269" s="7">
+        <v>0</v>
+      </c>
+      <c r="M269" s="7">
+        <v>0</v>
+      </c>
+      <c r="N269" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>1110020</v>
       </c>
@@ -8616,8 +11812,20 @@
       <c r="J270" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K270" s="7">
+        <v>0</v>
+      </c>
+      <c r="L270" s="7">
+        <v>0</v>
+      </c>
+      <c r="M270" s="7">
+        <v>0</v>
+      </c>
+      <c r="N270" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>1110010</v>
       </c>
@@ -8645,8 +11853,20 @@
       <c r="J271" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K271" s="7">
+        <v>0</v>
+      </c>
+      <c r="L271" s="7">
+        <v>0</v>
+      </c>
+      <c r="M271" s="7">
+        <v>0</v>
+      </c>
+      <c r="N271" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>1120020</v>
       </c>
@@ -8674,8 +11894,20 @@
       <c r="J272" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K272" s="7">
+        <v>0</v>
+      </c>
+      <c r="L272" s="7">
+        <v>0</v>
+      </c>
+      <c r="M272" s="7">
+        <v>0</v>
+      </c>
+      <c r="N272" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>1120010</v>
       </c>
@@ -8703,8 +11935,20 @@
       <c r="J273" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K273" s="7">
+        <v>0</v>
+      </c>
+      <c r="L273" s="7">
+        <v>0</v>
+      </c>
+      <c r="M273" s="7">
+        <v>0</v>
+      </c>
+      <c r="N273" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>1130020</v>
       </c>
@@ -8732,8 +11976,20 @@
       <c r="J274" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K274" s="7">
+        <v>0</v>
+      </c>
+      <c r="L274" s="7">
+        <v>0</v>
+      </c>
+      <c r="M274" s="7">
+        <v>0</v>
+      </c>
+      <c r="N274" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>1130010</v>
       </c>
@@ -8761,8 +12017,20 @@
       <c r="J275" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K275" s="7">
+        <v>0</v>
+      </c>
+      <c r="L275" s="7">
+        <v>0</v>
+      </c>
+      <c r="M275" s="7">
+        <v>0</v>
+      </c>
+      <c r="N275" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>1140020</v>
       </c>
@@ -8790,8 +12058,20 @@
       <c r="J276" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K276" s="7">
+        <v>0</v>
+      </c>
+      <c r="L276" s="7">
+        <v>0</v>
+      </c>
+      <c r="M276" s="7">
+        <v>0</v>
+      </c>
+      <c r="N276" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>1140010</v>
       </c>
@@ -8819,8 +12099,20 @@
       <c r="J277" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K277" s="7">
+        <v>0</v>
+      </c>
+      <c r="L277" s="7">
+        <v>0</v>
+      </c>
+      <c r="M277" s="7">
+        <v>0</v>
+      </c>
+      <c r="N277" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>1150020</v>
       </c>
@@ -8848,8 +12140,20 @@
       <c r="J278" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K278" s="7">
+        <v>0</v>
+      </c>
+      <c r="L278" s="7">
+        <v>0</v>
+      </c>
+      <c r="M278" s="7">
+        <v>0</v>
+      </c>
+      <c r="N278" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>1150010</v>
       </c>
@@ -8877,8 +12181,20 @@
       <c r="J279" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K279" s="7">
+        <v>0</v>
+      </c>
+      <c r="L279" s="7">
+        <v>0</v>
+      </c>
+      <c r="M279" s="7">
+        <v>0</v>
+      </c>
+      <c r="N279" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>1160020</v>
       </c>
@@ -8906,8 +12222,20 @@
       <c r="J280" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K280" s="7">
+        <v>0</v>
+      </c>
+      <c r="L280" s="7">
+        <v>0</v>
+      </c>
+      <c r="M280" s="7">
+        <v>0</v>
+      </c>
+      <c r="N280" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
         <v>1160010</v>
       </c>
@@ -8935,8 +12263,20 @@
       <c r="J281" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K281" s="7">
+        <v>0</v>
+      </c>
+      <c r="L281" s="7">
+        <v>0</v>
+      </c>
+      <c r="M281" s="7">
+        <v>0</v>
+      </c>
+      <c r="N281" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>1170020</v>
       </c>
@@ -8964,8 +12304,20 @@
       <c r="J282" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K282" s="7">
+        <v>0</v>
+      </c>
+      <c r="L282" s="7">
+        <v>0</v>
+      </c>
+      <c r="M282" s="7">
+        <v>0</v>
+      </c>
+      <c r="N282" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>1170010</v>
       </c>
@@ -8993,8 +12345,20 @@
       <c r="J283" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K283" s="7">
+        <v>0</v>
+      </c>
+      <c r="L283" s="7">
+        <v>0</v>
+      </c>
+      <c r="M283" s="7">
+        <v>0</v>
+      </c>
+      <c r="N283" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>1180020</v>
       </c>
@@ -9022,8 +12386,20 @@
       <c r="J284" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K284" s="7">
+        <v>0</v>
+      </c>
+      <c r="L284" s="7">
+        <v>0</v>
+      </c>
+      <c r="M284" s="7">
+        <v>0</v>
+      </c>
+      <c r="N284" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>1180010</v>
       </c>
@@ -9051,8 +12427,20 @@
       <c r="J285" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K285" s="7">
+        <v>0</v>
+      </c>
+      <c r="L285" s="7">
+        <v>0</v>
+      </c>
+      <c r="M285" s="7">
+        <v>0</v>
+      </c>
+      <c r="N285" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>1190020</v>
       </c>
@@ -9080,8 +12468,20 @@
       <c r="J286" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K286" s="7">
+        <v>0</v>
+      </c>
+      <c r="L286" s="7">
+        <v>0</v>
+      </c>
+      <c r="M286" s="7">
+        <v>0</v>
+      </c>
+      <c r="N286" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>1190010</v>
       </c>
@@ -9109,8 +12509,20 @@
       <c r="J287" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K287" s="7">
+        <v>0</v>
+      </c>
+      <c r="L287" s="7">
+        <v>0</v>
+      </c>
+      <c r="M287" s="7">
+        <v>0</v>
+      </c>
+      <c r="N287" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>1200020</v>
       </c>
@@ -9138,8 +12550,20 @@
       <c r="J288" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K288" s="7">
+        <v>0</v>
+      </c>
+      <c r="L288" s="7">
+        <v>0</v>
+      </c>
+      <c r="M288" s="7">
+        <v>0</v>
+      </c>
+      <c r="N288" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>1200010</v>
       </c>
@@ -9167,8 +12591,20 @@
       <c r="J289" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K289" s="7">
+        <v>0</v>
+      </c>
+      <c r="L289" s="7">
+        <v>0</v>
+      </c>
+      <c r="M289" s="7">
+        <v>0</v>
+      </c>
+      <c r="N289" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>1210020</v>
       </c>
@@ -9196,8 +12632,20 @@
       <c r="J290" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K290" s="7">
+        <v>0</v>
+      </c>
+      <c r="L290" s="7">
+        <v>0</v>
+      </c>
+      <c r="M290" s="7">
+        <v>0</v>
+      </c>
+      <c r="N290" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>1210010</v>
       </c>
@@ -9225,8 +12673,20 @@
       <c r="J291" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K291" s="7">
+        <v>0</v>
+      </c>
+      <c r="L291" s="7">
+        <v>0</v>
+      </c>
+      <c r="M291" s="7">
+        <v>0</v>
+      </c>
+      <c r="N291" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>1220020</v>
       </c>
@@ -9254,8 +12714,20 @@
       <c r="J292" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K292" s="7">
+        <v>0</v>
+      </c>
+      <c r="L292" s="7">
+        <v>0</v>
+      </c>
+      <c r="M292" s="7">
+        <v>0</v>
+      </c>
+      <c r="N292" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>1220010</v>
       </c>
@@ -9283,8 +12755,20 @@
       <c r="J293" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K293" s="7">
+        <v>0</v>
+      </c>
+      <c r="L293" s="7">
+        <v>0</v>
+      </c>
+      <c r="M293" s="7">
+        <v>0</v>
+      </c>
+      <c r="N293" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>1230020</v>
       </c>
@@ -9312,8 +12796,20 @@
       <c r="J294" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K294" s="7">
+        <v>0</v>
+      </c>
+      <c r="L294" s="7">
+        <v>0</v>
+      </c>
+      <c r="M294" s="7">
+        <v>0</v>
+      </c>
+      <c r="N294" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>1230010</v>
       </c>
@@ -9341,8 +12837,20 @@
       <c r="J295" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K295" s="7">
+        <v>0</v>
+      </c>
+      <c r="L295" s="7">
+        <v>0</v>
+      </c>
+      <c r="M295" s="7">
+        <v>0</v>
+      </c>
+      <c r="N295" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>1240020</v>
       </c>
@@ -9370,8 +12878,20 @@
       <c r="J296" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K296" s="7">
+        <v>0</v>
+      </c>
+      <c r="L296" s="7">
+        <v>0</v>
+      </c>
+      <c r="M296" s="7">
+        <v>0</v>
+      </c>
+      <c r="N296" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>1240010</v>
       </c>
@@ -9399,8 +12919,20 @@
       <c r="J297" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K297" s="7">
+        <v>0</v>
+      </c>
+      <c r="L297" s="7">
+        <v>0</v>
+      </c>
+      <c r="M297" s="7">
+        <v>0</v>
+      </c>
+      <c r="N297" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>1250020</v>
       </c>
@@ -9428,8 +12960,20 @@
       <c r="J298" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K298" s="7">
+        <v>0</v>
+      </c>
+      <c r="L298" s="7">
+        <v>0</v>
+      </c>
+      <c r="M298" s="7">
+        <v>0</v>
+      </c>
+      <c r="N298" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>1250010</v>
       </c>
@@ -9457,8 +13001,20 @@
       <c r="J299" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K299" s="7">
+        <v>0</v>
+      </c>
+      <c r="L299" s="7">
+        <v>0</v>
+      </c>
+      <c r="M299" s="7">
+        <v>0</v>
+      </c>
+      <c r="N299" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>1260020</v>
       </c>
@@ -9486,8 +13042,20 @@
       <c r="J300" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K300" s="7">
+        <v>0</v>
+      </c>
+      <c r="L300" s="7">
+        <v>0</v>
+      </c>
+      <c r="M300" s="7">
+        <v>0</v>
+      </c>
+      <c r="N300" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>1260010</v>
       </c>
@@ -9515,8 +13083,20 @@
       <c r="J301" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K301" s="7">
+        <v>0</v>
+      </c>
+      <c r="L301" s="7">
+        <v>0</v>
+      </c>
+      <c r="M301" s="7">
+        <v>0</v>
+      </c>
+      <c r="N301" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
         <v>1270020</v>
       </c>
@@ -9544,8 +13124,20 @@
       <c r="J302" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K302" s="7">
+        <v>0</v>
+      </c>
+      <c r="L302" s="7">
+        <v>0</v>
+      </c>
+      <c r="M302" s="7">
+        <v>0</v>
+      </c>
+      <c r="N302" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
         <v>1270010</v>
       </c>
@@ -9573,8 +13165,20 @@
       <c r="J303" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K303" s="7">
+        <v>0</v>
+      </c>
+      <c r="L303" s="7">
+        <v>0</v>
+      </c>
+      <c r="M303" s="7">
+        <v>0</v>
+      </c>
+      <c r="N303" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
         <v>1280020</v>
       </c>
@@ -9602,8 +13206,20 @@
       <c r="J304" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K304" s="7">
+        <v>0</v>
+      </c>
+      <c r="L304" s="7">
+        <v>0</v>
+      </c>
+      <c r="M304" s="7">
+        <v>0</v>
+      </c>
+      <c r="N304" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
         <v>1280010</v>
       </c>
@@ -9631,8 +13247,20 @@
       <c r="J305" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K305" s="7">
+        <v>0</v>
+      </c>
+      <c r="L305" s="7">
+        <v>0</v>
+      </c>
+      <c r="M305" s="7">
+        <v>0</v>
+      </c>
+      <c r="N305" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
         <v>1290020</v>
       </c>
@@ -9660,8 +13288,20 @@
       <c r="J306" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K306" s="7">
+        <v>0</v>
+      </c>
+      <c r="L306" s="7">
+        <v>0</v>
+      </c>
+      <c r="M306" s="7">
+        <v>0</v>
+      </c>
+      <c r="N306" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
         <v>1290010</v>
       </c>
@@ -9689,8 +13329,20 @@
       <c r="J307" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K307" s="7">
+        <v>0</v>
+      </c>
+      <c r="L307" s="7">
+        <v>0</v>
+      </c>
+      <c r="M307" s="7">
+        <v>0</v>
+      </c>
+      <c r="N307" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
         <v>1300020</v>
       </c>
@@ -9718,8 +13370,20 @@
       <c r="J308" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K308" s="7">
+        <v>0</v>
+      </c>
+      <c r="L308" s="7">
+        <v>0</v>
+      </c>
+      <c r="M308" s="7">
+        <v>0</v>
+      </c>
+      <c r="N308" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
         <v>1300010</v>
       </c>
@@ -9747,8 +13411,20 @@
       <c r="J309" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K309" s="7">
+        <v>0</v>
+      </c>
+      <c r="L309" s="7">
+        <v>0</v>
+      </c>
+      <c r="M309" s="7">
+        <v>0</v>
+      </c>
+      <c r="N309" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
         <v>1310020</v>
       </c>
@@ -9776,8 +13452,20 @@
       <c r="J310" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K310" s="7">
+        <v>0</v>
+      </c>
+      <c r="L310" s="7">
+        <v>0</v>
+      </c>
+      <c r="M310" s="7">
+        <v>0</v>
+      </c>
+      <c r="N310" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
         <v>1310010</v>
       </c>
@@ -9805,8 +13493,20 @@
       <c r="J311" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K311" s="7">
+        <v>0</v>
+      </c>
+      <c r="L311" s="7">
+        <v>0</v>
+      </c>
+      <c r="M311" s="7">
+        <v>0</v>
+      </c>
+      <c r="N311" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
         <v>1320020</v>
       </c>
@@ -9834,8 +13534,20 @@
       <c r="J312" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K312" s="7">
+        <v>0</v>
+      </c>
+      <c r="L312" s="7">
+        <v>0</v>
+      </c>
+      <c r="M312" s="7">
+        <v>0</v>
+      </c>
+      <c r="N312" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
         <v>1320010</v>
       </c>
@@ -9863,8 +13575,20 @@
       <c r="J313" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K313" s="7">
+        <v>0</v>
+      </c>
+      <c r="L313" s="7">
+        <v>0</v>
+      </c>
+      <c r="M313" s="7">
+        <v>0</v>
+      </c>
+      <c r="N313" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
         <v>1330020</v>
       </c>
@@ -9892,8 +13616,20 @@
       <c r="J314" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K314" s="7">
+        <v>0</v>
+      </c>
+      <c r="L314" s="7">
+        <v>0</v>
+      </c>
+      <c r="M314" s="7">
+        <v>0</v>
+      </c>
+      <c r="N314" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
         <v>1330010</v>
       </c>
@@ -9921,8 +13657,20 @@
       <c r="J315" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K315" s="7">
+        <v>0</v>
+      </c>
+      <c r="L315" s="7">
+        <v>0</v>
+      </c>
+      <c r="M315" s="7">
+        <v>0</v>
+      </c>
+      <c r="N315" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
         <v>1340020</v>
       </c>
@@ -9950,8 +13698,20 @@
       <c r="J316" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K316" s="7">
+        <v>0</v>
+      </c>
+      <c r="L316" s="7">
+        <v>0</v>
+      </c>
+      <c r="M316" s="7">
+        <v>0</v>
+      </c>
+      <c r="N316" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
         <v>1340010</v>
       </c>
@@ -9979,8 +13739,20 @@
       <c r="J317" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K317" s="7">
+        <v>0</v>
+      </c>
+      <c r="L317" s="7">
+        <v>0</v>
+      </c>
+      <c r="M317" s="7">
+        <v>0</v>
+      </c>
+      <c r="N317" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
         <v>1350020</v>
       </c>
@@ -10008,8 +13780,20 @@
       <c r="J318" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K318" s="7">
+        <v>0</v>
+      </c>
+      <c r="L318" s="7">
+        <v>0</v>
+      </c>
+      <c r="M318" s="7">
+        <v>0</v>
+      </c>
+      <c r="N318" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
         <v>1350010</v>
       </c>
@@ -10037,8 +13821,20 @@
       <c r="J319" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K319" s="7">
+        <v>0</v>
+      </c>
+      <c r="L319" s="7">
+        <v>0</v>
+      </c>
+      <c r="M319" s="7">
+        <v>0</v>
+      </c>
+      <c r="N319" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
         <v>1360020</v>
       </c>
@@ -10066,8 +13862,20 @@
       <c r="J320" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K320" s="7">
+        <v>0</v>
+      </c>
+      <c r="L320" s="7">
+        <v>0</v>
+      </c>
+      <c r="M320" s="7">
+        <v>0</v>
+      </c>
+      <c r="N320" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
         <v>1360010</v>
       </c>
@@ -10095,8 +13903,20 @@
       <c r="J321" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K321" s="7">
+        <v>0</v>
+      </c>
+      <c r="L321" s="7">
+        <v>0</v>
+      </c>
+      <c r="M321" s="7">
+        <v>0</v>
+      </c>
+      <c r="N321" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
         <v>1370020</v>
       </c>
@@ -10124,8 +13944,20 @@
       <c r="J322" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K322" s="7">
+        <v>0</v>
+      </c>
+      <c r="L322" s="7">
+        <v>0</v>
+      </c>
+      <c r="M322" s="7">
+        <v>0</v>
+      </c>
+      <c r="N322" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
         <v>1370010</v>
       </c>
@@ -10153,8 +13985,20 @@
       <c r="J323" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K323" s="7">
+        <v>0</v>
+      </c>
+      <c r="L323" s="7">
+        <v>0</v>
+      </c>
+      <c r="M323" s="7">
+        <v>0</v>
+      </c>
+      <c r="N323" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
         <v>1380020</v>
       </c>
@@ -10182,8 +14026,20 @@
       <c r="J324" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K324" s="7">
+        <v>0</v>
+      </c>
+      <c r="L324" s="7">
+        <v>0</v>
+      </c>
+      <c r="M324" s="7">
+        <v>0</v>
+      </c>
+      <c r="N324" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
         <v>1380010</v>
       </c>
@@ -10211,8 +14067,20 @@
       <c r="J325" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K325" s="7">
+        <v>0</v>
+      </c>
+      <c r="L325" s="7">
+        <v>0</v>
+      </c>
+      <c r="M325" s="7">
+        <v>0</v>
+      </c>
+      <c r="N325" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
         <v>1390020</v>
       </c>
@@ -10240,8 +14108,20 @@
       <c r="J326" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K326" s="7">
+        <v>0</v>
+      </c>
+      <c r="L326" s="7">
+        <v>0</v>
+      </c>
+      <c r="M326" s="7">
+        <v>0</v>
+      </c>
+      <c r="N326" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
         <v>1390010</v>
       </c>
@@ -10269,8 +14149,20 @@
       <c r="J327" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K327" s="7">
+        <v>0</v>
+      </c>
+      <c r="L327" s="7">
+        <v>0</v>
+      </c>
+      <c r="M327" s="7">
+        <v>0</v>
+      </c>
+      <c r="N327" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
         <v>1400020</v>
       </c>
@@ -10298,8 +14190,20 @@
       <c r="J328" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K328" s="7">
+        <v>0</v>
+      </c>
+      <c r="L328" s="7">
+        <v>0</v>
+      </c>
+      <c r="M328" s="7">
+        <v>0</v>
+      </c>
+      <c r="N328" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
         <v>1400010</v>
       </c>
@@ -10327,8 +14231,20 @@
       <c r="J329" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K329" s="7">
+        <v>0</v>
+      </c>
+      <c r="L329" s="7">
+        <v>0</v>
+      </c>
+      <c r="M329" s="7">
+        <v>0</v>
+      </c>
+      <c r="N329" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
         <v>1410020</v>
       </c>
@@ -10356,8 +14272,20 @@
       <c r="J330" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K330" s="7">
+        <v>0</v>
+      </c>
+      <c r="L330" s="7">
+        <v>0</v>
+      </c>
+      <c r="M330" s="7">
+        <v>0</v>
+      </c>
+      <c r="N330" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
         <v>1410010</v>
       </c>
@@ -10385,8 +14313,20 @@
       <c r="J331" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K331" s="7">
+        <v>0</v>
+      </c>
+      <c r="L331" s="7">
+        <v>0</v>
+      </c>
+      <c r="M331" s="7">
+        <v>0</v>
+      </c>
+      <c r="N331" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
         <v>1420020</v>
       </c>
@@ -10414,8 +14354,20 @@
       <c r="J332" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K332" s="7">
+        <v>0</v>
+      </c>
+      <c r="L332" s="7">
+        <v>0</v>
+      </c>
+      <c r="M332" s="7">
+        <v>0</v>
+      </c>
+      <c r="N332" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
         <v>1420010</v>
       </c>
@@ -10443,8 +14395,20 @@
       <c r="J333" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K333" s="7">
+        <v>0</v>
+      </c>
+      <c r="L333" s="7">
+        <v>0</v>
+      </c>
+      <c r="M333" s="7">
+        <v>0</v>
+      </c>
+      <c r="N333" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
         <v>1430020</v>
       </c>
@@ -10472,8 +14436,20 @@
       <c r="J334" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K334" s="7">
+        <v>0</v>
+      </c>
+      <c r="L334" s="7">
+        <v>0</v>
+      </c>
+      <c r="M334" s="7">
+        <v>0</v>
+      </c>
+      <c r="N334" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
         <v>1430010</v>
       </c>
@@ -10501,8 +14477,20 @@
       <c r="J335" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K335" s="7">
+        <v>0</v>
+      </c>
+      <c r="L335" s="7">
+        <v>0</v>
+      </c>
+      <c r="M335" s="7">
+        <v>0</v>
+      </c>
+      <c r="N335" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
         <v>1440020</v>
       </c>
@@ -10530,8 +14518,20 @@
       <c r="J336" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K336" s="7">
+        <v>0</v>
+      </c>
+      <c r="L336" s="7">
+        <v>0</v>
+      </c>
+      <c r="M336" s="7">
+        <v>0</v>
+      </c>
+      <c r="N336" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
         <v>1440010</v>
       </c>
@@ -10559,8 +14559,20 @@
       <c r="J337" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K337" s="7">
+        <v>0</v>
+      </c>
+      <c r="L337" s="7">
+        <v>0</v>
+      </c>
+      <c r="M337" s="7">
+        <v>0</v>
+      </c>
+      <c r="N337" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
         <v>1450020</v>
       </c>
@@ -10588,8 +14600,20 @@
       <c r="J338" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K338" s="7">
+        <v>0</v>
+      </c>
+      <c r="L338" s="7">
+        <v>0</v>
+      </c>
+      <c r="M338" s="7">
+        <v>0</v>
+      </c>
+      <c r="N338" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
         <v>1450010</v>
       </c>
@@ -10617,8 +14641,20 @@
       <c r="J339" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K339" s="7">
+        <v>0</v>
+      </c>
+      <c r="L339" s="7">
+        <v>0</v>
+      </c>
+      <c r="M339" s="7">
+        <v>0</v>
+      </c>
+      <c r="N339" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
         <v>1460020</v>
       </c>
@@ -10646,8 +14682,20 @@
       <c r="J340" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K340" s="7">
+        <v>0</v>
+      </c>
+      <c r="L340" s="7">
+        <v>0</v>
+      </c>
+      <c r="M340" s="7">
+        <v>0</v>
+      </c>
+      <c r="N340" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
         <v>1460010</v>
       </c>
@@ -10675,8 +14723,20 @@
       <c r="J341" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K341" s="7">
+        <v>0</v>
+      </c>
+      <c r="L341" s="7">
+        <v>0</v>
+      </c>
+      <c r="M341" s="7">
+        <v>0</v>
+      </c>
+      <c r="N341" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
         <v>1470020</v>
       </c>
@@ -10704,8 +14764,20 @@
       <c r="J342" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K342" s="7">
+        <v>0</v>
+      </c>
+      <c r="L342" s="7">
+        <v>0</v>
+      </c>
+      <c r="M342" s="7">
+        <v>0</v>
+      </c>
+      <c r="N342" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
         <v>1470010</v>
       </c>
@@ -10733,8 +14805,20 @@
       <c r="J343" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K343" s="7">
+        <v>0</v>
+      </c>
+      <c r="L343" s="7">
+        <v>0</v>
+      </c>
+      <c r="M343" s="7">
+        <v>0</v>
+      </c>
+      <c r="N343" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
         <v>1480020</v>
       </c>
@@ -10762,8 +14846,20 @@
       <c r="J344" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K344" s="7">
+        <v>0</v>
+      </c>
+      <c r="L344" s="7">
+        <v>0</v>
+      </c>
+      <c r="M344" s="7">
+        <v>0</v>
+      </c>
+      <c r="N344" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
         <v>1480010</v>
       </c>
@@ -10791,8 +14887,20 @@
       <c r="J345" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K345" s="7">
+        <v>0</v>
+      </c>
+      <c r="L345" s="7">
+        <v>0</v>
+      </c>
+      <c r="M345" s="7">
+        <v>0</v>
+      </c>
+      <c r="N345" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
         <v>1490020</v>
       </c>
@@ -10820,8 +14928,20 @@
       <c r="J346" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K346" s="7">
+        <v>0</v>
+      </c>
+      <c r="L346" s="7">
+        <v>0</v>
+      </c>
+      <c r="M346" s="7">
+        <v>0</v>
+      </c>
+      <c r="N346" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
         <v>1490010</v>
       </c>
@@ -10849,8 +14969,20 @@
       <c r="J347" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K347" s="7">
+        <v>0</v>
+      </c>
+      <c r="L347" s="7">
+        <v>0</v>
+      </c>
+      <c r="M347" s="7">
+        <v>0</v>
+      </c>
+      <c r="N347" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
         <v>1500020</v>
       </c>
@@ -10878,8 +15010,20 @@
       <c r="J348" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K348" s="7">
+        <v>0</v>
+      </c>
+      <c r="L348" s="7">
+        <v>0</v>
+      </c>
+      <c r="M348" s="7">
+        <v>0</v>
+      </c>
+      <c r="N348" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
         <v>1500010</v>
       </c>
@@ -10907,8 +15051,20 @@
       <c r="J349" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K349" s="7">
+        <v>0</v>
+      </c>
+      <c r="L349" s="7">
+        <v>0</v>
+      </c>
+      <c r="M349" s="7">
+        <v>0</v>
+      </c>
+      <c r="N349" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
         <v>1510020</v>
       </c>
@@ -10936,8 +15092,20 @@
       <c r="J350" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K350" s="7">
+        <v>0</v>
+      </c>
+      <c r="L350" s="7">
+        <v>0</v>
+      </c>
+      <c r="M350" s="7">
+        <v>0</v>
+      </c>
+      <c r="N350" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
         <v>1510010</v>
       </c>
@@ -10965,8 +15133,20 @@
       <c r="J351" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K351" s="7">
+        <v>0</v>
+      </c>
+      <c r="L351" s="7">
+        <v>0</v>
+      </c>
+      <c r="M351" s="7">
+        <v>0</v>
+      </c>
+      <c r="N351" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
         <v>1520020</v>
       </c>
@@ -10994,8 +15174,20 @@
       <c r="J352" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K352" s="7">
+        <v>0</v>
+      </c>
+      <c r="L352" s="7">
+        <v>0</v>
+      </c>
+      <c r="M352" s="7">
+        <v>0</v>
+      </c>
+      <c r="N352" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
         <v>1520010</v>
       </c>
@@ -11023,8 +15215,20 @@
       <c r="J353" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K353" s="7">
+        <v>0</v>
+      </c>
+      <c r="L353" s="7">
+        <v>0</v>
+      </c>
+      <c r="M353" s="7">
+        <v>0</v>
+      </c>
+      <c r="N353" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
         <v>1530020</v>
       </c>
@@ -11052,8 +15256,20 @@
       <c r="J354" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K354" s="7">
+        <v>0</v>
+      </c>
+      <c r="L354" s="7">
+        <v>0</v>
+      </c>
+      <c r="M354" s="7">
+        <v>0</v>
+      </c>
+      <c r="N354" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
         <v>1530010</v>
       </c>
@@ -11081,8 +15297,20 @@
       <c r="J355" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K355" s="7">
+        <v>0</v>
+      </c>
+      <c r="L355" s="7">
+        <v>0</v>
+      </c>
+      <c r="M355" s="7">
+        <v>0</v>
+      </c>
+      <c r="N355" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
         <v>1540020</v>
       </c>
@@ -11110,8 +15338,20 @@
       <c r="J356" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K356" s="7">
+        <v>0</v>
+      </c>
+      <c r="L356" s="7">
+        <v>0</v>
+      </c>
+      <c r="M356" s="7">
+        <v>0</v>
+      </c>
+      <c r="N356" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
         <v>1540010</v>
       </c>
@@ -11139,8 +15379,20 @@
       <c r="J357" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K357" s="7">
+        <v>0</v>
+      </c>
+      <c r="L357" s="7">
+        <v>0</v>
+      </c>
+      <c r="M357" s="7">
+        <v>0</v>
+      </c>
+      <c r="N357" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
         <v>1550020</v>
       </c>
@@ -11168,8 +15420,20 @@
       <c r="J358" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K358" s="7">
+        <v>0</v>
+      </c>
+      <c r="L358" s="7">
+        <v>0</v>
+      </c>
+      <c r="M358" s="7">
+        <v>0</v>
+      </c>
+      <c r="N358" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
         <v>1550010</v>
       </c>
@@ -11197,8 +15461,20 @@
       <c r="J359" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K359" s="7">
+        <v>0</v>
+      </c>
+      <c r="L359" s="7">
+        <v>0</v>
+      </c>
+      <c r="M359" s="7">
+        <v>0</v>
+      </c>
+      <c r="N359" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
         <v>1560020</v>
       </c>
@@ -11226,8 +15502,20 @@
       <c r="J360" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K360" s="7">
+        <v>0</v>
+      </c>
+      <c r="L360" s="7">
+        <v>0</v>
+      </c>
+      <c r="M360" s="7">
+        <v>0</v>
+      </c>
+      <c r="N360" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
         <v>1560010</v>
       </c>
@@ -11255,8 +15543,20 @@
       <c r="J361" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K361" s="7">
+        <v>0</v>
+      </c>
+      <c r="L361" s="7">
+        <v>0</v>
+      </c>
+      <c r="M361" s="7">
+        <v>0</v>
+      </c>
+      <c r="N361" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
         <v>1570020</v>
       </c>
@@ -11284,8 +15584,20 @@
       <c r="J362" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K362" s="7">
+        <v>0</v>
+      </c>
+      <c r="L362" s="7">
+        <v>0</v>
+      </c>
+      <c r="M362" s="7">
+        <v>0</v>
+      </c>
+      <c r="N362" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
         <v>1570010</v>
       </c>
@@ -11313,8 +15625,20 @@
       <c r="J363" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K363" s="7">
+        <v>0</v>
+      </c>
+      <c r="L363" s="7">
+        <v>0</v>
+      </c>
+      <c r="M363" s="7">
+        <v>0</v>
+      </c>
+      <c r="N363" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
         <v>1580020</v>
       </c>
@@ -11342,8 +15666,20 @@
       <c r="J364" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K364" s="7">
+        <v>0</v>
+      </c>
+      <c r="L364" s="7">
+        <v>0</v>
+      </c>
+      <c r="M364" s="7">
+        <v>0</v>
+      </c>
+      <c r="N364" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
         <v>1580010</v>
       </c>
@@ -11371,8 +15707,20 @@
       <c r="J365" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K365" s="7">
+        <v>0</v>
+      </c>
+      <c r="L365" s="7">
+        <v>0</v>
+      </c>
+      <c r="M365" s="7">
+        <v>0</v>
+      </c>
+      <c r="N365" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
         <v>1590020</v>
       </c>
@@ -11400,8 +15748,20 @@
       <c r="J366" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K366" s="7">
+        <v>0</v>
+      </c>
+      <c r="L366" s="7">
+        <v>0</v>
+      </c>
+      <c r="M366" s="7">
+        <v>0</v>
+      </c>
+      <c r="N366" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
         <v>1590010</v>
       </c>
@@ -11429,8 +15789,20 @@
       <c r="J367" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K367" s="7">
+        <v>0</v>
+      </c>
+      <c r="L367" s="7">
+        <v>0</v>
+      </c>
+      <c r="M367" s="7">
+        <v>0</v>
+      </c>
+      <c r="N367" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
         <v>1600020</v>
       </c>
@@ -11458,8 +15830,20 @@
       <c r="J368" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="K368" s="7">
+        <v>0</v>
+      </c>
+      <c r="L368" s="7">
+        <v>0</v>
+      </c>
+      <c r="M368" s="7">
+        <v>0</v>
+      </c>
+      <c r="N368" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
         <v>1600010</v>
       </c>
@@ -11486,6 +15870,18 @@
       </c>
       <c r="J369" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="K369" s="7">
+        <v>0</v>
+      </c>
+      <c r="L369" s="7">
+        <v>0</v>
+      </c>
+      <c r="M369" s="7">
+        <v>0</v>
+      </c>
+      <c r="N369" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52428D7-2812-4F24-85AF-4452DEF2990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D89972-57EE-4D80-91FC-D86B05144B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -351,17 +351,19 @@
     <t>res_type</t>
   </si>
   <si>
-    <t>res_type_id res_type_id_first</t>
-  </si>
-  <si>
-    <t>res_type_id_first</t>
-  </si>
-  <si>
-    <t>资源类型id</t>
+    <t>res_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资源类型id（首次）</t>
+    <t>res_id_first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源id（首次）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -457,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -472,7 +474,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -768,8 +769,8 @@
     <col min="10" max="10" width="29.875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.25" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -822,7 +823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -859,10 +860,10 @@
       <c r="L3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="7" t="s">
         <v>77</v>
       </c>
     </row>
@@ -15887,6 +15888,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D89972-57EE-4D80-91FC-D86B05144B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1E4D7D-B27D-4466-B4EF-5F3D38527A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$J$369</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$N$379</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="80">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -754,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N369"/>
+  <dimension ref="A1:N379"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -3833,25 +3833,25 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>140020</v>
+        <v>130001</v>
       </c>
       <c r="B76" s="1">
-        <v>14</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>16</v>
@@ -3860,36 +3860,36 @@
         <v>18</v>
       </c>
       <c r="K76" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L76" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>140010</v>
+        <v>130002</v>
       </c>
       <c r="B77" s="1">
-        <v>14</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3898,42 +3898,42 @@
         <v>16</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="K77" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L77" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>150020</v>
+        <v>130003</v>
       </c>
       <c r="B78" s="1">
-        <v>15</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D78" s="2">
+        <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>16</v>
@@ -3942,36 +3942,36 @@
         <v>18</v>
       </c>
       <c r="K78" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L78" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>150010</v>
+        <v>130004</v>
       </c>
       <c r="B79" s="1">
-        <v>15</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3980,39 +3980,39 @@
         <v>16</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K79" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L79" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N79" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>160020</v>
+        <v>130005</v>
       </c>
       <c r="B80" s="1">
-        <v>16</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -4021,42 +4021,42 @@
         <v>16</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K80" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L80" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N80" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>160010</v>
+        <v>130006</v>
       </c>
       <c r="B81" s="1">
-        <v>16</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>16</v>
@@ -4065,39 +4065,39 @@
         <v>18</v>
       </c>
       <c r="K81" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L81" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M81" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>170020</v>
+        <v>130007</v>
       </c>
       <c r="B82" s="1">
-        <v>17</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>16</v>
@@ -4106,36 +4106,36 @@
         <v>18</v>
       </c>
       <c r="K82" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L82" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M82" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>170010</v>
+        <v>130008</v>
       </c>
       <c r="B83" s="1">
-        <v>17</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
@@ -4144,39 +4144,39 @@
         <v>16</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="K83" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L83" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M83" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N83" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>180020</v>
+        <v>130009</v>
       </c>
       <c r="B84" s="1">
-        <v>18</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -4185,39 +4185,39 @@
         <v>16</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="K84" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L84" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M84" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N84" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>180010</v>
+        <v>130011</v>
       </c>
       <c r="B85" s="1">
-        <v>18</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -4226,27 +4226,27 @@
         <v>16</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K85" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L85" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M85" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N85" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>190020</v>
+        <v>140020</v>
       </c>
       <c r="B86" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>190010</v>
+        <v>140010</v>
       </c>
       <c r="B87" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>200020</v>
+        <v>150020</v>
       </c>
       <c r="B88" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>200010</v>
+        <v>150010</v>
       </c>
       <c r="B89" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -4407,10 +4407,10 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>210020</v>
+        <v>160020</v>
       </c>
       <c r="B90" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -4448,10 +4448,10 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>210010</v>
+        <v>160010</v>
       </c>
       <c r="B91" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>220020</v>
+        <v>170020</v>
       </c>
       <c r="B92" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>10</v>
@@ -4530,10 +4530,10 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>220010</v>
+        <v>170010</v>
       </c>
       <c r="B93" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>230020</v>
+        <v>180020</v>
       </c>
       <c r="B94" s="1">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>230010</v>
+        <v>180010</v>
       </c>
       <c r="B95" s="1">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>240020</v>
+        <v>190020</v>
       </c>
       <c r="B96" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>10</v>
@@ -4694,10 +4694,10 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>240010</v>
+        <v>190010</v>
       </c>
       <c r="B97" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>10</v>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>250020</v>
+        <v>200020</v>
       </c>
       <c r="B98" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>10</v>
@@ -4776,10 +4776,10 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>250010</v>
+        <v>200010</v>
       </c>
       <c r="B99" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>260020</v>
+        <v>210020</v>
       </c>
       <c r="B100" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>260010</v>
+        <v>210010</v>
       </c>
       <c r="B101" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>270020</v>
+        <v>220020</v>
       </c>
       <c r="B102" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>10</v>
@@ -4940,10 +4940,10 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>270010</v>
+        <v>220010</v>
       </c>
       <c r="B103" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>10</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>280020</v>
+        <v>230020</v>
       </c>
       <c r="B104" s="1">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>10</v>
@@ -5022,10 +5022,10 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>280010</v>
+        <v>230010</v>
       </c>
       <c r="B105" s="1">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>10</v>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>290020</v>
+        <v>240020</v>
       </c>
       <c r="B106" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>10</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>290010</v>
+        <v>240010</v>
       </c>
       <c r="B107" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>10</v>
@@ -5145,10 +5145,10 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>300020</v>
+        <v>250020</v>
       </c>
       <c r="B108" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>10</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>300010</v>
+        <v>250010</v>
       </c>
       <c r="B109" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>10</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>310020</v>
+        <v>260020</v>
       </c>
       <c r="B110" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>10</v>
@@ -5268,10 +5268,10 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>310010</v>
+        <v>260010</v>
       </c>
       <c r="B111" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>10</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>320020</v>
+        <v>270020</v>
       </c>
       <c r="B112" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>10</v>
@@ -5350,10 +5350,10 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>320010</v>
+        <v>270010</v>
       </c>
       <c r="B113" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>330020</v>
+        <v>280020</v>
       </c>
       <c r="B114" s="1">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>10</v>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>330010</v>
+        <v>280010</v>
       </c>
       <c r="B115" s="1">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>340020</v>
+        <v>290020</v>
       </c>
       <c r="B116" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>10</v>
@@ -5514,10 +5514,10 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>340010</v>
+        <v>290010</v>
       </c>
       <c r="B117" s="1">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>350020</v>
+        <v>300020</v>
       </c>
       <c r="B118" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>350010</v>
+        <v>300010</v>
       </c>
       <c r="B119" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>10</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>360020</v>
+        <v>310020</v>
       </c>
       <c r="B120" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>360010</v>
+        <v>310010</v>
       </c>
       <c r="B121" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>10</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>370020</v>
+        <v>320020</v>
       </c>
       <c r="B122" s="1">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>10</v>
@@ -5760,10 +5760,10 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>370010</v>
+        <v>320010</v>
       </c>
       <c r="B123" s="1">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>10</v>
@@ -5801,10 +5801,10 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>380020</v>
+        <v>330020</v>
       </c>
       <c r="B124" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>10</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>380010</v>
+        <v>330010</v>
       </c>
       <c r="B125" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>10</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>390020</v>
+        <v>340020</v>
       </c>
       <c r="B126" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>10</v>
@@ -5924,10 +5924,10 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>390010</v>
+        <v>340010</v>
       </c>
       <c r="B127" s="1">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>10</v>
@@ -5965,10 +5965,10 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>400020</v>
+        <v>350020</v>
       </c>
       <c r="B128" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>10</v>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>400010</v>
+        <v>350010</v>
       </c>
       <c r="B129" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>10</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>410020</v>
+        <v>360020</v>
       </c>
       <c r="B130" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>10</v>
@@ -6088,10 +6088,10 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>410010</v>
+        <v>360010</v>
       </c>
       <c r="B131" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>10</v>
@@ -6129,10 +6129,10 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>420020</v>
+        <v>370020</v>
       </c>
       <c r="B132" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>10</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>420010</v>
+        <v>370010</v>
       </c>
       <c r="B133" s="1">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>10</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>430020</v>
+        <v>380020</v>
       </c>
       <c r="B134" s="1">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>10</v>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>430010</v>
+        <v>380010</v>
       </c>
       <c r="B135" s="1">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>10</v>
@@ -6293,10 +6293,10 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>440020</v>
+        <v>390020</v>
       </c>
       <c r="B136" s="1">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>10</v>
@@ -6334,10 +6334,10 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>440010</v>
+        <v>390010</v>
       </c>
       <c r="B137" s="1">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>10</v>
@@ -6375,10 +6375,10 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>450020</v>
+        <v>400020</v>
       </c>
       <c r="B138" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>10</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>450010</v>
+        <v>400010</v>
       </c>
       <c r="B139" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>10</v>
@@ -6457,10 +6457,10 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>460020</v>
+        <v>410020</v>
       </c>
       <c r="B140" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>460010</v>
+        <v>410010</v>
       </c>
       <c r="B141" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>470020</v>
+        <v>420020</v>
       </c>
       <c r="B142" s="1">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>10</v>
@@ -6580,10 +6580,10 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>470010</v>
+        <v>420010</v>
       </c>
       <c r="B143" s="1">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>10</v>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>480020</v>
+        <v>430020</v>
       </c>
       <c r="B144" s="1">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>480010</v>
+        <v>430010</v>
       </c>
       <c r="B145" s="1">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>10</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>490020</v>
+        <v>440020</v>
       </c>
       <c r="B146" s="1">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>10</v>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>490010</v>
+        <v>440010</v>
       </c>
       <c r="B147" s="1">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>10</v>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>500020</v>
+        <v>450020</v>
       </c>
       <c r="B148" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>500010</v>
+        <v>450010</v>
       </c>
       <c r="B149" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>10</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>510020</v>
+        <v>460020</v>
       </c>
       <c r="B150" s="1">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>510010</v>
+        <v>460010</v>
       </c>
       <c r="B151" s="1">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>520020</v>
+        <v>470020</v>
       </c>
       <c r="B152" s="1">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>10</v>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>520010</v>
+        <v>470010</v>
       </c>
       <c r="B153" s="1">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>10</v>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>530020</v>
+        <v>480020</v>
       </c>
       <c r="B154" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>10</v>
@@ -7072,10 +7072,10 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>530010</v>
+        <v>480010</v>
       </c>
       <c r="B155" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>10</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>540020</v>
+        <v>490020</v>
       </c>
       <c r="B156" s="1">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>10</v>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>540010</v>
+        <v>490010</v>
       </c>
       <c r="B157" s="1">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>10</v>
@@ -7195,10 +7195,10 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>550020</v>
+        <v>500020</v>
       </c>
       <c r="B158" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>10</v>
@@ -7236,10 +7236,10 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>550010</v>
+        <v>500010</v>
       </c>
       <c r="B159" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>10</v>
@@ -7277,10 +7277,10 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>560020</v>
+        <v>510020</v>
       </c>
       <c r="B160" s="1">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>10</v>
@@ -7318,10 +7318,10 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>560010</v>
+        <v>510010</v>
       </c>
       <c r="B161" s="1">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>10</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>570020</v>
+        <v>520020</v>
       </c>
       <c r="B162" s="1">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>10</v>
@@ -7400,10 +7400,10 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>570010</v>
+        <v>520010</v>
       </c>
       <c r="B163" s="1">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>10</v>
@@ -7441,10 +7441,10 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>580020</v>
+        <v>530020</v>
       </c>
       <c r="B164" s="1">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>10</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>580010</v>
+        <v>530010</v>
       </c>
       <c r="B165" s="1">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>10</v>
@@ -7523,10 +7523,10 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>590020</v>
+        <v>540020</v>
       </c>
       <c r="B166" s="1">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>10</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>590010</v>
+        <v>540010</v>
       </c>
       <c r="B167" s="1">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>10</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>600020</v>
+        <v>550020</v>
       </c>
       <c r="B168" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>10</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>600010</v>
+        <v>550010</v>
       </c>
       <c r="B169" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>10</v>
@@ -7687,10 +7687,10 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>610020</v>
+        <v>560020</v>
       </c>
       <c r="B170" s="1">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>10</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>610010</v>
+        <v>560010</v>
       </c>
       <c r="B171" s="1">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>10</v>
@@ -7769,10 +7769,10 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>620020</v>
+        <v>570020</v>
       </c>
       <c r="B172" s="1">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>10</v>
@@ -7810,10 +7810,10 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>620010</v>
+        <v>570010</v>
       </c>
       <c r="B173" s="1">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>10</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>630020</v>
+        <v>580020</v>
       </c>
       <c r="B174" s="1">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>10</v>
@@ -7892,10 +7892,10 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>630010</v>
+        <v>580010</v>
       </c>
       <c r="B175" s="1">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>10</v>
@@ -7933,10 +7933,10 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>640020</v>
+        <v>590020</v>
       </c>
       <c r="B176" s="1">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>640010</v>
+        <v>590010</v>
       </c>
       <c r="B177" s="1">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>650020</v>
+        <v>600020</v>
       </c>
       <c r="B178" s="1">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>650010</v>
+        <v>600010</v>
       </c>
       <c r="B179" s="1">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>10</v>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>660020</v>
+        <v>610020</v>
       </c>
       <c r="B180" s="1">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>10</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>660010</v>
+        <v>610010</v>
       </c>
       <c r="B181" s="1">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>10</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>670020</v>
+        <v>620020</v>
       </c>
       <c r="B182" s="1">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>10</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>670010</v>
+        <v>620010</v>
       </c>
       <c r="B183" s="1">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>10</v>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>680020</v>
+        <v>630020</v>
       </c>
       <c r="B184" s="1">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>10</v>
@@ -8302,10 +8302,10 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>680010</v>
+        <v>630010</v>
       </c>
       <c r="B185" s="1">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>10</v>
@@ -8343,10 +8343,10 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>690020</v>
+        <v>640020</v>
       </c>
       <c r="B186" s="1">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>10</v>
@@ -8384,10 +8384,10 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>690010</v>
+        <v>640010</v>
       </c>
       <c r="B187" s="1">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>10</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>700020</v>
+        <v>650020</v>
       </c>
       <c r="B188" s="1">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>700010</v>
+        <v>650010</v>
       </c>
       <c r="B189" s="1">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>10</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>710020</v>
+        <v>660020</v>
       </c>
       <c r="B190" s="1">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>10</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>710010</v>
+        <v>660010</v>
       </c>
       <c r="B191" s="1">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>10</v>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>720020</v>
+        <v>670020</v>
       </c>
       <c r="B192" s="1">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>10</v>
@@ -8630,10 +8630,10 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>720010</v>
+        <v>670010</v>
       </c>
       <c r="B193" s="1">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>10</v>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>730020</v>
+        <v>680020</v>
       </c>
       <c r="B194" s="1">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>10</v>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>730010</v>
+        <v>680010</v>
       </c>
       <c r="B195" s="1">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>10</v>
@@ -8753,10 +8753,10 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>740020</v>
+        <v>690020</v>
       </c>
       <c r="B196" s="1">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>10</v>
@@ -8794,10 +8794,10 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>740010</v>
+        <v>690010</v>
       </c>
       <c r="B197" s="1">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>10</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>750020</v>
+        <v>700020</v>
       </c>
       <c r="B198" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>10</v>
@@ -8876,10 +8876,10 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>750010</v>
+        <v>700010</v>
       </c>
       <c r="B199" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>10</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>760020</v>
+        <v>710020</v>
       </c>
       <c r="B200" s="1">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>10</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>760010</v>
+        <v>710010</v>
       </c>
       <c r="B201" s="1">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>10</v>
@@ -8999,10 +8999,10 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>770020</v>
+        <v>720020</v>
       </c>
       <c r="B202" s="1">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>10</v>
@@ -9040,10 +9040,10 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>770010</v>
+        <v>720010</v>
       </c>
       <c r="B203" s="1">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>10</v>
@@ -9081,10 +9081,10 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>780020</v>
+        <v>730020</v>
       </c>
       <c r="B204" s="1">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>10</v>
@@ -9122,10 +9122,10 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>780010</v>
+        <v>730010</v>
       </c>
       <c r="B205" s="1">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>10</v>
@@ -9163,10 +9163,10 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>790020</v>
+        <v>740020</v>
       </c>
       <c r="B206" s="1">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>10</v>
@@ -9204,10 +9204,10 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>790010</v>
+        <v>740010</v>
       </c>
       <c r="B207" s="1">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>10</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>800020</v>
+        <v>750020</v>
       </c>
       <c r="B208" s="1">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>800010</v>
+        <v>750010</v>
       </c>
       <c r="B209" s="1">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>10</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>810020</v>
+        <v>760020</v>
       </c>
       <c r="B210" s="1">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>10</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>810010</v>
+        <v>760010</v>
       </c>
       <c r="B211" s="1">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>10</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>820020</v>
+        <v>770020</v>
       </c>
       <c r="B212" s="1">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>820010</v>
+        <v>770010</v>
       </c>
       <c r="B213" s="1">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>10</v>
@@ -9491,10 +9491,10 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>830020</v>
+        <v>780020</v>
       </c>
       <c r="B214" s="1">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>830010</v>
+        <v>780010</v>
       </c>
       <c r="B215" s="1">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>10</v>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>840020</v>
+        <v>790020</v>
       </c>
       <c r="B216" s="1">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>10</v>
@@ -9614,10 +9614,10 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>840010</v>
+        <v>790010</v>
       </c>
       <c r="B217" s="1">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>10</v>
@@ -9655,10 +9655,10 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>850020</v>
+        <v>800020</v>
       </c>
       <c r="B218" s="1">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>10</v>
@@ -9696,10 +9696,10 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>850010</v>
+        <v>800010</v>
       </c>
       <c r="B219" s="1">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>10</v>
@@ -9737,10 +9737,10 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>860020</v>
+        <v>810020</v>
       </c>
       <c r="B220" s="1">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>10</v>
@@ -9778,10 +9778,10 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>860010</v>
+        <v>810010</v>
       </c>
       <c r="B221" s="1">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>870020</v>
+        <v>820020</v>
       </c>
       <c r="B222" s="1">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>10</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>870010</v>
+        <v>820010</v>
       </c>
       <c r="B223" s="1">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>10</v>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>880020</v>
+        <v>830020</v>
       </c>
       <c r="B224" s="1">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>10</v>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>880010</v>
+        <v>830010</v>
       </c>
       <c r="B225" s="1">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>10</v>
@@ -9983,10 +9983,10 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>890020</v>
+        <v>840020</v>
       </c>
       <c r="B226" s="1">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>10</v>
@@ -10024,10 +10024,10 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>890010</v>
+        <v>840010</v>
       </c>
       <c r="B227" s="1">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>10</v>
@@ -10065,10 +10065,10 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>900020</v>
+        <v>850020</v>
       </c>
       <c r="B228" s="1">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>10</v>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>900010</v>
+        <v>850010</v>
       </c>
       <c r="B229" s="1">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>10</v>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>910020</v>
+        <v>860020</v>
       </c>
       <c r="B230" s="1">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>10</v>
@@ -10188,10 +10188,10 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>910010</v>
+        <v>860010</v>
       </c>
       <c r="B231" s="1">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>920020</v>
+        <v>870020</v>
       </c>
       <c r="B232" s="1">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>10</v>
@@ -10270,10 +10270,10 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>920010</v>
+        <v>870010</v>
       </c>
       <c r="B233" s="1">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>10</v>
@@ -10311,10 +10311,10 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>930020</v>
+        <v>880020</v>
       </c>
       <c r="B234" s="1">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>10</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>930010</v>
+        <v>880010</v>
       </c>
       <c r="B235" s="1">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>10</v>
@@ -10393,10 +10393,10 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>940020</v>
+        <v>890020</v>
       </c>
       <c r="B236" s="1">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>10</v>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>940010</v>
+        <v>890010</v>
       </c>
       <c r="B237" s="1">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>10</v>
@@ -10475,10 +10475,10 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>950020</v>
+        <v>900020</v>
       </c>
       <c r="B238" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>10</v>
@@ -10516,10 +10516,10 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>950010</v>
+        <v>900010</v>
       </c>
       <c r="B239" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>10</v>
@@ -10557,10 +10557,10 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>960020</v>
+        <v>910020</v>
       </c>
       <c r="B240" s="1">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>10</v>
@@ -10598,10 +10598,10 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>960010</v>
+        <v>910010</v>
       </c>
       <c r="B241" s="1">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>10</v>
@@ -10639,10 +10639,10 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>970020</v>
+        <v>920020</v>
       </c>
       <c r="B242" s="1">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>10</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>970010</v>
+        <v>920010</v>
       </c>
       <c r="B243" s="1">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>10</v>
@@ -10721,10 +10721,10 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>980020</v>
+        <v>930020</v>
       </c>
       <c r="B244" s="1">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>980010</v>
+        <v>930010</v>
       </c>
       <c r="B245" s="1">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>10</v>
@@ -10803,10 +10803,10 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>990020</v>
+        <v>940020</v>
       </c>
       <c r="B246" s="1">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>10</v>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>990010</v>
+        <v>940010</v>
       </c>
       <c r="B247" s="1">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>1000020</v>
+        <v>950020</v>
       </c>
       <c r="B248" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>10</v>
@@ -10926,10 +10926,10 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>1000010</v>
+        <v>950010</v>
       </c>
       <c r="B249" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>10</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>1010020</v>
+        <v>960020</v>
       </c>
       <c r="B250" s="1">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>10</v>
@@ -11008,10 +11008,10 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>1010010</v>
+        <v>960010</v>
       </c>
       <c r="B251" s="1">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>1020020</v>
+        <v>970020</v>
       </c>
       <c r="B252" s="1">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>10</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>1020010</v>
+        <v>970010</v>
       </c>
       <c r="B253" s="1">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>10</v>
@@ -11131,10 +11131,10 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>1030020</v>
+        <v>980020</v>
       </c>
       <c r="B254" s="1">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>10</v>
@@ -11172,10 +11172,10 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>1030010</v>
+        <v>980010</v>
       </c>
       <c r="B255" s="1">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>1040020</v>
+        <v>990020</v>
       </c>
       <c r="B256" s="1">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>10</v>
@@ -11254,10 +11254,10 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>1040010</v>
+        <v>990010</v>
       </c>
       <c r="B257" s="1">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>10</v>
@@ -11295,10 +11295,10 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1050020</v>
+        <v>1000020</v>
       </c>
       <c r="B258" s="1">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>10</v>
@@ -11336,10 +11336,10 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1050010</v>
+        <v>1000010</v>
       </c>
       <c r="B259" s="1">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>10</v>
@@ -11377,10 +11377,10 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1060020</v>
+        <v>1010020</v>
       </c>
       <c r="B260" s="1">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>10</v>
@@ -11418,10 +11418,10 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1060010</v>
+        <v>1010010</v>
       </c>
       <c r="B261" s="1">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>10</v>
@@ -11459,10 +11459,10 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1070020</v>
+        <v>1020020</v>
       </c>
       <c r="B262" s="1">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>10</v>
@@ -11500,10 +11500,10 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1070010</v>
+        <v>1020010</v>
       </c>
       <c r="B263" s="1">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>10</v>
@@ -11541,10 +11541,10 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>1080020</v>
+        <v>1030020</v>
       </c>
       <c r="B264" s="1">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>1080010</v>
+        <v>1030010</v>
       </c>
       <c r="B265" s="1">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>10</v>
@@ -11623,10 +11623,10 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>1090020</v>
+        <v>1040020</v>
       </c>
       <c r="B266" s="1">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>1090010</v>
+        <v>1040010</v>
       </c>
       <c r="B267" s="1">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>10</v>
@@ -11705,10 +11705,10 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>1100020</v>
+        <v>1050020</v>
       </c>
       <c r="B268" s="1">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>10</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>1100010</v>
+        <v>1050010</v>
       </c>
       <c r="B269" s="1">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>10</v>
@@ -11787,10 +11787,10 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1110020</v>
+        <v>1060020</v>
       </c>
       <c r="B270" s="1">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>10</v>
@@ -11828,10 +11828,10 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1110010</v>
+        <v>1060010</v>
       </c>
       <c r="B271" s="1">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>10</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1120020</v>
+        <v>1070020</v>
       </c>
       <c r="B272" s="1">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>10</v>
@@ -11910,10 +11910,10 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1120010</v>
+        <v>1070010</v>
       </c>
       <c r="B273" s="1">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>10</v>
@@ -11951,10 +11951,10 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1130020</v>
+        <v>1080020</v>
       </c>
       <c r="B274" s="1">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>10</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1130010</v>
+        <v>1080010</v>
       </c>
       <c r="B275" s="1">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>10</v>
@@ -12033,10 +12033,10 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1140020</v>
+        <v>1090020</v>
       </c>
       <c r="B276" s="1">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>10</v>
@@ -12074,10 +12074,10 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1140010</v>
+        <v>1090010</v>
       </c>
       <c r="B277" s="1">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>10</v>
@@ -12115,10 +12115,10 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1150020</v>
+        <v>1100020</v>
       </c>
       <c r="B278" s="1">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>10</v>
@@ -12156,10 +12156,10 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1150010</v>
+        <v>1100010</v>
       </c>
       <c r="B279" s="1">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>10</v>
@@ -12197,10 +12197,10 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1160020</v>
+        <v>1110020</v>
       </c>
       <c r="B280" s="1">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>10</v>
@@ -12238,10 +12238,10 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1160010</v>
+        <v>1110010</v>
       </c>
       <c r="B281" s="1">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1170020</v>
+        <v>1120020</v>
       </c>
       <c r="B282" s="1">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>10</v>
@@ -12320,10 +12320,10 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1170010</v>
+        <v>1120010</v>
       </c>
       <c r="B283" s="1">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>10</v>
@@ -12361,10 +12361,10 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1180020</v>
+        <v>1130020</v>
       </c>
       <c r="B284" s="1">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>10</v>
@@ -12402,10 +12402,10 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1180010</v>
+        <v>1130010</v>
       </c>
       <c r="B285" s="1">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>10</v>
@@ -12443,10 +12443,10 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1190020</v>
+        <v>1140020</v>
       </c>
       <c r="B286" s="1">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>10</v>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1190010</v>
+        <v>1140010</v>
       </c>
       <c r="B287" s="1">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>10</v>
@@ -12525,10 +12525,10 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1200020</v>
+        <v>1150020</v>
       </c>
       <c r="B288" s="1">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1200010</v>
+        <v>1150010</v>
       </c>
       <c r="B289" s="1">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1210020</v>
+        <v>1160020</v>
       </c>
       <c r="B290" s="1">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>10</v>
@@ -12648,10 +12648,10 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1210010</v>
+        <v>1160010</v>
       </c>
       <c r="B291" s="1">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>10</v>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1220020</v>
+        <v>1170020</v>
       </c>
       <c r="B292" s="1">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>10</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1220010</v>
+        <v>1170010</v>
       </c>
       <c r="B293" s="1">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>10</v>
@@ -12771,10 +12771,10 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1230020</v>
+        <v>1180020</v>
       </c>
       <c r="B294" s="1">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>10</v>
@@ -12812,10 +12812,10 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1230010</v>
+        <v>1180010</v>
       </c>
       <c r="B295" s="1">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>10</v>
@@ -12853,10 +12853,10 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1240020</v>
+        <v>1190020</v>
       </c>
       <c r="B296" s="1">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>10</v>
@@ -12894,10 +12894,10 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1240010</v>
+        <v>1190010</v>
       </c>
       <c r="B297" s="1">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>10</v>
@@ -12935,10 +12935,10 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1250020</v>
+        <v>1200020</v>
       </c>
       <c r="B298" s="1">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>10</v>
@@ -12976,10 +12976,10 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1250010</v>
+        <v>1200010</v>
       </c>
       <c r="B299" s="1">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>10</v>
@@ -13017,10 +13017,10 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1260020</v>
+        <v>1210020</v>
       </c>
       <c r="B300" s="1">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>10</v>
@@ -13058,10 +13058,10 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1260010</v>
+        <v>1210010</v>
       </c>
       <c r="B301" s="1">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>10</v>
@@ -13099,10 +13099,10 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1270020</v>
+        <v>1220020</v>
       </c>
       <c r="B302" s="1">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>10</v>
@@ -13140,10 +13140,10 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1270010</v>
+        <v>1220010</v>
       </c>
       <c r="B303" s="1">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>10</v>
@@ -13181,10 +13181,10 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1280020</v>
+        <v>1230020</v>
       </c>
       <c r="B304" s="1">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>10</v>
@@ -13222,10 +13222,10 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1280010</v>
+        <v>1230010</v>
       </c>
       <c r="B305" s="1">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>10</v>
@@ -13263,10 +13263,10 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1290020</v>
+        <v>1240020</v>
       </c>
       <c r="B306" s="1">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>10</v>
@@ -13304,10 +13304,10 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1290010</v>
+        <v>1240010</v>
       </c>
       <c r="B307" s="1">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>10</v>
@@ -13345,10 +13345,10 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1300020</v>
+        <v>1250020</v>
       </c>
       <c r="B308" s="1">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>10</v>
@@ -13386,10 +13386,10 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1300010</v>
+        <v>1250010</v>
       </c>
       <c r="B309" s="1">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>10</v>
@@ -13427,10 +13427,10 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1310020</v>
+        <v>1260020</v>
       </c>
       <c r="B310" s="1">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>10</v>
@@ -13468,10 +13468,10 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1310010</v>
+        <v>1260010</v>
       </c>
       <c r="B311" s="1">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>10</v>
@@ -13509,10 +13509,10 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1320020</v>
+        <v>1270020</v>
       </c>
       <c r="B312" s="1">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1320010</v>
+        <v>1270010</v>
       </c>
       <c r="B313" s="1">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>10</v>
@@ -13591,10 +13591,10 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1330020</v>
+        <v>1280020</v>
       </c>
       <c r="B314" s="1">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>10</v>
@@ -13632,10 +13632,10 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1330010</v>
+        <v>1280010</v>
       </c>
       <c r="B315" s="1">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>10</v>
@@ -13673,10 +13673,10 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1340020</v>
+        <v>1290020</v>
       </c>
       <c r="B316" s="1">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>10</v>
@@ -13714,10 +13714,10 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1340010</v>
+        <v>1290010</v>
       </c>
       <c r="B317" s="1">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>10</v>
@@ -13755,10 +13755,10 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1350020</v>
+        <v>1300020</v>
       </c>
       <c r="B318" s="1">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>10</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1350010</v>
+        <v>1300010</v>
       </c>
       <c r="B319" s="1">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>10</v>
@@ -13837,10 +13837,10 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1360020</v>
+        <v>1310020</v>
       </c>
       <c r="B320" s="1">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>10</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1360010</v>
+        <v>1310010</v>
       </c>
       <c r="B321" s="1">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>10</v>
@@ -13919,10 +13919,10 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1370020</v>
+        <v>1320020</v>
       </c>
       <c r="B322" s="1">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>10</v>
@@ -13960,10 +13960,10 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1370010</v>
+        <v>1320010</v>
       </c>
       <c r="B323" s="1">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>10</v>
@@ -14001,10 +14001,10 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1380020</v>
+        <v>1330020</v>
       </c>
       <c r="B324" s="1">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>10</v>
@@ -14042,10 +14042,10 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1380010</v>
+        <v>1330010</v>
       </c>
       <c r="B325" s="1">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>10</v>
@@ -14083,10 +14083,10 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1390020</v>
+        <v>1340020</v>
       </c>
       <c r="B326" s="1">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>10</v>
@@ -14124,10 +14124,10 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1390010</v>
+        <v>1340010</v>
       </c>
       <c r="B327" s="1">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>10</v>
@@ -14165,10 +14165,10 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1400020</v>
+        <v>1350020</v>
       </c>
       <c r="B328" s="1">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>10</v>
@@ -14206,10 +14206,10 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1400010</v>
+        <v>1350010</v>
       </c>
       <c r="B329" s="1">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>10</v>
@@ -14247,10 +14247,10 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1410020</v>
+        <v>1360020</v>
       </c>
       <c r="B330" s="1">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>10</v>
@@ -14288,10 +14288,10 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1410010</v>
+        <v>1360010</v>
       </c>
       <c r="B331" s="1">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>10</v>
@@ -14329,10 +14329,10 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1420020</v>
+        <v>1370020</v>
       </c>
       <c r="B332" s="1">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>10</v>
@@ -14370,10 +14370,10 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1420010</v>
+        <v>1370010</v>
       </c>
       <c r="B333" s="1">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>10</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1430020</v>
+        <v>1380020</v>
       </c>
       <c r="B334" s="1">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>10</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1430010</v>
+        <v>1380010</v>
       </c>
       <c r="B335" s="1">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1440020</v>
+        <v>1390020</v>
       </c>
       <c r="B336" s="1">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>10</v>
@@ -14534,10 +14534,10 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1440010</v>
+        <v>1390010</v>
       </c>
       <c r="B337" s="1">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>10</v>
@@ -14575,10 +14575,10 @@
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1450020</v>
+        <v>1400020</v>
       </c>
       <c r="B338" s="1">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>10</v>
@@ -14616,10 +14616,10 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1450010</v>
+        <v>1400010</v>
       </c>
       <c r="B339" s="1">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>10</v>
@@ -14657,10 +14657,10 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>1460020</v>
+        <v>1410020</v>
       </c>
       <c r="B340" s="1">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>10</v>
@@ -14698,10 +14698,10 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>1460010</v>
+        <v>1410010</v>
       </c>
       <c r="B341" s="1">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>10</v>
@@ -14739,10 +14739,10 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>1470020</v>
+        <v>1420020</v>
       </c>
       <c r="B342" s="1">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>10</v>
@@ -14780,10 +14780,10 @@
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>1470010</v>
+        <v>1420010</v>
       </c>
       <c r="B343" s="1">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>10</v>
@@ -14821,10 +14821,10 @@
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>1480020</v>
+        <v>1430020</v>
       </c>
       <c r="B344" s="1">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>10</v>
@@ -14862,10 +14862,10 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>1480010</v>
+        <v>1430010</v>
       </c>
       <c r="B345" s="1">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>10</v>
@@ -14903,10 +14903,10 @@
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>1490020</v>
+        <v>1440020</v>
       </c>
       <c r="B346" s="1">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>10</v>
@@ -14944,10 +14944,10 @@
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>1490010</v>
+        <v>1440010</v>
       </c>
       <c r="B347" s="1">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>10</v>
@@ -14985,10 +14985,10 @@
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>1500020</v>
+        <v>1450020</v>
       </c>
       <c r="B348" s="1">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>10</v>
@@ -15026,10 +15026,10 @@
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>1500010</v>
+        <v>1450010</v>
       </c>
       <c r="B349" s="1">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>10</v>
@@ -15067,10 +15067,10 @@
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>1510020</v>
+        <v>1460020</v>
       </c>
       <c r="B350" s="1">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>10</v>
@@ -15108,10 +15108,10 @@
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>1510010</v>
+        <v>1460010</v>
       </c>
       <c r="B351" s="1">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>10</v>
@@ -15149,10 +15149,10 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>1520020</v>
+        <v>1470020</v>
       </c>
       <c r="B352" s="1">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>10</v>
@@ -15190,10 +15190,10 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>1520010</v>
+        <v>1470010</v>
       </c>
       <c r="B353" s="1">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>10</v>
@@ -15231,10 +15231,10 @@
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>1530020</v>
+        <v>1480020</v>
       </c>
       <c r="B354" s="1">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>10</v>
@@ -15272,10 +15272,10 @@
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>1530010</v>
+        <v>1480010</v>
       </c>
       <c r="B355" s="1">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>10</v>
@@ -15313,10 +15313,10 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>1540020</v>
+        <v>1490020</v>
       </c>
       <c r="B356" s="1">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>10</v>
@@ -15354,10 +15354,10 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>1540010</v>
+        <v>1490010</v>
       </c>
       <c r="B357" s="1">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>10</v>
@@ -15395,10 +15395,10 @@
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>1550020</v>
+        <v>1500020</v>
       </c>
       <c r="B358" s="1">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>10</v>
@@ -15436,10 +15436,10 @@
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>1550010</v>
+        <v>1500010</v>
       </c>
       <c r="B359" s="1">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>10</v>
@@ -15477,10 +15477,10 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>1560020</v>
+        <v>1510020</v>
       </c>
       <c r="B360" s="1">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>10</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>1560010</v>
+        <v>1510010</v>
       </c>
       <c r="B361" s="1">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>10</v>
@@ -15559,10 +15559,10 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>1570020</v>
+        <v>1520020</v>
       </c>
       <c r="B362" s="1">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>10</v>
@@ -15600,10 +15600,10 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>1570010</v>
+        <v>1520010</v>
       </c>
       <c r="B363" s="1">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>10</v>
@@ -15641,10 +15641,10 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>1580020</v>
+        <v>1530020</v>
       </c>
       <c r="B364" s="1">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>10</v>
@@ -15682,10 +15682,10 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>1580010</v>
+        <v>1530010</v>
       </c>
       <c r="B365" s="1">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>10</v>
@@ -15723,10 +15723,10 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>1590020</v>
+        <v>1540020</v>
       </c>
       <c r="B366" s="1">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>10</v>
@@ -15764,10 +15764,10 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>1590010</v>
+        <v>1540010</v>
       </c>
       <c r="B367" s="1">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>10</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>1600020</v>
+        <v>1550020</v>
       </c>
       <c r="B368" s="1">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>10</v>
@@ -15846,42 +15846,452 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
+        <v>1550010</v>
+      </c>
+      <c r="B369" s="1">
+        <v>155</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G369" s="1">
+        <v>0</v>
+      </c>
+      <c r="H369" s="2">
+        <v>0</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J369" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K369" s="7">
+        <v>0</v>
+      </c>
+      <c r="L369" s="7">
+        <v>0</v>
+      </c>
+      <c r="M369" s="7">
+        <v>0</v>
+      </c>
+      <c r="N369" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A370" s="1">
+        <v>1560020</v>
+      </c>
+      <c r="B370" s="1">
+        <v>156</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G370" s="1">
+        <v>0</v>
+      </c>
+      <c r="H370" s="2">
+        <v>0</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J370" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K370" s="7">
+        <v>0</v>
+      </c>
+      <c r="L370" s="7">
+        <v>0</v>
+      </c>
+      <c r="M370" s="7">
+        <v>0</v>
+      </c>
+      <c r="N370" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A371" s="1">
+        <v>1560010</v>
+      </c>
+      <c r="B371" s="1">
+        <v>156</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G371" s="1">
+        <v>0</v>
+      </c>
+      <c r="H371" s="2">
+        <v>0</v>
+      </c>
+      <c r="I371" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J371" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K371" s="7">
+        <v>0</v>
+      </c>
+      <c r="L371" s="7">
+        <v>0</v>
+      </c>
+      <c r="M371" s="7">
+        <v>0</v>
+      </c>
+      <c r="N371" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A372" s="1">
+        <v>1570020</v>
+      </c>
+      <c r="B372" s="1">
+        <v>157</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G372" s="1">
+        <v>0</v>
+      </c>
+      <c r="H372" s="2">
+        <v>0</v>
+      </c>
+      <c r="I372" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J372" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K372" s="7">
+        <v>0</v>
+      </c>
+      <c r="L372" s="7">
+        <v>0</v>
+      </c>
+      <c r="M372" s="7">
+        <v>0</v>
+      </c>
+      <c r="N372" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A373" s="1">
+        <v>1570010</v>
+      </c>
+      <c r="B373" s="1">
+        <v>157</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E373" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G373" s="1">
+        <v>0</v>
+      </c>
+      <c r="H373" s="2">
+        <v>0</v>
+      </c>
+      <c r="I373" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J373" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K373" s="7">
+        <v>0</v>
+      </c>
+      <c r="L373" s="7">
+        <v>0</v>
+      </c>
+      <c r="M373" s="7">
+        <v>0</v>
+      </c>
+      <c r="N373" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A374" s="1">
+        <v>1580020</v>
+      </c>
+      <c r="B374" s="1">
+        <v>158</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G374" s="1">
+        <v>0</v>
+      </c>
+      <c r="H374" s="2">
+        <v>0</v>
+      </c>
+      <c r="I374" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J374" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K374" s="7">
+        <v>0</v>
+      </c>
+      <c r="L374" s="7">
+        <v>0</v>
+      </c>
+      <c r="M374" s="7">
+        <v>0</v>
+      </c>
+      <c r="N374" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A375" s="1">
+        <v>1580010</v>
+      </c>
+      <c r="B375" s="1">
+        <v>158</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G375" s="1">
+        <v>0</v>
+      </c>
+      <c r="H375" s="2">
+        <v>0</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J375" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K375" s="7">
+        <v>0</v>
+      </c>
+      <c r="L375" s="7">
+        <v>0</v>
+      </c>
+      <c r="M375" s="7">
+        <v>0</v>
+      </c>
+      <c r="N375" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A376" s="1">
+        <v>1590020</v>
+      </c>
+      <c r="B376" s="1">
+        <v>159</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G376" s="1">
+        <v>0</v>
+      </c>
+      <c r="H376" s="2">
+        <v>0</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J376" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K376" s="7">
+        <v>0</v>
+      </c>
+      <c r="L376" s="7">
+        <v>0</v>
+      </c>
+      <c r="M376" s="7">
+        <v>0</v>
+      </c>
+      <c r="N376" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A377" s="1">
+        <v>1590010</v>
+      </c>
+      <c r="B377" s="1">
+        <v>159</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G377" s="1">
+        <v>0</v>
+      </c>
+      <c r="H377" s="2">
+        <v>0</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J377" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K377" s="7">
+        <v>0</v>
+      </c>
+      <c r="L377" s="7">
+        <v>0</v>
+      </c>
+      <c r="M377" s="7">
+        <v>0</v>
+      </c>
+      <c r="N377" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A378" s="1">
+        <v>1600020</v>
+      </c>
+      <c r="B378" s="1">
+        <v>160</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G378" s="1">
+        <v>0</v>
+      </c>
+      <c r="H378" s="2">
+        <v>0</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J378" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K378" s="7">
+        <v>0</v>
+      </c>
+      <c r="L378" s="7">
+        <v>0</v>
+      </c>
+      <c r="M378" s="7">
+        <v>0</v>
+      </c>
+      <c r="N378" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A379" s="1">
         <v>1600010</v>
       </c>
-      <c r="B369" s="1">
+      <c r="B379" s="1">
         <v>160</v>
       </c>
-      <c r="D369" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F369" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G369" s="1">
-        <v>0</v>
-      </c>
-      <c r="H369" s="2">
-        <v>0</v>
-      </c>
-      <c r="I369" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J369" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K369" s="7">
-        <v>0</v>
-      </c>
-      <c r="L369" s="7">
-        <v>0</v>
-      </c>
-      <c r="M369" s="7">
-        <v>0</v>
-      </c>
-      <c r="N369" s="7">
+      <c r="D379" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G379" s="1">
+        <v>0</v>
+      </c>
+      <c r="H379" s="2">
+        <v>0</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J379" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K379" s="7">
+        <v>0</v>
+      </c>
+      <c r="L379" s="7">
+        <v>0</v>
+      </c>
+      <c r="M379" s="7">
+        <v>0</v>
+      </c>
+      <c r="N379" s="7">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1E4D7D-B27D-4466-B4EF-5F3D38527A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D99D0F-8814-4540-84BF-DAECA00DD5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$N$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$N$392</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="80">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -754,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N379"/>
+  <dimension ref="A1:N392"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -5637,19 +5637,19 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>310020</v>
+        <v>300001</v>
       </c>
       <c r="B120" s="1">
-        <v>31</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G120" s="1">
         <v>0</v>
@@ -5661,7 +5661,7 @@
         <v>16</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K120" s="7">
         <v>0</v>
@@ -5678,19 +5678,19 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>310010</v>
+        <v>300002</v>
       </c>
       <c r="B121" s="1">
-        <v>31</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G121" s="1">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>16</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K121" s="7">
         <v>0</v>
@@ -5719,19 +5719,19 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>320020</v>
+        <v>300003</v>
       </c>
       <c r="B122" s="1">
-        <v>32</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>16</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K122" s="7">
         <v>0</v>
@@ -5760,19 +5760,19 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>320010</v>
+        <v>300004</v>
       </c>
       <c r="B123" s="1">
-        <v>32</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G123" s="1">
         <v>0</v>
@@ -5784,7 +5784,7 @@
         <v>16</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K123" s="7">
         <v>0</v>
@@ -5801,19 +5801,19 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>330020</v>
+        <v>300005</v>
       </c>
       <c r="B124" s="1">
-        <v>33</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G124" s="1">
         <v>0</v>
@@ -5825,7 +5825,7 @@
         <v>16</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K124" s="7">
         <v>0</v>
@@ -5842,19 +5842,19 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>330010</v>
+        <v>300006</v>
       </c>
       <c r="B125" s="1">
-        <v>33</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G125" s="1">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>16</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K125" s="7">
         <v>0</v>
@@ -5883,19 +5883,19 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>340020</v>
+        <v>300007</v>
       </c>
       <c r="B126" s="1">
-        <v>34</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G126" s="1">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>16</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K126" s="7">
         <v>0</v>
@@ -5924,19 +5924,19 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>340010</v>
+        <v>300008</v>
       </c>
       <c r="B127" s="1">
-        <v>34</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G127" s="1">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>16</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K127" s="7">
         <v>0</v>
@@ -5965,19 +5965,19 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>350020</v>
+        <v>300009</v>
       </c>
       <c r="B128" s="1">
-        <v>35</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G128" s="1">
         <v>0</v>
@@ -5989,7 +5989,7 @@
         <v>16</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K128" s="7">
         <v>0</v>
@@ -6006,19 +6006,19 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>350010</v>
+        <v>300010</v>
       </c>
       <c r="B129" s="1">
-        <v>35</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G129" s="1">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>16</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K129" s="7">
         <v>0</v>
@@ -6047,19 +6047,19 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>360020</v>
+        <v>300011</v>
       </c>
       <c r="B130" s="1">
-        <v>36</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G130" s="1">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>16</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K130" s="7">
         <v>0</v>
@@ -6088,19 +6088,19 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>360010</v>
+        <v>300012</v>
       </c>
       <c r="B131" s="1">
-        <v>36</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>16</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K131" s="7">
         <v>0</v>
@@ -6129,19 +6129,19 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>370020</v>
+        <v>300013</v>
       </c>
       <c r="B132" s="1">
-        <v>37</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G132" s="1">
         <v>0</v>
@@ -6153,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K132" s="7">
         <v>0</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>370010</v>
+        <v>310020</v>
       </c>
       <c r="B133" s="1">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>10</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>380020</v>
+        <v>310010</v>
       </c>
       <c r="B134" s="1">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>10</v>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>380010</v>
+        <v>320020</v>
       </c>
       <c r="B135" s="1">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>10</v>
@@ -6293,10 +6293,10 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>390020</v>
+        <v>320010</v>
       </c>
       <c r="B136" s="1">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>10</v>
@@ -6334,10 +6334,10 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>390010</v>
+        <v>330020</v>
       </c>
       <c r="B137" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>10</v>
@@ -6375,10 +6375,10 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>400020</v>
+        <v>330010</v>
       </c>
       <c r="B138" s="1">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>10</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>400010</v>
+        <v>340020</v>
       </c>
       <c r="B139" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>10</v>
@@ -6457,10 +6457,10 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>410020</v>
+        <v>340010</v>
       </c>
       <c r="B140" s="1">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>410010</v>
+        <v>350020</v>
       </c>
       <c r="B141" s="1">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>10</v>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>420020</v>
+        <v>350010</v>
       </c>
       <c r="B142" s="1">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>10</v>
@@ -6580,10 +6580,10 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>420010</v>
+        <v>360020</v>
       </c>
       <c r="B143" s="1">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>10</v>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>430020</v>
+        <v>360010</v>
       </c>
       <c r="B144" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>430010</v>
+        <v>370020</v>
       </c>
       <c r="B145" s="1">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>10</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>440020</v>
+        <v>370010</v>
       </c>
       <c r="B146" s="1">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>10</v>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>440010</v>
+        <v>380020</v>
       </c>
       <c r="B147" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>10</v>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>450020</v>
+        <v>380010</v>
       </c>
       <c r="B148" s="1">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>450010</v>
+        <v>390020</v>
       </c>
       <c r="B149" s="1">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>10</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>460020</v>
+        <v>390010</v>
       </c>
       <c r="B150" s="1">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>460010</v>
+        <v>400020</v>
       </c>
       <c r="B151" s="1">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>470020</v>
+        <v>400010</v>
       </c>
       <c r="B152" s="1">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>10</v>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>470010</v>
+        <v>410020</v>
       </c>
       <c r="B153" s="1">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>10</v>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>480020</v>
+        <v>410010</v>
       </c>
       <c r="B154" s="1">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>10</v>
@@ -7072,10 +7072,10 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>480010</v>
+        <v>420020</v>
       </c>
       <c r="B155" s="1">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>10</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>490020</v>
+        <v>420010</v>
       </c>
       <c r="B156" s="1">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>10</v>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>490010</v>
+        <v>430020</v>
       </c>
       <c r="B157" s="1">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>10</v>
@@ -7195,10 +7195,10 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>500020</v>
+        <v>430010</v>
       </c>
       <c r="B158" s="1">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>10</v>
@@ -7236,10 +7236,10 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>500010</v>
+        <v>440020</v>
       </c>
       <c r="B159" s="1">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>10</v>
@@ -7277,10 +7277,10 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>510020</v>
+        <v>440010</v>
       </c>
       <c r="B160" s="1">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>10</v>
@@ -7318,10 +7318,10 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>510010</v>
+        <v>450020</v>
       </c>
       <c r="B161" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>10</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>520020</v>
+        <v>450010</v>
       </c>
       <c r="B162" s="1">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>10</v>
@@ -7400,10 +7400,10 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>520010</v>
+        <v>460020</v>
       </c>
       <c r="B163" s="1">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>10</v>
@@ -7441,10 +7441,10 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>530020</v>
+        <v>460010</v>
       </c>
       <c r="B164" s="1">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>10</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>530010</v>
+        <v>470020</v>
       </c>
       <c r="B165" s="1">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>10</v>
@@ -7523,10 +7523,10 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>540020</v>
+        <v>470010</v>
       </c>
       <c r="B166" s="1">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>10</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>540010</v>
+        <v>480020</v>
       </c>
       <c r="B167" s="1">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>10</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>550020</v>
+        <v>480010</v>
       </c>
       <c r="B168" s="1">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>10</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>550010</v>
+        <v>490020</v>
       </c>
       <c r="B169" s="1">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>10</v>
@@ -7687,10 +7687,10 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>560020</v>
+        <v>490010</v>
       </c>
       <c r="B170" s="1">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>10</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>560010</v>
+        <v>500020</v>
       </c>
       <c r="B171" s="1">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>10</v>
@@ -7769,10 +7769,10 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>570020</v>
+        <v>500010</v>
       </c>
       <c r="B172" s="1">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>10</v>
@@ -7810,10 +7810,10 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>570010</v>
+        <v>510020</v>
       </c>
       <c r="B173" s="1">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>10</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>580020</v>
+        <v>510010</v>
       </c>
       <c r="B174" s="1">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>10</v>
@@ -7892,10 +7892,10 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>580010</v>
+        <v>520020</v>
       </c>
       <c r="B175" s="1">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>10</v>
@@ -7933,10 +7933,10 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>590020</v>
+        <v>520010</v>
       </c>
       <c r="B176" s="1">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>590010</v>
+        <v>530020</v>
       </c>
       <c r="B177" s="1">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>600020</v>
+        <v>530010</v>
       </c>
       <c r="B178" s="1">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>10</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>600010</v>
+        <v>540020</v>
       </c>
       <c r="B179" s="1">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>10</v>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>610020</v>
+        <v>540010</v>
       </c>
       <c r="B180" s="1">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>10</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>610010</v>
+        <v>550020</v>
       </c>
       <c r="B181" s="1">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>10</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>620020</v>
+        <v>550010</v>
       </c>
       <c r="B182" s="1">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>10</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>620010</v>
+        <v>560020</v>
       </c>
       <c r="B183" s="1">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>10</v>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>630020</v>
+        <v>560010</v>
       </c>
       <c r="B184" s="1">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>10</v>
@@ -8302,10 +8302,10 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>630010</v>
+        <v>570020</v>
       </c>
       <c r="B185" s="1">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>10</v>
@@ -8343,10 +8343,10 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>640020</v>
+        <v>570010</v>
       </c>
       <c r="B186" s="1">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>10</v>
@@ -8384,10 +8384,10 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>640010</v>
+        <v>580020</v>
       </c>
       <c r="B187" s="1">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>10</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>650020</v>
+        <v>580010</v>
       </c>
       <c r="B188" s="1">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>650010</v>
+        <v>590020</v>
       </c>
       <c r="B189" s="1">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>10</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>660020</v>
+        <v>590010</v>
       </c>
       <c r="B190" s="1">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>10</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>660010</v>
+        <v>600020</v>
       </c>
       <c r="B191" s="1">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>10</v>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>670020</v>
+        <v>600010</v>
       </c>
       <c r="B192" s="1">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>10</v>
@@ -8630,10 +8630,10 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>670010</v>
+        <v>610020</v>
       </c>
       <c r="B193" s="1">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>10</v>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>680020</v>
+        <v>610010</v>
       </c>
       <c r="B194" s="1">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>10</v>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>680010</v>
+        <v>620020</v>
       </c>
       <c r="B195" s="1">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>10</v>
@@ -8753,10 +8753,10 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>690020</v>
+        <v>620010</v>
       </c>
       <c r="B196" s="1">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>10</v>
@@ -8794,10 +8794,10 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>690010</v>
+        <v>630020</v>
       </c>
       <c r="B197" s="1">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>10</v>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>700020</v>
+        <v>630010</v>
       </c>
       <c r="B198" s="1">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>10</v>
@@ -8876,10 +8876,10 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>700010</v>
+        <v>640020</v>
       </c>
       <c r="B199" s="1">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>10</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>710020</v>
+        <v>640010</v>
       </c>
       <c r="B200" s="1">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>10</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>710010</v>
+        <v>650020</v>
       </c>
       <c r="B201" s="1">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>10</v>
@@ -8999,10 +8999,10 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>720020</v>
+        <v>650010</v>
       </c>
       <c r="B202" s="1">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>10</v>
@@ -9040,10 +9040,10 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>720010</v>
+        <v>660020</v>
       </c>
       <c r="B203" s="1">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>10</v>
@@ -9081,10 +9081,10 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>730020</v>
+        <v>660010</v>
       </c>
       <c r="B204" s="1">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>10</v>
@@ -9122,10 +9122,10 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>730010</v>
+        <v>670020</v>
       </c>
       <c r="B205" s="1">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>10</v>
@@ -9163,10 +9163,10 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>740020</v>
+        <v>670010</v>
       </c>
       <c r="B206" s="1">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>10</v>
@@ -9204,10 +9204,10 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>740010</v>
+        <v>680020</v>
       </c>
       <c r="B207" s="1">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>10</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>750020</v>
+        <v>680010</v>
       </c>
       <c r="B208" s="1">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>750010</v>
+        <v>690020</v>
       </c>
       <c r="B209" s="1">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>10</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>760020</v>
+        <v>690010</v>
       </c>
       <c r="B210" s="1">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>10</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>760010</v>
+        <v>700020</v>
       </c>
       <c r="B211" s="1">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>10</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>770020</v>
+        <v>700010</v>
       </c>
       <c r="B212" s="1">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>770010</v>
+        <v>710020</v>
       </c>
       <c r="B213" s="1">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>10</v>
@@ -9491,10 +9491,10 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>780020</v>
+        <v>710010</v>
       </c>
       <c r="B214" s="1">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>10</v>
@@ -9532,10 +9532,10 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>780010</v>
+        <v>720020</v>
       </c>
       <c r="B215" s="1">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>10</v>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>790020</v>
+        <v>720010</v>
       </c>
       <c r="B216" s="1">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>10</v>
@@ -9614,10 +9614,10 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>790010</v>
+        <v>730020</v>
       </c>
       <c r="B217" s="1">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>10</v>
@@ -9655,10 +9655,10 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>800020</v>
+        <v>730010</v>
       </c>
       <c r="B218" s="1">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>10</v>
@@ -9696,10 +9696,10 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>800010</v>
+        <v>740020</v>
       </c>
       <c r="B219" s="1">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>10</v>
@@ -9737,10 +9737,10 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>810020</v>
+        <v>740010</v>
       </c>
       <c r="B220" s="1">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>10</v>
@@ -9778,10 +9778,10 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>810010</v>
+        <v>750020</v>
       </c>
       <c r="B221" s="1">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>820020</v>
+        <v>750010</v>
       </c>
       <c r="B222" s="1">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>10</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>820010</v>
+        <v>760020</v>
       </c>
       <c r="B223" s="1">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>10</v>
@@ -9901,10 +9901,10 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>830020</v>
+        <v>760010</v>
       </c>
       <c r="B224" s="1">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>10</v>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>830010</v>
+        <v>770020</v>
       </c>
       <c r="B225" s="1">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>10</v>
@@ -9983,10 +9983,10 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>840020</v>
+        <v>770010</v>
       </c>
       <c r="B226" s="1">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>10</v>
@@ -10024,10 +10024,10 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>840010</v>
+        <v>780020</v>
       </c>
       <c r="B227" s="1">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>10</v>
@@ -10065,10 +10065,10 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>850020</v>
+        <v>780010</v>
       </c>
       <c r="B228" s="1">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>10</v>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>850010</v>
+        <v>790020</v>
       </c>
       <c r="B229" s="1">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>10</v>
@@ -10147,10 +10147,10 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>860020</v>
+        <v>790010</v>
       </c>
       <c r="B230" s="1">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>10</v>
@@ -10188,10 +10188,10 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>860010</v>
+        <v>800020</v>
       </c>
       <c r="B231" s="1">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>10</v>
@@ -10229,10 +10229,10 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>870020</v>
+        <v>800010</v>
       </c>
       <c r="B232" s="1">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>10</v>
@@ -10270,10 +10270,10 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>870010</v>
+        <v>810020</v>
       </c>
       <c r="B233" s="1">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>10</v>
@@ -10311,10 +10311,10 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>880020</v>
+        <v>810010</v>
       </c>
       <c r="B234" s="1">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>10</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>880010</v>
+        <v>820020</v>
       </c>
       <c r="B235" s="1">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>10</v>
@@ -10393,10 +10393,10 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>890020</v>
+        <v>820010</v>
       </c>
       <c r="B236" s="1">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>10</v>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>890010</v>
+        <v>830020</v>
       </c>
       <c r="B237" s="1">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>10</v>
@@ -10475,10 +10475,10 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>900020</v>
+        <v>830010</v>
       </c>
       <c r="B238" s="1">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>10</v>
@@ -10516,10 +10516,10 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>900010</v>
+        <v>840020</v>
       </c>
       <c r="B239" s="1">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>10</v>
@@ -10557,10 +10557,10 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>910020</v>
+        <v>840010</v>
       </c>
       <c r="B240" s="1">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>10</v>
@@ -10598,10 +10598,10 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>910010</v>
+        <v>850020</v>
       </c>
       <c r="B241" s="1">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>10</v>
@@ -10639,10 +10639,10 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>920020</v>
+        <v>850010</v>
       </c>
       <c r="B242" s="1">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>10</v>
@@ -10680,10 +10680,10 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>920010</v>
+        <v>860020</v>
       </c>
       <c r="B243" s="1">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>10</v>
@@ -10721,10 +10721,10 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>930020</v>
+        <v>860010</v>
       </c>
       <c r="B244" s="1">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>930010</v>
+        <v>870020</v>
       </c>
       <c r="B245" s="1">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>10</v>
@@ -10803,10 +10803,10 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>940020</v>
+        <v>870010</v>
       </c>
       <c r="B246" s="1">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>10</v>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>940010</v>
+        <v>880020</v>
       </c>
       <c r="B247" s="1">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>950020</v>
+        <v>880010</v>
       </c>
       <c r="B248" s="1">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>10</v>
@@ -10926,10 +10926,10 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>950010</v>
+        <v>890020</v>
       </c>
       <c r="B249" s="1">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>10</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>960020</v>
+        <v>890010</v>
       </c>
       <c r="B250" s="1">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>10</v>
@@ -11008,10 +11008,10 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>960010</v>
+        <v>900020</v>
       </c>
       <c r="B251" s="1">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>10</v>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>970020</v>
+        <v>900010</v>
       </c>
       <c r="B252" s="1">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>10</v>
@@ -11090,10 +11090,10 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>970010</v>
+        <v>910020</v>
       </c>
       <c r="B253" s="1">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>10</v>
@@ -11131,10 +11131,10 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>980020</v>
+        <v>910010</v>
       </c>
       <c r="B254" s="1">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>10</v>
@@ -11172,10 +11172,10 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>980010</v>
+        <v>920020</v>
       </c>
       <c r="B255" s="1">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>990020</v>
+        <v>920010</v>
       </c>
       <c r="B256" s="1">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>10</v>
@@ -11254,10 +11254,10 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>990010</v>
+        <v>930020</v>
       </c>
       <c r="B257" s="1">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>10</v>
@@ -11295,10 +11295,10 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1000020</v>
+        <v>930010</v>
       </c>
       <c r="B258" s="1">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>10</v>
@@ -11336,10 +11336,10 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1000010</v>
+        <v>940020</v>
       </c>
       <c r="B259" s="1">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>10</v>
@@ -11377,10 +11377,10 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1010020</v>
+        <v>940010</v>
       </c>
       <c r="B260" s="1">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>10</v>
@@ -11418,10 +11418,10 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1010010</v>
+        <v>950020</v>
       </c>
       <c r="B261" s="1">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>10</v>
@@ -11459,10 +11459,10 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1020020</v>
+        <v>950010</v>
       </c>
       <c r="B262" s="1">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>10</v>
@@ -11500,10 +11500,10 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1020010</v>
+        <v>960020</v>
       </c>
       <c r="B263" s="1">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>10</v>
@@ -11541,10 +11541,10 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>1030020</v>
+        <v>960010</v>
       </c>
       <c r="B264" s="1">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>1030010</v>
+        <v>970020</v>
       </c>
       <c r="B265" s="1">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>10</v>
@@ -11623,10 +11623,10 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>1040020</v>
+        <v>970010</v>
       </c>
       <c r="B266" s="1">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>1040010</v>
+        <v>980020</v>
       </c>
       <c r="B267" s="1">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>10</v>
@@ -11705,10 +11705,10 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>1050020</v>
+        <v>980010</v>
       </c>
       <c r="B268" s="1">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>10</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>1050010</v>
+        <v>990020</v>
       </c>
       <c r="B269" s="1">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>10</v>
@@ -11787,10 +11787,10 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1060020</v>
+        <v>990010</v>
       </c>
       <c r="B270" s="1">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>10</v>
@@ -11828,10 +11828,10 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1060010</v>
+        <v>1000020</v>
       </c>
       <c r="B271" s="1">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>10</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1070020</v>
+        <v>1000010</v>
       </c>
       <c r="B272" s="1">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>10</v>
@@ -11910,10 +11910,10 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1070010</v>
+        <v>1010020</v>
       </c>
       <c r="B273" s="1">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>10</v>
@@ -11951,10 +11951,10 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1080020</v>
+        <v>1010010</v>
       </c>
       <c r="B274" s="1">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>10</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1080010</v>
+        <v>1020020</v>
       </c>
       <c r="B275" s="1">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>10</v>
@@ -12033,10 +12033,10 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1090020</v>
+        <v>1020010</v>
       </c>
       <c r="B276" s="1">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>10</v>
@@ -12074,10 +12074,10 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1090010</v>
+        <v>1030020</v>
       </c>
       <c r="B277" s="1">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>10</v>
@@ -12115,10 +12115,10 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1100020</v>
+        <v>1030010</v>
       </c>
       <c r="B278" s="1">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>10</v>
@@ -12156,10 +12156,10 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1100010</v>
+        <v>1040020</v>
       </c>
       <c r="B279" s="1">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>10</v>
@@ -12197,10 +12197,10 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1110020</v>
+        <v>1040010</v>
       </c>
       <c r="B280" s="1">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>10</v>
@@ -12238,10 +12238,10 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1110010</v>
+        <v>1050020</v>
       </c>
       <c r="B281" s="1">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1120020</v>
+        <v>1050010</v>
       </c>
       <c r="B282" s="1">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>10</v>
@@ -12320,10 +12320,10 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1120010</v>
+        <v>1060020</v>
       </c>
       <c r="B283" s="1">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>10</v>
@@ -12361,10 +12361,10 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1130020</v>
+        <v>1060010</v>
       </c>
       <c r="B284" s="1">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>10</v>
@@ -12402,10 +12402,10 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1130010</v>
+        <v>1070020</v>
       </c>
       <c r="B285" s="1">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>10</v>
@@ -12443,10 +12443,10 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1140020</v>
+        <v>1070010</v>
       </c>
       <c r="B286" s="1">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>10</v>
@@ -12484,10 +12484,10 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1140010</v>
+        <v>1080020</v>
       </c>
       <c r="B287" s="1">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>10</v>
@@ -12525,10 +12525,10 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1150020</v>
+        <v>1080010</v>
       </c>
       <c r="B288" s="1">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1150010</v>
+        <v>1090020</v>
       </c>
       <c r="B289" s="1">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1160020</v>
+        <v>1090010</v>
       </c>
       <c r="B290" s="1">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>10</v>
@@ -12648,10 +12648,10 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1160010</v>
+        <v>1100020</v>
       </c>
       <c r="B291" s="1">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>10</v>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1170020</v>
+        <v>1100010</v>
       </c>
       <c r="B292" s="1">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>10</v>
@@ -12730,10 +12730,10 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1170010</v>
+        <v>1110020</v>
       </c>
       <c r="B293" s="1">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>10</v>
@@ -12771,10 +12771,10 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1180020</v>
+        <v>1110010</v>
       </c>
       <c r="B294" s="1">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>10</v>
@@ -12812,10 +12812,10 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1180010</v>
+        <v>1120020</v>
       </c>
       <c r="B295" s="1">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>10</v>
@@ -12853,10 +12853,10 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1190020</v>
+        <v>1120010</v>
       </c>
       <c r="B296" s="1">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>10</v>
@@ -12894,10 +12894,10 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1190010</v>
+        <v>1130020</v>
       </c>
       <c r="B297" s="1">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>10</v>
@@ -12935,10 +12935,10 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1200020</v>
+        <v>1130010</v>
       </c>
       <c r="B298" s="1">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>10</v>
@@ -12976,10 +12976,10 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1200010</v>
+        <v>1140020</v>
       </c>
       <c r="B299" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>10</v>
@@ -13017,10 +13017,10 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1210020</v>
+        <v>1140010</v>
       </c>
       <c r="B300" s="1">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>10</v>
@@ -13058,10 +13058,10 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1210010</v>
+        <v>1150020</v>
       </c>
       <c r="B301" s="1">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>10</v>
@@ -13099,10 +13099,10 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1220020</v>
+        <v>1150010</v>
       </c>
       <c r="B302" s="1">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>10</v>
@@ -13140,10 +13140,10 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1220010</v>
+        <v>1160020</v>
       </c>
       <c r="B303" s="1">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>10</v>
@@ -13181,10 +13181,10 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1230020</v>
+        <v>1160010</v>
       </c>
       <c r="B304" s="1">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>10</v>
@@ -13222,10 +13222,10 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1230010</v>
+        <v>1170020</v>
       </c>
       <c r="B305" s="1">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>10</v>
@@ -13263,10 +13263,10 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1240020</v>
+        <v>1170010</v>
       </c>
       <c r="B306" s="1">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>10</v>
@@ -13304,10 +13304,10 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1240010</v>
+        <v>1180020</v>
       </c>
       <c r="B307" s="1">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>10</v>
@@ -13345,10 +13345,10 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1250020</v>
+        <v>1180010</v>
       </c>
       <c r="B308" s="1">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>10</v>
@@ -13386,10 +13386,10 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1250010</v>
+        <v>1190020</v>
       </c>
       <c r="B309" s="1">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>10</v>
@@ -13427,10 +13427,10 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1260020</v>
+        <v>1190010</v>
       </c>
       <c r="B310" s="1">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>10</v>
@@ -13468,10 +13468,10 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1260010</v>
+        <v>1200020</v>
       </c>
       <c r="B311" s="1">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>10</v>
@@ -13509,10 +13509,10 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1270020</v>
+        <v>1200010</v>
       </c>
       <c r="B312" s="1">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1270010</v>
+        <v>1210020</v>
       </c>
       <c r="B313" s="1">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>10</v>
@@ -13591,10 +13591,10 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1280020</v>
+        <v>1210010</v>
       </c>
       <c r="B314" s="1">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>10</v>
@@ -13632,10 +13632,10 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1280010</v>
+        <v>1220020</v>
       </c>
       <c r="B315" s="1">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>10</v>
@@ -13673,10 +13673,10 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1290020</v>
+        <v>1220010</v>
       </c>
       <c r="B316" s="1">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>10</v>
@@ -13714,10 +13714,10 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1290010</v>
+        <v>1230020</v>
       </c>
       <c r="B317" s="1">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>10</v>
@@ -13755,10 +13755,10 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1300020</v>
+        <v>1230010</v>
       </c>
       <c r="B318" s="1">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>10</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1300010</v>
+        <v>1240020</v>
       </c>
       <c r="B319" s="1">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>10</v>
@@ -13837,10 +13837,10 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1310020</v>
+        <v>1240010</v>
       </c>
       <c r="B320" s="1">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>10</v>
@@ -13878,10 +13878,10 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1310010</v>
+        <v>1250020</v>
       </c>
       <c r="B321" s="1">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>10</v>
@@ -13919,10 +13919,10 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1320020</v>
+        <v>1250010</v>
       </c>
       <c r="B322" s="1">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>10</v>
@@ -13960,10 +13960,10 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1320010</v>
+        <v>1260020</v>
       </c>
       <c r="B323" s="1">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>10</v>
@@ -14001,10 +14001,10 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1330020</v>
+        <v>1260010</v>
       </c>
       <c r="B324" s="1">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>10</v>
@@ -14042,10 +14042,10 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1330010</v>
+        <v>1270020</v>
       </c>
       <c r="B325" s="1">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>10</v>
@@ -14083,10 +14083,10 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1340020</v>
+        <v>1270010</v>
       </c>
       <c r="B326" s="1">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>10</v>
@@ -14124,10 +14124,10 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1340010</v>
+        <v>1280020</v>
       </c>
       <c r="B327" s="1">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>10</v>
@@ -14165,10 +14165,10 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1350020</v>
+        <v>1280010</v>
       </c>
       <c r="B328" s="1">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>10</v>
@@ -14206,10 +14206,10 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1350010</v>
+        <v>1290020</v>
       </c>
       <c r="B329" s="1">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>10</v>
@@ -14247,10 +14247,10 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1360020</v>
+        <v>1290010</v>
       </c>
       <c r="B330" s="1">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>10</v>
@@ -14288,10 +14288,10 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1360010</v>
+        <v>1300020</v>
       </c>
       <c r="B331" s="1">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>10</v>
@@ -14329,10 +14329,10 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1370020</v>
+        <v>1300010</v>
       </c>
       <c r="B332" s="1">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>10</v>
@@ -14370,10 +14370,10 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1370010</v>
+        <v>1310020</v>
       </c>
       <c r="B333" s="1">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>10</v>
@@ -14411,10 +14411,10 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1380020</v>
+        <v>1310010</v>
       </c>
       <c r="B334" s="1">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>10</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1380010</v>
+        <v>1320020</v>
       </c>
       <c r="B335" s="1">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1390020</v>
+        <v>1320010</v>
       </c>
       <c r="B336" s="1">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>10</v>
@@ -14534,10 +14534,10 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1390010</v>
+        <v>1330020</v>
       </c>
       <c r="B337" s="1">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>10</v>
@@ -14575,10 +14575,10 @@
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1400020</v>
+        <v>1330010</v>
       </c>
       <c r="B338" s="1">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>10</v>
@@ -14616,10 +14616,10 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1400010</v>
+        <v>1340020</v>
       </c>
       <c r="B339" s="1">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>10</v>
@@ -14657,10 +14657,10 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>1410020</v>
+        <v>1340010</v>
       </c>
       <c r="B340" s="1">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>10</v>
@@ -14698,10 +14698,10 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>1410010</v>
+        <v>1350020</v>
       </c>
       <c r="B341" s="1">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>10</v>
@@ -14739,10 +14739,10 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>1420020</v>
+        <v>1350010</v>
       </c>
       <c r="B342" s="1">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>10</v>
@@ -14780,10 +14780,10 @@
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>1420010</v>
+        <v>1360020</v>
       </c>
       <c r="B343" s="1">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>10</v>
@@ -14821,10 +14821,10 @@
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>1430020</v>
+        <v>1360010</v>
       </c>
       <c r="B344" s="1">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>10</v>
@@ -14862,10 +14862,10 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>1430010</v>
+        <v>1370020</v>
       </c>
       <c r="B345" s="1">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>10</v>
@@ -14903,10 +14903,10 @@
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>1440020</v>
+        <v>1370010</v>
       </c>
       <c r="B346" s="1">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>10</v>
@@ -14944,10 +14944,10 @@
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>1440010</v>
+        <v>1380020</v>
       </c>
       <c r="B347" s="1">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>10</v>
@@ -14985,10 +14985,10 @@
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>1450020</v>
+        <v>1380010</v>
       </c>
       <c r="B348" s="1">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>10</v>
@@ -15026,10 +15026,10 @@
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>1450010</v>
+        <v>1390020</v>
       </c>
       <c r="B349" s="1">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>10</v>
@@ -15067,10 +15067,10 @@
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>1460020</v>
+        <v>1390010</v>
       </c>
       <c r="B350" s="1">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>10</v>
@@ -15108,10 +15108,10 @@
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>1460010</v>
+        <v>1400020</v>
       </c>
       <c r="B351" s="1">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>10</v>
@@ -15149,10 +15149,10 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>1470020</v>
+        <v>1400010</v>
       </c>
       <c r="B352" s="1">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>10</v>
@@ -15190,10 +15190,10 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>1470010</v>
+        <v>1410020</v>
       </c>
       <c r="B353" s="1">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>10</v>
@@ -15231,10 +15231,10 @@
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>1480020</v>
+        <v>1410010</v>
       </c>
       <c r="B354" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>10</v>
@@ -15272,10 +15272,10 @@
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>1480010</v>
+        <v>1420020</v>
       </c>
       <c r="B355" s="1">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>10</v>
@@ -15313,10 +15313,10 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>1490020</v>
+        <v>1420010</v>
       </c>
       <c r="B356" s="1">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>10</v>
@@ -15354,10 +15354,10 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>1490010</v>
+        <v>1430020</v>
       </c>
       <c r="B357" s="1">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>10</v>
@@ -15395,10 +15395,10 @@
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>1500020</v>
+        <v>1430010</v>
       </c>
       <c r="B358" s="1">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>10</v>
@@ -15436,10 +15436,10 @@
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>1500010</v>
+        <v>1440020</v>
       </c>
       <c r="B359" s="1">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>10</v>
@@ -15477,10 +15477,10 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>1510020</v>
+        <v>1440010</v>
       </c>
       <c r="B360" s="1">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>10</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>1510010</v>
+        <v>1450020</v>
       </c>
       <c r="B361" s="1">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>10</v>
@@ -15559,10 +15559,10 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>1520020</v>
+        <v>1450010</v>
       </c>
       <c r="B362" s="1">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>10</v>
@@ -15600,10 +15600,10 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>1520010</v>
+        <v>1460020</v>
       </c>
       <c r="B363" s="1">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>10</v>
@@ -15641,10 +15641,10 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>1530020</v>
+        <v>1460010</v>
       </c>
       <c r="B364" s="1">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>10</v>
@@ -15682,10 +15682,10 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>1530010</v>
+        <v>1470020</v>
       </c>
       <c r="B365" s="1">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>10</v>
@@ -15723,10 +15723,10 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>1540020</v>
+        <v>1470010</v>
       </c>
       <c r="B366" s="1">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>10</v>
@@ -15764,10 +15764,10 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>1540010</v>
+        <v>1480020</v>
       </c>
       <c r="B367" s="1">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>10</v>
@@ -15805,10 +15805,10 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>1550020</v>
+        <v>1480010</v>
       </c>
       <c r="B368" s="1">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>10</v>
@@ -15846,10 +15846,10 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>1550010</v>
+        <v>1490020</v>
       </c>
       <c r="B369" s="1">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>10</v>
@@ -15887,10 +15887,10 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>1560020</v>
+        <v>1490010</v>
       </c>
       <c r="B370" s="1">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>10</v>
@@ -15928,10 +15928,10 @@
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>1560010</v>
+        <v>1500020</v>
       </c>
       <c r="B371" s="1">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>10</v>
@@ -15969,10 +15969,10 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>1570020</v>
+        <v>1500010</v>
       </c>
       <c r="B372" s="1">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>10</v>
@@ -16010,10 +16010,10 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>1570010</v>
+        <v>1510020</v>
       </c>
       <c r="B373" s="1">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>10</v>
@@ -16051,10 +16051,10 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>1580020</v>
+        <v>1510010</v>
       </c>
       <c r="B374" s="1">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>10</v>
@@ -16092,10 +16092,10 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>1580010</v>
+        <v>1520020</v>
       </c>
       <c r="B375" s="1">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>10</v>
@@ -16133,10 +16133,10 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>1590020</v>
+        <v>1520010</v>
       </c>
       <c r="B376" s="1">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>10</v>
@@ -16174,10 +16174,10 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>1590010</v>
+        <v>1530020</v>
       </c>
       <c r="B377" s="1">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>10</v>
@@ -16215,10 +16215,10 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>1600020</v>
+        <v>1530010</v>
       </c>
       <c r="B378" s="1">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>10</v>
@@ -16256,42 +16256,575 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
+        <v>1540020</v>
+      </c>
+      <c r="B379" s="1">
+        <v>154</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G379" s="1">
+        <v>0</v>
+      </c>
+      <c r="H379" s="2">
+        <v>0</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J379" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K379" s="7">
+        <v>0</v>
+      </c>
+      <c r="L379" s="7">
+        <v>0</v>
+      </c>
+      <c r="M379" s="7">
+        <v>0</v>
+      </c>
+      <c r="N379" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A380" s="1">
+        <v>1540010</v>
+      </c>
+      <c r="B380" s="1">
+        <v>154</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G380" s="1">
+        <v>0</v>
+      </c>
+      <c r="H380" s="2">
+        <v>0</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J380" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K380" s="7">
+        <v>0</v>
+      </c>
+      <c r="L380" s="7">
+        <v>0</v>
+      </c>
+      <c r="M380" s="7">
+        <v>0</v>
+      </c>
+      <c r="N380" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A381" s="1">
+        <v>1550020</v>
+      </c>
+      <c r="B381" s="1">
+        <v>155</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E381" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G381" s="1">
+        <v>0</v>
+      </c>
+      <c r="H381" s="2">
+        <v>0</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J381" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K381" s="7">
+        <v>0</v>
+      </c>
+      <c r="L381" s="7">
+        <v>0</v>
+      </c>
+      <c r="M381" s="7">
+        <v>0</v>
+      </c>
+      <c r="N381" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A382" s="1">
+        <v>1550010</v>
+      </c>
+      <c r="B382" s="1">
+        <v>155</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E382" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G382" s="1">
+        <v>0</v>
+      </c>
+      <c r="H382" s="2">
+        <v>0</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J382" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K382" s="7">
+        <v>0</v>
+      </c>
+      <c r="L382" s="7">
+        <v>0</v>
+      </c>
+      <c r="M382" s="7">
+        <v>0</v>
+      </c>
+      <c r="N382" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A383" s="1">
+        <v>1560020</v>
+      </c>
+      <c r="B383" s="1">
+        <v>156</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E383" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G383" s="1">
+        <v>0</v>
+      </c>
+      <c r="H383" s="2">
+        <v>0</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J383" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K383" s="7">
+        <v>0</v>
+      </c>
+      <c r="L383" s="7">
+        <v>0</v>
+      </c>
+      <c r="M383" s="7">
+        <v>0</v>
+      </c>
+      <c r="N383" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A384" s="1">
+        <v>1560010</v>
+      </c>
+      <c r="B384" s="1">
+        <v>156</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E384" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G384" s="1">
+        <v>0</v>
+      </c>
+      <c r="H384" s="2">
+        <v>0</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J384" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K384" s="7">
+        <v>0</v>
+      </c>
+      <c r="L384" s="7">
+        <v>0</v>
+      </c>
+      <c r="M384" s="7">
+        <v>0</v>
+      </c>
+      <c r="N384" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A385" s="1">
+        <v>1570020</v>
+      </c>
+      <c r="B385" s="1">
+        <v>157</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G385" s="1">
+        <v>0</v>
+      </c>
+      <c r="H385" s="2">
+        <v>0</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J385" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K385" s="7">
+        <v>0</v>
+      </c>
+      <c r="L385" s="7">
+        <v>0</v>
+      </c>
+      <c r="M385" s="7">
+        <v>0</v>
+      </c>
+      <c r="N385" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A386" s="1">
+        <v>1570010</v>
+      </c>
+      <c r="B386" s="1">
+        <v>157</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E386" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G386" s="1">
+        <v>0</v>
+      </c>
+      <c r="H386" s="2">
+        <v>0</v>
+      </c>
+      <c r="I386" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J386" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K386" s="7">
+        <v>0</v>
+      </c>
+      <c r="L386" s="7">
+        <v>0</v>
+      </c>
+      <c r="M386" s="7">
+        <v>0</v>
+      </c>
+      <c r="N386" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A387" s="1">
+        <v>1580020</v>
+      </c>
+      <c r="B387" s="1">
+        <v>158</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E387" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G387" s="1">
+        <v>0</v>
+      </c>
+      <c r="H387" s="2">
+        <v>0</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J387" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K387" s="7">
+        <v>0</v>
+      </c>
+      <c r="L387" s="7">
+        <v>0</v>
+      </c>
+      <c r="M387" s="7">
+        <v>0</v>
+      </c>
+      <c r="N387" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A388" s="1">
+        <v>1580010</v>
+      </c>
+      <c r="B388" s="1">
+        <v>158</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E388" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G388" s="1">
+        <v>0</v>
+      </c>
+      <c r="H388" s="2">
+        <v>0</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J388" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K388" s="7">
+        <v>0</v>
+      </c>
+      <c r="L388" s="7">
+        <v>0</v>
+      </c>
+      <c r="M388" s="7">
+        <v>0</v>
+      </c>
+      <c r="N388" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A389" s="1">
+        <v>1590020</v>
+      </c>
+      <c r="B389" s="1">
+        <v>159</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E389" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G389" s="1">
+        <v>0</v>
+      </c>
+      <c r="H389" s="2">
+        <v>0</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J389" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K389" s="7">
+        <v>0</v>
+      </c>
+      <c r="L389" s="7">
+        <v>0</v>
+      </c>
+      <c r="M389" s="7">
+        <v>0</v>
+      </c>
+      <c r="N389" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A390" s="1">
+        <v>1590010</v>
+      </c>
+      <c r="B390" s="1">
+        <v>159</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E390" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G390" s="1">
+        <v>0</v>
+      </c>
+      <c r="H390" s="2">
+        <v>0</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J390" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K390" s="7">
+        <v>0</v>
+      </c>
+      <c r="L390" s="7">
+        <v>0</v>
+      </c>
+      <c r="M390" s="7">
+        <v>0</v>
+      </c>
+      <c r="N390" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A391" s="1">
+        <v>1600020</v>
+      </c>
+      <c r="B391" s="1">
+        <v>160</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E391" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G391" s="1">
+        <v>0</v>
+      </c>
+      <c r="H391" s="2">
+        <v>0</v>
+      </c>
+      <c r="I391" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J391" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K391" s="7">
+        <v>0</v>
+      </c>
+      <c r="L391" s="7">
+        <v>0</v>
+      </c>
+      <c r="M391" s="7">
+        <v>0</v>
+      </c>
+      <c r="N391" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A392" s="1">
         <v>1600010</v>
       </c>
-      <c r="B379" s="1">
+      <c r="B392" s="1">
         <v>160</v>
       </c>
-      <c r="D379" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E379" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F379" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G379" s="1">
-        <v>0</v>
-      </c>
-      <c r="H379" s="2">
-        <v>0</v>
-      </c>
-      <c r="I379" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J379" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K379" s="7">
-        <v>0</v>
-      </c>
-      <c r="L379" s="7">
-        <v>0</v>
-      </c>
-      <c r="M379" s="7">
-        <v>0</v>
-      </c>
-      <c r="N379" s="7">
+      <c r="D392" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E392" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F392" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G392" s="1">
+        <v>0</v>
+      </c>
+      <c r="H392" s="2">
+        <v>0</v>
+      </c>
+      <c r="I392" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J392" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K392" s="7">
+        <v>0</v>
+      </c>
+      <c r="L392" s="7">
+        <v>0</v>
+      </c>
+      <c r="M392" s="7">
+        <v>0</v>
+      </c>
+      <c r="N392" s="7">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D99D0F-8814-4540-84BF-DAECA00DD5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452206F3-D27D-4EE5-B223-9A933DA7F8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$N$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$N$391</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="89">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -365,6 +365,33 @@
   <si>
     <t>资源id（首次）</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42633001</t>
+  </si>
+  <si>
+    <t>46200001:10</t>
+  </si>
+  <si>
+    <t>46200001:4</t>
+  </si>
+  <si>
+    <t>46200001:20</t>
+  </si>
+  <si>
+    <t>42751001</t>
+  </si>
+  <si>
+    <t>46200001:6</t>
+  </si>
+  <si>
+    <t>46200001:30</t>
+  </si>
+  <si>
+    <t>42663001</t>
+  </si>
+  <si>
+    <t>42761001</t>
   </si>
 </sst>
 </file>
@@ -754,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N392"/>
+  <dimension ref="A1:N391"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -5654,26 +5681,26 @@
       <c r="G120" s="1">
         <v>0</v>
       </c>
-      <c r="H120" s="2">
-        <v>0</v>
+      <c r="H120" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K120" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M120" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N120" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.15">
@@ -5690,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G121" s="1">
         <v>0</v>
@@ -5702,19 +5729,19 @@
         <v>16</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="K121" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L121" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M121" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.15">
@@ -5731,7 +5758,7 @@
         <v>16</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G122" s="1">
         <v>0</v>
@@ -5743,19 +5770,19 @@
         <v>16</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="K122" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L122" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M122" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N122" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.15">
@@ -5777,26 +5804,26 @@
       <c r="G123" s="1">
         <v>0</v>
       </c>
-      <c r="H123" s="2">
-        <v>0</v>
+      <c r="H123" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K123" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L123" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M123" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N123" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.15">
@@ -5813,31 +5840,31 @@
         <v>16</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G124" s="1">
         <v>0</v>
       </c>
-      <c r="H124" s="2">
-        <v>0</v>
+      <c r="H124" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K124" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M124" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N124" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.15">
@@ -5866,19 +5893,19 @@
         <v>16</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="K125" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L125" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M125" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N125" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.15">
@@ -5895,7 +5922,7 @@
         <v>16</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G126" s="1">
         <v>0</v>
@@ -5907,19 +5934,19 @@
         <v>16</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="K126" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L126" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M126" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N126" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.15">
@@ -5936,31 +5963,31 @@
         <v>16</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G127" s="1">
         <v>0</v>
       </c>
-      <c r="H127" s="2">
-        <v>0</v>
+      <c r="H127" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K127" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L127" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M127" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N127" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.15">
@@ -5977,7 +6004,7 @@
         <v>16</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="G128" s="1">
         <v>0</v>
@@ -5989,24 +6016,24 @@
         <v>16</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="K128" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L128" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M128" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N128" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>300010</v>
+        <v>300011</v>
       </c>
       <c r="B129" s="1">
         <v>30</v>
@@ -6018,36 +6045,36 @@
         <v>16</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G129" s="1">
         <v>0</v>
       </c>
-      <c r="H129" s="2">
-        <v>0</v>
+      <c r="H129" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K129" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M129" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N129" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>300011</v>
+        <v>300012</v>
       </c>
       <c r="B130" s="1">
         <v>30</v>
@@ -6059,36 +6086,36 @@
         <v>16</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G130" s="1">
         <v>0</v>
       </c>
-      <c r="H130" s="2">
-        <v>0</v>
+      <c r="H130" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K130" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L130" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M130" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N130" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>300012</v>
+        <v>300013</v>
       </c>
       <c r="B131" s="1">
         <v>30</v>
@@ -6100,7 +6127,7 @@
         <v>16</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
@@ -6112,36 +6139,36 @@
         <v>16</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="K131" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L131" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M131" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N131" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>300013</v>
+        <v>310020</v>
       </c>
       <c r="B132" s="1">
-        <v>30</v>
-      </c>
-      <c r="D132" s="2">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G132" s="1">
         <v>0</v>
@@ -6153,7 +6180,7 @@
         <v>16</v>
       </c>
       <c r="J132" s="4" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="K132" s="7">
         <v>0</v>
@@ -6170,7 +6197,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>310020</v>
+        <v>310010</v>
       </c>
       <c r="B133" s="1">
         <v>31</v>
@@ -6211,10 +6238,10 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>310010</v>
+        <v>320020</v>
       </c>
       <c r="B134" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>10</v>
@@ -6252,7 +6279,7 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>320020</v>
+        <v>320010</v>
       </c>
       <c r="B135" s="1">
         <v>32</v>
@@ -6293,10 +6320,10 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>320010</v>
+        <v>330020</v>
       </c>
       <c r="B136" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>10</v>
@@ -6334,7 +6361,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>330020</v>
+        <v>330010</v>
       </c>
       <c r="B137" s="1">
         <v>33</v>
@@ -6375,10 +6402,10 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>330010</v>
+        <v>340020</v>
       </c>
       <c r="B138" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>10</v>
@@ -6416,7 +6443,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>340020</v>
+        <v>340010</v>
       </c>
       <c r="B139" s="1">
         <v>34</v>
@@ -6457,10 +6484,10 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>340010</v>
+        <v>350020</v>
       </c>
       <c r="B140" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>10</v>
@@ -6498,7 +6525,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>350020</v>
+        <v>350010</v>
       </c>
       <c r="B141" s="1">
         <v>35</v>
@@ -6539,10 +6566,10 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>350010</v>
+        <v>360020</v>
       </c>
       <c r="B142" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>10</v>
@@ -6580,7 +6607,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>360020</v>
+        <v>360010</v>
       </c>
       <c r="B143" s="1">
         <v>36</v>
@@ -6621,10 +6648,10 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>360010</v>
+        <v>370020</v>
       </c>
       <c r="B144" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>10</v>
@@ -6662,7 +6689,7 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>370020</v>
+        <v>370010</v>
       </c>
       <c r="B145" s="1">
         <v>37</v>
@@ -6703,10 +6730,10 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>370010</v>
+        <v>380020</v>
       </c>
       <c r="B146" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>10</v>
@@ -6744,7 +6771,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>380020</v>
+        <v>380010</v>
       </c>
       <c r="B147" s="1">
         <v>38</v>
@@ -6785,10 +6812,10 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>380010</v>
+        <v>390020</v>
       </c>
       <c r="B148" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>10</v>
@@ -6826,7 +6853,7 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>390020</v>
+        <v>390010</v>
       </c>
       <c r="B149" s="1">
         <v>39</v>
@@ -6867,10 +6894,10 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>390010</v>
+        <v>400020</v>
       </c>
       <c r="B150" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>10</v>
@@ -6908,7 +6935,7 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>400020</v>
+        <v>400010</v>
       </c>
       <c r="B151" s="1">
         <v>40</v>
@@ -6949,10 +6976,10 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>400010</v>
+        <v>410020</v>
       </c>
       <c r="B152" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>10</v>
@@ -6990,7 +7017,7 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>410020</v>
+        <v>410010</v>
       </c>
       <c r="B153" s="1">
         <v>41</v>
@@ -7031,10 +7058,10 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>410010</v>
+        <v>420020</v>
       </c>
       <c r="B154" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>10</v>
@@ -7072,7 +7099,7 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>420020</v>
+        <v>420010</v>
       </c>
       <c r="B155" s="1">
         <v>42</v>
@@ -7113,10 +7140,10 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>420010</v>
+        <v>430020</v>
       </c>
       <c r="B156" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>10</v>
@@ -7154,7 +7181,7 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>430020</v>
+        <v>430010</v>
       </c>
       <c r="B157" s="1">
         <v>43</v>
@@ -7195,10 +7222,10 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>430010</v>
+        <v>440020</v>
       </c>
       <c r="B158" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>10</v>
@@ -7236,7 +7263,7 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>440020</v>
+        <v>440010</v>
       </c>
       <c r="B159" s="1">
         <v>44</v>
@@ -7277,10 +7304,10 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>440010</v>
+        <v>450020</v>
       </c>
       <c r="B160" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>10</v>
@@ -7318,7 +7345,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>450020</v>
+        <v>450010</v>
       </c>
       <c r="B161" s="1">
         <v>45</v>
@@ -7359,10 +7386,10 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>450010</v>
+        <v>460020</v>
       </c>
       <c r="B162" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>10</v>
@@ -7400,7 +7427,7 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>460020</v>
+        <v>460010</v>
       </c>
       <c r="B163" s="1">
         <v>46</v>
@@ -7441,10 +7468,10 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>460010</v>
+        <v>470020</v>
       </c>
       <c r="B164" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>10</v>
@@ -7482,7 +7509,7 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>470020</v>
+        <v>470010</v>
       </c>
       <c r="B165" s="1">
         <v>47</v>
@@ -7523,10 +7550,10 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>470010</v>
+        <v>480020</v>
       </c>
       <c r="B166" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>10</v>
@@ -7564,7 +7591,7 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>480020</v>
+        <v>480010</v>
       </c>
       <c r="B167" s="1">
         <v>48</v>
@@ -7605,10 +7632,10 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>480010</v>
+        <v>490020</v>
       </c>
       <c r="B168" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>10</v>
@@ -7646,7 +7673,7 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>490020</v>
+        <v>490010</v>
       </c>
       <c r="B169" s="1">
         <v>49</v>
@@ -7687,10 +7714,10 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>490010</v>
+        <v>500020</v>
       </c>
       <c r="B170" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>10</v>
@@ -7728,7 +7755,7 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>500020</v>
+        <v>500010</v>
       </c>
       <c r="B171" s="1">
         <v>50</v>
@@ -7769,10 +7796,10 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>500010</v>
+        <v>510020</v>
       </c>
       <c r="B172" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>10</v>
@@ -7810,7 +7837,7 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>510020</v>
+        <v>510010</v>
       </c>
       <c r="B173" s="1">
         <v>51</v>
@@ -7851,10 +7878,10 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>510010</v>
+        <v>520020</v>
       </c>
       <c r="B174" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>10</v>
@@ -7892,7 +7919,7 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>520020</v>
+        <v>520010</v>
       </c>
       <c r="B175" s="1">
         <v>52</v>
@@ -7933,10 +7960,10 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>520010</v>
+        <v>530020</v>
       </c>
       <c r="B176" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>10</v>
@@ -7974,7 +8001,7 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>530020</v>
+        <v>530010</v>
       </c>
       <c r="B177" s="1">
         <v>53</v>
@@ -8015,10 +8042,10 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>530010</v>
+        <v>540020</v>
       </c>
       <c r="B178" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>10</v>
@@ -8056,7 +8083,7 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>540020</v>
+        <v>540010</v>
       </c>
       <c r="B179" s="1">
         <v>54</v>
@@ -8097,10 +8124,10 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>540010</v>
+        <v>550020</v>
       </c>
       <c r="B180" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>10</v>
@@ -8138,7 +8165,7 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>550020</v>
+        <v>550010</v>
       </c>
       <c r="B181" s="1">
         <v>55</v>
@@ -8179,10 +8206,10 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>550010</v>
+        <v>560020</v>
       </c>
       <c r="B182" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>10</v>
@@ -8220,7 +8247,7 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>560020</v>
+        <v>560010</v>
       </c>
       <c r="B183" s="1">
         <v>56</v>
@@ -8261,10 +8288,10 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>560010</v>
+        <v>570020</v>
       </c>
       <c r="B184" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>10</v>
@@ -8302,7 +8329,7 @@
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>570020</v>
+        <v>570010</v>
       </c>
       <c r="B185" s="1">
         <v>57</v>
@@ -8343,10 +8370,10 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>570010</v>
+        <v>580020</v>
       </c>
       <c r="B186" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>10</v>
@@ -8384,7 +8411,7 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>580020</v>
+        <v>580010</v>
       </c>
       <c r="B187" s="1">
         <v>58</v>
@@ -8425,10 +8452,10 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>580010</v>
+        <v>590020</v>
       </c>
       <c r="B188" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>10</v>
@@ -8466,7 +8493,7 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>590020</v>
+        <v>590010</v>
       </c>
       <c r="B189" s="1">
         <v>59</v>
@@ -8507,10 +8534,10 @@
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>590010</v>
+        <v>600020</v>
       </c>
       <c r="B190" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>10</v>
@@ -8548,7 +8575,7 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>600020</v>
+        <v>600010</v>
       </c>
       <c r="B191" s="1">
         <v>60</v>
@@ -8589,10 +8616,10 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>600010</v>
+        <v>610020</v>
       </c>
       <c r="B192" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>10</v>
@@ -8630,7 +8657,7 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>610020</v>
+        <v>610010</v>
       </c>
       <c r="B193" s="1">
         <v>61</v>
@@ -8671,10 +8698,10 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>610010</v>
+        <v>620020</v>
       </c>
       <c r="B194" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>10</v>
@@ -8712,7 +8739,7 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>620020</v>
+        <v>620010</v>
       </c>
       <c r="B195" s="1">
         <v>62</v>
@@ -8753,10 +8780,10 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>620010</v>
+        <v>630020</v>
       </c>
       <c r="B196" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>10</v>
@@ -8794,7 +8821,7 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>630020</v>
+        <v>630010</v>
       </c>
       <c r="B197" s="1">
         <v>63</v>
@@ -8835,10 +8862,10 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>630010</v>
+        <v>640020</v>
       </c>
       <c r="B198" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>10</v>
@@ -8876,7 +8903,7 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>640020</v>
+        <v>640010</v>
       </c>
       <c r="B199" s="1">
         <v>64</v>
@@ -8917,10 +8944,10 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>640010</v>
+        <v>650020</v>
       </c>
       <c r="B200" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>10</v>
@@ -8958,7 +8985,7 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>650020</v>
+        <v>650010</v>
       </c>
       <c r="B201" s="1">
         <v>65</v>
@@ -8999,10 +9026,10 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>650010</v>
+        <v>660020</v>
       </c>
       <c r="B202" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>10</v>
@@ -9040,7 +9067,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>660020</v>
+        <v>660010</v>
       </c>
       <c r="B203" s="1">
         <v>66</v>
@@ -9081,10 +9108,10 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>660010</v>
+        <v>670020</v>
       </c>
       <c r="B204" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>10</v>
@@ -9122,7 +9149,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>670020</v>
+        <v>670010</v>
       </c>
       <c r="B205" s="1">
         <v>67</v>
@@ -9163,10 +9190,10 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>670010</v>
+        <v>680020</v>
       </c>
       <c r="B206" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>10</v>
@@ -9204,7 +9231,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>680020</v>
+        <v>680010</v>
       </c>
       <c r="B207" s="1">
         <v>68</v>
@@ -9245,10 +9272,10 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>680010</v>
+        <v>690020</v>
       </c>
       <c r="B208" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>10</v>
@@ -9286,7 +9313,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>690020</v>
+        <v>690010</v>
       </c>
       <c r="B209" s="1">
         <v>69</v>
@@ -9327,10 +9354,10 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>690010</v>
+        <v>700020</v>
       </c>
       <c r="B210" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>10</v>
@@ -9368,7 +9395,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>700020</v>
+        <v>700010</v>
       </c>
       <c r="B211" s="1">
         <v>70</v>
@@ -9409,10 +9436,10 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>700010</v>
+        <v>710020</v>
       </c>
       <c r="B212" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>10</v>
@@ -9450,7 +9477,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>710020</v>
+        <v>710010</v>
       </c>
       <c r="B213" s="1">
         <v>71</v>
@@ -9491,10 +9518,10 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>710010</v>
+        <v>720020</v>
       </c>
       <c r="B214" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>10</v>
@@ -9532,7 +9559,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>720020</v>
+        <v>720010</v>
       </c>
       <c r="B215" s="1">
         <v>72</v>
@@ -9573,10 +9600,10 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>720010</v>
+        <v>730020</v>
       </c>
       <c r="B216" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>10</v>
@@ -9614,7 +9641,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>730020</v>
+        <v>730010</v>
       </c>
       <c r="B217" s="1">
         <v>73</v>
@@ -9655,10 +9682,10 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>730010</v>
+        <v>740020</v>
       </c>
       <c r="B218" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>10</v>
@@ -9696,7 +9723,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>740020</v>
+        <v>740010</v>
       </c>
       <c r="B219" s="1">
         <v>74</v>
@@ -9737,10 +9764,10 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>740010</v>
+        <v>750020</v>
       </c>
       <c r="B220" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>10</v>
@@ -9778,7 +9805,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>750020</v>
+        <v>750010</v>
       </c>
       <c r="B221" s="1">
         <v>75</v>
@@ -9819,10 +9846,10 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>750010</v>
+        <v>760020</v>
       </c>
       <c r="B222" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>10</v>
@@ -9860,7 +9887,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>760020</v>
+        <v>760010</v>
       </c>
       <c r="B223" s="1">
         <v>76</v>
@@ -9901,10 +9928,10 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>760010</v>
+        <v>770020</v>
       </c>
       <c r="B224" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>10</v>
@@ -9942,7 +9969,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>770020</v>
+        <v>770010</v>
       </c>
       <c r="B225" s="1">
         <v>77</v>
@@ -9983,10 +10010,10 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>770010</v>
+        <v>780020</v>
       </c>
       <c r="B226" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>10</v>
@@ -10024,7 +10051,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>780020</v>
+        <v>780010</v>
       </c>
       <c r="B227" s="1">
         <v>78</v>
@@ -10065,10 +10092,10 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>780010</v>
+        <v>790020</v>
       </c>
       <c r="B228" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>10</v>
@@ -10106,7 +10133,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>790020</v>
+        <v>790010</v>
       </c>
       <c r="B229" s="1">
         <v>79</v>
@@ -10147,10 +10174,10 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>790010</v>
+        <v>800020</v>
       </c>
       <c r="B230" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>10</v>
@@ -10188,7 +10215,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>800020</v>
+        <v>800010</v>
       </c>
       <c r="B231" s="1">
         <v>80</v>
@@ -10229,10 +10256,10 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>800010</v>
+        <v>810020</v>
       </c>
       <c r="B232" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>10</v>
@@ -10270,7 +10297,7 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>810020</v>
+        <v>810010</v>
       </c>
       <c r="B233" s="1">
         <v>81</v>
@@ -10311,10 +10338,10 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>810010</v>
+        <v>820020</v>
       </c>
       <c r="B234" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>10</v>
@@ -10352,7 +10379,7 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>820020</v>
+        <v>820010</v>
       </c>
       <c r="B235" s="1">
         <v>82</v>
@@ -10393,10 +10420,10 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>820010</v>
+        <v>830020</v>
       </c>
       <c r="B236" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>10</v>
@@ -10434,7 +10461,7 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>830020</v>
+        <v>830010</v>
       </c>
       <c r="B237" s="1">
         <v>83</v>
@@ -10475,10 +10502,10 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>830010</v>
+        <v>840020</v>
       </c>
       <c r="B238" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>10</v>
@@ -10516,7 +10543,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>840020</v>
+        <v>840010</v>
       </c>
       <c r="B239" s="1">
         <v>84</v>
@@ -10557,10 +10584,10 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>840010</v>
+        <v>850020</v>
       </c>
       <c r="B240" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>10</v>
@@ -10598,7 +10625,7 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>850020</v>
+        <v>850010</v>
       </c>
       <c r="B241" s="1">
         <v>85</v>
@@ -10639,10 +10666,10 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>850010</v>
+        <v>860020</v>
       </c>
       <c r="B242" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>10</v>
@@ -10680,7 +10707,7 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>860020</v>
+        <v>860010</v>
       </c>
       <c r="B243" s="1">
         <v>86</v>
@@ -10721,10 +10748,10 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>860010</v>
+        <v>870020</v>
       </c>
       <c r="B244" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>10</v>
@@ -10762,7 +10789,7 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>870020</v>
+        <v>870010</v>
       </c>
       <c r="B245" s="1">
         <v>87</v>
@@ -10803,10 +10830,10 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>870010</v>
+        <v>880020</v>
       </c>
       <c r="B246" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>10</v>
@@ -10844,7 +10871,7 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>880020</v>
+        <v>880010</v>
       </c>
       <c r="B247" s="1">
         <v>88</v>
@@ -10885,10 +10912,10 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>880010</v>
+        <v>890020</v>
       </c>
       <c r="B248" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>10</v>
@@ -10926,7 +10953,7 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>890020</v>
+        <v>890010</v>
       </c>
       <c r="B249" s="1">
         <v>89</v>
@@ -10967,10 +10994,10 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>890010</v>
+        <v>900020</v>
       </c>
       <c r="B250" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>10</v>
@@ -11008,7 +11035,7 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>900020</v>
+        <v>900010</v>
       </c>
       <c r="B251" s="1">
         <v>90</v>
@@ -11049,10 +11076,10 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>900010</v>
+        <v>910020</v>
       </c>
       <c r="B252" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>10</v>
@@ -11090,7 +11117,7 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>910020</v>
+        <v>910010</v>
       </c>
       <c r="B253" s="1">
         <v>91</v>
@@ -11131,10 +11158,10 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>910010</v>
+        <v>920020</v>
       </c>
       <c r="B254" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>10</v>
@@ -11172,7 +11199,7 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>920020</v>
+        <v>920010</v>
       </c>
       <c r="B255" s="1">
         <v>92</v>
@@ -11213,10 +11240,10 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>920010</v>
+        <v>930020</v>
       </c>
       <c r="B256" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>10</v>
@@ -11254,7 +11281,7 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>930020</v>
+        <v>930010</v>
       </c>
       <c r="B257" s="1">
         <v>93</v>
@@ -11295,10 +11322,10 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>930010</v>
+        <v>940020</v>
       </c>
       <c r="B258" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>10</v>
@@ -11336,7 +11363,7 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>940020</v>
+        <v>940010</v>
       </c>
       <c r="B259" s="1">
         <v>94</v>
@@ -11377,10 +11404,10 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>940010</v>
+        <v>950020</v>
       </c>
       <c r="B260" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>10</v>
@@ -11418,7 +11445,7 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>950020</v>
+        <v>950010</v>
       </c>
       <c r="B261" s="1">
         <v>95</v>
@@ -11459,10 +11486,10 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>950010</v>
+        <v>960020</v>
       </c>
       <c r="B262" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>10</v>
@@ -11500,7 +11527,7 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>960020</v>
+        <v>960010</v>
       </c>
       <c r="B263" s="1">
         <v>96</v>
@@ -11541,10 +11568,10 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>960010</v>
+        <v>970020</v>
       </c>
       <c r="B264" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>10</v>
@@ -11582,7 +11609,7 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>970020</v>
+        <v>970010</v>
       </c>
       <c r="B265" s="1">
         <v>97</v>
@@ -11623,10 +11650,10 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>970010</v>
+        <v>980020</v>
       </c>
       <c r="B266" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>10</v>
@@ -11664,7 +11691,7 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>980020</v>
+        <v>980010</v>
       </c>
       <c r="B267" s="1">
         <v>98</v>
@@ -11705,10 +11732,10 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>980010</v>
+        <v>990020</v>
       </c>
       <c r="B268" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>10</v>
@@ -11746,7 +11773,7 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>990020</v>
+        <v>990010</v>
       </c>
       <c r="B269" s="1">
         <v>99</v>
@@ -11787,10 +11814,10 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>990010</v>
+        <v>1000020</v>
       </c>
       <c r="B270" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>10</v>
@@ -11828,7 +11855,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1000020</v>
+        <v>1000010</v>
       </c>
       <c r="B271" s="1">
         <v>100</v>
@@ -11869,10 +11896,10 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1000010</v>
+        <v>1010020</v>
       </c>
       <c r="B272" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>10</v>
@@ -11910,7 +11937,7 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1010020</v>
+        <v>1010010</v>
       </c>
       <c r="B273" s="1">
         <v>101</v>
@@ -11951,10 +11978,10 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1010010</v>
+        <v>1020020</v>
       </c>
       <c r="B274" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>10</v>
@@ -11992,7 +12019,7 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1020020</v>
+        <v>1020010</v>
       </c>
       <c r="B275" s="1">
         <v>102</v>
@@ -12033,10 +12060,10 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1020010</v>
+        <v>1030020</v>
       </c>
       <c r="B276" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>10</v>
@@ -12074,7 +12101,7 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1030020</v>
+        <v>1030010</v>
       </c>
       <c r="B277" s="1">
         <v>103</v>
@@ -12115,10 +12142,10 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1030010</v>
+        <v>1040020</v>
       </c>
       <c r="B278" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>10</v>
@@ -12156,7 +12183,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1040020</v>
+        <v>1040010</v>
       </c>
       <c r="B279" s="1">
         <v>104</v>
@@ -12197,10 +12224,10 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1040010</v>
+        <v>1050020</v>
       </c>
       <c r="B280" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>10</v>
@@ -12238,7 +12265,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1050020</v>
+        <v>1050010</v>
       </c>
       <c r="B281" s="1">
         <v>105</v>
@@ -12279,10 +12306,10 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1050010</v>
+        <v>1060020</v>
       </c>
       <c r="B282" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>10</v>
@@ -12320,7 +12347,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1060020</v>
+        <v>1060010</v>
       </c>
       <c r="B283" s="1">
         <v>106</v>
@@ -12361,10 +12388,10 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1060010</v>
+        <v>1070020</v>
       </c>
       <c r="B284" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>10</v>
@@ -12402,7 +12429,7 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1070020</v>
+        <v>1070010</v>
       </c>
       <c r="B285" s="1">
         <v>107</v>
@@ -12443,10 +12470,10 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1070010</v>
+        <v>1080020</v>
       </c>
       <c r="B286" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>10</v>
@@ -12484,7 +12511,7 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1080020</v>
+        <v>1080010</v>
       </c>
       <c r="B287" s="1">
         <v>108</v>
@@ -12525,10 +12552,10 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1080010</v>
+        <v>1090020</v>
       </c>
       <c r="B288" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>10</v>
@@ -12566,7 +12593,7 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1090020</v>
+        <v>1090010</v>
       </c>
       <c r="B289" s="1">
         <v>109</v>
@@ -12607,10 +12634,10 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1090010</v>
+        <v>1100020</v>
       </c>
       <c r="B290" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>10</v>
@@ -12648,7 +12675,7 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1100020</v>
+        <v>1100010</v>
       </c>
       <c r="B291" s="1">
         <v>110</v>
@@ -12689,10 +12716,10 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1100010</v>
+        <v>1110020</v>
       </c>
       <c r="B292" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>10</v>
@@ -12730,7 +12757,7 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1110020</v>
+        <v>1110010</v>
       </c>
       <c r="B293" s="1">
         <v>111</v>
@@ -12771,10 +12798,10 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1110010</v>
+        <v>1120020</v>
       </c>
       <c r="B294" s="1">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>10</v>
@@ -12812,7 +12839,7 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1120020</v>
+        <v>1120010</v>
       </c>
       <c r="B295" s="1">
         <v>112</v>
@@ -12853,10 +12880,10 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1120010</v>
+        <v>1130020</v>
       </c>
       <c r="B296" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>10</v>
@@ -12894,7 +12921,7 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1130020</v>
+        <v>1130010</v>
       </c>
       <c r="B297" s="1">
         <v>113</v>
@@ -12935,10 +12962,10 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1130010</v>
+        <v>1140020</v>
       </c>
       <c r="B298" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>10</v>
@@ -12976,7 +13003,7 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1140020</v>
+        <v>1140010</v>
       </c>
       <c r="B299" s="1">
         <v>114</v>
@@ -13017,10 +13044,10 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1140010</v>
+        <v>1150020</v>
       </c>
       <c r="B300" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>10</v>
@@ -13058,7 +13085,7 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1150020</v>
+        <v>1150010</v>
       </c>
       <c r="B301" s="1">
         <v>115</v>
@@ -13099,10 +13126,10 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1150010</v>
+        <v>1160020</v>
       </c>
       <c r="B302" s="1">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>10</v>
@@ -13140,7 +13167,7 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1160020</v>
+        <v>1160010</v>
       </c>
       <c r="B303" s="1">
         <v>116</v>
@@ -13181,10 +13208,10 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1160010</v>
+        <v>1170020</v>
       </c>
       <c r="B304" s="1">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>10</v>
@@ -13222,7 +13249,7 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1170020</v>
+        <v>1170010</v>
       </c>
       <c r="B305" s="1">
         <v>117</v>
@@ -13263,10 +13290,10 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1170010</v>
+        <v>1180020</v>
       </c>
       <c r="B306" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>10</v>
@@ -13304,7 +13331,7 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1180020</v>
+        <v>1180010</v>
       </c>
       <c r="B307" s="1">
         <v>118</v>
@@ -13345,10 +13372,10 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1180010</v>
+        <v>1190020</v>
       </c>
       <c r="B308" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>10</v>
@@ -13386,7 +13413,7 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1190020</v>
+        <v>1190010</v>
       </c>
       <c r="B309" s="1">
         <v>119</v>
@@ -13427,10 +13454,10 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1190010</v>
+        <v>1200020</v>
       </c>
       <c r="B310" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>10</v>
@@ -13468,7 +13495,7 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1200020</v>
+        <v>1200010</v>
       </c>
       <c r="B311" s="1">
         <v>120</v>
@@ -13509,10 +13536,10 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1200010</v>
+        <v>1210020</v>
       </c>
       <c r="B312" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>10</v>
@@ -13550,7 +13577,7 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1210020</v>
+        <v>1210010</v>
       </c>
       <c r="B313" s="1">
         <v>121</v>
@@ -13591,10 +13618,10 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1210010</v>
+        <v>1220020</v>
       </c>
       <c r="B314" s="1">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>10</v>
@@ -13632,7 +13659,7 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1220020</v>
+        <v>1220010</v>
       </c>
       <c r="B315" s="1">
         <v>122</v>
@@ -13673,10 +13700,10 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1220010</v>
+        <v>1230020</v>
       </c>
       <c r="B316" s="1">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>10</v>
@@ -13714,7 +13741,7 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1230020</v>
+        <v>1230010</v>
       </c>
       <c r="B317" s="1">
         <v>123</v>
@@ -13755,10 +13782,10 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1230010</v>
+        <v>1240020</v>
       </c>
       <c r="B318" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>10</v>
@@ -13796,7 +13823,7 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1240020</v>
+        <v>1240010</v>
       </c>
       <c r="B319" s="1">
         <v>124</v>
@@ -13837,10 +13864,10 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1240010</v>
+        <v>1250020</v>
       </c>
       <c r="B320" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>10</v>
@@ -13878,7 +13905,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1250020</v>
+        <v>1250010</v>
       </c>
       <c r="B321" s="1">
         <v>125</v>
@@ -13919,10 +13946,10 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1250010</v>
+        <v>1260020</v>
       </c>
       <c r="B322" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>10</v>
@@ -13960,7 +13987,7 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1260020</v>
+        <v>1260010</v>
       </c>
       <c r="B323" s="1">
         <v>126</v>
@@ -14001,10 +14028,10 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1260010</v>
+        <v>1270020</v>
       </c>
       <c r="B324" s="1">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>10</v>
@@ -14042,7 +14069,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1270020</v>
+        <v>1270010</v>
       </c>
       <c r="B325" s="1">
         <v>127</v>
@@ -14083,10 +14110,10 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1270010</v>
+        <v>1280020</v>
       </c>
       <c r="B326" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>10</v>
@@ -14124,7 +14151,7 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1280020</v>
+        <v>1280010</v>
       </c>
       <c r="B327" s="1">
         <v>128</v>
@@ -14165,10 +14192,10 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1280010</v>
+        <v>1290020</v>
       </c>
       <c r="B328" s="1">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>10</v>
@@ -14206,7 +14233,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1290020</v>
+        <v>1290010</v>
       </c>
       <c r="B329" s="1">
         <v>129</v>
@@ -14247,10 +14274,10 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1290010</v>
+        <v>1300020</v>
       </c>
       <c r="B330" s="1">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>10</v>
@@ -14288,7 +14315,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1300020</v>
+        <v>1300010</v>
       </c>
       <c r="B331" s="1">
         <v>130</v>
@@ -14329,10 +14356,10 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1300010</v>
+        <v>1310020</v>
       </c>
       <c r="B332" s="1">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>10</v>
@@ -14370,7 +14397,7 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1310020</v>
+        <v>1310010</v>
       </c>
       <c r="B333" s="1">
         <v>131</v>
@@ -14411,10 +14438,10 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1310010</v>
+        <v>1320020</v>
       </c>
       <c r="B334" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>10</v>
@@ -14452,7 +14479,7 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1320020</v>
+        <v>1320010</v>
       </c>
       <c r="B335" s="1">
         <v>132</v>
@@ -14493,10 +14520,10 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1320010</v>
+        <v>1330020</v>
       </c>
       <c r="B336" s="1">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>10</v>
@@ -14534,7 +14561,7 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1330020</v>
+        <v>1330010</v>
       </c>
       <c r="B337" s="1">
         <v>133</v>
@@ -14575,10 +14602,10 @@
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1330010</v>
+        <v>1340020</v>
       </c>
       <c r="B338" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>10</v>
@@ -14616,7 +14643,7 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1340020</v>
+        <v>1340010</v>
       </c>
       <c r="B339" s="1">
         <v>134</v>
@@ -14657,10 +14684,10 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>1340010</v>
+        <v>1350020</v>
       </c>
       <c r="B340" s="1">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>10</v>
@@ -14698,7 +14725,7 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>1350020</v>
+        <v>1350010</v>
       </c>
       <c r="B341" s="1">
         <v>135</v>
@@ -14739,10 +14766,10 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>1350010</v>
+        <v>1360020</v>
       </c>
       <c r="B342" s="1">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>10</v>
@@ -14780,7 +14807,7 @@
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>1360020</v>
+        <v>1360010</v>
       </c>
       <c r="B343" s="1">
         <v>136</v>
@@ -14821,10 +14848,10 @@
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>1360010</v>
+        <v>1370020</v>
       </c>
       <c r="B344" s="1">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>10</v>
@@ -14862,7 +14889,7 @@
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>1370020</v>
+        <v>1370010</v>
       </c>
       <c r="B345" s="1">
         <v>137</v>
@@ -14903,10 +14930,10 @@
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>1370010</v>
+        <v>1380020</v>
       </c>
       <c r="B346" s="1">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>10</v>
@@ -14944,7 +14971,7 @@
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>1380020</v>
+        <v>1380010</v>
       </c>
       <c r="B347" s="1">
         <v>138</v>
@@ -14985,10 +15012,10 @@
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>1380010</v>
+        <v>1390020</v>
       </c>
       <c r="B348" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>10</v>
@@ -15026,7 +15053,7 @@
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>1390020</v>
+        <v>1390010</v>
       </c>
       <c r="B349" s="1">
         <v>139</v>
@@ -15067,10 +15094,10 @@
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>1390010</v>
+        <v>1400020</v>
       </c>
       <c r="B350" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>10</v>
@@ -15108,7 +15135,7 @@
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>1400020</v>
+        <v>1400010</v>
       </c>
       <c r="B351" s="1">
         <v>140</v>
@@ -15149,10 +15176,10 @@
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>1400010</v>
+        <v>1410020</v>
       </c>
       <c r="B352" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>10</v>
@@ -15190,7 +15217,7 @@
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>1410020</v>
+        <v>1410010</v>
       </c>
       <c r="B353" s="1">
         <v>141</v>
@@ -15231,10 +15258,10 @@
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>1410010</v>
+        <v>1420020</v>
       </c>
       <c r="B354" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>10</v>
@@ -15272,7 +15299,7 @@
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>1420020</v>
+        <v>1420010</v>
       </c>
       <c r="B355" s="1">
         <v>142</v>
@@ -15313,10 +15340,10 @@
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>1420010</v>
+        <v>1430020</v>
       </c>
       <c r="B356" s="1">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>10</v>
@@ -15354,7 +15381,7 @@
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>1430020</v>
+        <v>1430010</v>
       </c>
       <c r="B357" s="1">
         <v>143</v>
@@ -15395,10 +15422,10 @@
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>1430010</v>
+        <v>1440020</v>
       </c>
       <c r="B358" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>10</v>
@@ -15436,7 +15463,7 @@
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>1440020</v>
+        <v>1440010</v>
       </c>
       <c r="B359" s="1">
         <v>144</v>
@@ -15477,10 +15504,10 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>1440010</v>
+        <v>1450020</v>
       </c>
       <c r="B360" s="1">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>10</v>
@@ -15518,7 +15545,7 @@
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>1450020</v>
+        <v>1450010</v>
       </c>
       <c r="B361" s="1">
         <v>145</v>
@@ -15559,10 +15586,10 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>1450010</v>
+        <v>1460020</v>
       </c>
       <c r="B362" s="1">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>10</v>
@@ -15600,7 +15627,7 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>1460020</v>
+        <v>1460010</v>
       </c>
       <c r="B363" s="1">
         <v>146</v>
@@ -15641,10 +15668,10 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>1460010</v>
+        <v>1470020</v>
       </c>
       <c r="B364" s="1">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>10</v>
@@ -15682,7 +15709,7 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>1470020</v>
+        <v>1470010</v>
       </c>
       <c r="B365" s="1">
         <v>147</v>
@@ -15723,10 +15750,10 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>1470010</v>
+        <v>1480020</v>
       </c>
       <c r="B366" s="1">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>10</v>
@@ -15764,7 +15791,7 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>1480020</v>
+        <v>1480010</v>
       </c>
       <c r="B367" s="1">
         <v>148</v>
@@ -15805,10 +15832,10 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>1480010</v>
+        <v>1490020</v>
       </c>
       <c r="B368" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>10</v>
@@ -15846,7 +15873,7 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>1490020</v>
+        <v>1490010</v>
       </c>
       <c r="B369" s="1">
         <v>149</v>
@@ -15887,10 +15914,10 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>1490010</v>
+        <v>1500020</v>
       </c>
       <c r="B370" s="1">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>10</v>
@@ -15928,7 +15955,7 @@
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>1500020</v>
+        <v>1500010</v>
       </c>
       <c r="B371" s="1">
         <v>150</v>
@@ -15969,10 +15996,10 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>1500010</v>
+        <v>1510020</v>
       </c>
       <c r="B372" s="1">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>10</v>
@@ -16010,7 +16037,7 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>1510020</v>
+        <v>1510010</v>
       </c>
       <c r="B373" s="1">
         <v>151</v>
@@ -16051,10 +16078,10 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>1510010</v>
+        <v>1520020</v>
       </c>
       <c r="B374" s="1">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>10</v>
@@ -16092,7 +16119,7 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>1520020</v>
+        <v>1520010</v>
       </c>
       <c r="B375" s="1">
         <v>152</v>
@@ -16133,10 +16160,10 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>1520010</v>
+        <v>1530020</v>
       </c>
       <c r="B376" s="1">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>10</v>
@@ -16174,7 +16201,7 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>1530020</v>
+        <v>1530010</v>
       </c>
       <c r="B377" s="1">
         <v>153</v>
@@ -16215,10 +16242,10 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>1530010</v>
+        <v>1540020</v>
       </c>
       <c r="B378" s="1">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>10</v>
@@ -16256,7 +16283,7 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>1540020</v>
+        <v>1540010</v>
       </c>
       <c r="B379" s="1">
         <v>154</v>
@@ -16297,10 +16324,10 @@
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>1540010</v>
+        <v>1550020</v>
       </c>
       <c r="B380" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>10</v>
@@ -16338,7 +16365,7 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>1550020</v>
+        <v>1550010</v>
       </c>
       <c r="B381" s="1">
         <v>155</v>
@@ -16379,10 +16406,10 @@
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>1550010</v>
+        <v>1560020</v>
       </c>
       <c r="B382" s="1">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>10</v>
@@ -16420,7 +16447,7 @@
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>1560020</v>
+        <v>1560010</v>
       </c>
       <c r="B383" s="1">
         <v>156</v>
@@ -16461,10 +16488,10 @@
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>1560010</v>
+        <v>1570020</v>
       </c>
       <c r="B384" s="1">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D384" s="2" t="s">
         <v>10</v>
@@ -16502,7 +16529,7 @@
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>1570020</v>
+        <v>1570010</v>
       </c>
       <c r="B385" s="1">
         <v>157</v>
@@ -16543,10 +16570,10 @@
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>1570010</v>
+        <v>1580020</v>
       </c>
       <c r="B386" s="1">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>10</v>
@@ -16584,7 +16611,7 @@
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>1580020</v>
+        <v>1580010</v>
       </c>
       <c r="B387" s="1">
         <v>158</v>
@@ -16625,10 +16652,10 @@
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>1580010</v>
+        <v>1590020</v>
       </c>
       <c r="B388" s="1">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>10</v>
@@ -16666,7 +16693,7 @@
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>1590020</v>
+        <v>1590010</v>
       </c>
       <c r="B389" s="1">
         <v>159</v>
@@ -16707,10 +16734,10 @@
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>1590010</v>
+        <v>1600020</v>
       </c>
       <c r="B390" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D390" s="2" t="s">
         <v>10</v>
@@ -16748,7 +16775,7 @@
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>1600020</v>
+        <v>1600010</v>
       </c>
       <c r="B391" s="1">
         <v>160</v>
@@ -16784,47 +16811,6 @@
         <v>0</v>
       </c>
       <c r="N391" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A392" s="1">
-        <v>1600010</v>
-      </c>
-      <c r="B392" s="1">
-        <v>160</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E392" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F392" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G392" s="1">
-        <v>0</v>
-      </c>
-      <c r="H392" s="2">
-        <v>0</v>
-      </c>
-      <c r="I392" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J392" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K392" s="7">
-        <v>0</v>
-      </c>
-      <c r="L392" s="7">
-        <v>0</v>
-      </c>
-      <c r="M392" s="7">
-        <v>0</v>
-      </c>
-      <c r="N392" s="7">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452206F3-D27D-4EE5-B223-9A933DA7F8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857DA0F9-C44D-45A0-BEEB-C80D523C254C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5691,16 +5691,16 @@
         <v>18</v>
       </c>
       <c r="K120" s="7">
+        <v>5</v>
+      </c>
+      <c r="L120" s="7">
         <v>2</v>
       </c>
-      <c r="L120" s="7">
-        <v>5</v>
-      </c>
       <c r="M120" s="7">
+        <v>1</v>
+      </c>
+      <c r="N120" s="7">
         <v>2</v>
-      </c>
-      <c r="N120" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.15">
@@ -5814,16 +5814,16 @@
         <v>18</v>
       </c>
       <c r="K123" s="7">
+        <v>5</v>
+      </c>
+      <c r="L123" s="7">
         <v>3</v>
       </c>
-      <c r="L123" s="7">
-        <v>5</v>
-      </c>
       <c r="M123" s="7">
+        <v>1</v>
+      </c>
+      <c r="N123" s="7">
         <v>2</v>
-      </c>
-      <c r="N123" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.15">
@@ -5855,16 +5855,16 @@
         <v>18</v>
       </c>
       <c r="K124" s="7">
+        <v>5</v>
+      </c>
+      <c r="L124" s="7">
         <v>2</v>
       </c>
-      <c r="L124" s="7">
-        <v>5</v>
-      </c>
       <c r="M124" s="7">
+        <v>1</v>
+      </c>
+      <c r="N124" s="7">
         <v>3</v>
-      </c>
-      <c r="N124" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.15">
@@ -5902,10 +5902,10 @@
         <v>5</v>
       </c>
       <c r="M125" s="7">
+        <v>1</v>
+      </c>
+      <c r="N125" s="7">
         <v>2</v>
-      </c>
-      <c r="N125" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.15">
@@ -5943,10 +5943,10 @@
         <v>4</v>
       </c>
       <c r="M126" s="7">
+        <v>1</v>
+      </c>
+      <c r="N126" s="7">
         <v>2</v>
-      </c>
-      <c r="N126" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.15">
@@ -5978,16 +5978,16 @@
         <v>18</v>
       </c>
       <c r="K127" s="7">
+        <v>5</v>
+      </c>
+      <c r="L127" s="7">
         <v>3</v>
       </c>
-      <c r="L127" s="7">
-        <v>5</v>
-      </c>
       <c r="M127" s="7">
+        <v>1</v>
+      </c>
+      <c r="N127" s="7">
         <v>3</v>
-      </c>
-      <c r="N127" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.15">
@@ -6025,10 +6025,10 @@
         <v>4</v>
       </c>
       <c r="M128" s="7">
+        <v>1</v>
+      </c>
+      <c r="N128" s="7">
         <v>3</v>
-      </c>
-      <c r="N128" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.15">
@@ -6060,16 +6060,16 @@
         <v>18</v>
       </c>
       <c r="K129" s="7">
+        <v>5</v>
+      </c>
+      <c r="L129" s="7">
         <v>2</v>
       </c>
-      <c r="L129" s="7">
-        <v>5</v>
-      </c>
       <c r="M129" s="7">
+        <v>1</v>
+      </c>
+      <c r="N129" s="7">
         <v>4</v>
-      </c>
-      <c r="N129" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.15">
@@ -6101,16 +6101,16 @@
         <v>18</v>
       </c>
       <c r="K130" s="7">
+        <v>5</v>
+      </c>
+      <c r="L130" s="7">
         <v>3</v>
       </c>
-      <c r="L130" s="7">
-        <v>5</v>
-      </c>
       <c r="M130" s="7">
+        <v>1</v>
+      </c>
+      <c r="N130" s="7">
         <v>4</v>
-      </c>
-      <c r="N130" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.15">
@@ -6148,10 +6148,10 @@
         <v>5</v>
       </c>
       <c r="M131" s="7">
+        <v>1</v>
+      </c>
+      <c r="N131" s="7">
         <v>3</v>
-      </c>
-      <c r="N131" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DFDA0E-3BDF-40F2-98DA-7FA43798DBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8DB87D-6C65-40B6-9AA8-45EFEACEE40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$M$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$M$398</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="102">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -381,6 +381,70 @@
   </si>
   <si>
     <t>42761001</t>
+  </si>
+  <si>
+    <t>测试宝箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第1关武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第3关强化石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第3关武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第2关铠甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第4关铠甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第4关强化石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第5关强化石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第5关金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第5关武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6关强化石1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6关金币1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6关武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6关金币2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6关强化石2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6关铠甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -770,11 +834,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M391"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="31.875" style="1" bestFit="1" customWidth="1"/>
@@ -917,30 +981,33 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>10020</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>15</v>
+    <row r="5" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>10001</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -955,30 +1022,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>10010</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>15</v>
+    <row r="6" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>10002</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -995,9 +1065,11 @@
     </row>
     <row r="7" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
-        <v>10001</v>
-      </c>
-      <c r="B7" s="6"/>
+        <v>10003</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
@@ -1034,9 +1106,11 @@
     </row>
     <row r="8" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
-        <v>10002</v>
-      </c>
-      <c r="B8" s="6"/>
+        <v>10004</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C8" s="5">
         <v>0</v>
       </c>
@@ -1073,9 +1147,11 @@
     </row>
     <row r="9" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
-        <v>10003</v>
-      </c>
-      <c r="B9" s="6"/>
+        <v>10005</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C9" s="5">
         <v>0</v>
       </c>
@@ -1112,9 +1188,11 @@
     </row>
     <row r="10" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
-        <v>10004</v>
-      </c>
-      <c r="B10" s="6"/>
+        <v>10006</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C10" s="5">
         <v>0</v>
       </c>
@@ -1151,9 +1229,11 @@
     </row>
     <row r="11" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
-        <v>10005</v>
-      </c>
-      <c r="B11" s="6"/>
+        <v>10007</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
@@ -1190,9 +1270,11 @@
     </row>
     <row r="12" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
-        <v>10006</v>
-      </c>
-      <c r="B12" s="6"/>
+        <v>10008</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C12" s="5">
         <v>0</v>
       </c>
@@ -1229,9 +1311,11 @@
     </row>
     <row r="13" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
-        <v>10007</v>
-      </c>
-      <c r="B13" s="6"/>
+        <v>10009</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
@@ -1266,31 +1350,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>10008</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>68</v>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
+        <v>10020</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
@@ -1305,31 +1388,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>10009</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="5">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>68</v>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="J15" s="7">
         <v>0</v>
@@ -1346,7 +1428,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <v>20020</v>
+        <v>10011</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -1355,13 +1440,13 @@
         <v>13</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -1370,21 +1455,21 @@
         <v>15</v>
       </c>
       <c r="J16" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>20010</v>
+        <v>20020</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -1393,7 +1478,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1422,7 +1507,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>30020</v>
+        <v>20010</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
@@ -1431,7 +1516,7 @@
         <v>13</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1460,7 +1545,10 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>30010</v>
+        <v>20001</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -1469,13 +1557,13 @@
         <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -1484,21 +1572,21 @@
         <v>15</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>40020</v>
+        <v>30020</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -1536,7 +1624,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>40010</v>
+        <v>30010</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -1545,7 +1633,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1574,7 +1662,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
-        <v>40002</v>
+        <v>30001</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -1583,13 +1674,13 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -1598,21 +1689,24 @@
         <v>15</v>
       </c>
       <c r="J22" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
-        <v>50020</v>
+        <v>30002</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
@@ -1621,13 +1715,13 @@
         <v>13</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -1636,21 +1730,21 @@
         <v>15</v>
       </c>
       <c r="J23" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K23" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
-        <v>50010</v>
+        <v>40020</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -1659,7 +1753,7 @@
         <v>13</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1688,7 +1782,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
-        <v>50002</v>
+        <v>40010</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -1697,7 +1791,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1726,7 +1820,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
-        <v>50003</v>
+        <v>40001</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1735,13 +1832,13 @@
         <v>13</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -1750,21 +1847,24 @@
         <v>15</v>
       </c>
       <c r="J26" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K26" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
-        <v>60020</v>
+        <v>40002</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -1773,13 +1873,13 @@
         <v>13</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -1788,21 +1888,21 @@
         <v>15</v>
       </c>
       <c r="J27" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K27" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
-        <v>60010</v>
+        <v>50020</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1811,7 +1911,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -1840,7 +1940,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
-        <v>60002</v>
+        <v>50010</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -1849,7 +1949,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1878,7 +1978,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
-        <v>60003</v>
+        <v>40001</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1887,13 +1990,13 @@
         <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -1902,21 +2005,24 @@
         <v>15</v>
       </c>
       <c r="J30" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
-        <v>60004</v>
+        <v>50002</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -1925,7 +2031,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -1954,7 +2060,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
-        <v>60005</v>
+        <v>50003</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1963,7 +2072,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -1992,7 +2101,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
-        <v>60006</v>
+        <v>60020</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -2001,7 +2110,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2030,7 +2139,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
-        <v>70020</v>
+        <v>60010</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -2039,7 +2148,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2068,7 +2177,10 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
-        <v>70010</v>
+        <v>60001</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -2077,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2106,7 +2218,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
-        <v>70002</v>
+        <v>60002</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -2115,19 +2230,19 @@
         <v>13</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2">
-        <v>42614001</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J36" s="7">
         <v>0</v>
@@ -2144,7 +2259,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>70003</v>
+        <v>60003</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -2153,10 +2271,10 @@
         <v>13</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
@@ -2165,7 +2283,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J37" s="7">
         <v>0</v>
@@ -2182,7 +2300,10 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>70004</v>
+        <v>60004</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -2191,10 +2312,10 @@
         <v>13</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F38" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -2203,7 +2324,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J38" s="7">
         <v>0</v>
@@ -2220,7 +2341,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>70005</v>
+        <v>60005</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -2229,10 +2353,10 @@
         <v>13</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
@@ -2241,7 +2365,7 @@
         <v>13</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J39" s="7">
         <v>0</v>
@@ -2258,7 +2382,10 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>70006</v>
+        <v>60006</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2267,13 +2394,13 @@
         <v>13</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
-        <v>42635001</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -2296,7 +2423,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>70007</v>
+        <v>70020</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -2305,10 +2432,10 @@
         <v>13</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
@@ -2317,7 +2444,7 @@
         <v>13</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J41" s="7">
         <v>0</v>
@@ -2334,7 +2461,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>70008</v>
+        <v>70010</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -2343,10 +2470,10 @@
         <v>13</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F42" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -2355,7 +2482,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J42" s="7">
         <v>0</v>
@@ -2372,7 +2499,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>80020</v>
+        <v>70002</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -2381,19 +2508,19 @@
         <v>13</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>0</v>
+        <v>42614001</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J43" s="7">
         <v>0</v>
@@ -2410,7 +2537,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>80010</v>
+        <v>70003</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -2419,10 +2546,10 @@
         <v>13</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
@@ -2431,7 +2558,7 @@
         <v>13</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J44" s="7">
         <v>0</v>
@@ -2448,7 +2575,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>90020</v>
+        <v>70004</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -2457,10 +2584,10 @@
         <v>13</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
@@ -2469,7 +2596,7 @@
         <v>13</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J45" s="7">
         <v>0</v>
@@ -2486,7 +2613,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>100020</v>
+        <v>70005</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -2495,10 +2622,10 @@
         <v>13</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F46" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G46" s="2">
         <v>0</v>
@@ -2507,7 +2634,7 @@
         <v>13</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="J46" s="7">
         <v>0</v>
@@ -2524,7 +2651,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>100010</v>
+        <v>70006</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -2533,13 +2660,13 @@
         <v>13</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G47" s="2">
-        <v>0</v>
+        <v>42635001</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -2562,7 +2689,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>110020</v>
+        <v>70007</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -2571,10 +2698,10 @@
         <v>13</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
@@ -2583,7 +2710,7 @@
         <v>13</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J48" s="7">
         <v>0</v>
@@ -2600,7 +2727,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>110010</v>
+        <v>70008</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -2609,10 +2736,10 @@
         <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
@@ -2621,7 +2748,7 @@
         <v>13</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J49" s="7">
         <v>0</v>
@@ -2638,7 +2765,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>110001</v>
+        <v>80020</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -2647,13 +2774,13 @@
         <v>13</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1">
-        <v>30</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -2662,21 +2789,21 @@
         <v>15</v>
       </c>
       <c r="J50" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K50" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>110002</v>
+        <v>80010</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -2685,10 +2812,10 @@
         <v>13</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
@@ -2697,24 +2824,24 @@
         <v>13</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="J51" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K51" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>110003</v>
+        <v>90020</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -2723,13 +2850,13 @@
         <v>13</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1">
-        <v>50</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -2738,21 +2865,21 @@
         <v>15</v>
       </c>
       <c r="J52" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K52" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>110004</v>
+        <v>100020</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -2761,10 +2888,10 @@
         <v>13</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2">
         <v>0</v>
@@ -2773,24 +2900,24 @@
         <v>13</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="J53" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>110005</v>
+        <v>100010</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -2799,10 +2926,10 @@
         <v>13</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2">
         <v>0</v>
@@ -2811,24 +2938,24 @@
         <v>13</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J54" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K54" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>110006</v>
+        <v>110020</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -2837,13 +2964,13 @@
         <v>13</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1">
-        <v>150</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>13</v>
@@ -2852,21 +2979,21 @@
         <v>15</v>
       </c>
       <c r="J55" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K55" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>110007</v>
+        <v>110010</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -2875,13 +3002,13 @@
         <v>13</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1">
-        <v>210</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>13</v>
@@ -2890,21 +3017,21 @@
         <v>15</v>
       </c>
       <c r="J56" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K56" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>110008</v>
+        <v>110001</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -2913,36 +3040,36 @@
         <v>13</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F57" s="1">
-        <v>250</v>
-      </c>
-      <c r="G57" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="J57" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K57" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>110009</v>
+        <v>110002</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -2951,10 +3078,10 @@
         <v>13</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F58" s="1">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
@@ -2963,24 +3090,24 @@
         <v>13</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J58" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K58" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="7">
+        <v>1</v>
+      </c>
+      <c r="M58" s="7">
         <v>2</v>
-      </c>
-      <c r="M58" s="7">
-        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>110011</v>
+        <v>110003</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -2992,33 +3119,33 @@
         <v>49</v>
       </c>
       <c r="F59" s="1">
-        <v>500</v>
-      </c>
-      <c r="G59" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J59" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K59" s="7">
+        <v>2</v>
+      </c>
+      <c r="L59" s="7">
+        <v>2</v>
+      </c>
+      <c r="M59" s="7">
         <v>3</v>
-      </c>
-      <c r="L59" s="7">
-        <v>3</v>
-      </c>
-      <c r="M59" s="7">
-        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>110012</v>
+        <v>110004</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -3027,36 +3154,36 @@
         <v>13</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F60" s="1">
-        <v>600</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="J60" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K60" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110013</v>
+        <v>110005</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -3068,7 +3195,7 @@
         <v>49</v>
       </c>
       <c r="F61" s="1">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
@@ -3080,21 +3207,21 @@
         <v>53</v>
       </c>
       <c r="J61" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K61" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M61" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>110014</v>
+        <v>110006</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -3103,13 +3230,13 @@
         <v>13</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F62" s="1">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>13</v>
@@ -3118,21 +3245,21 @@
         <v>15</v>
       </c>
       <c r="J62" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K62" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>110015</v>
+        <v>110007</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -3141,36 +3268,36 @@
         <v>13</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F63" s="1">
-        <v>1200</v>
-      </c>
-      <c r="G63" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="J63" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K63" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>110016</v>
+        <v>110008</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -3179,10 +3306,10 @@
         <v>13</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F64" s="1">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
@@ -3191,24 +3318,24 @@
         <v>13</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J64" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K64" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
-        <v>110017</v>
+        <v>110009</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -3217,10 +3344,10 @@
         <v>13</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F65" s="1">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
@@ -3229,24 +3356,24 @@
         <v>13</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J65" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K65" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>110018</v>
+        <v>110011</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -3255,10 +3382,10 @@
         <v>13</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F66" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
@@ -3267,24 +3394,24 @@
         <v>13</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J66" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K66" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M66" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>110019</v>
+        <v>110012</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -3293,13 +3420,13 @@
         <v>13</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F67" s="1">
-        <v>2500</v>
+        <v>600</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>13</v>
@@ -3322,7 +3449,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>110021</v>
+        <v>110013</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -3331,10 +3458,10 @@
         <v>13</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F68" s="1">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="G68" s="2">
         <v>0</v>
@@ -3343,7 +3470,7 @@
         <v>13</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J68" s="7">
         <v>0</v>
@@ -3360,7 +3487,7 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>110022</v>
+        <v>110014</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -3372,10 +3499,10 @@
         <v>53</v>
       </c>
       <c r="F69" s="1">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>13</v>
@@ -3398,7 +3525,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>110023</v>
+        <v>110015</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -3407,10 +3534,10 @@
         <v>13</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F70" s="1">
-        <v>8000</v>
+        <v>1200</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
@@ -3419,7 +3546,7 @@
         <v>13</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J70" s="7">
         <v>0</v>
@@ -3436,7 +3563,7 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>110024</v>
+        <v>110016</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -3445,10 +3572,10 @@
         <v>13</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F71" s="1">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
@@ -3457,7 +3584,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J71" s="7">
         <v>0</v>
@@ -3474,19 +3601,19 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>120020</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>8</v>
+        <v>110017</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F72" s="1">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
@@ -3495,7 +3622,7 @@
         <v>13</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="J72" s="7">
         <v>0</v>
@@ -3512,19 +3639,19 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>120010</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>8</v>
+        <v>110018</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F73" s="1">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
@@ -3533,7 +3660,7 @@
         <v>13</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J73" s="7">
         <v>0</v>
@@ -3550,22 +3677,22 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>130020</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>8</v>
+        <v>110019</v>
+      </c>
+      <c r="C74" s="2">
+        <v>0</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
-      </c>
-      <c r="G74" s="2">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>13</v>
@@ -3588,19 +3715,19 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>130010</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>8</v>
+        <v>110021</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
@@ -3609,7 +3736,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="J75" s="7">
         <v>0</v>
@@ -3626,7 +3753,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>130001</v>
+        <v>110022</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -3635,13 +3762,13 @@
         <v>13</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F76" s="1">
-        <v>30</v>
+        <v>6000</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>13</v>
@@ -3650,21 +3777,21 @@
         <v>15</v>
       </c>
       <c r="J76" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K76" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>130002</v>
+        <v>110023</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -3673,10 +3800,10 @@
         <v>13</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F77" s="1">
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
@@ -3685,24 +3812,24 @@
         <v>13</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="J77" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K77" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>130003</v>
+        <v>110024</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -3711,13 +3838,13 @@
         <v>13</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1">
-        <v>50</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="G78" s="2">
+        <v>0</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>13</v>
@@ -3726,33 +3853,33 @@
         <v>15</v>
       </c>
       <c r="J78" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K78" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>130004</v>
-      </c>
-      <c r="C79" s="2">
-        <v>0</v>
+        <v>120020</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
@@ -3761,36 +3888,36 @@
         <v>13</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="J79" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K79" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>130005</v>
-      </c>
-      <c r="C80" s="2">
-        <v>0</v>
+        <v>120010</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
@@ -3799,39 +3926,39 @@
         <v>13</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J80" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K80" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M80" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>130006</v>
-      </c>
-      <c r="C81" s="2">
-        <v>0</v>
+        <v>130020</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1">
-        <v>150</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="G81" s="2">
+        <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>13</v>
@@ -3840,36 +3967,36 @@
         <v>15</v>
       </c>
       <c r="J81" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K81" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>130007</v>
-      </c>
-      <c r="C82" s="2">
-        <v>0</v>
+        <v>130010</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F82" s="1">
-        <v>210</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="G82" s="2">
+        <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>13</v>
@@ -3878,21 +4005,21 @@
         <v>15</v>
       </c>
       <c r="J82" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K82" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>130008</v>
+        <v>130001</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -3901,36 +4028,36 @@
         <v>13</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F83" s="1">
-        <v>250</v>
-      </c>
-      <c r="G83" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="J83" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K83" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L83" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>130009</v>
+        <v>130002</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -3939,10 +4066,10 @@
         <v>13</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F84" s="1">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
@@ -3951,24 +4078,24 @@
         <v>13</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J84" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K84" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84" s="7">
+        <v>1</v>
+      </c>
+      <c r="M84" s="7">
         <v>2</v>
-      </c>
-      <c r="M84" s="7">
-        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>130011</v>
+        <v>130003</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -3980,45 +4107,45 @@
         <v>49</v>
       </c>
       <c r="F85" s="1">
-        <v>500</v>
-      </c>
-      <c r="G85" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J85" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K85" s="7">
+        <v>2</v>
+      </c>
+      <c r="L85" s="7">
+        <v>2</v>
+      </c>
+      <c r="M85" s="7">
         <v>3</v>
-      </c>
-      <c r="L85" s="7">
-        <v>3</v>
-      </c>
-      <c r="M85" s="7">
-        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>140020</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>8</v>
+        <v>130004</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F86" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
@@ -4027,36 +4154,36 @@
         <v>13</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="J86" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K86" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>140010</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>8</v>
+        <v>130005</v>
+      </c>
+      <c r="C87" s="2">
+        <v>0</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F87" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
@@ -4065,39 +4192,39 @@
         <v>13</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J87" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K87" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M87" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>150020</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>8</v>
+        <v>130006</v>
+      </c>
+      <c r="C88" s="2">
+        <v>0</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
-      </c>
-      <c r="G88" s="2">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>13</v>
@@ -4106,36 +4233,36 @@
         <v>15</v>
       </c>
       <c r="J88" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K88" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>150010</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>8</v>
+        <v>130007</v>
+      </c>
+      <c r="C89" s="2">
+        <v>0</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
-      </c>
-      <c r="G89" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>13</v>
@@ -4144,33 +4271,33 @@
         <v>15</v>
       </c>
       <c r="J89" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K89" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>160020</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>8</v>
+        <v>130008</v>
+      </c>
+      <c r="C90" s="2">
+        <v>0</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F90" s="1">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
@@ -4179,36 +4306,36 @@
         <v>13</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="J90" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K90" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>160010</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>8</v>
+        <v>130009</v>
+      </c>
+      <c r="C91" s="2">
+        <v>0</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F91" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
@@ -4217,36 +4344,36 @@
         <v>13</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J91" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K91" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L91" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>170020</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>8</v>
+        <v>130011</v>
+      </c>
+      <c r="C92" s="2">
+        <v>0</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F92" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
@@ -4255,24 +4382,24 @@
         <v>13</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="J92" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K92" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L92" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>170010</v>
+        <v>140020</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>8</v>
@@ -4310,7 +4437,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>180020</v>
+        <v>140010</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>8</v>
@@ -4348,7 +4475,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>180010</v>
+        <v>150020</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>8</v>
@@ -4386,7 +4513,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>190020</v>
+        <v>150010</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>8</v>
@@ -4424,7 +4551,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>190010</v>
+        <v>160020</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>8</v>
@@ -4462,7 +4589,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>200020</v>
+        <v>160010</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>8</v>
@@ -4500,7 +4627,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>200010</v>
+        <v>170020</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>8</v>
@@ -4538,7 +4665,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>210020</v>
+        <v>170010</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>8</v>
@@ -4576,7 +4703,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>210010</v>
+        <v>180020</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>8</v>
@@ -4614,7 +4741,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>220020</v>
+        <v>180010</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>8</v>
@@ -4652,7 +4779,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>220010</v>
+        <v>190020</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>8</v>
@@ -4690,7 +4817,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>230020</v>
+        <v>190010</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>8</v>
@@ -4728,7 +4855,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>230010</v>
+        <v>200020</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>8</v>
@@ -4766,7 +4893,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>240020</v>
+        <v>200010</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>8</v>
@@ -4804,7 +4931,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>240010</v>
+        <v>210020</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>8</v>
@@ -4842,7 +4969,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>250020</v>
+        <v>210010</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>8</v>
@@ -4880,7 +5007,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>250010</v>
+        <v>220020</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>8</v>
@@ -4918,7 +5045,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>260020</v>
+        <v>220010</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>8</v>
@@ -4956,7 +5083,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>260010</v>
+        <v>230020</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>8</v>
@@ -4994,7 +5121,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>270020</v>
+        <v>230010</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>8</v>
@@ -5032,7 +5159,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>270010</v>
+        <v>240020</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>8</v>
@@ -5070,7 +5197,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>280020</v>
+        <v>240010</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>8</v>
@@ -5108,7 +5235,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>280010</v>
+        <v>250020</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>8</v>
@@ -5146,7 +5273,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>290020</v>
+        <v>250010</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>8</v>
@@ -5184,7 +5311,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>290010</v>
+        <v>260020</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>8</v>
@@ -5222,7 +5349,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>300020</v>
+        <v>260010</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>8</v>
@@ -5260,7 +5387,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>300010</v>
+        <v>270020</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>8</v>
@@ -5298,22 +5425,22 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>300001</v>
-      </c>
-      <c r="C120" s="2">
-        <v>0</v>
+        <v>270010</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
       </c>
-      <c r="G120" s="2" t="s">
-        <v>77</v>
+      <c r="G120" s="2">
+        <v>0</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>13</v>
@@ -5322,30 +5449,30 @@
         <v>15</v>
       </c>
       <c r="J120" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K120" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>300002</v>
-      </c>
-      <c r="C121" s="2">
-        <v>0</v>
+        <v>280020</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
@@ -5357,33 +5484,33 @@
         <v>13</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J121" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K121" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L121" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>300003</v>
-      </c>
-      <c r="C122" s="2">
-        <v>0</v>
+        <v>280010</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -5395,39 +5522,39 @@
         <v>13</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="J122" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K122" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L122" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>300004</v>
-      </c>
-      <c r="C123" s="2">
-        <v>0</v>
+        <v>290020</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
       </c>
-      <c r="G123" s="2" t="s">
-        <v>56</v>
+      <c r="G123" s="2">
+        <v>0</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>13</v>
@@ -5436,36 +5563,36 @@
         <v>15</v>
       </c>
       <c r="J123" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K123" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L123" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>300005</v>
-      </c>
-      <c r="C124" s="2">
-        <v>0</v>
+        <v>290010</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
       </c>
-      <c r="G124" s="2" t="s">
-        <v>66</v>
+      <c r="G124" s="2">
+        <v>0</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>13</v>
@@ -5474,30 +5601,30 @@
         <v>15</v>
       </c>
       <c r="J124" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K124" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>300006</v>
-      </c>
-      <c r="C125" s="2">
-        <v>0</v>
+        <v>300020</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -5509,33 +5636,33 @@
         <v>13</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J125" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K125" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L125" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>300007</v>
-      </c>
-      <c r="C126" s="2">
-        <v>0</v>
+        <v>300010</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -5547,24 +5674,24 @@
         <v>13</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="J126" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K126" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L126" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>300008</v>
+        <v>300001</v>
       </c>
       <c r="C127" s="2">
         <v>0</v>
@@ -5573,13 +5700,13 @@
         <v>13</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>13</v>
@@ -5591,18 +5718,18 @@
         <v>5</v>
       </c>
       <c r="K127" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L127" s="7">
         <v>1</v>
       </c>
       <c r="M127" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>300009</v>
+        <v>300002</v>
       </c>
       <c r="C128" s="2">
         <v>0</v>
@@ -5611,7 +5738,7 @@
         <v>13</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -5623,24 +5750,24 @@
         <v>13</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="J128" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K128" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L128" s="7">
         <v>1</v>
       </c>
       <c r="M128" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>300011</v>
+        <v>300003</v>
       </c>
       <c r="C129" s="2">
         <v>0</v>
@@ -5649,36 +5776,36 @@
         <v>13</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
       </c>
-      <c r="G129" s="2" t="s">
-        <v>84</v>
+      <c r="G129" s="2">
+        <v>0</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="J129" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K129" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L129" s="7">
         <v>1</v>
       </c>
       <c r="M129" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>300012</v>
+        <v>300004</v>
       </c>
       <c r="C130" s="2">
         <v>0</v>
@@ -5687,13 +5814,13 @@
         <v>13</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>13</v>
@@ -5711,12 +5838,12 @@
         <v>1</v>
       </c>
       <c r="M130" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>300013</v>
+        <v>300005</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
@@ -5725,25 +5852,25 @@
         <v>13</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
       </c>
-      <c r="G131" s="2">
-        <v>0</v>
+      <c r="G131" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J131" s="7">
         <v>5</v>
       </c>
       <c r="K131" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L131" s="7">
         <v>1</v>
@@ -5754,16 +5881,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>310020</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>8</v>
+        <v>300006</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -5775,33 +5902,33 @@
         <v>13</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J132" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K132" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L132" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>310010</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>8</v>
+        <v>300007</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -5813,39 +5940,39 @@
         <v>13</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="J133" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K133" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L133" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>320020</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>8</v>
+        <v>300008</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
       </c>
-      <c r="G134" s="2">
-        <v>0</v>
+      <c r="G134" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>13</v>
@@ -5854,30 +5981,30 @@
         <v>15</v>
       </c>
       <c r="J134" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K134" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L134" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>320010</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>8</v>
+        <v>300009</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -5889,39 +6016,39 @@
         <v>13</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="J135" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K135" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L135" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>330020</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>8</v>
+        <v>300011</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
       </c>
-      <c r="G136" s="2">
-        <v>0</v>
+      <c r="G136" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>13</v>
@@ -5930,36 +6057,36 @@
         <v>15</v>
       </c>
       <c r="J136" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K136" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L136" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>330010</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>8</v>
+        <v>300012</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
       </c>
-      <c r="G137" s="2">
-        <v>0</v>
+      <c r="G137" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>13</v>
@@ -5968,30 +6095,30 @@
         <v>15</v>
       </c>
       <c r="J137" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K137" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L137" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>340020</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>8</v>
+        <v>300013</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6003,24 +6130,24 @@
         <v>13</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J138" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K138" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L138" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>340010</v>
+        <v>310020</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>8</v>
@@ -6058,7 +6185,7 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>350020</v>
+        <v>310010</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>8</v>
@@ -6096,7 +6223,7 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>350010</v>
+        <v>320020</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>8</v>
@@ -6134,7 +6261,7 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>360020</v>
+        <v>320010</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>8</v>
@@ -6172,7 +6299,7 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>360010</v>
+        <v>330020</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>8</v>
@@ -6210,7 +6337,7 @@
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>370020</v>
+        <v>330010</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>8</v>
@@ -6248,7 +6375,7 @@
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>370010</v>
+        <v>340020</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>8</v>
@@ -6286,7 +6413,7 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>380020</v>
+        <v>340010</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>8</v>
@@ -6324,7 +6451,7 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>380010</v>
+        <v>350020</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>8</v>
@@ -6362,7 +6489,7 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>390020</v>
+        <v>350010</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>8</v>
@@ -6400,7 +6527,7 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>390010</v>
+        <v>360020</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>8</v>
@@ -6438,7 +6565,7 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>400020</v>
+        <v>360010</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>8</v>
@@ -6476,7 +6603,7 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>400010</v>
+        <v>370020</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>8</v>
@@ -6514,7 +6641,7 @@
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>410020</v>
+        <v>370010</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>8</v>
@@ -6552,7 +6679,7 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>410010</v>
+        <v>380020</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>8</v>
@@ -6590,7 +6717,7 @@
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>420020</v>
+        <v>380010</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>8</v>
@@ -6628,7 +6755,7 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>420010</v>
+        <v>390020</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>8</v>
@@ -6666,7 +6793,7 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>430020</v>
+        <v>390010</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>8</v>
@@ -6704,7 +6831,7 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>430010</v>
+        <v>400020</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>8</v>
@@ -6742,7 +6869,7 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>440020</v>
+        <v>400010</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>8</v>
@@ -6780,7 +6907,7 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>440010</v>
+        <v>410020</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>8</v>
@@ -6818,7 +6945,7 @@
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>450020</v>
+        <v>410010</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>8</v>
@@ -6856,7 +6983,7 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>450010</v>
+        <v>420020</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>8</v>
@@ -6894,7 +7021,7 @@
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>460020</v>
+        <v>420010</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>8</v>
@@ -6932,7 +7059,7 @@
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>460010</v>
+        <v>430020</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>8</v>
@@ -6970,7 +7097,7 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>470020</v>
+        <v>430010</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>8</v>
@@ -7008,7 +7135,7 @@
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>470010</v>
+        <v>440020</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>8</v>
@@ -7046,7 +7173,7 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>480020</v>
+        <v>440010</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>8</v>
@@ -7084,7 +7211,7 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>480010</v>
+        <v>450020</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>8</v>
@@ -7122,7 +7249,7 @@
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>490020</v>
+        <v>450010</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>8</v>
@@ -7160,7 +7287,7 @@
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>490010</v>
+        <v>460020</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>8</v>
@@ -7198,7 +7325,7 @@
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>500020</v>
+        <v>460010</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>8</v>
@@ -7236,7 +7363,7 @@
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>500010</v>
+        <v>470020</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>8</v>
@@ -7274,7 +7401,7 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>510020</v>
+        <v>470010</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>8</v>
@@ -7312,7 +7439,7 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>510010</v>
+        <v>480020</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>8</v>
@@ -7350,7 +7477,7 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>520020</v>
+        <v>480010</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>8</v>
@@ -7388,7 +7515,7 @@
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>520010</v>
+        <v>490020</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>8</v>
@@ -7426,7 +7553,7 @@
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>530020</v>
+        <v>490010</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>8</v>
@@ -7464,7 +7591,7 @@
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>530010</v>
+        <v>500020</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>8</v>
@@ -7502,7 +7629,7 @@
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>540020</v>
+        <v>500010</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>8</v>
@@ -7540,7 +7667,7 @@
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>540010</v>
+        <v>510020</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>8</v>
@@ -7578,7 +7705,7 @@
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>550020</v>
+        <v>510010</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>8</v>
@@ -7616,7 +7743,7 @@
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>550010</v>
+        <v>520020</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>8</v>
@@ -7654,7 +7781,7 @@
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>560020</v>
+        <v>520010</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>8</v>
@@ -7692,7 +7819,7 @@
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>560010</v>
+        <v>530020</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>8</v>
@@ -7730,7 +7857,7 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>570020</v>
+        <v>530010</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>8</v>
@@ -7768,7 +7895,7 @@
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>570010</v>
+        <v>540020</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>8</v>
@@ -7806,7 +7933,7 @@
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>580020</v>
+        <v>540010</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>8</v>
@@ -7844,7 +7971,7 @@
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>580010</v>
+        <v>550020</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>8</v>
@@ -7882,7 +8009,7 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>590020</v>
+        <v>550010</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>8</v>
@@ -7920,7 +8047,7 @@
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>590010</v>
+        <v>560020</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>8</v>
@@ -7958,7 +8085,7 @@
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>600020</v>
+        <v>560010</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>8</v>
@@ -7996,7 +8123,7 @@
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>600010</v>
+        <v>570020</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>8</v>
@@ -8034,7 +8161,7 @@
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>610020</v>
+        <v>570010</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>8</v>
@@ -8072,7 +8199,7 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>610010</v>
+        <v>580020</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>8</v>
@@ -8110,7 +8237,7 @@
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>620020</v>
+        <v>580010</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>8</v>
@@ -8148,7 +8275,7 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>620010</v>
+        <v>590020</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>8</v>
@@ -8186,7 +8313,7 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>630020</v>
+        <v>590010</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>8</v>
@@ -8224,7 +8351,7 @@
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>630010</v>
+        <v>600020</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>8</v>
@@ -8262,7 +8389,7 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>640020</v>
+        <v>600010</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>8</v>
@@ -8300,7 +8427,7 @@
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>640010</v>
+        <v>610020</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>8</v>
@@ -8338,7 +8465,7 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>650020</v>
+        <v>610010</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>8</v>
@@ -8376,7 +8503,7 @@
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>650010</v>
+        <v>620020</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>8</v>
@@ -8414,7 +8541,7 @@
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>660020</v>
+        <v>620010</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>8</v>
@@ -8452,7 +8579,7 @@
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>660010</v>
+        <v>630020</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>8</v>
@@ -8490,7 +8617,7 @@
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>670020</v>
+        <v>630010</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>8</v>
@@ -8528,7 +8655,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>670010</v>
+        <v>640020</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>8</v>
@@ -8566,7 +8693,7 @@
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>680020</v>
+        <v>640010</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>8</v>
@@ -8604,7 +8731,7 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>680010</v>
+        <v>650020</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>8</v>
@@ -8642,7 +8769,7 @@
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>690020</v>
+        <v>650010</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>8</v>
@@ -8680,7 +8807,7 @@
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>690010</v>
+        <v>660020</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>8</v>
@@ -8718,7 +8845,7 @@
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>700020</v>
+        <v>660010</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>8</v>
@@ -8756,7 +8883,7 @@
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>700010</v>
+        <v>670020</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>8</v>
@@ -8794,7 +8921,7 @@
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>710020</v>
+        <v>670010</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>8</v>
@@ -8832,7 +8959,7 @@
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>710010</v>
+        <v>680020</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>8</v>
@@ -8870,7 +8997,7 @@
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>720020</v>
+        <v>680010</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>8</v>
@@ -8908,7 +9035,7 @@
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>720010</v>
+        <v>690020</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>8</v>
@@ -8946,7 +9073,7 @@
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>730020</v>
+        <v>690010</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>8</v>
@@ -8984,7 +9111,7 @@
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>730010</v>
+        <v>700020</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>8</v>
@@ -9022,7 +9149,7 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>740020</v>
+        <v>700010</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>8</v>
@@ -9060,7 +9187,7 @@
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>740010</v>
+        <v>710020</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
@@ -9098,7 +9225,7 @@
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>750020</v>
+        <v>710010</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>8</v>
@@ -9136,7 +9263,7 @@
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>750010</v>
+        <v>720020</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>8</v>
@@ -9174,7 +9301,7 @@
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>760020</v>
+        <v>720010</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>8</v>
@@ -9212,7 +9339,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>760010</v>
+        <v>730020</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>8</v>
@@ -9250,7 +9377,7 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>770020</v>
+        <v>730010</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>8</v>
@@ -9288,7 +9415,7 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>770010</v>
+        <v>740020</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
@@ -9326,7 +9453,7 @@
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>780020</v>
+        <v>740010</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
@@ -9364,7 +9491,7 @@
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>780010</v>
+        <v>750020</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>8</v>
@@ -9402,7 +9529,7 @@
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>790020</v>
+        <v>750010</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
@@ -9440,7 +9567,7 @@
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>790010</v>
+        <v>760020</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>8</v>
@@ -9478,7 +9605,7 @@
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>800020</v>
+        <v>760010</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
@@ -9516,7 +9643,7 @@
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>800010</v>
+        <v>770020</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>8</v>
@@ -9554,7 +9681,7 @@
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>810020</v>
+        <v>770010</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -9592,7 +9719,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>810010</v>
+        <v>780020</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>8</v>
@@ -9630,7 +9757,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>820020</v>
+        <v>780010</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>8</v>
@@ -9668,7 +9795,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>820010</v>
+        <v>790020</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>8</v>
@@ -9706,7 +9833,7 @@
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>830020</v>
+        <v>790010</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>8</v>
@@ -9744,7 +9871,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>830010</v>
+        <v>800020</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>8</v>
@@ -9782,7 +9909,7 @@
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>840020</v>
+        <v>800010</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>8</v>
@@ -9820,7 +9947,7 @@
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>840010</v>
+        <v>810020</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>8</v>
@@ -9858,7 +9985,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>850020</v>
+        <v>810010</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -9896,7 +10023,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>850010</v>
+        <v>820020</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>8</v>
@@ -9934,7 +10061,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>860020</v>
+        <v>820010</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -9972,7 +10099,7 @@
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>860010</v>
+        <v>830020</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -10010,7 +10137,7 @@
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>870020</v>
+        <v>830010</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -10048,7 +10175,7 @@
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>870010</v>
+        <v>840020</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -10086,7 +10213,7 @@
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>880020</v>
+        <v>840010</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -10124,7 +10251,7 @@
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>880010</v>
+        <v>850020</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -10162,7 +10289,7 @@
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>890020</v>
+        <v>850010</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>8</v>
@@ -10200,7 +10327,7 @@
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>890010</v>
+        <v>860020</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -10238,7 +10365,7 @@
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>900020</v>
+        <v>860010</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>8</v>
@@ -10276,7 +10403,7 @@
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>900010</v>
+        <v>870020</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
@@ -10314,7 +10441,7 @@
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>910020</v>
+        <v>870010</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -10352,7 +10479,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>910010</v>
+        <v>880020</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
@@ -10390,7 +10517,7 @@
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>920020</v>
+        <v>880010</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>8</v>
@@ -10428,7 +10555,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>920010</v>
+        <v>890020</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>8</v>
@@ -10466,7 +10593,7 @@
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>930020</v>
+        <v>890010</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -10504,7 +10631,7 @@
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>930010</v>
+        <v>900020</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -10542,7 +10669,7 @@
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>940020</v>
+        <v>900010</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -10580,7 +10707,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>940010</v>
+        <v>910020</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -10618,7 +10745,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>950020</v>
+        <v>910010</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
@@ -10656,7 +10783,7 @@
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>950010</v>
+        <v>920020</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
@@ -10694,7 +10821,7 @@
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>960020</v>
+        <v>920010</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>8</v>
@@ -10732,7 +10859,7 @@
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>960010</v>
+        <v>930020</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
@@ -10770,7 +10897,7 @@
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>970020</v>
+        <v>930010</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -10808,7 +10935,7 @@
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>970010</v>
+        <v>940020</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -10846,7 +10973,7 @@
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>980020</v>
+        <v>940010</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -10884,7 +11011,7 @@
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>980010</v>
+        <v>950020</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -10922,7 +11049,7 @@
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>990020</v>
+        <v>950010</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -10960,7 +11087,7 @@
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>990010</v>
+        <v>960020</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
@@ -10998,7 +11125,7 @@
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1000020</v>
+        <v>960010</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -11036,7 +11163,7 @@
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1000010</v>
+        <v>970020</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>8</v>
@@ -11074,7 +11201,7 @@
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1010020</v>
+        <v>970010</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -11112,7 +11239,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1010010</v>
+        <v>980020</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -11150,7 +11277,7 @@
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1020020</v>
+        <v>980010</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -11188,7 +11315,7 @@
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1020010</v>
+        <v>990020</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>8</v>
@@ -11226,7 +11353,7 @@
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1030020</v>
+        <v>990010</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>8</v>
@@ -11264,7 +11391,7 @@
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1030010</v>
+        <v>1000020</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -11302,7 +11429,7 @@
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1040020</v>
+        <v>1000010</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -11340,7 +11467,7 @@
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1040010</v>
+        <v>1010020</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>8</v>
@@ -11378,7 +11505,7 @@
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1050020</v>
+        <v>1010010</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>8</v>
@@ -11416,7 +11543,7 @@
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1050010</v>
+        <v>1020020</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>8</v>
@@ -11454,7 +11581,7 @@
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1060020</v>
+        <v>1020010</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>8</v>
@@ -11492,7 +11619,7 @@
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1060010</v>
+        <v>1030020</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -11530,7 +11657,7 @@
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1070020</v>
+        <v>1030010</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -11568,7 +11695,7 @@
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1070010</v>
+        <v>1040020</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -11606,7 +11733,7 @@
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1080020</v>
+        <v>1040010</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -11644,7 +11771,7 @@
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1080010</v>
+        <v>1050020</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -11682,7 +11809,7 @@
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1090020</v>
+        <v>1050010</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -11720,7 +11847,7 @@
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1090010</v>
+        <v>1060020</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -11758,7 +11885,7 @@
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1100020</v>
+        <v>1060010</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -11796,7 +11923,7 @@
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1100010</v>
+        <v>1070020</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -11834,7 +11961,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1110020</v>
+        <v>1070010</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -11872,7 +11999,7 @@
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1110010</v>
+        <v>1080020</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>8</v>
@@ -11910,7 +12037,7 @@
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1120020</v>
+        <v>1080010</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>8</v>
@@ -11948,7 +12075,7 @@
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1120010</v>
+        <v>1090020</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>8</v>
@@ -11986,7 +12113,7 @@
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1130020</v>
+        <v>1090010</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -12024,7 +12151,7 @@
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1130010</v>
+        <v>1100020</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -12062,7 +12189,7 @@
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1140020</v>
+        <v>1100010</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -12100,7 +12227,7 @@
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1140010</v>
+        <v>1110020</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -12138,7 +12265,7 @@
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1150020</v>
+        <v>1110010</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>8</v>
@@ -12176,7 +12303,7 @@
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1150010</v>
+        <v>1120020</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -12214,7 +12341,7 @@
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1160020</v>
+        <v>1120010</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>8</v>
@@ -12252,7 +12379,7 @@
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1160010</v>
+        <v>1130020</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>8</v>
@@ -12290,7 +12417,7 @@
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1170020</v>
+        <v>1130010</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>8</v>
@@ -12328,7 +12455,7 @@
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1170010</v>
+        <v>1140020</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -12366,7 +12493,7 @@
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1180020</v>
+        <v>1140010</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>8</v>
@@ -12404,7 +12531,7 @@
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1180010</v>
+        <v>1150020</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -12442,7 +12569,7 @@
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1190020</v>
+        <v>1150010</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>8</v>
@@ -12480,7 +12607,7 @@
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1190010</v>
+        <v>1160020</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>8</v>
@@ -12518,7 +12645,7 @@
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1200020</v>
+        <v>1160010</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>8</v>
@@ -12556,7 +12683,7 @@
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1200010</v>
+        <v>1170020</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>8</v>
@@ -12594,7 +12721,7 @@
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1210020</v>
+        <v>1170010</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>8</v>
@@ -12632,7 +12759,7 @@
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1210010</v>
+        <v>1180020</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>8</v>
@@ -12670,7 +12797,7 @@
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1220020</v>
+        <v>1180010</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>8</v>
@@ -12708,7 +12835,7 @@
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1220010</v>
+        <v>1190020</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -12746,7 +12873,7 @@
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1230020</v>
+        <v>1190010</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -12784,7 +12911,7 @@
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1230010</v>
+        <v>1200020</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -12822,7 +12949,7 @@
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1240020</v>
+        <v>1200010</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -12860,7 +12987,7 @@
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1240010</v>
+        <v>1210020</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -12898,7 +13025,7 @@
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1250020</v>
+        <v>1210010</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>8</v>
@@ -12936,7 +13063,7 @@
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1250010</v>
+        <v>1220020</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>8</v>
@@ -12974,7 +13101,7 @@
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1260020</v>
+        <v>1220010</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -13012,7 +13139,7 @@
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1260010</v>
+        <v>1230020</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>8</v>
@@ -13050,7 +13177,7 @@
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1270020</v>
+        <v>1230010</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>8</v>
@@ -13088,7 +13215,7 @@
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1270010</v>
+        <v>1240020</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -13126,7 +13253,7 @@
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1280020</v>
+        <v>1240010</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -13164,7 +13291,7 @@
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1280010</v>
+        <v>1250020</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -13202,7 +13329,7 @@
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1290020</v>
+        <v>1250010</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -13240,7 +13367,7 @@
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1290010</v>
+        <v>1260020</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -13278,7 +13405,7 @@
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1300020</v>
+        <v>1260010</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>8</v>
@@ -13316,7 +13443,7 @@
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1300010</v>
+        <v>1270020</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -13354,7 +13481,7 @@
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1310020</v>
+        <v>1270010</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -13392,7 +13519,7 @@
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1310010</v>
+        <v>1280020</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>8</v>
@@ -13430,7 +13557,7 @@
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1320020</v>
+        <v>1280010</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -13468,7 +13595,7 @@
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1320010</v>
+        <v>1290020</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>8</v>
@@ -13506,7 +13633,7 @@
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1330020</v>
+        <v>1290010</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -13544,7 +13671,7 @@
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1330010</v>
+        <v>1300020</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -13582,7 +13709,7 @@
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1340020</v>
+        <v>1300010</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>8</v>
@@ -13620,7 +13747,7 @@
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1340010</v>
+        <v>1310020</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -13658,7 +13785,7 @@
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>1350020</v>
+        <v>1310010</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -13696,7 +13823,7 @@
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>1350010</v>
+        <v>1320020</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -13734,7 +13861,7 @@
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>1360020</v>
+        <v>1320010</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>8</v>
@@ -13772,7 +13899,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>1360010</v>
+        <v>1330020</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
@@ -13810,7 +13937,7 @@
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>1370020</v>
+        <v>1330010</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
@@ -13848,7 +13975,7 @@
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>1370010</v>
+        <v>1340020</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>8</v>
@@ -13886,7 +14013,7 @@
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>1380020</v>
+        <v>1340010</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>8</v>
@@ -13924,7 +14051,7 @@
     </row>
     <row r="347" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>1380010</v>
+        <v>1350020</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>8</v>
@@ -13962,7 +14089,7 @@
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>1390020</v>
+        <v>1350010</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>8</v>
@@ -14000,7 +14127,7 @@
     </row>
     <row r="349" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>1390010</v>
+        <v>1360020</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>8</v>
@@ -14038,7 +14165,7 @@
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>1400020</v>
+        <v>1360010</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>8</v>
@@ -14076,7 +14203,7 @@
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>1400010</v>
+        <v>1370020</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>8</v>
@@ -14114,7 +14241,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>1410020</v>
+        <v>1370010</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -14152,7 +14279,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>1410010</v>
+        <v>1380020</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -14190,7 +14317,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>1420020</v>
+        <v>1380010</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -14228,7 +14355,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>1420010</v>
+        <v>1390020</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -14266,7 +14393,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>1430020</v>
+        <v>1390010</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -14304,7 +14431,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>1430010</v>
+        <v>1400020</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -14342,7 +14469,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>1440020</v>
+        <v>1400010</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -14380,7 +14507,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>1440010</v>
+        <v>1410020</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -14418,7 +14545,7 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>1450020</v>
+        <v>1410010</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -14456,7 +14583,7 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>1450010</v>
+        <v>1420020</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
@@ -14494,7 +14621,7 @@
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>1460020</v>
+        <v>1420010</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -14532,7 +14659,7 @@
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>1460010</v>
+        <v>1430020</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>8</v>
@@ -14570,7 +14697,7 @@
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>1470020</v>
+        <v>1430010</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -14608,7 +14735,7 @@
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>1470010</v>
+        <v>1440020</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>8</v>
@@ -14646,7 +14773,7 @@
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>1480020</v>
+        <v>1440010</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>8</v>
@@ -14684,7 +14811,7 @@
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>1480010</v>
+        <v>1450020</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>8</v>
@@ -14722,7 +14849,7 @@
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>1490020</v>
+        <v>1450010</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -14760,7 +14887,7 @@
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>1490010</v>
+        <v>1460020</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>8</v>
@@ -14798,7 +14925,7 @@
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>1500020</v>
+        <v>1460010</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>8</v>
@@ -14836,7 +14963,7 @@
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>1500010</v>
+        <v>1470020</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>8</v>
@@ -14874,7 +15001,7 @@
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>1510020</v>
+        <v>1470010</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
@@ -14912,7 +15039,7 @@
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>1510010</v>
+        <v>1480020</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>8</v>
@@ -14950,7 +15077,7 @@
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>1520020</v>
+        <v>1480010</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>8</v>
@@ -14988,7 +15115,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>1520010</v>
+        <v>1490020</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>8</v>
@@ -15026,7 +15153,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>1530020</v>
+        <v>1490010</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>8</v>
@@ -15064,7 +15191,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>1530010</v>
+        <v>1500020</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>8</v>
@@ -15102,7 +15229,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>1540020</v>
+        <v>1500010</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>8</v>
@@ -15140,7 +15267,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>1540010</v>
+        <v>1510020</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>8</v>
@@ -15178,7 +15305,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>1550020</v>
+        <v>1510010</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>8</v>
@@ -15216,7 +15343,7 @@
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>1550010</v>
+        <v>1520020</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>8</v>
@@ -15254,7 +15381,7 @@
     </row>
     <row r="382" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>1560020</v>
+        <v>1520010</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>8</v>
@@ -15292,7 +15419,7 @@
     </row>
     <row r="383" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>1560010</v>
+        <v>1530020</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>8</v>
@@ -15330,7 +15457,7 @@
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>1570020</v>
+        <v>1530010</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>8</v>
@@ -15368,7 +15495,7 @@
     </row>
     <row r="385" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>1570010</v>
+        <v>1540020</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>8</v>
@@ -15406,7 +15533,7 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>1580020</v>
+        <v>1540010</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>8</v>
@@ -15444,7 +15571,7 @@
     </row>
     <row r="387" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>1580010</v>
+        <v>1550020</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>8</v>
@@ -15482,7 +15609,7 @@
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>1590020</v>
+        <v>1550010</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>8</v>
@@ -15520,7 +15647,7 @@
     </row>
     <row r="389" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>1590010</v>
+        <v>1560020</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>8</v>
@@ -15558,7 +15685,7 @@
     </row>
     <row r="390" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>1600020</v>
+        <v>1560010</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>8</v>
@@ -15596,39 +15723,305 @@
     </row>
     <row r="391" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
+        <v>1570020</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E391" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F391" s="1">
+        <v>0</v>
+      </c>
+      <c r="G391" s="2">
+        <v>0</v>
+      </c>
+      <c r="H391" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I391" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J391" s="7">
+        <v>0</v>
+      </c>
+      <c r="K391" s="7">
+        <v>0</v>
+      </c>
+      <c r="L391" s="7">
+        <v>0</v>
+      </c>
+      <c r="M391" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A392" s="1">
+        <v>1570010</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E392" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F392" s="1">
+        <v>0</v>
+      </c>
+      <c r="G392" s="2">
+        <v>0</v>
+      </c>
+      <c r="H392" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I392" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J392" s="7">
+        <v>0</v>
+      </c>
+      <c r="K392" s="7">
+        <v>0</v>
+      </c>
+      <c r="L392" s="7">
+        <v>0</v>
+      </c>
+      <c r="M392" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A393" s="1">
+        <v>1580020</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E393" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F393" s="1">
+        <v>0</v>
+      </c>
+      <c r="G393" s="2">
+        <v>0</v>
+      </c>
+      <c r="H393" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I393" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J393" s="7">
+        <v>0</v>
+      </c>
+      <c r="K393" s="7">
+        <v>0</v>
+      </c>
+      <c r="L393" s="7">
+        <v>0</v>
+      </c>
+      <c r="M393" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A394" s="1">
+        <v>1580010</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E394" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F394" s="1">
+        <v>0</v>
+      </c>
+      <c r="G394" s="2">
+        <v>0</v>
+      </c>
+      <c r="H394" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I394" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J394" s="7">
+        <v>0</v>
+      </c>
+      <c r="K394" s="7">
+        <v>0</v>
+      </c>
+      <c r="L394" s="7">
+        <v>0</v>
+      </c>
+      <c r="M394" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A395" s="1">
+        <v>1590020</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E395" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F395" s="1">
+        <v>0</v>
+      </c>
+      <c r="G395" s="2">
+        <v>0</v>
+      </c>
+      <c r="H395" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I395" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J395" s="7">
+        <v>0</v>
+      </c>
+      <c r="K395" s="7">
+        <v>0</v>
+      </c>
+      <c r="L395" s="7">
+        <v>0</v>
+      </c>
+      <c r="M395" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A396" s="1">
+        <v>1590010</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E396" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F396" s="1">
+        <v>0</v>
+      </c>
+      <c r="G396" s="2">
+        <v>0</v>
+      </c>
+      <c r="H396" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I396" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J396" s="7">
+        <v>0</v>
+      </c>
+      <c r="K396" s="7">
+        <v>0</v>
+      </c>
+      <c r="L396" s="7">
+        <v>0</v>
+      </c>
+      <c r="M396" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A397" s="1">
+        <v>1600020</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E397" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F397" s="1">
+        <v>0</v>
+      </c>
+      <c r="G397" s="2">
+        <v>0</v>
+      </c>
+      <c r="H397" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I397" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J397" s="7">
+        <v>0</v>
+      </c>
+      <c r="K397" s="7">
+        <v>0</v>
+      </c>
+      <c r="L397" s="7">
+        <v>0</v>
+      </c>
+      <c r="M397" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A398" s="1">
         <v>1600010</v>
       </c>
-      <c r="C391" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D391" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E391" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F391" s="1">
-        <v>0</v>
-      </c>
-      <c r="G391" s="2">
-        <v>0</v>
-      </c>
-      <c r="H391" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I391" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J391" s="7">
-        <v>0</v>
-      </c>
-      <c r="K391" s="7">
-        <v>0</v>
-      </c>
-      <c r="L391" s="7">
-        <v>0</v>
-      </c>
-      <c r="M391" s="7">
+      <c r="C398" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E398" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F398" s="1">
+        <v>0</v>
+      </c>
+      <c r="G398" s="2">
+        <v>0</v>
+      </c>
+      <c r="H398" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I398" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J398" s="7">
+        <v>0</v>
+      </c>
+      <c r="K398" s="7">
+        <v>0</v>
+      </c>
+      <c r="L398" s="7">
+        <v>0</v>
+      </c>
+      <c r="M398" s="7">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8DB87D-6C65-40B6-9AA8-45EFEACEE40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113CCDBD-84DE-45D3-B15D-C617182E82DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$M$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$M$403</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="106">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -189,30 +189,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>48200001:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300003:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300004:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300002:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300005:1_46700001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300006:1_46700001:5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LIST&lt;INT&gt;_C_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -250,14 +226,6 @@
   </si>
   <si>
     <t>drop_item_first</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300005:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300006:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -444,6 +412,53 @@
   </si>
   <si>
     <t>第6关铠甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关强化石1</t>
+  </si>
+  <si>
+    <t>第7关铠甲1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关金币1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关武器1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关铠甲2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关强化石2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关金币2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关武器2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关金币3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关铠甲3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关武器3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第7关强化石3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -834,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M398"/>
+  <dimension ref="A1:M403"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -878,7 +893,7 @@
         <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
@@ -910,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
@@ -919,25 +934,25 @@
         <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
@@ -948,37 +963,37 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
@@ -986,7 +1001,7 @@
         <v>10001</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -995,7 +1010,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
@@ -1007,7 +1022,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -1027,7 +1042,7 @@
         <v>10002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -1036,7 +1051,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -1048,7 +1063,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -1068,7 +1083,7 @@
         <v>10003</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
@@ -1077,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -1089,7 +1104,7 @@
         <v>13</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J7" s="7">
         <v>0</v>
@@ -1109,7 +1124,7 @@
         <v>10004</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -1118,7 +1133,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -1130,7 +1145,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J8" s="7">
         <v>0</v>
@@ -1150,7 +1165,7 @@
         <v>10005</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -1159,7 +1174,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -1171,7 +1186,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -1191,7 +1206,7 @@
         <v>10006</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
@@ -1200,7 +1215,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -1212,7 +1227,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J10" s="7">
         <v>0</v>
@@ -1232,7 +1247,7 @@
         <v>10007</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
@@ -1241,7 +1256,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1253,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J11" s="7">
         <v>0</v>
@@ -1273,7 +1288,7 @@
         <v>10008</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -1282,7 +1297,7 @@
         <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1294,7 +1309,7 @@
         <v>13</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J12" s="7">
         <v>0</v>
@@ -1314,7 +1329,7 @@
         <v>10009</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -1323,7 +1338,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
@@ -1335,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J13" s="7">
         <v>0</v>
@@ -1431,7 +1446,7 @@
         <v>10011</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -1440,13 +1455,13 @@
         <v>13</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -1548,7 +1563,7 @@
         <v>20001</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -1557,13 +1572,13 @@
         <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1">
         <v>30</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -1665,7 +1680,7 @@
         <v>30001</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -1674,13 +1689,13 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F22" s="1">
         <v>30</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -1706,7 +1721,7 @@
         <v>30002</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
@@ -1715,13 +1730,13 @@
         <v>13</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F23" s="1">
         <v>30</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -1823,7 +1838,7 @@
         <v>40001</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1832,13 +1847,13 @@
         <v>13</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F26" s="1">
         <v>30</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -1864,7 +1879,7 @@
         <v>40002</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -1873,13 +1888,13 @@
         <v>13</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1">
         <v>30</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -1981,7 +1996,7 @@
         <v>40001</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1990,13 +2005,13 @@
         <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F30" s="1">
         <v>30</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -2022,7 +2037,7 @@
         <v>50002</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -2063,7 +2078,7 @@
         <v>50003</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -2180,7 +2195,7 @@
         <v>60001</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -2221,7 +2236,7 @@
         <v>60002</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -2262,7 +2277,7 @@
         <v>60003</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -2303,7 +2318,7 @@
         <v>60004</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -2344,7 +2359,7 @@
         <v>60005</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -2385,7 +2400,7 @@
         <v>60006</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2499,7 +2514,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>70002</v>
+        <v>70001</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -2508,36 +2526,39 @@
         <v>13</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F43" s="1">
-        <v>50</v>
-      </c>
-      <c r="G43" s="2">
-        <v>42614001</v>
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J43" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K43" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>70003</v>
+        <v>70002</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -2546,10 +2567,10 @@
         <v>13</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
@@ -2558,24 +2579,27 @@
         <v>13</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J44" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K44" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>70004</v>
+        <v>70003</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -2584,10 +2608,10 @@
         <v>13</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F45" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
         <v>0</v>
@@ -2596,24 +2620,27 @@
         <v>13</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J45" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>70005</v>
+        <v>70004</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -2622,36 +2649,39 @@
         <v>13</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F46" s="1">
-        <v>360</v>
-      </c>
-      <c r="G46" s="2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J46" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K46" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>70006</v>
+        <v>70005</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -2660,13 +2690,13 @@
         <v>13</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F47" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G47" s="2">
-        <v>42635001</v>
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -2675,21 +2705,24 @@
         <v>15</v>
       </c>
       <c r="J47" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K47" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>70007</v>
+        <v>70006</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -2698,10 +2731,10 @@
         <v>13</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F48" s="1">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
@@ -2710,24 +2743,27 @@
         <v>13</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J48" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K48" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>70008</v>
+        <v>70007</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -2736,10 +2772,10 @@
         <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F49" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
@@ -2748,24 +2784,27 @@
         <v>13</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="J49" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K49" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L49" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>80020</v>
+        <v>70008</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -2774,13 +2813,13 @@
         <v>13</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
-      <c r="G50" s="2">
-        <v>0</v>
+      <c r="G50" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -2789,21 +2828,24 @@
         <v>15</v>
       </c>
       <c r="J50" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K50" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>80010</v>
+        <v>70009</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -2812,7 +2854,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2824,24 +2866,27 @@
         <v>13</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="J51" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K51" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>90020</v>
+        <v>70011</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -2850,13 +2895,13 @@
         <v>13</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
-      <c r="G52" s="2">
-        <v>0</v>
+      <c r="G52" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -2865,21 +2910,24 @@
         <v>15</v>
       </c>
       <c r="J52" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K52" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>100020</v>
+        <v>70012</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -2888,13 +2936,13 @@
         <v>13</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
-      <c r="G53" s="2">
-        <v>0</v>
+      <c r="G53" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -2903,21 +2951,24 @@
         <v>15</v>
       </c>
       <c r="J53" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K53" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>100010</v>
+        <v>70013</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -2926,7 +2977,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -2938,24 +2989,24 @@
         <v>13</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J54" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K54" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>110020</v>
+        <v>80020</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -2993,7 +3044,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>110010</v>
+        <v>80010</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -3031,7 +3082,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>110001</v>
+        <v>90020</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -3040,13 +3091,13 @@
         <v>13</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1">
-        <v>30</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>13</v>
@@ -3055,21 +3106,21 @@
         <v>15</v>
       </c>
       <c r="J57" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K57" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>110002</v>
+        <v>100020</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -3078,10 +3129,10 @@
         <v>13</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
@@ -3090,24 +3141,24 @@
         <v>13</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="J58" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K58" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>110003</v>
+        <v>100010</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -3116,13 +3167,13 @@
         <v>13</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1">
-        <v>50</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>13</v>
@@ -3131,21 +3182,21 @@
         <v>15</v>
       </c>
       <c r="J59" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K59" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>110004</v>
+        <v>110020</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -3154,10 +3205,10 @@
         <v>13</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
         <v>0</v>
@@ -3166,24 +3217,24 @@
         <v>13</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="J60" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K60" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110005</v>
+        <v>110010</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -3192,10 +3243,10 @@
         <v>13</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
@@ -3204,24 +3255,24 @@
         <v>13</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J61" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K61" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M61" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>110006</v>
+        <v>110001</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -3230,13 +3281,13 @@
         <v>13</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F62" s="1">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>13</v>
@@ -3245,10 +3296,10 @@
         <v>15</v>
       </c>
       <c r="J62" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K62" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" s="7">
         <v>1</v>
@@ -3259,7 +3310,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>110007</v>
+        <v>110002</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -3268,25 +3319,25 @@
         <v>13</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F63" s="1">
-        <v>210</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="J63" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" s="7">
         <v>1</v>
@@ -3297,7 +3348,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>110008</v>
+        <v>110003</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -3306,25 +3357,25 @@
         <v>13</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F64" s="1">
-        <v>250</v>
-      </c>
-      <c r="G64" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="J64" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L64" s="7">
         <v>2</v>
@@ -3335,7 +3386,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
-        <v>110009</v>
+        <v>110004</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -3344,10 +3395,10 @@
         <v>13</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F65" s="1">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="G65" s="2">
         <v>0</v>
@@ -3356,13 +3407,13 @@
         <v>13</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J65" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L65" s="7">
         <v>2</v>
@@ -3373,7 +3424,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>110011</v>
+        <v>110005</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -3382,10 +3433,10 @@
         <v>13</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F66" s="1">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
@@ -3394,13 +3445,13 @@
         <v>13</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J66" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K66" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" s="7">
         <v>3</v>
@@ -3411,7 +3462,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>110012</v>
+        <v>110006</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -3420,13 +3471,13 @@
         <v>13</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F67" s="1">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>13</v>
@@ -3435,21 +3486,21 @@
         <v>15</v>
       </c>
       <c r="J67" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K67" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>110013</v>
+        <v>110007</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -3458,36 +3509,36 @@
         <v>13</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F68" s="1">
-        <v>800</v>
-      </c>
-      <c r="G68" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J68" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K68" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>110014</v>
+        <v>110008</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -3496,36 +3547,36 @@
         <v>13</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F69" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>61</v>
+        <v>250</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J69" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K69" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>110015</v>
+        <v>110009</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -3534,10 +3585,10 @@
         <v>13</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F70" s="1">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
@@ -3546,24 +3597,24 @@
         <v>13</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J70" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K70" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>110016</v>
+        <v>110011</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -3572,10 +3623,10 @@
         <v>13</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F71" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
@@ -3584,24 +3635,24 @@
         <v>13</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="J71" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K71" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M71" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>110017</v>
+        <v>110012</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -3610,19 +3661,19 @@
         <v>13</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="F72" s="1">
-        <v>1800</v>
-      </c>
-      <c r="G72" s="2">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="J72" s="7">
         <v>0</v>
@@ -3639,7 +3690,7 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>110018</v>
+        <v>110013</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -3648,10 +3699,10 @@
         <v>13</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F73" s="1">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
@@ -3660,7 +3711,7 @@
         <v>13</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="J73" s="7">
         <v>0</v>
@@ -3677,7 +3728,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>110019</v>
+        <v>110014</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -3686,13 +3737,13 @@
         <v>13</v>
       </c>
       <c r="E74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="F74" s="1">
-        <v>2500</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>13</v>
@@ -3715,7 +3766,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>110021</v>
+        <v>110015</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -3724,10 +3775,10 @@
         <v>13</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F75" s="1">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
@@ -3736,7 +3787,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="J75" s="7">
         <v>0</v>
@@ -3753,7 +3804,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>110022</v>
+        <v>110016</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -3762,19 +3813,19 @@
         <v>13</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F76" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>66</v>
+        <v>1500</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="J76" s="7">
         <v>0</v>
@@ -3791,7 +3842,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>110023</v>
+        <v>110017</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -3800,10 +3851,10 @@
         <v>13</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F77" s="1">
-        <v>8000</v>
+        <v>1800</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
@@ -3812,7 +3863,7 @@
         <v>13</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J77" s="7">
         <v>0</v>
@@ -3829,7 +3880,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>110024</v>
+        <v>110018</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -3838,10 +3889,10 @@
         <v>13</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F78" s="1">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
@@ -3850,7 +3901,7 @@
         <v>13</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="J78" s="7">
         <v>0</v>
@@ -3867,22 +3918,22 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>120020</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>8</v>
+        <v>110019</v>
+      </c>
+      <c r="C79" s="2">
+        <v>0</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F79" s="1">
-        <v>0</v>
-      </c>
-      <c r="G79" s="2">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>13</v>
@@ -3905,19 +3956,19 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>120010</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>8</v>
+        <v>110021</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F80" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G80" s="2">
         <v>0</v>
@@ -3926,7 +3977,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J80" s="7">
         <v>0</v>
@@ -3943,22 +3994,22 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>130020</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>8</v>
+        <v>110022</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
-      </c>
-      <c r="G81" s="2">
-        <v>0</v>
+        <v>6000</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>13</v>
@@ -3981,19 +4032,19 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>130010</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>8</v>
+        <v>110023</v>
+      </c>
+      <c r="C82" s="2">
+        <v>0</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
@@ -4002,7 +4053,7 @@
         <v>13</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J82" s="7">
         <v>0</v>
@@ -4019,7 +4070,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>130001</v>
+        <v>110024</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -4028,13 +4079,13 @@
         <v>13</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1">
-        <v>30</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="G83" s="2">
+        <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>13</v>
@@ -4043,33 +4094,33 @@
         <v>15</v>
       </c>
       <c r="J83" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K83" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>130002</v>
-      </c>
-      <c r="C84" s="2">
-        <v>0</v>
+        <v>120020</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F84" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
@@ -4078,39 +4129,39 @@
         <v>13</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="J84" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K84" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>130003</v>
-      </c>
-      <c r="C85" s="2">
-        <v>0</v>
+        <v>120010</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1">
-        <v>50</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="G85" s="2">
+        <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>13</v>
@@ -4119,33 +4170,33 @@
         <v>15</v>
       </c>
       <c r="J85" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K85" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M85" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>130004</v>
-      </c>
-      <c r="C86" s="2">
-        <v>0</v>
+        <v>130020</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
@@ -4154,36 +4205,36 @@
         <v>13</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="J86" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K86" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>130005</v>
-      </c>
-      <c r="C87" s="2">
-        <v>0</v>
+        <v>130010</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
@@ -4192,24 +4243,24 @@
         <v>13</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="J87" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K87" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M87" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>130006</v>
+        <v>130001</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -4218,13 +4269,13 @@
         <v>13</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F88" s="1">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>13</v>
@@ -4233,10 +4284,10 @@
         <v>15</v>
       </c>
       <c r="J88" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K88" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L88" s="7">
         <v>1</v>
@@ -4247,7 +4298,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>130007</v>
+        <v>130002</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -4256,25 +4307,25 @@
         <v>13</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F89" s="1">
-        <v>210</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="G89" s="2">
+        <v>0</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="J89" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K89" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L89" s="7">
         <v>1</v>
@@ -4285,7 +4336,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>130008</v>
+        <v>130003</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -4294,25 +4345,25 @@
         <v>13</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F90" s="1">
-        <v>250</v>
-      </c>
-      <c r="G90" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="J90" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K90" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L90" s="7">
         <v>2</v>
@@ -4323,7 +4374,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>130009</v>
+        <v>130004</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -4332,10 +4383,10 @@
         <v>13</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F91" s="1">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
@@ -4344,13 +4395,13 @@
         <v>13</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J91" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K91" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L91" s="7">
         <v>2</v>
@@ -4361,7 +4412,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>130011</v>
+        <v>130005</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -4370,10 +4421,10 @@
         <v>13</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F92" s="1">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
@@ -4382,13 +4433,13 @@
         <v>13</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J92" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K92" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L92" s="7">
         <v>3</v>
@@ -4399,22 +4450,22 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>140020</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>8</v>
+        <v>130006</v>
+      </c>
+      <c r="C93" s="2">
+        <v>0</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F93" s="1">
-        <v>0</v>
-      </c>
-      <c r="G93" s="2">
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>13</v>
@@ -4423,36 +4474,36 @@
         <v>15</v>
       </c>
       <c r="J93" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K93" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>140010</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>8</v>
+        <v>130007</v>
+      </c>
+      <c r="C94" s="2">
+        <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F94" s="1">
-        <v>0</v>
-      </c>
-      <c r="G94" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>13</v>
@@ -4461,33 +4512,33 @@
         <v>15</v>
       </c>
       <c r="J94" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K94" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L94" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>150020</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>8</v>
+        <v>130008</v>
+      </c>
+      <c r="C95" s="2">
+        <v>0</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
@@ -4496,36 +4547,36 @@
         <v>13</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J95" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K95" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L95" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>150010</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>8</v>
+        <v>130009</v>
+      </c>
+      <c r="C96" s="2">
+        <v>0</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F96" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
@@ -4534,36 +4585,36 @@
         <v>13</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="J96" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K96" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L96" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>160020</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>8</v>
+        <v>130011</v>
+      </c>
+      <c r="C97" s="2">
+        <v>0</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F97" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
@@ -4572,24 +4623,24 @@
         <v>13</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J97" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K97" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M97" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>160010</v>
+        <v>140020</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>8</v>
@@ -4627,7 +4678,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>170020</v>
+        <v>140010</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>8</v>
@@ -4665,7 +4716,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>170010</v>
+        <v>150020</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>8</v>
@@ -4703,7 +4754,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>180020</v>
+        <v>150010</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>8</v>
@@ -4741,7 +4792,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>180010</v>
+        <v>160020</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>8</v>
@@ -4779,7 +4830,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>190020</v>
+        <v>160010</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>8</v>
@@ -4817,7 +4868,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>190010</v>
+        <v>170020</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>8</v>
@@ -4855,7 +4906,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>200020</v>
+        <v>170010</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>8</v>
@@ -4893,7 +4944,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>200010</v>
+        <v>180020</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>8</v>
@@ -4931,7 +4982,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>210020</v>
+        <v>180010</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>8</v>
@@ -4969,7 +5020,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>210010</v>
+        <v>190020</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>8</v>
@@ -5007,7 +5058,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>220020</v>
+        <v>190010</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>8</v>
@@ -5045,7 +5096,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>220010</v>
+        <v>200020</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>8</v>
@@ -5083,7 +5134,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>230020</v>
+        <v>200010</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>8</v>
@@ -5121,7 +5172,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>230010</v>
+        <v>210020</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>8</v>
@@ -5159,7 +5210,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>240020</v>
+        <v>210010</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>8</v>
@@ -5197,7 +5248,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>240010</v>
+        <v>220020</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>8</v>
@@ -5235,7 +5286,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>250020</v>
+        <v>220010</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>8</v>
@@ -5273,7 +5324,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>250010</v>
+        <v>230020</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>8</v>
@@ -5311,7 +5362,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>260020</v>
+        <v>230010</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>8</v>
@@ -5349,7 +5400,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>260010</v>
+        <v>240020</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>8</v>
@@ -5387,7 +5438,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>270020</v>
+        <v>240010</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>8</v>
@@ -5425,7 +5476,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>270010</v>
+        <v>250020</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>8</v>
@@ -5463,7 +5514,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>280020</v>
+        <v>250010</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>8</v>
@@ -5501,7 +5552,7 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>280010</v>
+        <v>260020</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>8</v>
@@ -5539,7 +5590,7 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>290020</v>
+        <v>260010</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>8</v>
@@ -5577,7 +5628,7 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>290010</v>
+        <v>270020</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>8</v>
@@ -5615,7 +5666,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>300020</v>
+        <v>270010</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>8</v>
@@ -5653,7 +5704,7 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>300010</v>
+        <v>280020</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>8</v>
@@ -5691,22 +5742,22 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>300001</v>
-      </c>
-      <c r="C127" s="2">
-        <v>0</v>
+        <v>280010</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
       </c>
-      <c r="G127" s="2" t="s">
-        <v>77</v>
+      <c r="G127" s="2">
+        <v>0</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>13</v>
@@ -5715,30 +5766,30 @@
         <v>15</v>
       </c>
       <c r="J127" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K127" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L127" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>300002</v>
-      </c>
-      <c r="C128" s="2">
-        <v>0</v>
+        <v>290020</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -5750,33 +5801,33 @@
         <v>13</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J128" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K128" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L128" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>300003</v>
-      </c>
-      <c r="C129" s="2">
-        <v>0</v>
+        <v>290010</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -5788,39 +5839,39 @@
         <v>13</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="J129" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K129" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L129" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>300004</v>
-      </c>
-      <c r="C130" s="2">
-        <v>0</v>
+        <v>300020</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
       </c>
-      <c r="G130" s="2" t="s">
-        <v>56</v>
+      <c r="G130" s="2">
+        <v>0</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>13</v>
@@ -5829,36 +5880,36 @@
         <v>15</v>
       </c>
       <c r="J130" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K130" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L130" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>300005</v>
-      </c>
-      <c r="C131" s="2">
-        <v>0</v>
+        <v>300010</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
       </c>
-      <c r="G131" s="2" t="s">
-        <v>66</v>
+      <c r="G131" s="2">
+        <v>0</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>13</v>
@@ -5867,21 +5918,21 @@
         <v>15</v>
       </c>
       <c r="J131" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K131" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L131" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>300006</v>
+        <v>300001</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
@@ -5890,25 +5941,25 @@
         <v>13</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
       </c>
-      <c r="G132" s="2">
-        <v>0</v>
+      <c r="G132" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J132" s="7">
         <v>5</v>
       </c>
       <c r="K132" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L132" s="7">
         <v>1</v>
@@ -5919,7 +5970,7 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>300007</v>
+        <v>300002</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
@@ -5928,7 +5979,7 @@
         <v>13</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -5940,24 +5991,24 @@
         <v>13</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="J133" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K133" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L133" s="7">
         <v>1</v>
       </c>
       <c r="M133" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>300008</v>
+        <v>300003</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
@@ -5966,36 +6017,36 @@
         <v>13</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>81</v>
+      <c r="G134" s="2">
+        <v>0</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="J134" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K134" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L134" s="7">
         <v>1</v>
       </c>
       <c r="M134" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>300009</v>
+        <v>300004</v>
       </c>
       <c r="C135" s="2">
         <v>0</v>
@@ -6004,36 +6055,36 @@
         <v>13</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
       </c>
-      <c r="G135" s="2">
-        <v>0</v>
+      <c r="G135" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="J135" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K135" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L135" s="7">
         <v>1</v>
       </c>
       <c r="M135" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>300011</v>
+        <v>300005</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
@@ -6042,13 +6093,13 @@
         <v>13</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>13</v>
@@ -6066,12 +6117,12 @@
         <v>1</v>
       </c>
       <c r="M136" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>300012</v>
+        <v>300006</v>
       </c>
       <c r="C137" s="2">
         <v>0</v>
@@ -6080,36 +6131,36 @@
         <v>13</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
       </c>
-      <c r="G137" s="2" t="s">
-        <v>85</v>
+      <c r="G137" s="2">
+        <v>0</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J137" s="7">
         <v>5</v>
       </c>
       <c r="K137" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L137" s="7">
         <v>1</v>
       </c>
       <c r="M137" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>300013</v>
+        <v>300007</v>
       </c>
       <c r="C138" s="2">
         <v>0</v>
@@ -6118,7 +6169,7 @@
         <v>13</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6130,39 +6181,39 @@
         <v>13</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="J138" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K138" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L138" s="7">
         <v>1</v>
       </c>
       <c r="M138" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>310020</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>8</v>
+        <v>300008</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
       </c>
-      <c r="G139" s="2">
-        <v>0</v>
+      <c r="G139" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>13</v>
@@ -6171,30 +6222,30 @@
         <v>15</v>
       </c>
       <c r="J139" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K139" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L139" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>310010</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>8</v>
+        <v>300009</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -6206,39 +6257,39 @@
         <v>13</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="J140" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K140" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L140" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>320020</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>8</v>
+        <v>300011</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
       </c>
-      <c r="G141" s="2">
-        <v>0</v>
+      <c r="G141" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>13</v>
@@ -6247,36 +6298,36 @@
         <v>15</v>
       </c>
       <c r="J141" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K141" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L141" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>320010</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>8</v>
+        <v>300012</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
       </c>
-      <c r="G142" s="2">
-        <v>0</v>
+      <c r="G142" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>13</v>
@@ -6285,30 +6336,30 @@
         <v>15</v>
       </c>
       <c r="J142" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K142" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L142" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>330020</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>8</v>
+        <v>300013</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -6320,24 +6371,24 @@
         <v>13</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J143" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K143" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L143" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>330010</v>
+        <v>310020</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>8</v>
@@ -6375,7 +6426,7 @@
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>340020</v>
+        <v>310010</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>8</v>
@@ -6413,7 +6464,7 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>340010</v>
+        <v>320020</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>8</v>
@@ -6451,7 +6502,7 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>350020</v>
+        <v>320010</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>8</v>
@@ -6489,7 +6540,7 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>350010</v>
+        <v>330020</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>8</v>
@@ -6527,7 +6578,7 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>360020</v>
+        <v>330010</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>8</v>
@@ -6565,7 +6616,7 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>360010</v>
+        <v>340020</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>8</v>
@@ -6603,7 +6654,7 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>370020</v>
+        <v>340010</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>8</v>
@@ -6641,7 +6692,7 @@
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>370010</v>
+        <v>350020</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>8</v>
@@ -6679,7 +6730,7 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>380020</v>
+        <v>350010</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>8</v>
@@ -6717,7 +6768,7 @@
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>380010</v>
+        <v>360020</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>8</v>
@@ -6755,7 +6806,7 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>390020</v>
+        <v>360010</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>8</v>
@@ -6793,7 +6844,7 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>390010</v>
+        <v>370020</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>8</v>
@@ -6831,7 +6882,7 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>400020</v>
+        <v>370010</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>8</v>
@@ -6869,7 +6920,7 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>400010</v>
+        <v>380020</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>8</v>
@@ -6907,7 +6958,7 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>410020</v>
+        <v>380010</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>8</v>
@@ -6945,7 +6996,7 @@
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>410010</v>
+        <v>390020</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>8</v>
@@ -6983,7 +7034,7 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>420020</v>
+        <v>390010</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>8</v>
@@ -7021,7 +7072,7 @@
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>420010</v>
+        <v>400020</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>8</v>
@@ -7059,7 +7110,7 @@
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>430020</v>
+        <v>400010</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>8</v>
@@ -7097,7 +7148,7 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>430010</v>
+        <v>410020</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>8</v>
@@ -7135,7 +7186,7 @@
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>440020</v>
+        <v>410010</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>8</v>
@@ -7173,7 +7224,7 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>440010</v>
+        <v>420020</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>8</v>
@@ -7211,7 +7262,7 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>450020</v>
+        <v>420010</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>8</v>
@@ -7249,7 +7300,7 @@
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>450010</v>
+        <v>430020</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>8</v>
@@ -7287,7 +7338,7 @@
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>460020</v>
+        <v>430010</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>8</v>
@@ -7325,7 +7376,7 @@
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>460010</v>
+        <v>440020</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>8</v>
@@ -7363,7 +7414,7 @@
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>470020</v>
+        <v>440010</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>8</v>
@@ -7401,7 +7452,7 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>470010</v>
+        <v>450020</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>8</v>
@@ -7439,7 +7490,7 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>480020</v>
+        <v>450010</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>8</v>
@@ -7477,7 +7528,7 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>480010</v>
+        <v>460020</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>8</v>
@@ -7515,7 +7566,7 @@
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>490020</v>
+        <v>460010</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>8</v>
@@ -7553,7 +7604,7 @@
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>490010</v>
+        <v>470020</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>8</v>
@@ -7591,7 +7642,7 @@
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>500020</v>
+        <v>470010</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>8</v>
@@ -7629,7 +7680,7 @@
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>500010</v>
+        <v>480020</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>8</v>
@@ -7667,7 +7718,7 @@
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>510020</v>
+        <v>480010</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>8</v>
@@ -7705,7 +7756,7 @@
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>510010</v>
+        <v>490020</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>8</v>
@@ -7743,7 +7794,7 @@
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>520020</v>
+        <v>490010</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>8</v>
@@ -7781,7 +7832,7 @@
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>520010</v>
+        <v>500020</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>8</v>
@@ -7819,7 +7870,7 @@
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>530020</v>
+        <v>500010</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>8</v>
@@ -7857,7 +7908,7 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>530010</v>
+        <v>510020</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>8</v>
@@ -7895,7 +7946,7 @@
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>540020</v>
+        <v>510010</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>8</v>
@@ -7933,7 +7984,7 @@
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>540010</v>
+        <v>520020</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>8</v>
@@ -7971,7 +8022,7 @@
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>550020</v>
+        <v>520010</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>8</v>
@@ -8009,7 +8060,7 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>550010</v>
+        <v>530020</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>8</v>
@@ -8047,7 +8098,7 @@
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>560020</v>
+        <v>530010</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>8</v>
@@ -8085,7 +8136,7 @@
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>560010</v>
+        <v>540020</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>8</v>
@@ -8123,7 +8174,7 @@
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>570020</v>
+        <v>540010</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>8</v>
@@ -8161,7 +8212,7 @@
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>570010</v>
+        <v>550020</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>8</v>
@@ -8199,7 +8250,7 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>580020</v>
+        <v>550010</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>8</v>
@@ -8237,7 +8288,7 @@
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>580010</v>
+        <v>560020</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>8</v>
@@ -8275,7 +8326,7 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>590020</v>
+        <v>560010</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>8</v>
@@ -8313,7 +8364,7 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>590010</v>
+        <v>570020</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>8</v>
@@ -8351,7 +8402,7 @@
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>600020</v>
+        <v>570010</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>8</v>
@@ -8389,7 +8440,7 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>600010</v>
+        <v>580020</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>8</v>
@@ -8427,7 +8478,7 @@
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>610020</v>
+        <v>580010</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>8</v>
@@ -8465,7 +8516,7 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>610010</v>
+        <v>590020</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>8</v>
@@ -8503,7 +8554,7 @@
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>620020</v>
+        <v>590010</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>8</v>
@@ -8541,7 +8592,7 @@
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>620010</v>
+        <v>600020</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>8</v>
@@ -8579,7 +8630,7 @@
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>630020</v>
+        <v>600010</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>8</v>
@@ -8617,7 +8668,7 @@
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>630010</v>
+        <v>610020</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>8</v>
@@ -8655,7 +8706,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>640020</v>
+        <v>610010</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>8</v>
@@ -8693,7 +8744,7 @@
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>640010</v>
+        <v>620020</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>8</v>
@@ -8731,7 +8782,7 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>650020</v>
+        <v>620010</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>8</v>
@@ -8769,7 +8820,7 @@
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>650010</v>
+        <v>630020</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>8</v>
@@ -8807,7 +8858,7 @@
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>660020</v>
+        <v>630010</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>8</v>
@@ -8845,7 +8896,7 @@
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>660010</v>
+        <v>640020</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>8</v>
@@ -8883,7 +8934,7 @@
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>670020</v>
+        <v>640010</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>8</v>
@@ -8921,7 +8972,7 @@
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>670010</v>
+        <v>650020</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>8</v>
@@ -8959,7 +9010,7 @@
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>680020</v>
+        <v>650010</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>8</v>
@@ -8997,7 +9048,7 @@
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>680010</v>
+        <v>660020</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>8</v>
@@ -9035,7 +9086,7 @@
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>690020</v>
+        <v>660010</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>8</v>
@@ -9073,7 +9124,7 @@
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>690010</v>
+        <v>670020</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>8</v>
@@ -9111,7 +9162,7 @@
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>700020</v>
+        <v>670010</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>8</v>
@@ -9149,7 +9200,7 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>700010</v>
+        <v>680020</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>8</v>
@@ -9187,7 +9238,7 @@
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>710020</v>
+        <v>680010</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
@@ -9225,7 +9276,7 @@
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>710010</v>
+        <v>690020</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>8</v>
@@ -9263,7 +9314,7 @@
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>720020</v>
+        <v>690010</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>8</v>
@@ -9301,7 +9352,7 @@
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>720010</v>
+        <v>700020</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>8</v>
@@ -9339,7 +9390,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>730020</v>
+        <v>700010</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>8</v>
@@ -9377,7 +9428,7 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>730010</v>
+        <v>710020</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>8</v>
@@ -9415,7 +9466,7 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>740020</v>
+        <v>710010</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
@@ -9453,7 +9504,7 @@
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>740010</v>
+        <v>720020</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
@@ -9491,7 +9542,7 @@
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>750020</v>
+        <v>720010</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>8</v>
@@ -9529,7 +9580,7 @@
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>750010</v>
+        <v>730020</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
@@ -9567,7 +9618,7 @@
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>760020</v>
+        <v>730010</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>8</v>
@@ -9605,7 +9656,7 @@
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>760010</v>
+        <v>740020</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
@@ -9643,7 +9694,7 @@
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>770020</v>
+        <v>740010</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>8</v>
@@ -9681,7 +9732,7 @@
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>770010</v>
+        <v>750020</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -9719,7 +9770,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>780020</v>
+        <v>750010</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>8</v>
@@ -9757,7 +9808,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>780010</v>
+        <v>760020</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>8</v>
@@ -9795,7 +9846,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>790020</v>
+        <v>760010</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>8</v>
@@ -9833,7 +9884,7 @@
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>790010</v>
+        <v>770020</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>8</v>
@@ -9871,7 +9922,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>800020</v>
+        <v>770010</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>8</v>
@@ -9909,7 +9960,7 @@
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>800010</v>
+        <v>780020</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>8</v>
@@ -9947,7 +9998,7 @@
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>810020</v>
+        <v>780010</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>8</v>
@@ -9985,7 +10036,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>810010</v>
+        <v>790020</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -10023,7 +10074,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>820020</v>
+        <v>790010</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>8</v>
@@ -10061,7 +10112,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>820010</v>
+        <v>800020</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -10099,7 +10150,7 @@
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>830020</v>
+        <v>800010</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -10137,7 +10188,7 @@
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>830010</v>
+        <v>810020</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -10175,7 +10226,7 @@
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>840020</v>
+        <v>810010</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -10213,7 +10264,7 @@
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>840010</v>
+        <v>820020</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -10251,7 +10302,7 @@
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>850020</v>
+        <v>820010</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -10289,7 +10340,7 @@
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>850010</v>
+        <v>830020</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>8</v>
@@ -10327,7 +10378,7 @@
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>860020</v>
+        <v>830010</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -10365,7 +10416,7 @@
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>860010</v>
+        <v>840020</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>8</v>
@@ -10403,7 +10454,7 @@
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>870020</v>
+        <v>840010</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
@@ -10441,7 +10492,7 @@
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>870010</v>
+        <v>850020</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -10479,7 +10530,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>880020</v>
+        <v>850010</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
@@ -10517,7 +10568,7 @@
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>880010</v>
+        <v>860020</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>8</v>
@@ -10555,7 +10606,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>890020</v>
+        <v>860010</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>8</v>
@@ -10593,7 +10644,7 @@
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>890010</v>
+        <v>870020</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -10631,7 +10682,7 @@
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>900020</v>
+        <v>870010</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -10669,7 +10720,7 @@
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>900010</v>
+        <v>880020</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -10707,7 +10758,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>910020</v>
+        <v>880010</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -10745,7 +10796,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>910010</v>
+        <v>890020</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
@@ -10783,7 +10834,7 @@
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>920020</v>
+        <v>890010</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
@@ -10821,7 +10872,7 @@
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>920010</v>
+        <v>900020</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>8</v>
@@ -10859,7 +10910,7 @@
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>930020</v>
+        <v>900010</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
@@ -10897,7 +10948,7 @@
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>930010</v>
+        <v>910020</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -10935,7 +10986,7 @@
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>940020</v>
+        <v>910010</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -10973,7 +11024,7 @@
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>940010</v>
+        <v>920020</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -11011,7 +11062,7 @@
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>950020</v>
+        <v>920010</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -11049,7 +11100,7 @@
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>950010</v>
+        <v>930020</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -11087,7 +11138,7 @@
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>960020</v>
+        <v>930010</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
@@ -11125,7 +11176,7 @@
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>960010</v>
+        <v>940020</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -11163,7 +11214,7 @@
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>970020</v>
+        <v>940010</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>8</v>
@@ -11201,7 +11252,7 @@
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>970010</v>
+        <v>950020</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -11239,7 +11290,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>980020</v>
+        <v>950010</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -11277,7 +11328,7 @@
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>980010</v>
+        <v>960020</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -11315,7 +11366,7 @@
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>990020</v>
+        <v>960010</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>8</v>
@@ -11353,7 +11404,7 @@
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>990010</v>
+        <v>970020</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>8</v>
@@ -11391,7 +11442,7 @@
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1000020</v>
+        <v>970010</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -11429,7 +11480,7 @@
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1000010</v>
+        <v>980020</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -11467,7 +11518,7 @@
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1010020</v>
+        <v>980010</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>8</v>
@@ -11505,7 +11556,7 @@
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1010010</v>
+        <v>990020</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>8</v>
@@ -11543,7 +11594,7 @@
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1020020</v>
+        <v>990010</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>8</v>
@@ -11581,7 +11632,7 @@
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1020010</v>
+        <v>1000020</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>8</v>
@@ -11619,7 +11670,7 @@
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1030020</v>
+        <v>1000010</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -11657,7 +11708,7 @@
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1030010</v>
+        <v>1010020</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -11695,7 +11746,7 @@
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1040020</v>
+        <v>1010010</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -11733,7 +11784,7 @@
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1040010</v>
+        <v>1020020</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -11771,7 +11822,7 @@
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1050020</v>
+        <v>1020010</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -11809,7 +11860,7 @@
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1050010</v>
+        <v>1030020</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -11847,7 +11898,7 @@
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1060020</v>
+        <v>1030010</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -11885,7 +11936,7 @@
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1060010</v>
+        <v>1040020</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -11923,7 +11974,7 @@
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1070020</v>
+        <v>1040010</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -11961,7 +12012,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1070010</v>
+        <v>1050020</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -11999,7 +12050,7 @@
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1080020</v>
+        <v>1050010</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>8</v>
@@ -12037,7 +12088,7 @@
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1080010</v>
+        <v>1060020</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>8</v>
@@ -12075,7 +12126,7 @@
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1090020</v>
+        <v>1060010</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>8</v>
@@ -12113,7 +12164,7 @@
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1090010</v>
+        <v>1070020</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -12151,7 +12202,7 @@
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1100020</v>
+        <v>1070010</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -12189,7 +12240,7 @@
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1100010</v>
+        <v>1080020</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -12227,7 +12278,7 @@
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1110020</v>
+        <v>1080010</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -12265,7 +12316,7 @@
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1110010</v>
+        <v>1090020</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>8</v>
@@ -12303,7 +12354,7 @@
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1120020</v>
+        <v>1090010</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -12341,7 +12392,7 @@
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1120010</v>
+        <v>1100020</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>8</v>
@@ -12379,7 +12430,7 @@
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1130020</v>
+        <v>1100010</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>8</v>
@@ -12417,7 +12468,7 @@
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1130010</v>
+        <v>1110020</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>8</v>
@@ -12455,7 +12506,7 @@
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1140020</v>
+        <v>1110010</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -12493,7 +12544,7 @@
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1140010</v>
+        <v>1120020</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>8</v>
@@ -12531,7 +12582,7 @@
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1150020</v>
+        <v>1120010</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -12569,7 +12620,7 @@
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1150010</v>
+        <v>1130020</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>8</v>
@@ -12607,7 +12658,7 @@
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1160020</v>
+        <v>1130010</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>8</v>
@@ -12645,7 +12696,7 @@
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1160010</v>
+        <v>1140020</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>8</v>
@@ -12683,7 +12734,7 @@
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1170020</v>
+        <v>1140010</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>8</v>
@@ -12721,7 +12772,7 @@
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1170010</v>
+        <v>1150020</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>8</v>
@@ -12759,7 +12810,7 @@
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1180020</v>
+        <v>1150010</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>8</v>
@@ -12797,7 +12848,7 @@
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1180010</v>
+        <v>1160020</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>8</v>
@@ -12835,7 +12886,7 @@
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1190020</v>
+        <v>1160010</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -12873,7 +12924,7 @@
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1190010</v>
+        <v>1170020</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -12911,7 +12962,7 @@
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1200020</v>
+        <v>1170010</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -12949,7 +13000,7 @@
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1200010</v>
+        <v>1180020</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -12987,7 +13038,7 @@
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1210020</v>
+        <v>1180010</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -13025,7 +13076,7 @@
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1210010</v>
+        <v>1190020</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>8</v>
@@ -13063,7 +13114,7 @@
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1220020</v>
+        <v>1190010</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>8</v>
@@ -13101,7 +13152,7 @@
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1220010</v>
+        <v>1200020</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -13139,7 +13190,7 @@
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1230020</v>
+        <v>1200010</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>8</v>
@@ -13177,7 +13228,7 @@
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1230010</v>
+        <v>1210020</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>8</v>
@@ -13215,7 +13266,7 @@
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1240020</v>
+        <v>1210010</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -13253,7 +13304,7 @@
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1240010</v>
+        <v>1220020</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -13291,7 +13342,7 @@
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1250020</v>
+        <v>1220010</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -13329,7 +13380,7 @@
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1250010</v>
+        <v>1230020</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -13367,7 +13418,7 @@
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1260020</v>
+        <v>1230010</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -13405,7 +13456,7 @@
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1260010</v>
+        <v>1240020</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>8</v>
@@ -13443,7 +13494,7 @@
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1270020</v>
+        <v>1240010</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -13481,7 +13532,7 @@
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1270010</v>
+        <v>1250020</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -13519,7 +13570,7 @@
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1280020</v>
+        <v>1250010</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>8</v>
@@ -13557,7 +13608,7 @@
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1280010</v>
+        <v>1260020</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -13595,7 +13646,7 @@
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1290020</v>
+        <v>1260010</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>8</v>
@@ -13633,7 +13684,7 @@
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1290010</v>
+        <v>1270020</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -13671,7 +13722,7 @@
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1300020</v>
+        <v>1270010</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -13709,7 +13760,7 @@
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1300010</v>
+        <v>1280020</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>8</v>
@@ -13747,7 +13798,7 @@
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1310020</v>
+        <v>1280010</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -13785,7 +13836,7 @@
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>1310010</v>
+        <v>1290020</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -13823,7 +13874,7 @@
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>1320020</v>
+        <v>1290010</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -13861,7 +13912,7 @@
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>1320010</v>
+        <v>1300020</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>8</v>
@@ -13899,7 +13950,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>1330020</v>
+        <v>1300010</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
@@ -13937,7 +13988,7 @@
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>1330010</v>
+        <v>1310020</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
@@ -13975,7 +14026,7 @@
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>1340020</v>
+        <v>1310010</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>8</v>
@@ -14013,7 +14064,7 @@
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>1340010</v>
+        <v>1320020</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>8</v>
@@ -14051,7 +14102,7 @@
     </row>
     <row r="347" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>1350020</v>
+        <v>1320010</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>8</v>
@@ -14089,7 +14140,7 @@
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>1350010</v>
+        <v>1330020</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>8</v>
@@ -14127,7 +14178,7 @@
     </row>
     <row r="349" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>1360020</v>
+        <v>1330010</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>8</v>
@@ -14165,7 +14216,7 @@
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>1360010</v>
+        <v>1340020</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>8</v>
@@ -14203,7 +14254,7 @@
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>1370020</v>
+        <v>1340010</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>8</v>
@@ -14241,7 +14292,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>1370010</v>
+        <v>1350020</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -14279,7 +14330,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>1380020</v>
+        <v>1350010</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -14317,7 +14368,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>1380010</v>
+        <v>1360020</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -14355,7 +14406,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>1390020</v>
+        <v>1360010</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -14393,7 +14444,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>1390010</v>
+        <v>1370020</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -14431,7 +14482,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>1400020</v>
+        <v>1370010</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -14469,7 +14520,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>1400010</v>
+        <v>1380020</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -14507,7 +14558,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>1410020</v>
+        <v>1380010</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -14545,7 +14596,7 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>1410010</v>
+        <v>1390020</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -14583,7 +14634,7 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>1420020</v>
+        <v>1390010</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
@@ -14621,7 +14672,7 @@
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>1420010</v>
+        <v>1400020</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -14659,7 +14710,7 @@
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>1430020</v>
+        <v>1400010</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>8</v>
@@ -14697,7 +14748,7 @@
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>1430010</v>
+        <v>1410020</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -14735,7 +14786,7 @@
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>1440020</v>
+        <v>1410010</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>8</v>
@@ -14773,7 +14824,7 @@
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>1440010</v>
+        <v>1420020</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>8</v>
@@ -14811,7 +14862,7 @@
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>1450020</v>
+        <v>1420010</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>8</v>
@@ -14849,7 +14900,7 @@
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>1450010</v>
+        <v>1430020</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -14887,7 +14938,7 @@
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>1460020</v>
+        <v>1430010</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>8</v>
@@ -14925,7 +14976,7 @@
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>1460010</v>
+        <v>1440020</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>8</v>
@@ -14963,7 +15014,7 @@
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>1470020</v>
+        <v>1440010</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>8</v>
@@ -15001,7 +15052,7 @@
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>1470010</v>
+        <v>1450020</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
@@ -15039,7 +15090,7 @@
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>1480020</v>
+        <v>1450010</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>8</v>
@@ -15077,7 +15128,7 @@
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>1480010</v>
+        <v>1460020</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>8</v>
@@ -15115,7 +15166,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>1490020</v>
+        <v>1460010</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>8</v>
@@ -15153,7 +15204,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>1490010</v>
+        <v>1470020</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>8</v>
@@ -15191,7 +15242,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>1500020</v>
+        <v>1470010</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>8</v>
@@ -15229,7 +15280,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>1500010</v>
+        <v>1480020</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>8</v>
@@ -15267,7 +15318,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>1510020</v>
+        <v>1480010</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>8</v>
@@ -15305,7 +15356,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>1510010</v>
+        <v>1490020</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>8</v>
@@ -15343,7 +15394,7 @@
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>1520020</v>
+        <v>1490010</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>8</v>
@@ -15381,7 +15432,7 @@
     </row>
     <row r="382" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>1520010</v>
+        <v>1500020</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>8</v>
@@ -15419,7 +15470,7 @@
     </row>
     <row r="383" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>1530020</v>
+        <v>1500010</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>8</v>
@@ -15457,7 +15508,7 @@
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>1530010</v>
+        <v>1510020</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>8</v>
@@ -15495,7 +15546,7 @@
     </row>
     <row r="385" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>1540020</v>
+        <v>1510010</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>8</v>
@@ -15533,7 +15584,7 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>1540010</v>
+        <v>1520020</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>8</v>
@@ -15571,7 +15622,7 @@
     </row>
     <row r="387" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>1550020</v>
+        <v>1520010</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>8</v>
@@ -15609,7 +15660,7 @@
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>1550010</v>
+        <v>1530020</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>8</v>
@@ -15647,7 +15698,7 @@
     </row>
     <row r="389" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>1560020</v>
+        <v>1530010</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>8</v>
@@ -15685,7 +15736,7 @@
     </row>
     <row r="390" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>1560010</v>
+        <v>1540020</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>8</v>
@@ -15723,7 +15774,7 @@
     </row>
     <row r="391" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>1570020</v>
+        <v>1540010</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>8</v>
@@ -15761,7 +15812,7 @@
     </row>
     <row r="392" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>1570010</v>
+        <v>1550020</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>8</v>
@@ -15799,7 +15850,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>1580020</v>
+        <v>1550010</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>8</v>
@@ -15837,7 +15888,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>1580010</v>
+        <v>1560020</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>8</v>
@@ -15875,7 +15926,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>1590020</v>
+        <v>1560010</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>8</v>
@@ -15913,7 +15964,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>1590010</v>
+        <v>1570020</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>8</v>
@@ -15951,7 +16002,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>1600020</v>
+        <v>1570010</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>8</v>
@@ -15989,39 +16040,229 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
+        <v>1580020</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E398" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F398" s="1">
+        <v>0</v>
+      </c>
+      <c r="G398" s="2">
+        <v>0</v>
+      </c>
+      <c r="H398" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I398" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J398" s="7">
+        <v>0</v>
+      </c>
+      <c r="K398" s="7">
+        <v>0</v>
+      </c>
+      <c r="L398" s="7">
+        <v>0</v>
+      </c>
+      <c r="M398" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A399" s="1">
+        <v>1580010</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E399" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F399" s="1">
+        <v>0</v>
+      </c>
+      <c r="G399" s="2">
+        <v>0</v>
+      </c>
+      <c r="H399" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I399" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J399" s="7">
+        <v>0</v>
+      </c>
+      <c r="K399" s="7">
+        <v>0</v>
+      </c>
+      <c r="L399" s="7">
+        <v>0</v>
+      </c>
+      <c r="M399" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A400" s="1">
+        <v>1590020</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E400" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F400" s="1">
+        <v>0</v>
+      </c>
+      <c r="G400" s="2">
+        <v>0</v>
+      </c>
+      <c r="H400" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I400" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J400" s="7">
+        <v>0</v>
+      </c>
+      <c r="K400" s="7">
+        <v>0</v>
+      </c>
+      <c r="L400" s="7">
+        <v>0</v>
+      </c>
+      <c r="M400" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A401" s="1">
+        <v>1590010</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E401" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F401" s="1">
+        <v>0</v>
+      </c>
+      <c r="G401" s="2">
+        <v>0</v>
+      </c>
+      <c r="H401" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I401" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J401" s="7">
+        <v>0</v>
+      </c>
+      <c r="K401" s="7">
+        <v>0</v>
+      </c>
+      <c r="L401" s="7">
+        <v>0</v>
+      </c>
+      <c r="M401" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A402" s="1">
+        <v>1600020</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E402" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F402" s="1">
+        <v>0</v>
+      </c>
+      <c r="G402" s="2">
+        <v>0</v>
+      </c>
+      <c r="H402" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I402" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J402" s="7">
+        <v>0</v>
+      </c>
+      <c r="K402" s="7">
+        <v>0</v>
+      </c>
+      <c r="L402" s="7">
+        <v>0</v>
+      </c>
+      <c r="M402" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A403" s="1">
         <v>1600010</v>
       </c>
-      <c r="C398" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E398" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F398" s="1">
-        <v>0</v>
-      </c>
-      <c r="G398" s="2">
-        <v>0</v>
-      </c>
-      <c r="H398" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I398" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J398" s="7">
-        <v>0</v>
-      </c>
-      <c r="K398" s="7">
-        <v>0</v>
-      </c>
-      <c r="L398" s="7">
-        <v>0</v>
-      </c>
-      <c r="M398" s="7">
+      <c r="C403" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F403" s="1">
+        <v>0</v>
+      </c>
+      <c r="G403" s="2">
+        <v>0</v>
+      </c>
+      <c r="H403" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I403" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J403" s="7">
+        <v>0</v>
+      </c>
+      <c r="K403" s="7">
+        <v>0</v>
+      </c>
+      <c r="L403" s="7">
+        <v>0</v>
+      </c>
+      <c r="M403" s="7">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113CCDBD-84DE-45D3-B15D-C617182E82DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC3C9C5-AB8E-4F1F-86CE-C8EED4EE76C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="107">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,25 +152,10 @@
     <t>46700001:6</t>
   </si>
   <si>
-    <t>46700001:7</t>
-  </si>
-  <si>
     <t>46700001:12</t>
   </si>
   <si>
     <t>46700001:8</t>
-  </si>
-  <si>
-    <t>46200001:60</t>
-  </si>
-  <si>
-    <t>46700001:13</t>
-  </si>
-  <si>
-    <t>46700001:10</t>
-  </si>
-  <si>
-    <t>46200001:80</t>
   </si>
   <si>
     <t>add_kongfu</t>
@@ -459,6 +444,30 @@
   </si>
   <si>
     <t>第7关强化石3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -890,10 +899,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
@@ -902,16 +911,16 @@
         <v>12</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.15">
@@ -925,34 +934,34 @@
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
@@ -963,37 +972,37 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="J4" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="M4" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
@@ -1001,7 +1010,7 @@
         <v>10001</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -1010,7 +1019,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
@@ -1022,7 +1031,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -1042,7 +1051,7 @@
         <v>10002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -1051,7 +1060,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -1063,7 +1072,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -1083,7 +1092,7 @@
         <v>10003</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
@@ -1092,7 +1101,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -1104,7 +1113,7 @@
         <v>13</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J7" s="7">
         <v>0</v>
@@ -1124,7 +1133,7 @@
         <v>10004</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -1133,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -1145,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J8" s="7">
         <v>0</v>
@@ -1165,7 +1174,7 @@
         <v>10005</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -1174,7 +1183,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -1186,7 +1195,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -1206,7 +1215,7 @@
         <v>10006</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
@@ -1215,7 +1224,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -1227,7 +1236,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J10" s="7">
         <v>0</v>
@@ -1247,7 +1256,7 @@
         <v>10007</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
@@ -1256,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1268,7 +1277,7 @@
         <v>13</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J11" s="7">
         <v>0</v>
@@ -1288,7 +1297,7 @@
         <v>10008</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -1297,7 +1306,7 @@
         <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1309,7 +1318,7 @@
         <v>13</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J12" s="7">
         <v>0</v>
@@ -1329,7 +1338,7 @@
         <v>10009</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -1338,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
@@ -1350,7 +1359,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J13" s="7">
         <v>0</v>
@@ -1369,6 +1378,9 @@
       <c r="A14" s="1">
         <v>10020</v>
       </c>
+      <c r="B14" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="C14" s="2">
         <v>0</v>
       </c>
@@ -1388,7 +1400,7 @@
         <v>13</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
@@ -1407,6 +1419,9 @@
       <c r="A15" s="1">
         <v>10010</v>
       </c>
+      <c r="B15" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
@@ -1414,7 +1429,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1426,7 +1441,7 @@
         <v>13</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="J15" s="7">
         <v>0</v>
@@ -1446,7 +1461,7 @@
         <v>10011</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -1455,13 +1470,13 @@
         <v>13</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1">
-        <v>30</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -1470,22 +1485,25 @@
         <v>15</v>
       </c>
       <c r="J16" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>20020</v>
       </c>
+      <c r="B17" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
@@ -1505,7 +1523,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J17" s="7">
         <v>0</v>
@@ -1524,6 +1542,9 @@
       <c r="A18" s="1">
         <v>20010</v>
       </c>
+      <c r="B18" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
@@ -1531,7 +1552,7 @@
         <v>13</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1543,7 +1564,7 @@
         <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="J18" s="7">
         <v>0</v>
@@ -1563,7 +1584,7 @@
         <v>20001</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -1572,13 +1593,13 @@
         <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1">
-        <v>30</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -1587,16 +1608,16 @@
         <v>15</v>
       </c>
       <c r="J19" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.15">
@@ -1648,7 +1669,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1680,7 +1701,7 @@
         <v>30001</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -1689,13 +1710,13 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1">
-        <v>30</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -1704,16 +1725,16 @@
         <v>15</v>
       </c>
       <c r="J22" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.15">
@@ -1721,7 +1742,7 @@
         <v>30002</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
@@ -1730,13 +1751,13 @@
         <v>13</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1">
-        <v>30</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -1745,16 +1766,16 @@
         <v>15</v>
       </c>
       <c r="J23" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.15">
@@ -1806,7 +1827,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1838,7 +1859,7 @@
         <v>40001</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1847,13 +1868,13 @@
         <v>13</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1">
-        <v>30</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -1862,16 +1883,16 @@
         <v>15</v>
       </c>
       <c r="J26" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.15">
@@ -1879,7 +1900,7 @@
         <v>40002</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -1888,13 +1909,13 @@
         <v>13</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1">
-        <v>30</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -1903,16 +1924,16 @@
         <v>15</v>
       </c>
       <c r="J27" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K27" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1964,7 +1985,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1996,7 +2017,7 @@
         <v>40001</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -2005,13 +2026,13 @@
         <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1">
-        <v>30</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>42</v>
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -2020,16 +2041,16 @@
         <v>15</v>
       </c>
       <c r="J30" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K30" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.15">
@@ -2037,7 +2058,7 @@
         <v>50002</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -2046,7 +2067,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2078,7 +2099,7 @@
         <v>50003</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -2087,7 +2108,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2163,7 +2184,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2195,7 +2216,7 @@
         <v>60001</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -2236,7 +2257,7 @@
         <v>60002</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -2277,7 +2298,7 @@
         <v>60003</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -2286,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2318,7 +2339,7 @@
         <v>60004</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -2327,7 +2348,7 @@
         <v>13</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2359,7 +2380,7 @@
         <v>60005</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -2400,7 +2421,7 @@
         <v>60006</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2409,7 +2430,7 @@
         <v>13</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2485,7 +2506,7 @@
         <v>13</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2517,7 +2538,7 @@
         <v>70001</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -2526,13 +2547,13 @@
         <v>13</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>69</v>
+      <c r="G43" s="2">
+        <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
@@ -2558,7 +2579,7 @@
         <v>70002</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -2567,7 +2588,7 @@
         <v>13</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2599,7 +2620,7 @@
         <v>70003</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -2608,7 +2629,7 @@
         <v>13</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2620,7 +2641,7 @@
         <v>13</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J45" s="7">
         <v>4</v>
@@ -2640,7 +2661,7 @@
         <v>70004</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -2649,13 +2670,13 @@
         <v>13</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>48</v>
+      <c r="G46" s="2">
+        <v>0</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
@@ -2681,7 +2702,7 @@
         <v>70005</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -2695,8 +2716,8 @@
       <c r="F47" s="1">
         <v>0</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>58</v>
+      <c r="G47" s="2">
+        <v>0</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -2722,7 +2743,7 @@
         <v>70006</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -2731,7 +2752,7 @@
         <v>13</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -2743,7 +2764,7 @@
         <v>13</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J48" s="7">
         <v>5</v>
@@ -2763,7 +2784,7 @@
         <v>70007</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -2772,7 +2793,7 @@
         <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2784,7 +2805,7 @@
         <v>13</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="J49" s="7">
         <v>4</v>
@@ -2804,7 +2825,7 @@
         <v>70008</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -2819,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -2845,7 +2866,7 @@
         <v>70009</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -2854,7 +2875,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2866,7 +2887,7 @@
         <v>13</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J51" s="7">
         <v>4</v>
@@ -2886,7 +2907,7 @@
         <v>70011</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -2901,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -2927,7 +2948,7 @@
         <v>70012</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -2942,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -2968,7 +2989,7 @@
         <v>70013</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -2977,7 +2998,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -2989,7 +3010,7 @@
         <v>13</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J54" s="7">
         <v>5</v>
@@ -3281,13 +3302,13 @@
         <v>13</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1">
         <v>30</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>13</v>
@@ -3319,7 +3340,7 @@
         <v>13</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="1">
         <v>40</v>
@@ -3331,7 +3352,7 @@
         <v>13</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J63" s="7">
         <v>4</v>
@@ -3357,13 +3378,13 @@
         <v>13</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1">
         <v>50</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>13</v>
@@ -3395,7 +3416,7 @@
         <v>13</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F65" s="1">
         <v>70</v>
@@ -3407,7 +3428,7 @@
         <v>13</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J65" s="7">
         <v>4</v>
@@ -3433,7 +3454,7 @@
         <v>13</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F66" s="1">
         <v>120</v>
@@ -3445,7 +3466,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J66" s="7">
         <v>4</v>
@@ -3471,13 +3492,13 @@
         <v>13</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F67" s="1">
         <v>150</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>13</v>
@@ -3509,13 +3530,13 @@
         <v>13</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F68" s="1">
         <v>210</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>13</v>
@@ -3547,7 +3568,7 @@
         <v>13</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F69" s="1">
         <v>250</v>
@@ -3559,7 +3580,7 @@
         <v>13</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J69" s="7">
         <v>5</v>
@@ -3585,7 +3606,7 @@
         <v>13</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F70" s="1">
         <v>400</v>
@@ -3597,7 +3618,7 @@
         <v>13</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J70" s="7">
         <v>5</v>
@@ -3623,7 +3644,7 @@
         <v>13</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F71" s="1">
         <v>500</v>
@@ -3635,7 +3656,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J71" s="7">
         <v>5</v>
@@ -3661,13 +3682,13 @@
         <v>13</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F72" s="1">
         <v>600</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>13</v>
@@ -3699,7 +3720,7 @@
         <v>13</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F73" s="1">
         <v>800</v>
@@ -3711,7 +3732,7 @@
         <v>13</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J73" s="7">
         <v>0</v>
@@ -3737,13 +3758,13 @@
         <v>13</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F74" s="1">
         <v>1000</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>13</v>
@@ -3775,7 +3796,7 @@
         <v>13</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F75" s="1">
         <v>1200</v>
@@ -3787,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J75" s="7">
         <v>0</v>
@@ -3813,7 +3834,7 @@
         <v>13</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F76" s="1">
         <v>1500</v>
@@ -3825,7 +3846,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J76" s="7">
         <v>0</v>
@@ -3851,7 +3872,7 @@
         <v>13</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F77" s="1">
         <v>1800</v>
@@ -3863,7 +3884,7 @@
         <v>13</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J77" s="7">
         <v>0</v>
@@ -3889,7 +3910,7 @@
         <v>13</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F78" s="1">
         <v>2000</v>
@@ -3901,7 +3922,7 @@
         <v>13</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J78" s="7">
         <v>0</v>
@@ -3927,13 +3948,13 @@
         <v>13</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F79" s="1">
         <v>2500</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>13</v>
@@ -3965,7 +3986,7 @@
         <v>13</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F80" s="1">
         <v>3000</v>
@@ -3977,7 +3998,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J80" s="7">
         <v>0</v>
@@ -4003,13 +4024,13 @@
         <v>13</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F81" s="1">
         <v>6000</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>13</v>
@@ -4041,7 +4062,7 @@
         <v>13</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F82" s="1">
         <v>8000</v>
@@ -4269,13 +4290,13 @@
         <v>13</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F88" s="1">
         <v>30</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>13</v>
@@ -4307,7 +4328,7 @@
         <v>13</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F89" s="1">
         <v>40</v>
@@ -4319,7 +4340,7 @@
         <v>13</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J89" s="7">
         <v>4</v>
@@ -4345,13 +4366,13 @@
         <v>13</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F90" s="1">
         <v>50</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>13</v>
@@ -4383,7 +4404,7 @@
         <v>13</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F91" s="1">
         <v>70</v>
@@ -4395,7 +4416,7 @@
         <v>13</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J91" s="7">
         <v>4</v>
@@ -4421,7 +4442,7 @@
         <v>13</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F92" s="1">
         <v>120</v>
@@ -4433,7 +4454,7 @@
         <v>13</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J92" s="7">
         <v>4</v>
@@ -4459,13 +4480,13 @@
         <v>13</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F93" s="1">
         <v>150</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>13</v>
@@ -4497,13 +4518,13 @@
         <v>13</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F94" s="1">
         <v>210</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>13</v>
@@ -4535,7 +4556,7 @@
         <v>13</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F95" s="1">
         <v>250</v>
@@ -4547,7 +4568,7 @@
         <v>13</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J95" s="7">
         <v>5</v>
@@ -4573,7 +4594,7 @@
         <v>13</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F96" s="1">
         <v>400</v>
@@ -4585,7 +4606,7 @@
         <v>13</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J96" s="7">
         <v>5</v>
@@ -4611,7 +4632,7 @@
         <v>13</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F97" s="1">
         <v>500</v>
@@ -4623,7 +4644,7 @@
         <v>13</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J97" s="7">
         <v>5</v>
@@ -5941,13 +5962,13 @@
         <v>13</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>13</v>
@@ -5979,7 +6000,7 @@
         <v>13</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -6017,7 +6038,7 @@
         <v>13</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -6029,7 +6050,7 @@
         <v>13</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J134" s="7">
         <v>4</v>
@@ -6055,13 +6076,13 @@
         <v>13</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>13</v>
@@ -6099,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>13</v>
@@ -6131,7 +6152,7 @@
         <v>13</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -6143,7 +6164,7 @@
         <v>13</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J137" s="7">
         <v>5</v>
@@ -6169,7 +6190,7 @@
         <v>13</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6181,7 +6202,7 @@
         <v>13</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="J138" s="7">
         <v>4</v>
@@ -6213,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>13</v>
@@ -6245,7 +6266,7 @@
         <v>13</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -6257,7 +6278,7 @@
         <v>13</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J140" s="7">
         <v>4</v>
@@ -6289,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>13</v>
@@ -6327,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>13</v>
@@ -6359,7 +6380,7 @@
         <v>13</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -6371,7 +6392,7 @@
         <v>13</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J143" s="7">
         <v>5</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC3C9C5-AB8E-4F1F-86CE-C8EED4EE76C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E93BAE-ED53-4D50-82A4-EDF06D5B7E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$M$403</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_box_v8!$A$2:$M$404</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="150">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -447,14 +447,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>首通宝箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通关宝箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>46700001:8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -468,6 +460,182 @@
   </si>
   <si>
     <t>46700001:6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关宝箱8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首通宝箱9</t>
+  </si>
+  <si>
+    <t>通关宝箱9</t>
+  </si>
+  <si>
+    <t>首通宝箱10</t>
+  </si>
+  <si>
+    <t>通关宝箱10</t>
+  </si>
+  <si>
+    <t>46700001:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46700001:60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42751007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42663007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42761007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42653007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42731007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42731006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42633006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42633007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -522,7 +690,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -532,6 +700,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,7 +737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -576,6 +750,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -858,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M403"/>
+  <dimension ref="A1:M404"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" bestFit="1" customWidth="1"/>
@@ -1379,17 +1564,17 @@
         <v>10020</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
@@ -1400,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
@@ -1420,17 +1605,17 @@
         <v>10010</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
@@ -1441,7 +1626,7 @@
         <v>13</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J15" s="7">
         <v>0</v>
@@ -1456,44 +1641,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A16" s="1">
+    <row r="16" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="8">
         <v>10011</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="7">
-        <v>0</v>
-      </c>
-      <c r="K16" s="7">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7">
+      <c r="C16" s="10">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1502,7 +1687,7 @@
         <v>20020</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -1511,7 +1696,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1523,7 +1708,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J17" s="7">
         <v>0</v>
@@ -1543,7 +1728,7 @@
         <v>20010</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
@@ -1552,7 +1737,7 @@
         <v>13</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1564,7 +1749,7 @@
         <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J18" s="7">
         <v>0</v>
@@ -1579,44 +1764,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
+    <row r="19" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="8">
         <v>20001</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="2">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="7">
-        <v>0</v>
-      </c>
-      <c r="K19" s="7">
-        <v>0</v>
-      </c>
-      <c r="L19" s="7">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7">
+      <c r="C19" s="10">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="12">
+        <v>0</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1624,6 +1809,9 @@
       <c r="A20" s="1">
         <v>30020</v>
       </c>
+      <c r="B20" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
@@ -1631,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1643,7 +1831,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J20" s="7">
         <v>0</v>
@@ -1662,6 +1850,9 @@
       <c r="A21" s="1">
         <v>30010</v>
       </c>
+      <c r="B21" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
@@ -1669,7 +1860,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1681,7 +1872,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="J21" s="7">
         <v>0</v>
@@ -1710,7 +1901,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1722,59 +1913,59 @@
         <v>13</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K22" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="8">
         <v>30002</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="2">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>0</v>
-      </c>
-      <c r="K23" s="7">
-        <v>0</v>
-      </c>
-      <c r="L23" s="7">
-        <v>0</v>
-      </c>
-      <c r="M23" s="7">
+      <c r="C23" s="10">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="12">
+        <v>0</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0</v>
+      </c>
+      <c r="L23" s="12">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1782,6 +1973,9 @@
       <c r="A24" s="1">
         <v>40020</v>
       </c>
+      <c r="B24" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="C24" s="2">
         <v>0</v>
       </c>
@@ -1789,7 +1983,7 @@
         <v>13</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1801,7 +1995,7 @@
         <v>13</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="J24" s="7">
         <v>0</v>
@@ -1820,6 +2014,9 @@
       <c r="A25" s="1">
         <v>40010</v>
       </c>
+      <c r="B25" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="C25" s="2">
         <v>0</v>
       </c>
@@ -1827,7 +2024,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1839,7 +2036,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="J25" s="7">
         <v>0</v>
@@ -1868,7 +2065,7 @@
         <v>13</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1880,59 +2077,59 @@
         <v>13</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K26" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="8">
         <v>40002</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="2">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="7">
-        <v>0</v>
-      </c>
-      <c r="K27" s="7">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7">
-        <v>0</v>
-      </c>
-      <c r="M27" s="7">
+      <c r="C27" s="10">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0</v>
+      </c>
+      <c r="K27" s="12">
+        <v>0</v>
+      </c>
+      <c r="L27" s="12">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1940,6 +2137,9 @@
       <c r="A28" s="1">
         <v>50020</v>
       </c>
+      <c r="B28" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="C28" s="2">
         <v>0</v>
       </c>
@@ -1947,7 +2147,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -1959,7 +2159,7 @@
         <v>13</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="J28" s="7">
         <v>0</v>
@@ -1978,6 +2178,9 @@
       <c r="A29" s="1">
         <v>50010</v>
       </c>
+      <c r="B29" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="C29" s="2">
         <v>0</v>
       </c>
@@ -1985,7 +2188,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1997,7 +2200,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="J29" s="7">
         <v>0</v>
@@ -2026,7 +2229,7 @@
         <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2038,100 +2241,100 @@
         <v>13</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J30" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="8">
         <v>50002</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="2">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="7">
-        <v>0</v>
-      </c>
-      <c r="K31" s="7">
-        <v>0</v>
-      </c>
-      <c r="L31" s="7">
-        <v>0</v>
-      </c>
-      <c r="M31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A32" s="1">
+      <c r="C31" s="10">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J31" s="12">
+        <v>4</v>
+      </c>
+      <c r="K31" s="12">
+        <v>4</v>
+      </c>
+      <c r="L31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="8">
         <v>50003</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="2">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="7">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7">
-        <v>0</v>
-      </c>
-      <c r="M32" s="7">
+      <c r="C32" s="10">
+        <v>0</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="12">
+        <v>0</v>
+      </c>
+      <c r="K32" s="12">
+        <v>0</v>
+      </c>
+      <c r="L32" s="12">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2139,6 +2342,9 @@
       <c r="A33" s="1">
         <v>60020</v>
       </c>
+      <c r="B33" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="C33" s="2">
         <v>0</v>
       </c>
@@ -2146,7 +2352,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2158,7 +2364,7 @@
         <v>13</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="J33" s="7">
         <v>0</v>
@@ -2177,6 +2383,9 @@
       <c r="A34" s="1">
         <v>60010</v>
       </c>
+      <c r="B34" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="C34" s="2">
         <v>0</v>
       </c>
@@ -2184,7 +2393,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2196,7 +2405,7 @@
         <v>13</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="J34" s="7">
         <v>0</v>
@@ -2225,7 +2434,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2237,19 +2446,19 @@
         <v>13</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L35" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.15">
@@ -2266,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2278,19 +2487,19 @@
         <v>13</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="J36" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K36" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L36" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.15">
@@ -2307,13 +2516,13 @@
         <v>13</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
-      <c r="G37" s="2">
-        <v>0</v>
+      <c r="G37" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -2322,16 +2531,16 @@
         <v>15</v>
       </c>
       <c r="J37" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K37" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.15">
@@ -2348,7 +2557,7 @@
         <v>13</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2360,19 +2569,19 @@
         <v>13</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="J38" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K38" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.15">
@@ -2389,7 +2598,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2401,19 +2610,19 @@
         <v>13</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J39" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K39" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.15">
@@ -2430,13 +2639,13 @@
         <v>13</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
-      <c r="G40" s="2">
-        <v>0</v>
+      <c r="G40" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -2445,22 +2654,25 @@
         <v>15</v>
       </c>
       <c r="J40" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>70020</v>
       </c>
+      <c r="B41" s="6" t="s">
+        <v>117</v>
+      </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
@@ -2468,7 +2680,7 @@
         <v>13</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2480,7 +2692,7 @@
         <v>13</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="J41" s="7">
         <v>0</v>
@@ -2499,6 +2711,9 @@
       <c r="A42" s="1">
         <v>70010</v>
       </c>
+      <c r="B42" s="6" t="s">
+        <v>118</v>
+      </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
@@ -2506,7 +2721,7 @@
         <v>13</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2518,7 +2733,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="J42" s="7">
         <v>0</v>
@@ -2552,8 +2767,8 @@
       <c r="F43" s="1">
         <v>0</v>
       </c>
-      <c r="G43" s="2">
-        <v>0</v>
+      <c r="G43" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
@@ -2629,7 +2844,7 @@
         <v>13</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2641,7 +2856,7 @@
         <v>13</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="J45" s="7">
         <v>4</v>
@@ -2675,8 +2890,8 @@
       <c r="F46" s="1">
         <v>0</v>
       </c>
-      <c r="G46" s="2">
-        <v>0</v>
+      <c r="G46" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
@@ -2716,8 +2931,8 @@
       <c r="F47" s="1">
         <v>0</v>
       </c>
-      <c r="G47" s="2">
-        <v>0</v>
+      <c r="G47" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -2793,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2805,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="J49" s="7">
         <v>4</v>
@@ -2840,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -2875,7 +3090,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2887,7 +3102,7 @@
         <v>13</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="J51" s="7">
         <v>4</v>
@@ -2922,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -2963,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -3029,6 +3244,9 @@
       <c r="A55" s="1">
         <v>80020</v>
       </c>
+      <c r="B55" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="C55" s="2">
         <v>0</v>
       </c>
@@ -3036,7 +3254,7 @@
         <v>13</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3048,7 +3266,7 @@
         <v>13</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="J55" s="7">
         <v>0</v>
@@ -3067,6 +3285,9 @@
       <c r="A56" s="1">
         <v>80010</v>
       </c>
+      <c r="B56" s="6" t="s">
+        <v>120</v>
+      </c>
       <c r="C56" s="2">
         <v>0</v>
       </c>
@@ -3074,7 +3295,7 @@
         <v>13</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3086,7 +3307,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="J56" s="7">
         <v>0</v>
@@ -3105,6 +3326,9 @@
       <c r="A57" s="1">
         <v>90020</v>
       </c>
+      <c r="B57" s="6" t="s">
+        <v>121</v>
+      </c>
       <c r="C57" s="2">
         <v>0</v>
       </c>
@@ -3112,7 +3336,7 @@
         <v>13</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3124,7 +3348,7 @@
         <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="J57" s="7">
         <v>0</v>
@@ -3141,7 +3365,10 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>100020</v>
+        <v>90010</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -3150,7 +3377,7 @@
         <v>13</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3162,7 +3389,7 @@
         <v>13</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J58" s="7">
         <v>0</v>
@@ -3179,7 +3406,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>100010</v>
+        <v>100020</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -3188,7 +3418,7 @@
         <v>13</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3200,7 +3430,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="J59" s="7">
         <v>0</v>
@@ -3217,7 +3447,10 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>110020</v>
+        <v>100010</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -3226,7 +3459,7 @@
         <v>13</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3238,7 +3471,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J60" s="7">
         <v>0</v>
@@ -3255,7 +3488,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>110010</v>
+        <v>110020</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -3293,7 +3526,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>110001</v>
+        <v>110010</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -3302,13 +3535,13 @@
         <v>13</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1">
-        <v>30</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>37</v>
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>0</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>13</v>
@@ -3317,21 +3550,21 @@
         <v>15</v>
       </c>
       <c r="J62" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K62" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>110002</v>
+        <v>110001</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -3340,19 +3573,19 @@
         <v>13</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F63" s="1">
-        <v>40</v>
-      </c>
-      <c r="G63" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="J63" s="7">
         <v>4</v>
@@ -3364,12 +3597,12 @@
         <v>1</v>
       </c>
       <c r="M63" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>110003</v>
+        <v>110002</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -3378,19 +3611,19 @@
         <v>13</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F64" s="1">
-        <v>50</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J64" s="7">
         <v>4</v>
@@ -3399,15 +3632,15 @@
         <v>2</v>
       </c>
       <c r="L64" s="7">
+        <v>1</v>
+      </c>
+      <c r="M64" s="7">
         <v>2</v>
-      </c>
-      <c r="M64" s="7">
-        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
-        <v>110004</v>
+        <v>110003</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -3416,19 +3649,19 @@
         <v>13</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F65" s="1">
-        <v>70</v>
-      </c>
-      <c r="G65" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J65" s="7">
         <v>4</v>
@@ -3440,12 +3673,12 @@
         <v>2</v>
       </c>
       <c r="M65" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>110005</v>
+        <v>110004</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -3454,10 +3687,10 @@
         <v>13</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F66" s="1">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="G66" s="2">
         <v>0</v>
@@ -3466,7 +3699,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J66" s="7">
         <v>4</v>
@@ -3475,15 +3708,15 @@
         <v>2</v>
       </c>
       <c r="L66" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M66" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>110006</v>
+        <v>110005</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -3495,33 +3728,33 @@
         <v>36</v>
       </c>
       <c r="F67" s="1">
-        <v>150</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>42</v>
+        <v>120</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J67" s="7">
+        <v>4</v>
+      </c>
+      <c r="K67" s="7">
+        <v>2</v>
+      </c>
+      <c r="L67" s="7">
+        <v>3</v>
+      </c>
+      <c r="M67" s="7">
         <v>5</v>
-      </c>
-      <c r="K67" s="7">
-        <v>3</v>
-      </c>
-      <c r="L67" s="7">
-        <v>1</v>
-      </c>
-      <c r="M67" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>110007</v>
+        <v>110006</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -3530,13 +3763,13 @@
         <v>13</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F68" s="1">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>13</v>
@@ -3554,12 +3787,12 @@
         <v>1</v>
       </c>
       <c r="M68" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>110008</v>
+        <v>110007</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -3568,19 +3801,19 @@
         <v>13</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F69" s="1">
-        <v>250</v>
-      </c>
-      <c r="G69" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="J69" s="7">
         <v>5</v>
@@ -3589,15 +3822,15 @@
         <v>3</v>
       </c>
       <c r="L69" s="7">
+        <v>1</v>
+      </c>
+      <c r="M69" s="7">
         <v>2</v>
-      </c>
-      <c r="M69" s="7">
-        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>110009</v>
+        <v>110008</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -3606,10 +3839,10 @@
         <v>13</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F70" s="1">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
@@ -3618,7 +3851,7 @@
         <v>13</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J70" s="7">
         <v>5</v>
@@ -3630,12 +3863,12 @@
         <v>2</v>
       </c>
       <c r="M70" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>110011</v>
+        <v>110009</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -3644,10 +3877,10 @@
         <v>13</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F71" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G71" s="2">
         <v>0</v>
@@ -3656,7 +3889,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J71" s="7">
         <v>5</v>
@@ -3665,15 +3898,15 @@
         <v>3</v>
       </c>
       <c r="L71" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M71" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>110012</v>
+        <v>110011</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -3682,36 +3915,36 @@
         <v>13</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F72" s="1">
-        <v>600</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>47</v>
+        <v>500</v>
+      </c>
+      <c r="G72" s="2">
+        <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J72" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K72" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M72" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>110013</v>
+        <v>110012</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -3720,19 +3953,19 @@
         <v>13</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F73" s="1">
-        <v>800</v>
-      </c>
-      <c r="G73" s="2">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J73" s="7">
         <v>0</v>
@@ -3749,7 +3982,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>110014</v>
+        <v>110013</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -3758,19 +3991,19 @@
         <v>13</v>
       </c>
       <c r="E74" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="1">
+        <v>800</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F74" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="J74" s="7">
         <v>0</v>
@@ -3787,7 +4020,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>110015</v>
+        <v>110014</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -3796,19 +4029,19 @@
         <v>13</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F75" s="1">
-        <v>1200</v>
-      </c>
-      <c r="G75" s="2">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="J75" s="7">
         <v>0</v>
@@ -3825,7 +4058,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>110016</v>
+        <v>110015</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -3834,10 +4067,10 @@
         <v>13</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
@@ -3846,7 +4079,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J76" s="7">
         <v>0</v>
@@ -3863,7 +4096,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>110017</v>
+        <v>110016</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -3872,10 +4105,10 @@
         <v>13</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F77" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
@@ -3884,7 +4117,7 @@
         <v>13</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J77" s="7">
         <v>0</v>
@@ -3901,7 +4134,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>110018</v>
+        <v>110017</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -3910,10 +4143,10 @@
         <v>13</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F78" s="1">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
@@ -3922,7 +4155,7 @@
         <v>13</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J78" s="7">
         <v>0</v>
@@ -3939,7 +4172,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>110019</v>
+        <v>110018</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -3948,19 +4181,19 @@
         <v>13</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F79" s="1">
-        <v>2500</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>49</v>
+        <v>2000</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J79" s="7">
         <v>0</v>
@@ -3977,7 +4210,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>110021</v>
+        <v>110019</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -3986,19 +4219,19 @@
         <v>13</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F80" s="1">
-        <v>3000</v>
-      </c>
-      <c r="G80" s="2">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="J80" s="7">
         <v>0</v>
@@ -4015,7 +4248,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>110022</v>
+        <v>110021</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -4024,19 +4257,19 @@
         <v>13</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F81" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>3000</v>
+      </c>
+      <c r="G81" s="2">
+        <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="J81" s="7">
         <v>0</v>
@@ -4053,7 +4286,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>110023</v>
+        <v>110022</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -4062,19 +4295,19 @@
         <v>13</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F82" s="1">
-        <v>8000</v>
-      </c>
-      <c r="G82" s="2">
-        <v>0</v>
+        <v>6000</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J82" s="7">
         <v>0</v>
@@ -4091,7 +4324,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>110024</v>
+        <v>110023</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -4100,10 +4333,10 @@
         <v>13</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
@@ -4112,7 +4345,7 @@
         <v>13</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J83" s="7">
         <v>0</v>
@@ -4129,16 +4362,16 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>120020</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>8</v>
+        <v>110024</v>
+      </c>
+      <c r="C84" s="2">
+        <v>0</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -4167,7 +4400,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>120010</v>
+        <v>120020</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>8</v>
@@ -4205,7 +4438,7 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>130020</v>
+        <v>120010</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>8</v>
@@ -4243,7 +4476,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>130010</v>
+        <v>130020</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>8</v>
@@ -4281,22 +4514,22 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>130001</v>
-      </c>
-      <c r="C88" s="2">
-        <v>0</v>
+        <v>130010</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1">
-        <v>30</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>37</v>
+        <v>0</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>13</v>
@@ -4305,21 +4538,21 @@
         <v>15</v>
       </c>
       <c r="J88" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K88" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>130002</v>
+        <v>130001</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -4328,19 +4561,19 @@
         <v>13</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F89" s="1">
-        <v>40</v>
-      </c>
-      <c r="G89" s="2">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="J89" s="7">
         <v>4</v>
@@ -4352,12 +4585,12 @@
         <v>1</v>
       </c>
       <c r="M89" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>130003</v>
+        <v>130002</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -4366,19 +4599,19 @@
         <v>13</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F90" s="1">
-        <v>50</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J90" s="7">
         <v>4</v>
@@ -4387,15 +4620,15 @@
         <v>2</v>
       </c>
       <c r="L90" s="7">
+        <v>1</v>
+      </c>
+      <c r="M90" s="7">
         <v>2</v>
-      </c>
-      <c r="M90" s="7">
-        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>130004</v>
+        <v>130003</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -4404,19 +4637,19 @@
         <v>13</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F91" s="1">
-        <v>70</v>
-      </c>
-      <c r="G91" s="2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J91" s="7">
         <v>4</v>
@@ -4428,12 +4661,12 @@
         <v>2</v>
       </c>
       <c r="M91" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>130005</v>
+        <v>130004</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -4442,10 +4675,10 @@
         <v>13</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F92" s="1">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
@@ -4454,7 +4687,7 @@
         <v>13</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J92" s="7">
         <v>4</v>
@@ -4463,15 +4696,15 @@
         <v>2</v>
       </c>
       <c r="L92" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M92" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>130006</v>
+        <v>130005</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -4483,33 +4716,33 @@
         <v>36</v>
       </c>
       <c r="F93" s="1">
-        <v>150</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>42</v>
+        <v>120</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J93" s="7">
+        <v>4</v>
+      </c>
+      <c r="K93" s="7">
+        <v>2</v>
+      </c>
+      <c r="L93" s="7">
+        <v>3</v>
+      </c>
+      <c r="M93" s="7">
         <v>5</v>
-      </c>
-      <c r="K93" s="7">
-        <v>3</v>
-      </c>
-      <c r="L93" s="7">
-        <v>1</v>
-      </c>
-      <c r="M93" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>130007</v>
+        <v>130006</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -4518,13 +4751,13 @@
         <v>13</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F94" s="1">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>13</v>
@@ -4542,12 +4775,12 @@
         <v>1</v>
       </c>
       <c r="M94" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>130008</v>
+        <v>130007</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -4556,19 +4789,19 @@
         <v>13</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F95" s="1">
-        <v>250</v>
-      </c>
-      <c r="G95" s="2">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="J95" s="7">
         <v>5</v>
@@ -4577,15 +4810,15 @@
         <v>3</v>
       </c>
       <c r="L95" s="7">
+        <v>1</v>
+      </c>
+      <c r="M95" s="7">
         <v>2</v>
-      </c>
-      <c r="M95" s="7">
-        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>130009</v>
+        <v>130008</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -4594,10 +4827,10 @@
         <v>13</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F96" s="1">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
@@ -4606,7 +4839,7 @@
         <v>13</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J96" s="7">
         <v>5</v>
@@ -4618,12 +4851,12 @@
         <v>2</v>
       </c>
       <c r="M96" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>130011</v>
+        <v>130009</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -4632,10 +4865,10 @@
         <v>13</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F97" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
@@ -4644,7 +4877,7 @@
         <v>13</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J97" s="7">
         <v>5</v>
@@ -4653,27 +4886,27 @@
         <v>3</v>
       </c>
       <c r="L97" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M97" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>140020</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>8</v>
+        <v>130011</v>
+      </c>
+      <c r="C98" s="2">
+        <v>0</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F98" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
@@ -4682,24 +4915,24 @@
         <v>13</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J98" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K98" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M98" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>140010</v>
+        <v>140020</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>8</v>
@@ -4737,7 +4970,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>150020</v>
+        <v>140010</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>8</v>
@@ -4775,7 +5008,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>150010</v>
+        <v>150020</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>8</v>
@@ -4813,7 +5046,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>160020</v>
+        <v>150010</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>8</v>
@@ -4851,7 +5084,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>160010</v>
+        <v>160020</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>8</v>
@@ -4889,7 +5122,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>170020</v>
+        <v>160010</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>8</v>
@@ -4927,7 +5160,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>170010</v>
+        <v>170020</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>8</v>
@@ -4965,7 +5198,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>180020</v>
+        <v>170010</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>8</v>
@@ -5003,7 +5236,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>180010</v>
+        <v>180020</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>8</v>
@@ -5041,7 +5274,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>190020</v>
+        <v>180010</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>8</v>
@@ -5079,7 +5312,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>190010</v>
+        <v>190020</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>8</v>
@@ -5117,7 +5350,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>200020</v>
+        <v>190010</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>8</v>
@@ -5155,7 +5388,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>200010</v>
+        <v>200020</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>8</v>
@@ -5193,7 +5426,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>210020</v>
+        <v>200010</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>8</v>
@@ -5231,7 +5464,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>210010</v>
+        <v>210020</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>8</v>
@@ -5269,7 +5502,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>220020</v>
+        <v>210010</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>8</v>
@@ -5307,7 +5540,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>220010</v>
+        <v>220020</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>8</v>
@@ -5345,7 +5578,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>230020</v>
+        <v>220010</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>8</v>
@@ -5383,7 +5616,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>230010</v>
+        <v>230020</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>8</v>
@@ -5421,7 +5654,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>240020</v>
+        <v>230010</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>8</v>
@@ -5459,7 +5692,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>240010</v>
+        <v>240020</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>8</v>
@@ -5497,7 +5730,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>250020</v>
+        <v>240010</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>8</v>
@@ -5535,7 +5768,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>250010</v>
+        <v>250020</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>8</v>
@@ -5573,7 +5806,7 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>260020</v>
+        <v>250010</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>8</v>
@@ -5611,7 +5844,7 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>260010</v>
+        <v>260020</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>8</v>
@@ -5649,7 +5882,7 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>270020</v>
+        <v>260010</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>8</v>
@@ -5687,7 +5920,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>270010</v>
+        <v>270020</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>8</v>
@@ -5725,7 +5958,7 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>280020</v>
+        <v>270010</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>8</v>
@@ -5763,7 +5996,7 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>280010</v>
+        <v>280020</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>8</v>
@@ -5801,7 +6034,7 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>290020</v>
+        <v>280010</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>8</v>
@@ -5839,7 +6072,7 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>290010</v>
+        <v>290020</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>8</v>
@@ -5877,7 +6110,7 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>300020</v>
+        <v>290010</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>8</v>
@@ -5915,7 +6148,7 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>300010</v>
+        <v>300020</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>8</v>
@@ -5953,22 +6186,22 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>300001</v>
-      </c>
-      <c r="C132" s="2">
-        <v>0</v>
+        <v>300010</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
       </c>
-      <c r="G132" s="2" t="s">
-        <v>64</v>
+      <c r="G132" s="2">
+        <v>0</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>13</v>
@@ -5977,21 +6210,21 @@
         <v>15</v>
       </c>
       <c r="J132" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K132" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L132" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>300002</v>
+        <v>300001</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
@@ -6000,36 +6233,36 @@
         <v>13</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
       </c>
-      <c r="G133" s="2">
-        <v>0</v>
+      <c r="G133" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J133" s="7">
         <v>5</v>
       </c>
       <c r="K133" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L133" s="7">
         <v>1</v>
       </c>
       <c r="M133" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>300003</v>
+        <v>300002</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
@@ -6038,7 +6271,7 @@
         <v>13</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -6050,13 +6283,13 @@
         <v>13</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="J134" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K134" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L134" s="7">
         <v>1</v>
@@ -6067,7 +6300,7 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>300004</v>
+        <v>300003</v>
       </c>
       <c r="C135" s="2">
         <v>0</v>
@@ -6076,36 +6309,36 @@
         <v>13</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
       </c>
-      <c r="G135" s="2" t="s">
-        <v>43</v>
+      <c r="G135" s="2">
+        <v>0</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="J135" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K135" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L135" s="7">
         <v>1</v>
       </c>
       <c r="M135" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>300005</v>
+        <v>300004</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
@@ -6114,13 +6347,13 @@
         <v>13</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>13</v>
@@ -6132,18 +6365,18 @@
         <v>5</v>
       </c>
       <c r="K136" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L136" s="7">
         <v>1</v>
       </c>
       <c r="M136" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>300006</v>
+        <v>300005</v>
       </c>
       <c r="C137" s="2">
         <v>0</v>
@@ -6152,36 +6385,36 @@
         <v>13</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
       </c>
-      <c r="G137" s="2">
-        <v>0</v>
+      <c r="G137" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J137" s="7">
         <v>5</v>
       </c>
       <c r="K137" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L137" s="7">
         <v>1</v>
       </c>
       <c r="M137" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>300007</v>
+        <v>300006</v>
       </c>
       <c r="C138" s="2">
         <v>0</v>
@@ -6190,7 +6423,7 @@
         <v>13</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6202,13 +6435,13 @@
         <v>13</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="J138" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K138" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L138" s="7">
         <v>1</v>
@@ -6219,7 +6452,7 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>300008</v>
+        <v>300007</v>
       </c>
       <c r="C139" s="2">
         <v>0</v>
@@ -6228,36 +6461,36 @@
         <v>13</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
       </c>
-      <c r="G139" s="2" t="s">
-        <v>68</v>
+      <c r="G139" s="2">
+        <v>0</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="J139" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K139" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L139" s="7">
         <v>1</v>
       </c>
       <c r="M139" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>300009</v>
+        <v>300008</v>
       </c>
       <c r="C140" s="2">
         <v>0</v>
@@ -6266,25 +6499,25 @@
         <v>13</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
       </c>
-      <c r="G140" s="2">
-        <v>0</v>
+      <c r="G140" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="J140" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K140" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L140" s="7">
         <v>1</v>
@@ -6295,7 +6528,7 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>300011</v>
+        <v>300009</v>
       </c>
       <c r="C141" s="2">
         <v>0</v>
@@ -6304,36 +6537,36 @@
         <v>13</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
       </c>
-      <c r="G141" s="2" t="s">
-        <v>71</v>
+      <c r="G141" s="2">
+        <v>0</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="J141" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K141" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L141" s="7">
         <v>1</v>
       </c>
       <c r="M141" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>300012</v>
+        <v>300011</v>
       </c>
       <c r="C142" s="2">
         <v>0</v>
@@ -6348,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>13</v>
@@ -6360,7 +6593,7 @@
         <v>5</v>
       </c>
       <c r="K142" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L142" s="7">
         <v>1</v>
@@ -6371,7 +6604,7 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>300013</v>
+        <v>300012</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
@@ -6380,45 +6613,45 @@
         <v>13</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
       </c>
-      <c r="G143" s="2">
-        <v>0</v>
+      <c r="G143" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J143" s="7">
         <v>5</v>
       </c>
       <c r="K143" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L143" s="7">
         <v>1</v>
       </c>
       <c r="M143" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>310020</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>8</v>
+        <v>300013</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -6430,24 +6663,24 @@
         <v>13</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J144" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K144" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L144" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>310010</v>
+        <v>310020</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>8</v>
@@ -6485,7 +6718,7 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>320020</v>
+        <v>310010</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>8</v>
@@ -6523,7 +6756,7 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>320010</v>
+        <v>320020</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>8</v>
@@ -6561,7 +6794,7 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>330020</v>
+        <v>320010</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>8</v>
@@ -6599,7 +6832,7 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>330010</v>
+        <v>330020</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>8</v>
@@ -6637,7 +6870,7 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>340020</v>
+        <v>330010</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>8</v>
@@ -6675,7 +6908,7 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>340010</v>
+        <v>340020</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>8</v>
@@ -6713,7 +6946,7 @@
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>350020</v>
+        <v>340010</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>8</v>
@@ -6751,7 +6984,7 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>350010</v>
+        <v>350020</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>8</v>
@@ -6789,7 +7022,7 @@
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>360020</v>
+        <v>350010</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>8</v>
@@ -6827,7 +7060,7 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>360010</v>
+        <v>360020</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>8</v>
@@ -6865,7 +7098,7 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>370020</v>
+        <v>360010</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>8</v>
@@ -6903,7 +7136,7 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>370010</v>
+        <v>370020</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>8</v>
@@ -6941,7 +7174,7 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>380020</v>
+        <v>370010</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>8</v>
@@ -6979,7 +7212,7 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>380010</v>
+        <v>380020</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>8</v>
@@ -7017,7 +7250,7 @@
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>390020</v>
+        <v>380010</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>8</v>
@@ -7055,7 +7288,7 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>390010</v>
+        <v>390020</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>8</v>
@@ -7093,7 +7326,7 @@
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>400020</v>
+        <v>390010</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>8</v>
@@ -7131,7 +7364,7 @@
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>400010</v>
+        <v>400020</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>8</v>
@@ -7169,7 +7402,7 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>410020</v>
+        <v>400010</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>8</v>
@@ -7207,7 +7440,7 @@
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>410010</v>
+        <v>410020</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>8</v>
@@ -7245,7 +7478,7 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>420020</v>
+        <v>410010</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>8</v>
@@ -7283,7 +7516,7 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>420010</v>
+        <v>420020</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>8</v>
@@ -7321,7 +7554,7 @@
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>430020</v>
+        <v>420010</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>8</v>
@@ -7359,7 +7592,7 @@
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>430010</v>
+        <v>430020</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>8</v>
@@ -7397,7 +7630,7 @@
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>440020</v>
+        <v>430010</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>8</v>
@@ -7435,7 +7668,7 @@
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>440010</v>
+        <v>440020</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>8</v>
@@ -7473,7 +7706,7 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>450020</v>
+        <v>440010</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>8</v>
@@ -7511,7 +7744,7 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>450010</v>
+        <v>450020</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>8</v>
@@ -7549,7 +7782,7 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>460020</v>
+        <v>450010</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>8</v>
@@ -7587,7 +7820,7 @@
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>460010</v>
+        <v>460020</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>8</v>
@@ -7625,7 +7858,7 @@
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>470020</v>
+        <v>460010</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>8</v>
@@ -7663,7 +7896,7 @@
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>470010</v>
+        <v>470020</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>8</v>
@@ -7701,7 +7934,7 @@
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>480020</v>
+        <v>470010</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>8</v>
@@ -7739,7 +7972,7 @@
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>480010</v>
+        <v>480020</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>8</v>
@@ -7777,7 +8010,7 @@
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>490020</v>
+        <v>480010</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>8</v>
@@ -7815,7 +8048,7 @@
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>490010</v>
+        <v>490020</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>8</v>
@@ -7853,7 +8086,7 @@
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>500020</v>
+        <v>490010</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>8</v>
@@ -7891,7 +8124,7 @@
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>500010</v>
+        <v>500020</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>8</v>
@@ -7929,7 +8162,7 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>510020</v>
+        <v>500010</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>8</v>
@@ -7967,7 +8200,7 @@
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>510010</v>
+        <v>510020</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>8</v>
@@ -8005,7 +8238,7 @@
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>520020</v>
+        <v>510010</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>8</v>
@@ -8043,7 +8276,7 @@
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>520010</v>
+        <v>520020</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>8</v>
@@ -8081,7 +8314,7 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>530020</v>
+        <v>520010</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>8</v>
@@ -8119,7 +8352,7 @@
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>530010</v>
+        <v>530020</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>8</v>
@@ -8157,7 +8390,7 @@
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>540020</v>
+        <v>530010</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>8</v>
@@ -8195,7 +8428,7 @@
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>540010</v>
+        <v>540020</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>8</v>
@@ -8233,7 +8466,7 @@
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>550020</v>
+        <v>540010</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>8</v>
@@ -8271,7 +8504,7 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>550010</v>
+        <v>550020</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>8</v>
@@ -8309,7 +8542,7 @@
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>560020</v>
+        <v>550010</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>8</v>
@@ -8347,7 +8580,7 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>560010</v>
+        <v>560020</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>8</v>
@@ -8385,7 +8618,7 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>570020</v>
+        <v>560010</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>8</v>
@@ -8423,7 +8656,7 @@
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>570010</v>
+        <v>570020</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>8</v>
@@ -8461,7 +8694,7 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>580020</v>
+        <v>570010</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>8</v>
@@ -8499,7 +8732,7 @@
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>580010</v>
+        <v>580020</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>8</v>
@@ -8537,7 +8770,7 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>590020</v>
+        <v>580010</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>8</v>
@@ -8575,7 +8808,7 @@
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>590010</v>
+        <v>590020</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>8</v>
@@ -8613,7 +8846,7 @@
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>600020</v>
+        <v>590010</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>8</v>
@@ -8651,7 +8884,7 @@
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>600010</v>
+        <v>600020</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>8</v>
@@ -8689,7 +8922,7 @@
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>610020</v>
+        <v>600010</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>8</v>
@@ -8727,7 +8960,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>610010</v>
+        <v>610020</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>8</v>
@@ -8765,7 +8998,7 @@
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>620020</v>
+        <v>610010</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>8</v>
@@ -8803,7 +9036,7 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>620010</v>
+        <v>620020</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>8</v>
@@ -8841,7 +9074,7 @@
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>630020</v>
+        <v>620010</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>8</v>
@@ -8879,7 +9112,7 @@
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>630010</v>
+        <v>630020</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>8</v>
@@ -8917,7 +9150,7 @@
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>640020</v>
+        <v>630010</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>8</v>
@@ -8955,7 +9188,7 @@
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>640010</v>
+        <v>640020</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>8</v>
@@ -8993,7 +9226,7 @@
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>650020</v>
+        <v>640010</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>8</v>
@@ -9031,7 +9264,7 @@
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>650010</v>
+        <v>650020</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>8</v>
@@ -9069,7 +9302,7 @@
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>660020</v>
+        <v>650010</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>8</v>
@@ -9107,7 +9340,7 @@
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>660010</v>
+        <v>660020</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>8</v>
@@ -9145,7 +9378,7 @@
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>670020</v>
+        <v>660010</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>8</v>
@@ -9183,7 +9416,7 @@
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>670010</v>
+        <v>670020</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>8</v>
@@ -9221,7 +9454,7 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>680020</v>
+        <v>670010</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>8</v>
@@ -9259,7 +9492,7 @@
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>680010</v>
+        <v>680020</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
@@ -9297,7 +9530,7 @@
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>690020</v>
+        <v>680010</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>8</v>
@@ -9335,7 +9568,7 @@
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>690010</v>
+        <v>690020</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>8</v>
@@ -9373,7 +9606,7 @@
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>700020</v>
+        <v>690010</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>8</v>
@@ -9411,7 +9644,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>700010</v>
+        <v>700020</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>8</v>
@@ -9449,7 +9682,7 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>710020</v>
+        <v>700010</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>8</v>
@@ -9487,7 +9720,7 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>710010</v>
+        <v>710020</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
@@ -9525,7 +9758,7 @@
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>720020</v>
+        <v>710010</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
@@ -9563,7 +9796,7 @@
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>720010</v>
+        <v>720020</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>8</v>
@@ -9601,7 +9834,7 @@
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>730020</v>
+        <v>720010</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
@@ -9639,7 +9872,7 @@
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>730010</v>
+        <v>730020</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>8</v>
@@ -9677,7 +9910,7 @@
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>740020</v>
+        <v>730010</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
@@ -9715,7 +9948,7 @@
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>740010</v>
+        <v>740020</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>8</v>
@@ -9753,7 +9986,7 @@
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>750020</v>
+        <v>740010</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -9791,7 +10024,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>750010</v>
+        <v>750020</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>8</v>
@@ -9829,7 +10062,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>760020</v>
+        <v>750010</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>8</v>
@@ -9867,7 +10100,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>760010</v>
+        <v>760020</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>8</v>
@@ -9905,7 +10138,7 @@
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>770020</v>
+        <v>760010</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>8</v>
@@ -9943,7 +10176,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>770010</v>
+        <v>770020</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>8</v>
@@ -9981,7 +10214,7 @@
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>780020</v>
+        <v>770010</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>8</v>
@@ -10019,7 +10252,7 @@
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>780010</v>
+        <v>780020</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>8</v>
@@ -10057,7 +10290,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>790020</v>
+        <v>780010</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -10095,7 +10328,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>790010</v>
+        <v>790020</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>8</v>
@@ -10133,7 +10366,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>800020</v>
+        <v>790010</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -10171,7 +10404,7 @@
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>800010</v>
+        <v>800020</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -10209,7 +10442,7 @@
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>810020</v>
+        <v>800010</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -10247,7 +10480,7 @@
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>810010</v>
+        <v>810020</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -10285,7 +10518,7 @@
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>820020</v>
+        <v>810010</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -10323,7 +10556,7 @@
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>820010</v>
+        <v>820020</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -10361,7 +10594,7 @@
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>830020</v>
+        <v>820010</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>8</v>
@@ -10399,7 +10632,7 @@
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>830010</v>
+        <v>830020</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -10437,7 +10670,7 @@
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>840020</v>
+        <v>830010</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>8</v>
@@ -10475,7 +10708,7 @@
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>840010</v>
+        <v>840020</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
@@ -10513,7 +10746,7 @@
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>850020</v>
+        <v>840010</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -10551,7 +10784,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>850010</v>
+        <v>850020</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
@@ -10589,7 +10822,7 @@
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>860020</v>
+        <v>850010</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>8</v>
@@ -10627,7 +10860,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>860010</v>
+        <v>860020</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>8</v>
@@ -10665,7 +10898,7 @@
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>870020</v>
+        <v>860010</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -10703,7 +10936,7 @@
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>870010</v>
+        <v>870020</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -10741,7 +10974,7 @@
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>880020</v>
+        <v>870010</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -10779,7 +11012,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>880010</v>
+        <v>880020</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -10817,7 +11050,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>890020</v>
+        <v>880010</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
@@ -10855,7 +11088,7 @@
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>890010</v>
+        <v>890020</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
@@ -10893,7 +11126,7 @@
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>900020</v>
+        <v>890010</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>8</v>
@@ -10931,7 +11164,7 @@
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>900010</v>
+        <v>900020</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
@@ -10969,7 +11202,7 @@
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>910020</v>
+        <v>900010</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -11007,7 +11240,7 @@
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>910010</v>
+        <v>910020</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -11045,7 +11278,7 @@
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>920020</v>
+        <v>910010</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -11083,7 +11316,7 @@
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>920010</v>
+        <v>920020</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -11121,7 +11354,7 @@
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>930020</v>
+        <v>920010</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -11159,7 +11392,7 @@
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>930010</v>
+        <v>930020</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
@@ -11197,7 +11430,7 @@
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>940020</v>
+        <v>930010</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -11235,7 +11468,7 @@
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>940010</v>
+        <v>940020</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>8</v>
@@ -11273,7 +11506,7 @@
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>950020</v>
+        <v>940010</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -11311,7 +11544,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>950010</v>
+        <v>950020</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -11349,7 +11582,7 @@
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>960020</v>
+        <v>950010</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -11387,7 +11620,7 @@
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>960010</v>
+        <v>960020</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>8</v>
@@ -11425,7 +11658,7 @@
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>970020</v>
+        <v>960010</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>8</v>
@@ -11463,7 +11696,7 @@
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>970010</v>
+        <v>970020</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -11501,7 +11734,7 @@
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>980020</v>
+        <v>970010</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -11539,7 +11772,7 @@
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>980010</v>
+        <v>980020</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>8</v>
@@ -11577,7 +11810,7 @@
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>990020</v>
+        <v>980010</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>8</v>
@@ -11615,7 +11848,7 @@
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>990010</v>
+        <v>990020</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>8</v>
@@ -11653,7 +11886,7 @@
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1000020</v>
+        <v>990010</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>8</v>
@@ -11691,7 +11924,7 @@
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1000010</v>
+        <v>1000020</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -11729,7 +11962,7 @@
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1010020</v>
+        <v>1000010</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -11767,7 +12000,7 @@
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1010010</v>
+        <v>1010020</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -11805,7 +12038,7 @@
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1020020</v>
+        <v>1010010</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -11843,7 +12076,7 @@
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1020010</v>
+        <v>1020020</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -11881,7 +12114,7 @@
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1030020</v>
+        <v>1020010</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -11919,7 +12152,7 @@
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1030010</v>
+        <v>1030020</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -11957,7 +12190,7 @@
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1040020</v>
+        <v>1030010</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -11995,7 +12228,7 @@
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1040010</v>
+        <v>1040020</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -12033,7 +12266,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1050020</v>
+        <v>1040010</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -12071,7 +12304,7 @@
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1050010</v>
+        <v>1050020</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>8</v>
@@ -12109,7 +12342,7 @@
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1060020</v>
+        <v>1050010</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>8</v>
@@ -12147,7 +12380,7 @@
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1060010</v>
+        <v>1060020</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>8</v>
@@ -12185,7 +12418,7 @@
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1070020</v>
+        <v>1060010</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -12223,7 +12456,7 @@
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1070010</v>
+        <v>1070020</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -12261,7 +12494,7 @@
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1080020</v>
+        <v>1070010</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -12299,7 +12532,7 @@
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1080010</v>
+        <v>1080020</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -12337,7 +12570,7 @@
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1090020</v>
+        <v>1080010</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>8</v>
@@ -12375,7 +12608,7 @@
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1090010</v>
+        <v>1090020</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -12413,7 +12646,7 @@
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1100020</v>
+        <v>1090010</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>8</v>
@@ -12451,7 +12684,7 @@
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>1100010</v>
+        <v>1100020</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>8</v>
@@ -12489,7 +12722,7 @@
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>1110020</v>
+        <v>1100010</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>8</v>
@@ -12527,7 +12760,7 @@
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>1110010</v>
+        <v>1110020</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -12565,7 +12798,7 @@
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>1120020</v>
+        <v>1110010</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>8</v>
@@ -12603,7 +12836,7 @@
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>1120010</v>
+        <v>1120020</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -12641,7 +12874,7 @@
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>1130020</v>
+        <v>1120010</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>8</v>
@@ -12679,7 +12912,7 @@
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>1130010</v>
+        <v>1130020</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>8</v>
@@ -12717,7 +12950,7 @@
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>1140020</v>
+        <v>1130010</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>8</v>
@@ -12755,7 +12988,7 @@
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>1140010</v>
+        <v>1140020</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>8</v>
@@ -12793,7 +13026,7 @@
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>1150020</v>
+        <v>1140010</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>8</v>
@@ -12831,7 +13064,7 @@
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>1150010</v>
+        <v>1150020</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>8</v>
@@ -12869,7 +13102,7 @@
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>1160020</v>
+        <v>1150010</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>8</v>
@@ -12907,7 +13140,7 @@
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>1160010</v>
+        <v>1160020</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -12945,7 +13178,7 @@
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>1170020</v>
+        <v>1160010</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -12983,7 +13216,7 @@
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>1170010</v>
+        <v>1170020</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -13021,7 +13254,7 @@
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>1180020</v>
+        <v>1170010</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -13059,7 +13292,7 @@
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>1180010</v>
+        <v>1180020</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -13097,7 +13330,7 @@
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>1190020</v>
+        <v>1180010</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>8</v>
@@ -13135,7 +13368,7 @@
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>1190010</v>
+        <v>1190020</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>8</v>
@@ -13173,7 +13406,7 @@
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>1200020</v>
+        <v>1190010</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -13211,7 +13444,7 @@
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>1200010</v>
+        <v>1200020</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>8</v>
@@ -13249,7 +13482,7 @@
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>1210020</v>
+        <v>1200010</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>8</v>
@@ -13287,7 +13520,7 @@
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>1210010</v>
+        <v>1210020</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -13325,7 +13558,7 @@
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>1220020</v>
+        <v>1210010</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -13363,7 +13596,7 @@
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>1220010</v>
+        <v>1220020</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -13401,7 +13634,7 @@
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>1230020</v>
+        <v>1220010</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -13439,7 +13672,7 @@
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>1230010</v>
+        <v>1230020</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -13477,7 +13710,7 @@
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>1240020</v>
+        <v>1230010</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>8</v>
@@ -13515,7 +13748,7 @@
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>1240010</v>
+        <v>1240020</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -13553,7 +13786,7 @@
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>1250020</v>
+        <v>1240010</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -13591,7 +13824,7 @@
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>1250010</v>
+        <v>1250020</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>8</v>
@@ -13629,7 +13862,7 @@
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>1260020</v>
+        <v>1250010</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -13667,7 +13900,7 @@
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>1260010</v>
+        <v>1260020</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>8</v>
@@ -13705,7 +13938,7 @@
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>1270020</v>
+        <v>1260010</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -13743,7 +13976,7 @@
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>1270010</v>
+        <v>1270020</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -13781,7 +14014,7 @@
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>1280020</v>
+        <v>1270010</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>8</v>
@@ -13819,7 +14052,7 @@
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>1280010</v>
+        <v>1280020</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -13857,7 +14090,7 @@
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>1290020</v>
+        <v>1280010</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -13895,7 +14128,7 @@
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>1290010</v>
+        <v>1290020</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -13933,7 +14166,7 @@
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>1300020</v>
+        <v>1290010</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>8</v>
@@ -13971,7 +14204,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>1300010</v>
+        <v>1300020</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
@@ -14009,7 +14242,7 @@
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>1310020</v>
+        <v>1300010</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
@@ -14047,7 +14280,7 @@
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>1310010</v>
+        <v>1310020</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>8</v>
@@ -14085,7 +14318,7 @@
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>1320020</v>
+        <v>1310010</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>8</v>
@@ -14123,7 +14356,7 @@
     </row>
     <row r="347" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>1320010</v>
+        <v>1320020</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>8</v>
@@ -14161,7 +14394,7 @@
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>1330020</v>
+        <v>1320010</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>8</v>
@@ -14199,7 +14432,7 @@
     </row>
     <row r="349" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>1330010</v>
+        <v>1330020</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>8</v>
@@ -14237,7 +14470,7 @@
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>1340020</v>
+        <v>1330010</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>8</v>
@@ -14275,7 +14508,7 @@
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>1340010</v>
+        <v>1340020</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>8</v>
@@ -14313,7 +14546,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>1350020</v>
+        <v>1340010</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -14351,7 +14584,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>1350010</v>
+        <v>1350020</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -14389,7 +14622,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>1360020</v>
+        <v>1350010</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -14427,7 +14660,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>1360010</v>
+        <v>1360020</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -14465,7 +14698,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>1370020</v>
+        <v>1360010</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -14503,7 +14736,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>1370010</v>
+        <v>1370020</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -14541,7 +14774,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>1380020</v>
+        <v>1370010</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -14579,7 +14812,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>1380010</v>
+        <v>1380020</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -14617,7 +14850,7 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>1390020</v>
+        <v>1380010</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -14655,7 +14888,7 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>1390010</v>
+        <v>1390020</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
@@ -14693,7 +14926,7 @@
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>1400020</v>
+        <v>1390010</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -14731,7 +14964,7 @@
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>1400010</v>
+        <v>1400020</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>8</v>
@@ -14769,7 +15002,7 @@
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>1410020</v>
+        <v>1400010</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -14807,7 +15040,7 @@
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>1410010</v>
+        <v>1410020</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>8</v>
@@ -14845,7 +15078,7 @@
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>1420020</v>
+        <v>1410010</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>8</v>
@@ -14883,7 +15116,7 @@
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>1420010</v>
+        <v>1420020</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>8</v>
@@ -14921,7 +15154,7 @@
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>1430020</v>
+        <v>1420010</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -14959,7 +15192,7 @@
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>1430010</v>
+        <v>1430020</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>8</v>
@@ -14997,7 +15230,7 @@
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>1440020</v>
+        <v>1430010</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>8</v>
@@ -15035,7 +15268,7 @@
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>1440010</v>
+        <v>1440020</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>8</v>
@@ -15073,7 +15306,7 @@
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>1450020</v>
+        <v>1440010</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
@@ -15111,7 +15344,7 @@
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>1450010</v>
+        <v>1450020</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>8</v>
@@ -15149,7 +15382,7 @@
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>1460020</v>
+        <v>1450010</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>8</v>
@@ -15187,7 +15420,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>1460010</v>
+        <v>1460020</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>8</v>
@@ -15225,7 +15458,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>1470020</v>
+        <v>1460010</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>8</v>
@@ -15263,7 +15496,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>1470010</v>
+        <v>1470020</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>8</v>
@@ -15301,7 +15534,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>1480020</v>
+        <v>1470010</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>8</v>
@@ -15339,7 +15572,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>1480010</v>
+        <v>1480020</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>8</v>
@@ -15377,7 +15610,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>1490020</v>
+        <v>1480010</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>8</v>
@@ -15415,7 +15648,7 @@
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>1490010</v>
+        <v>1490020</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>8</v>
@@ -15453,7 +15686,7 @@
     </row>
     <row r="382" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>1500020</v>
+        <v>1490010</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>8</v>
@@ -15491,7 +15724,7 @@
     </row>
     <row r="383" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>1500010</v>
+        <v>1500020</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>8</v>
@@ -15529,7 +15762,7 @@
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>1510020</v>
+        <v>1500010</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>8</v>
@@ -15567,7 +15800,7 @@
     </row>
     <row r="385" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>1510010</v>
+        <v>1510020</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>8</v>
@@ -15605,7 +15838,7 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>1520020</v>
+        <v>1510010</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>8</v>
@@ -15643,7 +15876,7 @@
     </row>
     <row r="387" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>1520010</v>
+        <v>1520020</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>8</v>
@@ -15681,7 +15914,7 @@
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>1530020</v>
+        <v>1520010</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>8</v>
@@ -15719,7 +15952,7 @@
     </row>
     <row r="389" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>1530010</v>
+        <v>1530020</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>8</v>
@@ -15757,7 +15990,7 @@
     </row>
     <row r="390" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>1540020</v>
+        <v>1530010</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>8</v>
@@ -15795,7 +16028,7 @@
     </row>
     <row r="391" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>1540010</v>
+        <v>1540020</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>8</v>
@@ -15833,7 +16066,7 @@
     </row>
     <row r="392" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>1550020</v>
+        <v>1540010</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>8</v>
@@ -15871,7 +16104,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>1550010</v>
+        <v>1550020</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>8</v>
@@ -15909,7 +16142,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>1560020</v>
+        <v>1550010</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>8</v>
@@ -15947,7 +16180,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>1560010</v>
+        <v>1560020</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>8</v>
@@ -15985,7 +16218,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>1570020</v>
+        <v>1560010</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>8</v>
@@ -16023,7 +16256,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>1570010</v>
+        <v>1570020</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>8</v>
@@ -16061,7 +16294,7 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>1580020</v>
+        <v>1570010</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>8</v>
@@ -16099,7 +16332,7 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>1580010</v>
+        <v>1580020</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>8</v>
@@ -16137,7 +16370,7 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>1590020</v>
+        <v>1580010</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>8</v>
@@ -16175,7 +16408,7 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>1590010</v>
+        <v>1590020</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>8</v>
@@ -16213,7 +16446,7 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>1600020</v>
+        <v>1590010</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>8</v>
@@ -16251,39 +16484,77 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
+        <v>1600020</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F403" s="1">
+        <v>0</v>
+      </c>
+      <c r="G403" s="2">
+        <v>0</v>
+      </c>
+      <c r="H403" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I403" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J403" s="7">
+        <v>0</v>
+      </c>
+      <c r="K403" s="7">
+        <v>0</v>
+      </c>
+      <c r="L403" s="7">
+        <v>0</v>
+      </c>
+      <c r="M403" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A404" s="1">
         <v>1600010</v>
       </c>
-      <c r="C403" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D403" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E403" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F403" s="1">
-        <v>0</v>
-      </c>
-      <c r="G403" s="2">
-        <v>0</v>
-      </c>
-      <c r="H403" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I403" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J403" s="7">
-        <v>0</v>
-      </c>
-      <c r="K403" s="7">
-        <v>0</v>
-      </c>
-      <c r="L403" s="7">
-        <v>0</v>
-      </c>
-      <c r="M403" s="7">
+      <c r="C404" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E404" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F404" s="1">
+        <v>0</v>
+      </c>
+      <c r="G404" s="2">
+        <v>0</v>
+      </c>
+      <c r="H404" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I404" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J404" s="7">
+        <v>0</v>
+      </c>
+      <c r="K404" s="7">
+        <v>0</v>
+      </c>
+      <c r="L404" s="7">
+        <v>0</v>
+      </c>
+      <c r="M404" s="7">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E93BAE-ED53-4D50-82A4-EDF06D5B7E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C719B38-7EB7-478C-AE83-0A8907689B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2217,7 +2217,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
-        <v>40001</v>
+        <v>50001</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>80</v>

--- a/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_box_v8【迷宫-宝箱】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C719B38-7EB7-478C-AE83-0A8907689B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC248619-148C-4DD7-8BCA-01023676E92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_box_v8" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="136">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,10 +167,6 @@
   </si>
   <si>
     <t>增加通关值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -447,19 +443,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46700001:8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>46700001:16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -539,47 +523,7 @@
     <t>通关宝箱10</t>
   </si>
   <si>
-    <t>46700001:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:36</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>46700001:42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:48</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46700001:60</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1087,7 +1031,7 @@
         <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
@@ -1119,7 +1063,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
@@ -1128,25 +1072,25 @@
         <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
@@ -1157,37 +1101,37 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="L4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
@@ -1195,7 +1139,7 @@
         <v>10001</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -1204,7 +1148,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
@@ -1216,7 +1160,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -1236,7 +1180,7 @@
         <v>10002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -1245,7 +1189,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -1257,7 +1201,7 @@
         <v>13</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -1277,7 +1221,7 @@
         <v>10003</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
@@ -1286,7 +1230,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -1298,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J7" s="7">
         <v>0</v>
@@ -1318,7 +1262,7 @@
         <v>10004</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -1327,7 +1271,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -1339,7 +1283,7 @@
         <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J8" s="7">
         <v>0</v>
@@ -1359,7 +1303,7 @@
         <v>10005</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -1368,7 +1312,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -1380,7 +1324,7 @@
         <v>13</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -1400,7 +1344,7 @@
         <v>10006</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
@@ -1409,7 +1353,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -1421,7 +1365,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="7">
         <v>0</v>
@@ -1441,7 +1385,7 @@
         <v>10007</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
@@ -1450,7 +1394,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1462,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J11" s="7">
         <v>0</v>
@@ -1482,7 +1426,7 @@
         <v>10008</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -1491,7 +1435,7 @@
         <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1503,7 +1447,7 @@
         <v>13</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J12" s="7">
         <v>0</v>
@@ -1523,7 +1467,7 @@
         <v>10009</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -1532,7 +1476,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
@@ -1544,7 +1488,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J13" s="7">
         <v>0</v>
@@ -1564,7 +1508,7 @@
         <v>10020</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -1573,7 +1517,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1585,7 +1529,7 @@
         <v>13</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
@@ -1605,7 +1549,7 @@
         <v>10010</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
@@ -1614,7 +1558,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1626,7 +1570,7 @@
         <v>13</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="J15" s="7">
         <v>0</v>
@@ -1646,7 +1590,7 @@
         <v>10011</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -1687,7 +1631,7 @@
         <v>20020</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -1696,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1708,7 +1652,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="J17" s="7">
         <v>0</v>
@@ -1728,7 +1672,7 @@
         <v>20010</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
@@ -1737,7 +1681,7 @@
         <v>13</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1749,7 +1693,7 @@
         <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="J18" s="7">
         <v>0</v>
@@ -1769,7 +1713,7 @@
         <v>20001</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -1810,7 +1754,7 @@
         <v>30020</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -1819,7 +1763,7 @@
         <v>13</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1831,7 +1775,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J20" s="7">
         <v>0</v>
@@ -1851,7 +1795,7 @@
         <v>30010</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -1860,7 +1804,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1872,7 +1816,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="J21" s="7">
         <v>0</v>
@@ -1892,7 +1836,7 @@
         <v>30001</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -1901,7 +1845,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1933,7 +1877,7 @@
         <v>30002</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -1974,7 +1918,7 @@
         <v>40020</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -1983,7 +1927,7 @@
         <v>13</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1995,7 +1939,7 @@
         <v>13</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="J24" s="7">
         <v>0</v>
@@ -2015,7 +1959,7 @@
         <v>40010</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -2024,7 +1968,7 @@
         <v>13</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2036,7 +1980,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="J25" s="7">
         <v>0</v>
@@ -2056,7 +2000,7 @@
         <v>40001</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -2065,7 +2009,7 @@
         <v>13</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2097,7 +2041,7 @@
         <v>40002</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C27" s="10">
         <v>0</v>
@@ -2138,7 +2082,7 @@
         <v>50020</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -2147,7 +2091,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2159,7 +2103,7 @@
         <v>13</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="J28" s="7">
         <v>0</v>
@@ -2179,7 +2123,7 @@
         <v>50010</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -2188,7 +2132,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2200,7 +2144,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="J29" s="7">
         <v>0</v>
@@ -2220,7 +2164,7 @@
         <v>50001</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -2229,7 +2173,7 @@
         <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2261,7 +2205,7 @@
         <v>50002</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" s="10">
         <v>0</v>
@@ -2270,7 +2214,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F31" s="8">
         <v>0</v>
@@ -2282,7 +2226,7 @@
         <v>13</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J31" s="12">
         <v>4</v>
@@ -2302,7 +2246,7 @@
         <v>50003</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="10">
         <v>0</v>
@@ -2343,7 +2287,7 @@
         <v>60020</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -2352,7 +2296,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2364,7 +2308,7 @@
         <v>13</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="J33" s="7">
         <v>0</v>
@@ -2384,7 +2328,7 @@
         <v>60010</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -2393,7 +2337,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2405,7 +2349,7 @@
         <v>13</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="J34" s="7">
         <v>0</v>
@@ -2425,7 +2369,7 @@
         <v>60001</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -2434,7 +2378,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2466,7 +2410,7 @@
         <v>60002</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -2475,7 +2419,7 @@
         <v>13</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2487,7 +2431,7 @@
         <v>13</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J36" s="7">
         <v>4</v>
@@ -2507,7 +2451,7 @@
         <v>60003</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -2516,13 +2460,13 @@
         <v>13</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -2548,7 +2492,7 @@
         <v>60004</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -2557,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2569,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="J38" s="7">
         <v>4</v>
@@ -2589,7 +2533,7 @@
         <v>60005</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -2598,7 +2542,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2630,7 +2574,7 @@
         <v>60006</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -2639,13 +2583,13 @@
         <v>13</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -2671,7 +2615,7 @@
         <v>70020</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -2680,7 +2624,7 @@
         <v>13</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>131</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2692,7 +2636,7 @@
         <v>13</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="J41" s="7">
         <v>0</v>
@@ -2712,7 +2656,7 @@
         <v>70010</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -2721,7 +2665,7 @@
         <v>13</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2733,7 +2677,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J42" s="7">
         <v>0</v>
@@ -2753,7 +2697,7 @@
         <v>70001</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -2762,13 +2706,13 @@
         <v>13</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
@@ -2794,7 +2738,7 @@
         <v>70002</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -2803,7 +2747,7 @@
         <v>13</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2835,7 +2779,7 @@
         <v>70003</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -2844,7 +2788,7 @@
         <v>13</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2856,7 +2800,7 @@
         <v>13</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J45" s="7">
         <v>4</v>
@@ -2876,7 +2820,7 @@
         <v>70004</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -2885,13 +2829,13 @@
         <v>13</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
@@ -2917,7 +2861,7 @@
         <v>70005</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -2932,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -2958,7 +2902,7 @@
         <v>70006</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -2967,7 +2911,7 @@
         <v>13</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -2999,7 +2943,7 @@
         <v>70007</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -3008,7 +2952,7 @@
         <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3020,7 +2964,7 @@
         <v>13</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="J49" s="7">
         <v>4</v>
@@ -3040,7 +2984,7 @@
         <v>70008</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -3055,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -3081,7 +3025,7 @@
         <v>70009</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -3090,7 +3034,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3102,7 +3046,7 @@
         <v>13</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J51" s="7">
         <v>4</v>
@@ -3122,7 +3066,7 @@
         <v>70011</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -3137,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -3163,7 +3107,7 @@
         <v>70012</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -3178,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -3204,7 +3148,7 @@
         <v>70013</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -3213,7 +3157,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3245,7 +3189,7 @@
         <v>80020</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -3254,7 +3198,7 @@
         <v>13</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3266,7 +3210,7 @@
         <v>13</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="J55" s="7">
         <v>0</v>
@@ -3286,7 +3230,7 @@
         <v>80010</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -3295,7 +3239,7 @@
         <v>13</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3307,7 +3251,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="J56" s="7">
         <v>0</v>
@@ -3327,7 +3271,7 @@
         <v>90020</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -3336,7 +3280,7 @@
         <v>13</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3348,7 +3292,7 @@
         <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="J57" s="7">
         <v>0</v>
@@ -3368,7 +3312,7 @@
         <v>90010</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -3377,7 +3321,7 @@
         <v>13</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3389,7 +3333,7 @@
         <v>13</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J58" s="7">
         <v>0</v>
@@ -3409,7 +3353,7 @@
         <v>100020</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -3418,7 +3362,7 @@
         <v>13</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3430,7 +3374,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="J59" s="7">
         <v>0</v>
@@ -3450,7 +3394,7 @@
         <v>100010</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -3459,7 +3403,7 @@
         <v>13</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3471,7 +3415,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J60" s="7">
         <v>0</v>
@@ -3573,13 +3517,13 @@
         <v>13</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F63" s="1">
         <v>30</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>13</v>
@@ -3611,7 +3555,7 @@
         <v>13</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F64" s="1">
         <v>40</v>
@@ -3623,7 +3567,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J64" s="7">
         <v>4</v>
@@ -3649,13 +3593,13 @@
         <v>13</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" s="1">
         <v>50</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>13</v>
@@ -3687,7 +3631,7 @@
         <v>13</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F66" s="1">
         <v>70</v>
@@ -3699,7 +3643,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J66" s="7">
         <v>4</v>
@@ -3725,7 +3669,7 @@
         <v>13</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F67" s="1">
         <v>120</v>
@@ -3737,7 +3681,7 @@
         <v>13</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J67" s="7">
         <v>4</v>
@@ -3763,13 +3707,13 @@
         <v>13</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F68" s="1">
         <v>150</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>13</v>
@@ -3801,13 +3745,13 @@
         <v>13</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F69" s="1">
         <v>210</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>13</v>
@@ -3839,7 +3783,7 @@
         <v>13</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F70" s="1">
         <v>250</v>
@@ -3851,7 +3795,7 @@
         <v>13</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J70" s="7">
         <v>5</v>
@@ -3877,7 +3821,7 @@
         <v>13</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F71" s="1">
         <v>400</v>
@@ -3889,7 +3833,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J71" s="7">
         <v>5</v>
@@ -3915,7 +3859,7 @@
         <v>13</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F72" s="1">
         <v>500</v>
@@ -3927,7 +3871,7 @@
         <v>13</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J72" s="7">
         <v>5</v>
@@ -3953,13 +3897,13 @@
         <v>13</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F73" s="1">
         <v>600</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>13</v>
@@ -3991,7 +3935,7 @@
         <v>13</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F74" s="1">
         <v>800</v>
@@ -4003,7 +3947,7 @@
         <v>13</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J74" s="7">
         <v>0</v>
@@ -4029,13 +3973,13 @@
         <v>13</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F75" s="1">
         <v>1000</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>13</v>
@@ -4067,7 +4011,7 @@
         <v>13</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F76" s="1">
         <v>1200</v>
@@ -4079,7 +4023,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J76" s="7">
         <v>0</v>
@@ -4105,7 +4049,7 @@
         <v>13</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F77" s="1">
         <v>1500</v>
@@ -4117,7 +4061,7 @@
         <v>13</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J77" s="7">
         <v>0</v>
@@ -4143,7 +4087,7 @@
         <v>13</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F78" s="1">
         <v>1800</v>
@@ -4155,7 +4099,7 @@
         <v>13</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J78" s="7">
         <v>0</v>
@@ -4181,7 +4125,7 @@
         <v>13</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F79" s="1">
         <v>2000</v>
@@ -4193,7 +4137,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J79" s="7">
         <v>0</v>
@@ -4219,13 +4163,13 @@
         <v>13</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F80" s="1">
         <v>2500</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>13</v>
@@ -4257,7 +4201,7 @@
         <v>13</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F81" s="1">
         <v>3000</v>
@@ -4269,7 +4213,7 @@
         <v>13</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J81" s="7">
         <v>0</v>
@@ -4295,13 +4239,13 @@
         <v>13</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F82" s="1">
         <v>6000</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>13</v>
@@ -4333,7 +4277,7 @@
         <v>13</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F83" s="1">
         <v>8000</v>
@@ -4561,13 +4505,13 @@
         <v>13</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" s="1">
         <v>30</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>13</v>
@@ -4599,7 +4543,7 @@
         <v>13</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F90" s="1">
         <v>40</v>
@@ -4611,7 +4555,7 @@
         <v>13</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J90" s="7">
         <v>4</v>
@@ -4637,13 +4581,13 @@
         <v>13</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F91" s="1">
         <v>50</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>13</v>
@@ -4675,7 +4619,7 @@
         <v>13</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F92" s="1">
         <v>70</v>
@@ -4687,7 +4631,7 @@
         <v>13</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J92" s="7">
         <v>4</v>
@@ -4713,7 +4657,7 @@
         <v>13</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F93" s="1">
         <v>120</v>
@@ -4725,7 +4669,7 @@
         <v>13</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J93" s="7">
         <v>4</v>
@@ -4751,13 +4695,13 @@
         <v>13</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F94" s="1">
         <v>150</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>13</v>
@@ -4789,13 +4733,13 @@
         <v>13</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F95" s="1">
         <v>210</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>13</v>
@@ -4827,7 +4771,7 @@
         <v>13</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F96" s="1">
         <v>250</v>
@@ -4839,7 +4783,7 @@
         <v>13</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J96" s="7">
         <v>5</v>
@@ -4865,7 +4809,7 @@
         <v>13</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F97" s="1">
         <v>400</v>
@@ -4877,7 +4821,7 @@
         <v>13</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J97" s="7">
         <v>5</v>
@@ -4903,7 +4847,7 @@
         <v>13</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F98" s="1">
         <v>500</v>
@@ -4915,7 +4859,7 @@
         <v>13</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J98" s="7">
         <v>5</v>
@@ -6233,13 +6177,13 @@
         <v>13</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>13</v>
@@ -6271,7 +6215,7 @@
         <v>13</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -6309,7 +6253,7 @@
         <v>13</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -6321,7 +6265,7 @@
         <v>13</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J135" s="7">
         <v>4</v>
@@ -6347,13 +6291,13 @@
         <v>13</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>13</v>
@@ -6391,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>13</v>
@@ -6423,7 +6367,7 @@
         <v>13</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -6461,19 +6405,19 @@
         <v>13</v>
       </c>
       <c r="E139" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="2">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="F139" s="1">
-        <v>0</v>
-      </c>
-      <c r="G139" s="2">
-        <v>0</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I139" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="J139" s="7">
         <v>4</v>
@@ -6505,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>13</v>
@@ -6537,19 +6481,19 @@
         <v>13</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="2">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="F141" s="1">
-        <v>0</v>
-      </c>
-      <c r="G141" s="2">
-        <v>0</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I141" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="J141" s="7">
         <v>4</v>
@@ -6581,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>13</v>
@@ -6619,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>13</v>
@@ -6651,7 +6595,7 @@
         <v>13</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
